--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -742,15 +742,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.rofenashim.co.il/faq/faq-fertility/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>6</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -891,15 +891,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>256122</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>768366</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://www.dr-ravhon.co.il/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>355023</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>1065069</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.e-piryon.com/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1189,15 +1189,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://www.dr-yinon.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1338,15 +1338,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://www.profyinoncohen.com/</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1487,15 +1487,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://drbraunstein.co.il/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1636,15 +1636,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://www.dr-domniz.co.il/</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1786,15 +1786,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1933,15 +1933,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>3</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2080,15 +2080,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://kerenzohar.com/%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2229,15 +2229,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://hmc.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%93%D7%95%D7%93-%D7%9C%D7%91-%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>19</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2376,15 +2376,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://www.israelidoula.co.il/courses-1/embryo-%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>7</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2525,15 +2525,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>https://www.dr-paz.co.il/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2664,15 +2664,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>https://www.nashim.net/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2811,15 +2811,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>17</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2959,15 +2959,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://boneiolam.co.il/%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA-%D7%94%D7%90%D7%A8%D7%92%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3098,15 +3098,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://www.dranatlavie.com/</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3237,15 +3237,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://www.shvil-haleida.co.il/%D7%A8%D7%99%D7%A9%D7%95%D7%9D-%D7%9C%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%9C%D7%99%D7%93%D7%94/</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3384,15 +3384,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2358</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3532,15 +3532,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3681,15 +3681,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94-9/</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3820,15 +3820,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://harechem.com/</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>3</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -3963,15 +3963,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>http://www.amotatchen.org/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>3</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4110,15 +4110,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://www.hourvitz.co.il/fertility/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4249,15 +4249,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%91%D7%A0%D7%A7%D7%99-%D7%96%D7%A8%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4388,15 +4388,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%91%D7%A0%D7%A7%D7%99-%D7%96%D7%A8%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4527,15 +4527,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://www.shamirbaby.co.il/</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4676,15 +4676,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4825,15 +4825,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>2</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -4974,15 +4974,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://drehudg.co.il/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5123,15 +5123,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://atufa.co.il/team/%D7%93%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%9C%D7%95%D7%99%D7%A0%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5268,15 +5268,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://levitasaesthetic.com/</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5417,15 +5417,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://darkred-ram-504111.hostingersite.com/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>1</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5566,15 +5566,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://www.infomed.co.il/experts/93782/</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>1</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5715,15 +5715,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://doctor-ariel.co.il/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5864,15 +5864,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://www.dr-ariella.com/blank-3</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>1</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -6013,15 +6013,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://www.dr-pomp.com/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6162,15 +6162,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://blinker.co.il/%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA/%D7%9E%D7%93%D7%95%D7%A8%D7%AA-%D7%94%D7%A9%D7%91%D7%98-%D7%91%D7%94%D7%93-%D7%94%D7%A7%D7%A8%D7%99%D7%95%D7%AA/%D7%93%D7%A8-%D7%90%D7%91%D7%95-%D7%96%D7%94%D7%99%D7%94-%D7%A2%D7%90%D7%99%D7%93-%D7%94%D7%A6%D7%98%D7%A8%D7%A3-%D7%9C%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%91%D7%98/443381/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6311,15 +6311,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://roni-avrahami.co.il/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>1</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6460,15 +6460,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://drostrovsky.com/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>1</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6609,15 +6609,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://web.minicard.co.il/card/idelsondoc/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>1</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6758,15 +6758,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://drblecher.co.il/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>1</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6903,15 +6903,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://drblecher.co.il/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>1</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -7052,15 +7052,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>315657</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>946971</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://www.drukker.co.il/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7201,15 +7201,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://stop-pregnancy.co.il/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>1</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7350,15 +7350,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>256122</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>768366</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://arireissmd.com/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>1</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7499,15 +7499,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>256122</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>768366</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://drmeiravschmidt.co.il/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>1</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7648,15 +7648,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://dinadoula.com/%D7%93%D7%95%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7795,15 +7795,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://www.lidoula.co.il/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>1</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -7940,15 +7940,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://dr-carp.co.il/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>1</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -8089,15 +8089,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://dr-carp.co.il/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -8238,15 +8238,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://krissiclinic.com/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>1</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8387,15 +8387,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://krissiclinic.com/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8536,15 +8536,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>242757</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>728271</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://fetalmedicine.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8685,15 +8685,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://admcmedical.com/%D7%93%D7%A8-%D7%9C%D7%90%D7%94-%D7%A7%D7%A4%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>1</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8820,15 +8820,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%9C%D7%99%D7%93%D7%94-%D7%A8%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>1</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -8955,15 +8955,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%9C%D7%99%D7%93%D7%94-%D7%A8%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>1</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -9090,15 +9090,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%9C%D7%99%D7%93%D7%94-%D7%A8%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>1</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -9239,15 +9239,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>236952</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>710856</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%9E%D7%95%D7%A0%D7%96%D7%A8-%D7%A2%D7%96%D7%90%D7%9D-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%91%D7%97%D7%99%D7%A4%D7%94</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>1</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9388,15 +9388,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>236952</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>710856</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://drlewit.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>1</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9537,15 +9537,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>236952</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>710856</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://medstream.co.il/doctor/ido-elder/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>1</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9686,15 +9686,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>236934</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>710802</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://dr-schwed.co.il/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>1</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9836,15 +9836,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://mdjacob.co.il/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>1</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -9981,15 +9981,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://dr-ivf.co.il/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>1</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -10126,15 +10126,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>295491</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>886473</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://www.hypnobirthing.co.il/pashut/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>1</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -10275,15 +10275,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://www.ultra-sound.co.il/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>1</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10424,15 +10424,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://rb-skirot.co.il/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>1</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10573,15 +10573,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://drroteminbar.co.il/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>1</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>236934</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>710802</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://bmc-medical.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%99%D7%A7%D7%99-%D7%91%D7%A8%D7%92%D7%9C-%D7%91%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>1</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10871,15 +10871,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>http://www.prof-haimovich.ipn.co.il/about-2-3/</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>1</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -11020,15 +11020,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%9C%D7%9E%D7%94_%D7%9E%D7%A8%D7%A7%D7%95%D7%91</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>1</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -11169,15 +11169,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://dr-yagel.co.il/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>1</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -11308,15 +11308,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://www.hadoula.co.il/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>1</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11447,15 +11447,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://www.nashim.net/?CategoryID=1146</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>1</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11596,15 +11596,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://www.surmom.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/%D7%A4%D7%A8%D7%95%D7%A4-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F-%D7%90%D7%93%D7%A8%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11745,15 +11745,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://iwn.org.il/%D7%93%D7%95%D7%A8%D7%A9%D7%95%D7%AA-%D7%9C%D7%A9%D7%9C%D7%95%D7%9C-%D7%90%D7%AA-%D7%A8%D7%A9%D7%99%D7%95%D7%A0%D7%95-%D7%A9%D7%9C-%D7%91%D7%A0%D7%99-%D7%A9%D7%9B%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>1</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -11894,15 +11894,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://iwn.org.il/%D7%93%D7%95%D7%A8%D7%A9%D7%95%D7%AA-%D7%9C%D7%A9%D7%9C%D7%95%D7%9C-%D7%90%D7%AA-%D7%A8%D7%A9%D7%99%D7%95%D7%A0%D7%95-%D7%A9%D7%9C-%D7%91%D7%A0%D7%99-%D7%A9%D7%9B%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>1</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -12043,15 +12043,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://iwn.org.il/%D7%93%D7%95%D7%A8%D7%A9%D7%95%D7%AA-%D7%9C%D7%A9%D7%9C%D7%95%D7%9C-%D7%90%D7%AA-%D7%A8%D7%A9%D7%99%D7%95%D7%A0%D7%95-%D7%A9%D7%9C-%D7%91%D7%A0%D7%99-%D7%A9%D7%9B%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>1</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -12192,15 +12192,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://hfhosp.org/he/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/%D7%93%D7%A8-%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%90-%D7%A4%D7%A8%D7%97</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>5</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -12341,15 +12341,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://www.ha-makom.co.il/post-galit-geni-new/</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>1</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12490,15 +12490,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://www.ha-makom.co.il/post-galit-geni-new/</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>1</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12639,15 +12639,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://www.ha-makom.co.il/post-galit-geni-new/</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>1</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12788,15 +12788,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://www.yarongilmd.com/</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>1</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -12927,15 +12927,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://midwives.org.il/%D7%9C%D7%99%D7%95%D7%95%D7%99-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%96%D7%94-%D7%9E%D7%99%D7%99%D7%9C%D7%93%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>9</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -13076,15 +13076,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://sharapplus.co.il/doctors/shlomi-sagi/</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>1</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -13225,15 +13225,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://www.eryaveladan.com/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>1</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -13374,15 +13374,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>1</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13523,15 +13523,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://www.michlalot.co.il/limudim/madrichat-leida.php</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>1</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13670,15 +13670,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>8</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13817,15 +13817,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>11</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -13956,15 +13956,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://www.israelibaby.co.il/where-to-get-birth</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>11</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -14095,15 +14095,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>2</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -14234,15 +14234,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>1</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -14373,15 +14373,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>1</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -14516,15 +14516,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/fertility-research/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>3</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14655,15 +14655,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://www.cryobank.co.il/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>1</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14797,15 +14797,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://www.cryobank.co.il/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>1</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -14946,15 +14946,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>315657</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>946971</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://www.mdliora.com/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>1</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -15095,15 +15095,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://www.shellclinic.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A9%D7%9C-%D7%91%D7%99%D7%AA-%D7%A9%D7%9C-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA/%D7%93%D7%A8-%D7%9E%D7%90%D7%A9%D7%94-%D7%93%D7%9B%D7%99%D7%A1</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>1</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -15234,15 +15234,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://barakivf.com/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>3</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -15377,15 +15377,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://demayo.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>3</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -15524,15 +15524,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://bri.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>17</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15663,15 +15663,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>4</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15802,15 +15802,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>4</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -15941,15 +15941,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>4</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -16080,15 +16080,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://www.patients-rights.org/%D7%97%D7%9F-%D7%9C%D7%A4%D7%A8%D7%99%D7%95%D7%9F-%D7%95%D7%9C%D7%97%D7%99%D7%99%D7%9D</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>1</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -16229,15 +16229,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>http://dorclinic.co.il/about-us/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%94%D7%95%D7%A9%D7%A2-%D7%93%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>1</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -16376,15 +16376,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://www.chesedmatch.org/%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F-%D7%A2%D7%99%D7%9C%D7%99%D7%AA/chesed-categories/%D7%9C%D7%92%D7%93%D7%9C-%D7%99%D7%A2%D7%95%D7%A5-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>1</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -16523,15 +16523,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://www.laniado.org.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%9C%D7%99%D7%93%D7%94-%D7%98%D7%91%D7%A2%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>2</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16672,15 +16672,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://www.drmayasharonweiner.com/</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>1</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16811,15 +16811,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=572A93E43CD3B3402A26D525588617E3&amp;RequestId=00000000-0000-0000-0001-000000000086</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>1</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -16950,15 +16950,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=624E1E4C81052B986D35A02439C2DE20&amp;RequestId=00000000-0000-0000-0001-000000000213</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>1</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -17089,15 +17089,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=F6BA64E342379D7CF6706D6EF9A4D7C4&amp;RequestId=00000000-0000-0000-0001-000000000399</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>1</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -17228,15 +17228,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=A6B809CAFEA13537A84D783709CF5EBB&amp;RequestId=00000000-0000-0000-0001-000000000325</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>2</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
@@ -17367,15 +17367,15 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE116" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF116" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF116" t="n">
-        <v>8</v>
       </c>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
@@ -17516,15 +17516,15 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE117" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF117" t="inlineStr">
         <is>
           <t>https://professorneuman.com/he/</t>
         </is>
-      </c>
-      <c r="AF117" t="n">
-        <v>1</v>
       </c>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
@@ -17655,15 +17655,15 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE118" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF118" t="inlineStr">
         <is>
           <t>https://aviv-center.co.il/</t>
         </is>
-      </c>
-      <c r="AF118" t="n">
-        <v>1</v>
       </c>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
@@ -17804,15 +17804,15 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE119" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF119" t="inlineStr">
         <is>
           <t>https://www.laliv.clinic/dr-adi-orenstein</t>
         </is>
-      </c>
-      <c r="AF119" t="n">
-        <v>1</v>
       </c>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
@@ -17943,15 +17943,15 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE120" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="inlineStr">
         <is>
           <t>https://machon-dorot.org.il/</t>
         </is>
-      </c>
-      <c r="AF120" t="n">
-        <v>1</v>
       </c>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
@@ -18092,15 +18092,15 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE121" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="inlineStr">
         <is>
           <t>https://dr-ravid.co.il/dr-eran-kasif/</t>
         </is>
-      </c>
-      <c r="AF121" t="n">
-        <v>1</v>
       </c>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
@@ -18241,15 +18241,15 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE122" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF122" t="inlineStr">
         <is>
           <t>https://drrazbahar.co.il/</t>
         </is>
-      </c>
-      <c r="AF122" t="n">
-        <v>1</v>
       </c>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
@@ -18390,15 +18390,15 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE123" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF123" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/gynecology/</t>
         </is>
-      </c>
-      <c r="AF123" t="n">
-        <v>1</v>
       </c>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
@@ -18539,15 +18539,15 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE124" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF124" t="inlineStr">
         <is>
           <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
-      </c>
-      <c r="AF124" t="n">
-        <v>1</v>
       </c>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
@@ -18688,15 +18688,15 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE125" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF125" t="inlineStr">
         <is>
           <t>https://www.yarongilmd.com/</t>
         </is>
-      </c>
-      <c r="AF125" t="n">
-        <v>1</v>
       </c>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
@@ -18837,15 +18837,15 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE126" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF126" t="inlineStr">
         <is>
           <t>https://sharapplus.co.il/doctors/shlomi-sagi/</t>
         </is>
-      </c>
-      <c r="AF126" t="n">
-        <v>1</v>
       </c>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
@@ -18986,15 +18986,15 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE127" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF127" t="inlineStr">
         <is>
           <t>https://sharapplus.co.il/doctors/shlomi-sagi/</t>
         </is>
-      </c>
-      <c r="AF127" t="n">
-        <v>1</v>
       </c>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
@@ -19125,15 +19125,15 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE128" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF128" t="inlineStr">
         <is>
           <t>https://healthwise.co.il/embryologist-ivf-lab/</t>
         </is>
-      </c>
-      <c r="AF128" t="n">
-        <v>1</v>
       </c>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
@@ -19270,15 +19270,15 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE129" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="inlineStr">
         <is>
           <t>https://rtmcmed.co.il/he/mumhim-shelanu/professor-amnon-amit</t>
         </is>
-      </c>
-      <c r="AF129" t="n">
-        <v>1</v>
       </c>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
@@ -19419,15 +19419,15 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE130" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF130" t="inlineStr">
         <is>
           <t>https://www.drw.co.il/%D7%A7%D7%A6%D7%AA-%D7%A2%D7%9C%D7%99/%D7%A7%D7%A6%D7%AA-%D7%A2%D7%9C%D7%99</t>
         </is>
-      </c>
-      <c r="AF130" t="n">
-        <v>1</v>
       </c>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
@@ -19568,15 +19568,15 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>256122</v>
-      </c>
-      <c r="AE131" t="inlineStr">
+        <v>768366</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF131" t="inlineStr">
         <is>
           <t>https://www.liatmd.com/%D7%93-%D7%A8-%D7%9C%D7%99%D7%90%D7%AA-%D7%A9%D7%99%D7%9C%D7%94-%D7%96%D7%9C%D7%A6%D7%A8</t>
         </is>
-      </c>
-      <c r="AF131" t="n">
-        <v>1</v>
       </c>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
@@ -19717,15 +19717,15 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE132" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF132" t="inlineStr">
         <is>
           <t>https://www.ksn.co.il/%D7%93%D7%A8-%D7%94%D7%99%D7%9C%D7%94-%D7%94%D7%95%D7%9B%D7%9C%D7%A8-%D7%AA%D7%A9%D7%9E%D7%A9-%D7%A8%D7%90%D7%A9-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%91/</t>
         </is>
-      </c>
-      <c r="AF132" t="n">
-        <v>1</v>
       </c>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
@@ -19866,15 +19866,15 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE133" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF133" t="inlineStr">
         <is>
           <t>https://drzilberberg.co.il/</t>
         </is>
-      </c>
-      <c r="AF133" t="n">
-        <v>1</v>
       </c>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
@@ -20015,15 +20015,15 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE134" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF134" t="inlineStr">
         <is>
           <t>https://medicabri.com/prof-odeh-marwan/</t>
         </is>
-      </c>
-      <c r="AF134" t="n">
-        <v>1</v>
       </c>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
@@ -20160,15 +20160,15 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE135" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF135" t="inlineStr">
         <is>
           <t>https://www.edna-center.co.il/%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%A0%D7%A9%D7%99%D7%9D</t>
         </is>
-      </c>
-      <c r="AF135" t="n">
-        <v>1</v>
       </c>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
@@ -20299,15 +20299,15 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE136" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF136" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%91%D7%9C%D7%94-%D7%A2%D7%91%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF136" t="n">
-        <v>2</v>
       </c>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
@@ -20438,15 +20438,15 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE137" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF137" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%92%D7%9E%D7%95/</t>
         </is>
-      </c>
-      <c r="AF137" t="n">
-        <v>2</v>
       </c>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
@@ -20577,15 +20577,15 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE138" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF138" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%99%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF138" t="n">
-        <v>2</v>
       </c>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
@@ -20716,15 +20716,15 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE139" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF139" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%9F-%D7%90%D7%A8%D7%99-%D7%A6%D7%90%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF139" t="n">
-        <v>2</v>
       </c>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
@@ -20855,15 +20855,15 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE140" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF140" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF140" t="n">
-        <v>2</v>
       </c>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
@@ -20994,15 +20994,15 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE141" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF141" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%95%D7%A8%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%97%D7%99%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF141" t="n">
-        <v>2</v>
       </c>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
@@ -21133,15 +21133,15 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE142" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF142" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%9C%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF142" t="n">
-        <v>2</v>
       </c>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
@@ -21272,15 +21272,15 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE143" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF143" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%9C%D7%A0%D7%93%D7%94-%D7%A1%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF143" t="n">
-        <v>2</v>
       </c>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
@@ -21411,15 +21411,15 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE144" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF144" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%95%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%9C%D7%90/</t>
         </is>
-      </c>
-      <c r="AF144" t="n">
-        <v>2</v>
       </c>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
@@ -21550,15 +21550,15 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE145" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF145" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%9C%D7%99%D7%94-%D7%94%D7%95%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF145" t="n">
-        <v>2</v>
       </c>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
@@ -21689,15 +21689,15 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE146" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF146" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%9E%D7%99%D7%AA-%D7%93%D7%A0%D7%A1%D7%99%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF146" t="n">
-        <v>2</v>
       </c>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
@@ -21828,15 +21828,15 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE147" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF147" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%9E%D7%95%D7%96%D7%A1-%D7%90%D7%9C%D7%91%D7%96/</t>
         </is>
-      </c>
-      <c r="AF147" t="n">
-        <v>2</v>
       </c>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
@@ -21967,15 +21967,15 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE148" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF148" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%A8%D7%95%D7%9F-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF148" t="n">
-        <v>2</v>
       </c>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
@@ -22106,15 +22106,15 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE149" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF149" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%99%D7%A2%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF149" t="n">
-        <v>2</v>
       </c>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
@@ -22245,15 +22245,15 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE150" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF150" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%98%D7%94-%D7%A0%D7%95%D7%91%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF150" t="n">
-        <v>2</v>
       </c>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
@@ -22384,15 +22384,15 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE151" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF151" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%94-%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%A7%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF151" t="n">
-        <v>2</v>
       </c>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
@@ -22523,15 +22523,15 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE152" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF152" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%94-%D7%93%D7%9E%D7%A0%D7%98%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF152" t="n">
-        <v>2</v>
       </c>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
@@ -22662,15 +22662,15 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE153" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF153" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF153" t="n">
-        <v>2</v>
       </c>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
@@ -22801,15 +22801,15 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE154" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF154" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%96%D7%92%D7%95%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF154" t="n">
-        <v>2</v>
       </c>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
@@ -22940,15 +22940,15 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE155" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF155" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF155" t="n">
-        <v>2</v>
       </c>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
@@ -23079,15 +23079,15 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE156" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF156" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF156" t="n">
-        <v>2</v>
       </c>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
@@ -23218,15 +23218,15 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE157" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF157" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%9C%D7%91%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF157" t="n">
-        <v>2</v>
       </c>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
@@ -23357,15 +23357,15 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE158" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF158" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%90%D7%9D-%D7%9E%D7%95%D7%A8%D7%94-%D7%97%D7%9E%D7%90%D7%A8%D7%A9%D7%99/</t>
         </is>
-      </c>
-      <c r="AF158" t="n">
-        <v>2</v>
       </c>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
@@ -23496,15 +23496,15 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE159" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF159" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%91%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF159" t="n">
-        <v>2</v>
       </c>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
@@ -23635,15 +23635,15 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE160" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF160" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%A6%D7%99%D7%91%D7%99%D7%90%D7%A7-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF160" t="n">
-        <v>2</v>
       </c>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
@@ -23774,15 +23774,15 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE161" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF161" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%9E%D7%95%D7%91%D7%A9%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF161" t="n">
-        <v>2</v>
       </c>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
@@ -23913,15 +23913,15 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE162" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF162" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%94-%D7%90%D7%96%D7%91%D7%A0%D7%93/</t>
         </is>
-      </c>
-      <c r="AF162" t="n">
-        <v>2</v>
       </c>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
@@ -24052,15 +24052,15 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE163" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF163" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%AA%D7%A9%D7%91%D7%A2-%D7%92%D7%A8%D7%A0%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF163" t="n">
-        <v>2</v>
       </c>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
@@ -24191,15 +24191,15 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE164" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF164" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%99%D7%9C%D7%99-%D7%90%D7%95%D7%91%D7%A8%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF164" t="n">
-        <v>2</v>
       </c>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
@@ -24330,15 +24330,15 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE165" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF165" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%9C%D7%99%D7%99%D7%A8-%D7%90%D7%9C%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF165" t="n">
-        <v>2</v>
       </c>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
@@ -24469,15 +24469,15 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE166" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF166" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%94%D7%A9%D7%9B%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF166" t="n">
-        <v>2</v>
       </c>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
@@ -24608,15 +24608,15 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE167" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF167" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%98%D7%9C-%D7%91%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF167" t="n">
-        <v>2</v>
       </c>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
@@ -24747,15 +24747,15 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE168" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF168" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%97%D7%95%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF168" t="n">
-        <v>2</v>
       </c>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
@@ -24886,15 +24886,15 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE169" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF169" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%9C%D7%90%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF169" t="n">
-        <v>2</v>
       </c>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
@@ -25025,15 +25025,15 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE170" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF170" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%92%D7%93%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF170" t="n">
-        <v>2</v>
       </c>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
@@ -25164,15 +25164,15 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE171" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF171" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%9E%D7%A8%D7%90%D7%93/</t>
         </is>
-      </c>
-      <c r="AF171" t="n">
-        <v>2</v>
       </c>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
@@ -25303,15 +25303,15 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE172" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF172" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%A9%D7%95%D7%95%D7%A8%D7%A6%D7%91%D7%A8%D7%92/</t>
         </is>
-      </c>
-      <c r="AF172" t="n">
-        <v>2</v>
       </c>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
@@ -25442,15 +25442,15 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE173" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF173" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%99%D7%90%D7%9F-%D7%A9%D7%A4%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF173" t="n">
-        <v>2</v>
       </c>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
@@ -25581,15 +25581,15 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE174" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF174" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8-%D7%91%D7%99%D7%98%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF174" t="n">
-        <v>2</v>
       </c>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
@@ -25720,15 +25720,15 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE175" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF175" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8%D7%99%D7%9F-%D7%90%D7%9C%D7%A2%D7%93/</t>
         </is>
-      </c>
-      <c r="AF175" t="n">
-        <v>2</v>
       </c>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
@@ -25859,15 +25859,15 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE176" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF176" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/332/</t>
         </is>
-      </c>
-      <c r="AF176" t="n">
-        <v>2</v>
       </c>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
@@ -25998,15 +25998,15 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE177" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF177" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%91%D7%9F-%D7%A9%D7%A5-%D7%A4%D7%95%D7%A8%D7%A9%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF177" t="n">
-        <v>2</v>
       </c>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
@@ -26137,15 +26137,15 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE178" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF178" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%95%D7%95%D7%A8%D7%99%D7%99%D7%98/</t>
         </is>
-      </c>
-      <c r="AF178" t="n">
-        <v>2</v>
       </c>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
@@ -26276,15 +26276,15 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE179" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF179" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%99%D7%90%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF179" t="n">
-        <v>2</v>
       </c>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
@@ -26415,15 +26415,15 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE180" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF180" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%91%D7%92%D7%9C%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF180" t="n">
-        <v>2</v>
       </c>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
@@ -26554,15 +26554,15 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE181" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF181" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF181" t="n">
-        <v>2</v>
       </c>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
@@ -26693,15 +26693,15 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE182" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF182" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%9C%D7%A0%D7%94-%D7%A9%D7%99%D7%9C%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF182" t="n">
-        <v>2</v>
       </c>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
@@ -26832,15 +26832,15 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE183" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF183" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A2%D7%A0%D7%94-%D7%92%D7%95%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF183" t="n">
-        <v>2</v>
       </c>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
@@ -26971,15 +26971,15 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE184" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF184" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%91%D7%A8%D7%A7%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF184" t="n">
-        <v>2</v>
       </c>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
@@ -27110,15 +27110,15 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE185" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF185" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A8%D7%96-%D7%92%D7%99%D7%9C%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF185" t="n">
-        <v>2</v>
       </c>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
@@ -27249,15 +27249,15 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE186" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF186" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A9%D7%91%D7%A2-%D7%92%D7%95%D7%A8%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF186" t="n">
-        <v>2</v>
       </c>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
@@ -27388,15 +27388,15 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE187" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF187" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%9C%D7%95%D7%A0%D7%92%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF187" t="n">
-        <v>2</v>
       </c>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
@@ -27527,15 +27527,15 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE188" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF188" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%9F-%D7%A9%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF188" t="n">
-        <v>2</v>
       </c>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
@@ -27666,15 +27666,15 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE189" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF189" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%94-%D7%90%D7%99%D7%AA%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF189" t="n">
-        <v>2</v>
       </c>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
@@ -27805,15 +27805,15 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE190" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF190" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%95%D7%A0%D7%94-%D7%95%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF190" t="n">
-        <v>2</v>
       </c>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
@@ -27944,15 +27944,15 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE191" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF191" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%90%D7%9C%D7%94-%D7%99%D7%A8%D7%A7%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF191" t="n">
-        <v>2</v>
       </c>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
@@ -28083,15 +28083,15 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE192" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF192" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A1%D7%AA%D7%A8-%D7%A4%D7%9C%D7%99%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF192" t="n">
-        <v>2</v>
       </c>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
@@ -28222,15 +28222,15 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE193" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF193" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%AA%D7%99-%D7%A1%D7%93%D7%9F-%D7%A7%D7%A0%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF193" t="n">
-        <v>2</v>
       </c>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
@@ -28361,15 +28361,15 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE194" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF194" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%A8%D7%A0%D7%A1%D7%99%D7%A1-%D7%A4%D7%A8%D7%9F-%D7%91%D7%A8%D7%95%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF194" t="n">
-        <v>2</v>
       </c>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
@@ -28500,15 +28500,15 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE195" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF195" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%91%D7%99-%D7%A4%D7%99%D7%A9%D7%9E%D7%9F-%D7%A4%D7%95%D7%A1%D7%91%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF195" t="n">
-        <v>2</v>
       </c>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
@@ -28639,15 +28639,15 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE196" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF196" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99-%D7%A7%D7%9E%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF196" t="n">
-        <v>2</v>
       </c>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
@@ -28778,15 +28778,15 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE197" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF197" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%90%D7%A4%D7%9C%D7%91%D7%95%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF197" t="n">
-        <v>2</v>
       </c>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
@@ -28917,15 +28917,15 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE198" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF198" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%AA-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF198" t="n">
-        <v>2</v>
       </c>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
@@ -29056,15 +29056,15 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE199" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF199" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF199" t="n">
-        <v>2</v>
       </c>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
@@ -29195,15 +29195,15 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE200" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF200" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%90%D7%99%D7%94-%D7%92%D7%95%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF200" t="n">
-        <v>2</v>
       </c>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
@@ -29334,15 +29334,15 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE201" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF201" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%94-%D7%90%D7%95%D7%A0%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF201" t="n">
-        <v>2</v>
       </c>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
@@ -29473,15 +29473,15 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE202" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF202" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%99%D7%94-%D7%93%D7%95%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF202" t="n">
-        <v>2</v>
       </c>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
@@ -29612,15 +29612,15 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE203" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF203" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%AA%D7%99%D7%AA-%D7%A9%D7%A4%D7%A8%D7%9C%D7%99%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF203" t="n">
-        <v>2</v>
       </c>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
@@ -29751,15 +29751,15 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE204" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF204" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%9E%D7%95%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF204" t="n">
-        <v>2</v>
       </c>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
@@ -29890,15 +29890,15 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE205" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF205" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%98%D7%A1%D7%94/</t>
         </is>
-      </c>
-      <c r="AF205" t="n">
-        <v>2</v>
       </c>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
@@ -30029,15 +30029,15 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE206" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF206" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1%D7%94-%D7%A4%D7%97%D7%9C%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF206" t="n">
-        <v>2</v>
       </c>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
@@ -30168,15 +30168,15 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE207" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF207" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%A0%D7%94-%D7%94%D7%A8%D7%95%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF207" t="n">
-        <v>2</v>
       </c>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
@@ -30307,15 +30307,15 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE208" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF208" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%99-%D7%94%D7%A8%D7%A4%D7%96/</t>
         </is>
-      </c>
-      <c r="AF208" t="n">
-        <v>2</v>
       </c>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
@@ -30446,15 +30446,15 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE209" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF209" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9E%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF209" t="n">
-        <v>2</v>
       </c>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
@@ -30585,15 +30585,15 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE210" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF210" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%99%D7%9C%D7%94-%D7%9C%D7%91-%D7%A8%D7%9F-%D7%97%D7%95%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF210" t="n">
-        <v>2</v>
       </c>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
@@ -30724,15 +30724,15 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE211" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF211" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%95%D7%93%D7%99%D7%94-%D7%90%D7%99%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF211" t="n">
-        <v>2</v>
       </c>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
@@ -30863,15 +30863,15 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE212" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF212" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%9C-%D7%91%D7%95%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF212" t="n">
-        <v>2</v>
       </c>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
@@ -31002,15 +31002,15 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE213" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF213" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%A8-%D7%A7%D7%A8%D7%9F-%D7%A8%D7%98%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF213" t="n">
-        <v>2</v>
       </c>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
@@ -31141,15 +31141,15 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE214" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF214" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%B3%D7%95%D7%9C%D7%99-%D7%90%D7%A1%D7%AA%D7%99-%D7%A9%D7%9E%D7%A2%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF214" t="n">
-        <v>2</v>
       </c>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
@@ -31280,15 +31280,15 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE215" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF215" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%95%D7%9C%D7%99-%D7%A7%D7%A8%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF215" t="n">
-        <v>2</v>
       </c>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
@@ -31419,15 +31419,15 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE216" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF216" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%92%D7%9C%D7%99%D7%9F-%D7%A1%D7%9C%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF216" t="n">
-        <v>2</v>
       </c>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
@@ -31558,15 +31558,15 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE217" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF217" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%92%D7%99%D7%91%D7%A8-%D7%A9%D7%92%D7%91/</t>
         </is>
-      </c>
-      <c r="AF217" t="n">
-        <v>2</v>
       </c>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
@@ -31697,15 +31697,15 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE218" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF218" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%A1%D7%9C%D7%91%D7%95%D7%93%D7%A0%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF218" t="n">
-        <v>2</v>
       </c>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
@@ -31836,15 +31836,15 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE219" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF219" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF219" t="n">
-        <v>2</v>
       </c>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
@@ -31975,15 +31975,15 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE220" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF220" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%90%D7%A0%D7%94-%D7%91%D7%A8%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF220" t="n">
-        <v>2</v>
       </c>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
@@ -32114,15 +32114,15 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE221" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF221" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99-%D7%90%D7%95%D7%A8-%D7%9C%D7%91%D7%A0%D7%96%D7%95%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF221" t="n">
-        <v>2</v>
       </c>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
@@ -32253,15 +32253,15 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE222" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF222" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%A8%D7%95%D7%9F-%D7%A4%D7%99%D7%90%D7%97%D7%95%D7%98%D7%94-%D7%A1%D7%90%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF222" t="n">
-        <v>2</v>
       </c>
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
@@ -32392,15 +32392,15 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE223" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF223" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF223" t="n">
-        <v>2</v>
       </c>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
@@ -32531,15 +32531,15 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE224" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF224" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%94-%D7%A7%D7%95%D7%92%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF224" t="n">
-        <v>2</v>
       </c>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
@@ -32670,15 +32670,15 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE225" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF225" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%90%D7%9F-%D7%A9%D7%95%D7%97%D7%98/</t>
         </is>
-      </c>
-      <c r="AF225" t="n">
-        <v>2</v>
       </c>
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
@@ -32809,15 +32809,15 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE226" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF226" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99-%D7%A2%D7%95%D7%96%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF226" t="n">
-        <v>2</v>
       </c>
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" t="inlineStr"/>
@@ -32948,15 +32948,15 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE227" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF227" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF227" t="n">
-        <v>2</v>
       </c>
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr"/>
@@ -33087,15 +33087,15 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE228" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF228" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8-%D7%9C%D7%95%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF228" t="n">
-        <v>2</v>
       </c>
       <c r="AG228" t="inlineStr"/>
       <c r="AH228" t="inlineStr"/>
@@ -33226,15 +33226,15 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE229" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF229" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF229" t="n">
-        <v>2</v>
       </c>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
@@ -33365,15 +33365,15 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE230" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF230" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%98%D7%95%D7%91-%D7%97%D7%99%D7%94-%D7%90%D7%99%D7%98%D7%94/</t>
         </is>
-      </c>
-      <c r="AF230" t="n">
-        <v>2</v>
       </c>
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
@@ -33504,15 +33504,15 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE231" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF231" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A2%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%9E%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF231" t="n">
-        <v>2</v>
       </c>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr"/>
@@ -33643,15 +33643,15 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE232" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF232" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99-%D7%93%D7%A8%D7%95%D7%A7%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF232" t="n">
-        <v>2</v>
       </c>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
@@ -33782,15 +33782,15 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE233" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%94-%D7%92%D7%95%D7%A8%D7%92%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF233" t="n">
-        <v>2</v>
       </c>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
@@ -33921,15 +33921,15 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE234" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF234" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%99-%D7%90%D7%95%D7%A4%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF234" t="n">
-        <v>2</v>
       </c>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
@@ -34060,15 +34060,15 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE235" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF235" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%A9%D7%97%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF235" t="n">
-        <v>2</v>
       </c>
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" t="inlineStr"/>
@@ -34199,15 +34199,15 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE236" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF236" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%95%D7%A4%D7%A8%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF236" t="n">
-        <v>2</v>
       </c>
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
@@ -34338,15 +34338,15 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE237" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF237" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99-%D7%9C%D7%91-%D7%A7%D7%9C%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF237" t="n">
-        <v>2</v>
       </c>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
@@ -34477,15 +34477,15 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE238" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF238" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99%D7%94-%D7%90%D7%A0%D7%95%D7%9A/</t>
         </is>
-      </c>
-      <c r="AF238" t="n">
-        <v>2</v>
       </c>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
@@ -34616,15 +34616,15 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE239" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF239" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%94-%D7%90%D7%99%D7%96%D7%A7%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF239" t="n">
-        <v>2</v>
       </c>
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
@@ -34755,15 +34755,15 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE240" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF240" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%91-%D7%A0%D7%97%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF240" t="n">
-        <v>2</v>
       </c>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
@@ -34894,15 +34894,15 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE241" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF241" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99%D7%A1%D7%94-%D7%91%D7%A8-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF241" t="n">
-        <v>2</v>
       </c>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
@@ -35033,15 +35033,15 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE242" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF242" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%9B%D7%9C-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%99%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF242" t="n">
-        <v>2</v>
       </c>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
@@ -35172,15 +35172,15 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE243" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF243" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A7%D7%94-%D7%9B%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF243" t="n">
-        <v>2</v>
       </c>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
@@ -35311,15 +35311,15 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE244" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF244" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99-%D7%A4%D7%91%D7%96%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF244" t="n">
-        <v>2</v>
       </c>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
@@ -35450,15 +35450,15 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE245" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF245" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99%D7%AA-%D7%A8%D7%95%D7%96%D7%A0%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF245" t="n">
-        <v>2</v>
       </c>
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
@@ -35589,15 +35589,15 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE246" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF246" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8-%D7%92%D7%95%D7%9C%D7%93%D7%A0%D7%92%D7%95%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF246" t="n">
-        <v>2</v>
       </c>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
@@ -35728,15 +35728,15 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE247" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF247" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%9E%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF247" t="n">
-        <v>2</v>
       </c>
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr"/>
@@ -35867,15 +35867,15 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE248" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF248" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%9C%D7%92%D7%99/</t>
         </is>
-      </c>
-      <c r="AF248" t="n">
-        <v>2</v>
       </c>
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr"/>
@@ -36006,15 +36006,15 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE249" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF249" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%95%D7%95%D7%9C%D7%A4%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF249" t="n">
-        <v>2</v>
       </c>
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr"/>
@@ -36145,15 +36145,15 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE250" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF250" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A2%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF250" t="n">
-        <v>2</v>
       </c>
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr"/>
@@ -36284,15 +36284,15 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE251" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF251" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A8%D7%99%D7%91%D7%9C%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF251" t="n">
-        <v>2</v>
       </c>
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" t="inlineStr"/>
@@ -36423,15 +36423,15 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE252" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF252" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A8%D7%A7%D7%99%D7%A1-%D7%A0%D7%A4%D7%AA%D7%9C%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF252" t="n">
-        <v>2</v>
       </c>
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr"/>
@@ -36562,15 +36562,15 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE253" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF253" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%A7%D7%A9%D7%99%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF253" t="n">
-        <v>2</v>
       </c>
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr"/>
@@ -36701,15 +36701,15 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE254" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF254" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%91%D7%9F-%D7%A9%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF254" t="n">
-        <v>2</v>
       </c>
       <c r="AG254" t="inlineStr"/>
       <c r="AH254" t="inlineStr"/>
@@ -36840,15 +36840,15 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE255" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF255" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%A2-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF255" t="n">
-        <v>2</v>
       </c>
       <c r="AG255" t="inlineStr"/>
       <c r="AH255" t="inlineStr"/>
@@ -36979,15 +36979,15 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE256" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF256" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A0%D7%94-%D7%91%D7%AA%D7%90%D7%A9%D7%95%D7%99%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF256" t="n">
-        <v>2</v>
       </c>
       <c r="AG256" t="inlineStr"/>
       <c r="AH256" t="inlineStr"/>
@@ -37118,15 +37118,15 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE257" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF257" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A8%D7%99%D7%AA-%D7%90%D7%95%D7%9C%D7%99%D7%91%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF257" t="n">
-        <v>2</v>
       </c>
       <c r="AG257" t="inlineStr"/>
       <c r="AH257" t="inlineStr"/>
@@ -37257,15 +37257,15 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE258" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF258" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A6%D7%9F-%D7%99%D7%9E%D7%99%D7%A0%D7%99-%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF258" t="n">
-        <v>2</v>
       </c>
       <c r="AG258" t="inlineStr"/>
       <c r="AH258" t="inlineStr"/>
@@ -37396,15 +37396,15 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE259" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF259" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%91%D7%99-%D7%99%D7%A2%D7%A7%D7%91/</t>
         </is>
-      </c>
-      <c r="AF259" t="n">
-        <v>2</v>
       </c>
       <c r="AG259" t="inlineStr"/>
       <c r="AH259" t="inlineStr"/>
@@ -37535,15 +37535,15 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE260" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF260" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A2%D7%94-%D7%95%D7%99%D7%A6%D7%9E%D7%9F-%D7%A8%D7%91%D7%99%D7%91%D7%95/</t>
         </is>
-      </c>
-      <c r="AF260" t="n">
-        <v>2</v>
       </c>
       <c r="AG260" t="inlineStr"/>
       <c r="AH260" t="inlineStr"/>
@@ -37674,15 +37674,15 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE261" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF261" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%91%D7%95%D7%A8%D7%92-%D7%A1%D7%92%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF261" t="n">
-        <v>2</v>
       </c>
       <c r="AG261" t="inlineStr"/>
       <c r="AH261" t="inlineStr"/>
@@ -37813,15 +37813,15 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE262" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF262" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF262" t="n">
-        <v>2</v>
       </c>
       <c r="AG262" t="inlineStr"/>
       <c r="AH262" t="inlineStr"/>
@@ -37952,15 +37952,15 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE263" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF263" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%A4%D7%99%D7%9C%D7%95%D7%A1%D7%95%D7%A3/</t>
         </is>
-      </c>
-      <c r="AF263" t="n">
-        <v>2</v>
       </c>
       <c r="AG263" t="inlineStr"/>
       <c r="AH263" t="inlineStr"/>
@@ -38091,15 +38091,15 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE264" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF264" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%98%D7%95%D7%A9%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF264" t="n">
-        <v>2</v>
       </c>
       <c r="AG264" t="inlineStr"/>
       <c r="AH264" t="inlineStr"/>
@@ -38230,15 +38230,15 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE265" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF265" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A8%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF265" t="n">
-        <v>2</v>
       </c>
       <c r="AG265" t="inlineStr"/>
       <c r="AH265" t="inlineStr"/>
@@ -38369,15 +38369,15 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE266" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF266" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%9C%D7%9B%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF266" t="n">
-        <v>2</v>
       </c>
       <c r="AG266" t="inlineStr"/>
       <c r="AH266" t="inlineStr"/>
@@ -38508,15 +38508,15 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE267" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF267" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%9C%D7%92%D7%94-%D7%95%D7%A7%D7%A1%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF267" t="n">
-        <v>2</v>
       </c>
       <c r="AG267" t="inlineStr"/>
       <c r="AH267" t="inlineStr"/>
@@ -38647,15 +38647,15 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE268" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF268" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF268" t="n">
-        <v>2</v>
       </c>
       <c r="AG268" t="inlineStr"/>
       <c r="AH268" t="inlineStr"/>
@@ -38786,15 +38786,15 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE269" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF269" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%9E%D7%9C%D7%99-%D7%94%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF269" t="n">
-        <v>2</v>
       </c>
       <c r="AG269" t="inlineStr"/>
       <c r="AH269" t="inlineStr"/>
@@ -38925,15 +38925,15 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE270" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF270" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF270" t="n">
-        <v>2</v>
       </c>
       <c r="AG270" t="inlineStr"/>
       <c r="AH270" t="inlineStr"/>
@@ -39064,15 +39064,15 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE271" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF271" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%99%D7%A2%D7%A7%D7%91%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF271" t="n">
-        <v>2</v>
       </c>
       <c r="AG271" t="inlineStr"/>
       <c r="AH271" t="inlineStr"/>
@@ -39203,15 +39203,15 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE272" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF272" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7-%D7%A0%D7%A7%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF272" t="n">
-        <v>2</v>
       </c>
       <c r="AG272" t="inlineStr"/>
       <c r="AH272" t="inlineStr"/>
@@ -39342,15 +39342,15 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE273" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF273" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF273" t="n">
-        <v>2</v>
       </c>
       <c r="AG273" t="inlineStr"/>
       <c r="AH273" t="inlineStr"/>
@@ -39481,15 +39481,15 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE274" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF274" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%96-%D7%A8%D7%99%D7%99%D7%9B%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF274" t="n">
-        <v>2</v>
       </c>
       <c r="AG274" t="inlineStr"/>
       <c r="AH274" t="inlineStr"/>
@@ -39620,15 +39620,15 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE275" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF275" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%97%D7%9C-%D7%A4%D7%99%D7%A8%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF275" t="n">
-        <v>2</v>
       </c>
       <c r="AG275" t="inlineStr"/>
       <c r="AH275" t="inlineStr"/>
@@ -39759,15 +39759,15 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE276" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF276" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%AA-%D7%9C%D7%91%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF276" t="n">
-        <v>2</v>
       </c>
       <c r="AG276" t="inlineStr"/>
       <c r="AH276" t="inlineStr"/>
@@ -39898,15 +39898,15 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE277" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF277" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%96-%D7%A2%D7%96%D7%A8%D7%90/</t>
         </is>
-      </c>
-      <c r="AF277" t="n">
-        <v>2</v>
       </c>
       <c r="AG277" t="inlineStr"/>
       <c r="AH277" t="inlineStr"/>
@@ -40037,15 +40037,15 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE278" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF278" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A0%D7%A0%D7%94-%D7%95%D7%99%D7%A8%D7%A6%D7%91%D7%95%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF278" t="n">
-        <v>2</v>
       </c>
       <c r="AG278" t="inlineStr"/>
       <c r="AH278" t="inlineStr"/>
@@ -40176,15 +40176,15 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE279" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF279" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A2%D7%95%D7%AA-%D7%94%D7%A8%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF279" t="n">
-        <v>2</v>
       </c>
       <c r="AG279" t="inlineStr"/>
       <c r="AH279" t="inlineStr"/>
@@ -40315,15 +40315,15 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE280" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF280" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%98%D7%9C-%D7%90%D7%99%D7%A9-%D7%A9%D7%9C%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF280" t="n">
-        <v>2</v>
       </c>
       <c r="AG280" t="inlineStr"/>
       <c r="AH280" t="inlineStr"/>
@@ -40454,15 +40454,15 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE281" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF281" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A7%D7%99-%D7%96%D7%9C%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF281" t="n">
-        <v>2</v>
       </c>
       <c r="AG281" t="inlineStr"/>
       <c r="AH281" t="inlineStr"/>
@@ -40593,15 +40593,15 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE282" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF282" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A0%D7%AA-%D7%90%D7%9C%D7%93%D7%A8-%D7%92%D7%A8%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF282" t="n">
-        <v>2</v>
       </c>
       <c r="AG282" t="inlineStr"/>
       <c r="AH282" t="inlineStr"/>
@@ -40732,15 +40732,15 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE283" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF283" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%97%D7%99-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF283" t="n">
-        <v>2</v>
       </c>
       <c r="AG283" t="inlineStr"/>
       <c r="AH283" t="inlineStr"/>
@@ -40871,15 +40871,15 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE284" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF284" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99-%D7%A4%D7%A8%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF284" t="n">
-        <v>2</v>
       </c>
       <c r="AG284" t="inlineStr"/>
       <c r="AH284" t="inlineStr"/>
@@ -41010,15 +41010,15 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE285" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF285" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF285" t="n">
-        <v>2</v>
       </c>
       <c r="AG285" t="inlineStr"/>
       <c r="AH285" t="inlineStr"/>
@@ -41149,15 +41149,15 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE286" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF286" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%9D-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
-      </c>
-      <c r="AF286" t="n">
-        <v>2</v>
       </c>
       <c r="AG286" t="inlineStr"/>
       <c r="AH286" t="inlineStr"/>
@@ -41288,15 +41288,15 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE287" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF287" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%99-%D7%98%D7%9C-%D7%9E%D7%99%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF287" t="n">
-        <v>2</v>
       </c>
       <c r="AG287" t="inlineStr"/>
       <c r="AH287" t="inlineStr"/>
@@ -41427,15 +41427,15 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE288" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF288" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%92%D7%99%D7%AA-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF288" t="n">
-        <v>2</v>
       </c>
       <c r="AG288" t="inlineStr"/>
       <c r="AH288" t="inlineStr"/>
@@ -41566,15 +41566,15 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE289" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF289" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF289" t="n">
-        <v>2</v>
       </c>
       <c r="AG289" t="inlineStr"/>
       <c r="AH289" t="inlineStr"/>
@@ -41705,15 +41705,15 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE290" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF290" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%A9%D7%97%D7%A8-%D7%91%D7%9F-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF290" t="n">
-        <v>2</v>
       </c>
       <c r="AG290" t="inlineStr"/>
       <c r="AH290" t="inlineStr"/>
@@ -41844,15 +41844,15 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE291" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF291" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A7%D7%93-%D7%9C%D7%99%D7%91%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF291" t="n">
-        <v>2</v>
       </c>
       <c r="AG291" t="inlineStr"/>
       <c r="AH291" t="inlineStr"/>
@@ -41983,15 +41983,15 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE292" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF292" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%A0%D7%94-%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF292" t="n">
-        <v>2</v>
       </c>
       <c r="AG292" t="inlineStr"/>
       <c r="AH292" t="inlineStr"/>
@@ -42122,15 +42122,15 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE293" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF293" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%9F-%D7%96%D7%9C%D7%9E%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF293" t="n">
-        <v>2</v>
       </c>
       <c r="AG293" t="inlineStr"/>
       <c r="AH293" t="inlineStr"/>
@@ -42261,15 +42261,15 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE294" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF294" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%99-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF294" t="n">
-        <v>2</v>
       </c>
       <c r="AG294" t="inlineStr"/>
       <c r="AH294" t="inlineStr"/>
@@ -42400,15 +42400,15 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE295" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF295" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%94-%D7%A1%D7%95%D7%A1%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF295" t="n">
-        <v>2</v>
       </c>
       <c r="AG295" t="inlineStr"/>
       <c r="AH295" t="inlineStr"/>
@@ -42539,15 +42539,15 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE296" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF296" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%90%D7%9C-%D7%A8%D7%91%D7%A7%D7%94-%D7%99%D7%A4%D7%94/</t>
         </is>
-      </c>
-      <c r="AF296" t="n">
-        <v>2</v>
       </c>
       <c r="AG296" t="inlineStr"/>
       <c r="AH296" t="inlineStr"/>
@@ -42678,15 +42678,15 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE297" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF297" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A4%D7%99%D7%99%D7%98%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF297" t="n">
-        <v>2</v>
       </c>
       <c r="AG297" t="inlineStr"/>
       <c r="AH297" t="inlineStr"/>
@@ -42817,15 +42817,15 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE298" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF298" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%95%D7%98%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF298" t="n">
-        <v>2</v>
       </c>
       <c r="AG298" t="inlineStr"/>
       <c r="AH298" t="inlineStr"/>
@@ -42956,15 +42956,15 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE299" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF299" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%A8%D7%95%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF299" t="n">
-        <v>2</v>
       </c>
       <c r="AG299" t="inlineStr"/>
       <c r="AH299" t="inlineStr"/>
@@ -43095,15 +43095,15 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE300" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF300" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%98-%D7%93%D7%A8%D7%A1%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF300" t="n">
-        <v>2</v>
       </c>
       <c r="AG300" t="inlineStr"/>
       <c r="AH300" t="inlineStr"/>
@@ -43234,15 +43234,15 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE301" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF301" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%92%D7%95%D7%96%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF301" t="n">
-        <v>2</v>
       </c>
       <c r="AG301" t="inlineStr"/>
       <c r="AH301" t="inlineStr"/>
@@ -43373,15 +43373,15 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE302" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF302" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%94%D7%95%D7%9C%D7%A6%D7%91%D7%A8%D7%92-%D7%97%D7%99%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF302" t="n">
-        <v>2</v>
       </c>
       <c r="AG302" t="inlineStr"/>
       <c r="AH302" t="inlineStr"/>
@@ -43512,15 +43512,15 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE303" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF303" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A0%D7%93%D7%9C%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF303" t="n">
-        <v>2</v>
       </c>
       <c r="AG303" t="inlineStr"/>
       <c r="AH303" t="inlineStr"/>
@@ -43651,15 +43651,15 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE304" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF304" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF304" t="n">
-        <v>2</v>
       </c>
       <c r="AG304" t="inlineStr"/>
       <c r="AH304" t="inlineStr"/>
@@ -43790,15 +43790,15 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE305" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF305" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%9E%D7%9C%D7%9B%D7%94-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF305" t="n">
-        <v>2</v>
       </c>
       <c r="AG305" t="inlineStr"/>
       <c r="AH305" t="inlineStr"/>
@@ -43929,15 +43929,15 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE306" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF306" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%94%D7%9C%D7%A4%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF306" t="n">
-        <v>2</v>
       </c>
       <c r="AG306" t="inlineStr"/>
       <c r="AH306" t="inlineStr"/>
@@ -44068,15 +44068,15 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE307" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF307" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%95%D7%A4%D7%99%D7%94-%D7%9E%D7%9C%D7%97%D7%96%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF307" t="n">
-        <v>2</v>
       </c>
       <c r="AG307" t="inlineStr"/>
       <c r="AH307" t="inlineStr"/>
@@ -44207,15 +44207,15 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE308" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF308" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%9E%D7%99%D7%98%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF308" t="n">
-        <v>2</v>
       </c>
       <c r="AG308" t="inlineStr"/>
       <c r="AH308" t="inlineStr"/>
@@ -44346,15 +44346,15 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE309" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF309" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%A6%D7%A0%D7%A6%D7%99%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF309" t="n">
-        <v>2</v>
       </c>
       <c r="AG309" t="inlineStr"/>
       <c r="AH309" t="inlineStr"/>
@@ -44485,15 +44485,15 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE310" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF310" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%91%D7%99%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF310" t="n">
-        <v>2</v>
       </c>
       <c r="AG310" t="inlineStr"/>
       <c r="AH310" t="inlineStr"/>
@@ -44624,15 +44624,15 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE311" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF311" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF311" t="n">
-        <v>2</v>
       </c>
       <c r="AG311" t="inlineStr"/>
       <c r="AH311" t="inlineStr"/>
@@ -44763,15 +44763,15 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE312" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF312" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99%D7%94-%D7%91%D7%9F-%D7%9E%D7%96%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF312" t="n">
-        <v>2</v>
       </c>
       <c r="AG312" t="inlineStr"/>
       <c r="AH312" t="inlineStr"/>
@@ -44902,15 +44902,15 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE313" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF313" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%A8-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF313" t="n">
-        <v>3</v>
       </c>
       <c r="AG313" t="inlineStr"/>
       <c r="AH313" t="inlineStr"/>
@@ -45041,15 +45041,15 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE314" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF314" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A9%D7%92%D7%91-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF314" t="n">
-        <v>2</v>
       </c>
       <c r="AG314" t="inlineStr"/>
       <c r="AH314" t="inlineStr"/>
@@ -45180,15 +45180,15 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE315" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF315" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A2%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF315" t="n">
-        <v>2</v>
       </c>
       <c r="AG315" t="inlineStr"/>
       <c r="AH315" t="inlineStr"/>
@@ -45319,15 +45319,15 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE316" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF316" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99%D7%9E%D7%94-%D7%A9%D7%A2%D7%A9%D7%95%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF316" t="n">
-        <v>2</v>
       </c>
       <c r="AG316" t="inlineStr"/>
       <c r="AH316" t="inlineStr"/>
@@ -45458,15 +45458,15 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE317" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF317" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%A7%D7%95%D7%94-%D7%A6%D7%93%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF317" t="n">
-        <v>3</v>
       </c>
       <c r="AG317" t="inlineStr"/>
       <c r="AH317" t="inlineStr"/>
@@ -45597,15 +45597,15 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE318" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF318" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%95%D7%91%D7%94-%D7%99%D7%95%D7%A1%D7%A4%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF318" t="n">
-        <v>2</v>
       </c>
       <c r="AG318" t="inlineStr"/>
       <c r="AH318" t="inlineStr"/>
@@ -45736,15 +45736,15 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE319" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF319" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%91%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF319" t="n">
-        <v>2</v>
       </c>
       <c r="AG319" t="inlineStr"/>
       <c r="AH319" t="inlineStr"/>
@@ -45875,15 +45875,15 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE320" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF320" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%95%D7%A4%D7%99%D7%AA-%D7%93%D7%99%D7%A1%D7%98%D7%9C%D7%9E%D7%9F-%D7%9E%D7%99%D7%A8%D7%A7%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF320" t="n">
-        <v>2</v>
       </c>
       <c r="AG320" t="inlineStr"/>
       <c r="AH320" t="inlineStr"/>
@@ -46014,15 +46014,15 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE321" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF321" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%9C%D7%A8%D7%99-%D7%9E%D7%99%D7%9C%D7%94%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF321" t="n">
-        <v>2</v>
       </c>
       <c r="AG321" t="inlineStr"/>
       <c r="AH321" t="inlineStr"/>
@@ -46153,15 +46153,15 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE322" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF322" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%91%D7%90%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF322" t="n">
-        <v>2</v>
       </c>
       <c r="AG322" t="inlineStr"/>
       <c r="AH322" t="inlineStr"/>
@@ -46292,15 +46292,15 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE323" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF323" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%99%D7%A7%D7%98%D7%95%D7%A8%D7%99%D7%94-%D7%A7%D7%9E%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF323" t="n">
-        <v>2</v>
       </c>
       <c r="AG323" t="inlineStr"/>
       <c r="AH323" t="inlineStr"/>
@@ -46431,15 +46431,15 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE324" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF324" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A4%D7%90%D7%90-%D7%90%D7%91%D7%95-%D7%90%D7%A1%D7%9E%D7%90%D7%A2%D7%99%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF324" t="n">
-        <v>2</v>
       </c>
       <c r="AG324" t="inlineStr"/>
       <c r="AH324" t="inlineStr"/>
@@ -46570,15 +46570,15 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE325" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF325" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%91%D7%90%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF325" t="n">
-        <v>2</v>
       </c>
       <c r="AG325" t="inlineStr"/>
       <c r="AH325" t="inlineStr"/>
@@ -46709,15 +46709,15 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE326" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF326" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%93%D7%95%D7%91%D7%93%D7%91%D7%9F-%D7%92%D7%9C%D7%95%D7%96%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF326" t="n">
-        <v>2</v>
       </c>
       <c r="AG326" t="inlineStr"/>
       <c r="AH326" t="inlineStr"/>
@@ -46848,15 +46848,15 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE327" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF327" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%90%D7%98%D7%99%D7%90%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF327" t="n">
-        <v>2</v>
       </c>
       <c r="AG327" t="inlineStr"/>
       <c r="AH327" t="inlineStr"/>
@@ -46987,15 +46987,15 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE328" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF328" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%93%D7%95%D7%91%D7%A1%D7%98%D7%A8-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF328" t="n">
-        <v>2</v>
       </c>
       <c r="AG328" t="inlineStr"/>
       <c r="AH328" t="inlineStr"/>
@@ -47126,15 +47126,15 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE329" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF329" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/291/</t>
         </is>
-      </c>
-      <c r="AF329" t="n">
-        <v>2</v>
       </c>
       <c r="AG329" t="inlineStr"/>
       <c r="AH329" t="inlineStr"/>
@@ -47265,15 +47265,15 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE330" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF330" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%96%D7%99%D7%AA-%D7%97%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF330" t="n">
-        <v>2</v>
       </c>
       <c r="AG330" t="inlineStr"/>
       <c r="AH330" t="inlineStr"/>
@@ -47404,15 +47404,15 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE331" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF331" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%A6%D7%A0%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF331" t="n">
-        <v>2</v>
       </c>
       <c r="AG331" t="inlineStr"/>
       <c r="AH331" t="inlineStr"/>
@@ -47543,15 +47543,15 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE332" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF332" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A4%D7%9C%D7%92/</t>
         </is>
-      </c>
-      <c r="AF332" t="n">
-        <v>2</v>
       </c>
       <c r="AG332" t="inlineStr"/>
       <c r="AH332" t="inlineStr"/>
@@ -47682,15 +47682,15 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE333" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF333" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF333" t="n">
-        <v>2</v>
       </c>
       <c r="AG333" t="inlineStr"/>
       <c r="AH333" t="inlineStr"/>
@@ -47821,15 +47821,15 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE334" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF334" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%90%D7%A0%D7%94-%D7%A4%D7%99%D7%A9%D7%91%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF334" t="n">
-        <v>2</v>
       </c>
       <c r="AG334" t="inlineStr"/>
       <c r="AH334" t="inlineStr"/>
@@ -47960,15 +47960,15 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE335" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF335" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%9E%D7%95%D7%A8%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF335" t="n">
-        <v>2</v>
       </c>
       <c r="AG335" t="inlineStr"/>
       <c r="AH335" t="inlineStr"/>
@@ -48099,15 +48099,15 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE336" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF336" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%A8%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF336" t="n">
-        <v>2</v>
       </c>
       <c r="AG336" t="inlineStr"/>
       <c r="AH336" t="inlineStr"/>
@@ -48238,15 +48238,15 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE337" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE337" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF337" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%99%D7%AA-%D7%9B%D7%A5-%D7%91%D7%A1%D7%98%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF337" t="n">
-        <v>2</v>
       </c>
       <c r="AG337" t="inlineStr"/>
       <c r="AH337" t="inlineStr"/>
@@ -48377,15 +48377,15 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE338" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF338" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A2%D7%9E%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF338" t="n">
-        <v>2</v>
       </c>
       <c r="AG338" t="inlineStr"/>
       <c r="AH338" t="inlineStr"/>
@@ -48516,15 +48516,15 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE339" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF339" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A8%D7%91%D7%99%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF339" t="n">
-        <v>2</v>
       </c>
       <c r="AG339" t="inlineStr"/>
       <c r="AH339" t="inlineStr"/>
@@ -48655,15 +48655,15 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE340" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF340" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%91%D7%9C-%D7%A7%D7%A1%D7%98%D7%99%D7%9F-%D7%9B%D7%94%D7%A0%D7%90/</t>
         </is>
-      </c>
-      <c r="AF340" t="n">
-        <v>2</v>
       </c>
       <c r="AG340" t="inlineStr"/>
       <c r="AH340" t="inlineStr"/>
@@ -48794,15 +48794,15 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE341" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF341" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF341" t="n">
-        <v>2</v>
       </c>
       <c r="AG341" t="inlineStr"/>
       <c r="AH341" t="inlineStr"/>
@@ -48943,15 +48943,15 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>242784</v>
-      </c>
-      <c r="AE342" t="inlineStr">
+        <v>728352</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF342" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%96%D7%94%D7%99-%D7%A1%D7%A2%D7%99%D7%93-%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A6%D7%A4%D7%95%D7%9F-%D7%92%D7%9C%D7%99%D7%9C</t>
         </is>
-      </c>
-      <c r="AF342" t="n">
-        <v>1</v>
       </c>
       <c r="AG342" t="inlineStr"/>
       <c r="AH342" t="inlineStr"/>
@@ -49088,15 +49088,15 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>295248</v>
-      </c>
-      <c r="AE343" t="inlineStr">
+        <v>885744</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF343" t="inlineStr">
         <is>
           <t>https://nefeshachat.co.il/</t>
         </is>
-      </c>
-      <c r="AF343" t="n">
-        <v>2</v>
       </c>
       <c r="AG343" t="inlineStr"/>
       <c r="AH343" t="inlineStr"/>
@@ -49227,15 +49227,15 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE344" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF344" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9B%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF344" t="n">
-        <v>2</v>
       </c>
       <c r="AG344" t="inlineStr"/>
       <c r="AH344" t="inlineStr"/>
@@ -49366,15 +49366,15 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE345" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF345" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A9%D7%9C-%D7%98%D7%95%D7%94%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF345" t="n">
-        <v>2</v>
       </c>
       <c r="AG345" t="inlineStr"/>
       <c r="AH345" t="inlineStr"/>
@@ -49505,15 +49505,15 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE346" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF346" t="inlineStr">
         <is>
           <t>https://tzuna-tova.co.il/</t>
         </is>
-      </c>
-      <c r="AF346" t="n">
-        <v>2</v>
       </c>
       <c r="AG346" t="inlineStr"/>
       <c r="AH346" t="inlineStr"/>
@@ -49644,15 +49644,15 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE347" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF347" t="inlineStr">
         <is>
           <t>https://www.shiri-sleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF347" t="n">
-        <v>2</v>
       </c>
       <c r="AG347" t="inlineStr"/>
       <c r="AH347" t="inlineStr"/>
@@ -49783,15 +49783,15 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE348" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF348" t="inlineStr">
         <is>
           <t>https://www.lev-hasharon.co.il/?page_id=35</t>
         </is>
-      </c>
-      <c r="AF348" t="n">
-        <v>1</v>
       </c>
       <c r="AG348" t="inlineStr"/>
       <c r="AH348" t="inlineStr"/>
@@ -49922,15 +49922,15 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE349" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF349" t="inlineStr">
         <is>
           <t>https://www.ofirbaby.com/</t>
         </is>
-      </c>
-      <c r="AF349" t="n">
-        <v>1</v>
       </c>
       <c r="AG349" t="inlineStr"/>
       <c r="AH349" t="inlineStr"/>
@@ -50061,15 +50061,15 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE350" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF350" t="inlineStr">
         <is>
           <t>https://www.friendsoftzafon.org.il/</t>
         </is>
-      </c>
-      <c r="AF350" t="n">
-        <v>1</v>
       </c>
       <c r="AG350" t="inlineStr"/>
       <c r="AH350" t="inlineStr"/>
@@ -50210,15 +50210,15 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE351" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF351" t="inlineStr">
         <is>
           <t>https://www.medicalhasharon.co.il/home</t>
         </is>
-      </c>
-      <c r="AF351" t="n">
-        <v>1</v>
       </c>
       <c r="AG351" t="inlineStr"/>
       <c r="AH351" t="inlineStr"/>
@@ -50349,15 +50349,15 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE352" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF352" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=7E14A2CD72AD61B21153C2A004D48174&amp;RequestId=00000000-0005-0000-0000-000000000352&amp;Source=undefinedResults</t>
         </is>
-      </c>
-      <c r="AF352" t="n">
-        <v>1</v>
       </c>
       <c r="AG352" t="inlineStr"/>
       <c r="AH352" t="inlineStr"/>
@@ -50488,15 +50488,15 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE353" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF353" t="inlineStr">
         <is>
           <t>https://hpmc-prime.com/</t>
         </is>
-      </c>
-      <c r="AF353" t="n">
-        <v>1</v>
       </c>
       <c r="AG353" t="inlineStr"/>
       <c r="AH353" t="inlineStr"/>
@@ -50635,15 +50635,15 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE354" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF354" t="inlineStr">
         <is>
           <t>https://serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKey=eSo86qER4ZaETCy38wvA4mjeISWyXbtFtJE0SP1qB0MfcsZFamqNWVBcon12iX8vQI0ry3v3SHcFjBSvLlmzhA==</t>
         </is>
-      </c>
-      <c r="AF354" t="n">
-        <v>1</v>
       </c>
       <c r="AG354" t="inlineStr"/>
       <c r="AH354" t="inlineStr"/>
@@ -50783,15 +50783,15 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE355" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF355" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=2CA020F3C4C5B067993FAF75328AF758&amp;RequestId=00000000-0000-0000-0005-000000000105</t>
         </is>
-      </c>
-      <c r="AF355" t="n">
-        <v>1</v>
       </c>
       <c r="AG355" t="inlineStr"/>
       <c r="AH355" t="inlineStr"/>
@@ -50922,15 +50922,15 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE356" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF356" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=BA945B3FBAF6DC188D0C119454B56441&amp;RequestId=00000000-0000-0000-0005-000000000233</t>
         </is>
-      </c>
-      <c r="AF356" t="n">
-        <v>1</v>
       </c>
       <c r="AG356" t="inlineStr"/>
       <c r="AH356" t="inlineStr"/>
@@ -51061,15 +51061,15 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE357" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF357" t="inlineStr">
         <is>
           <t>https://serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKey=rdeOMLyOOZ3wrrZqiL2qbhlKZltQO6skkT2FVfXJExM50B1rgVU80GQZKUJnBoyTj1TxaXxEeeb6fiB1NDU5pw==</t>
         </is>
-      </c>
-      <c r="AF357" t="n">
-        <v>1</v>
       </c>
       <c r="AG357" t="inlineStr"/>
       <c r="AH357" t="inlineStr"/>
@@ -51208,15 +51208,15 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE358" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF358" t="inlineStr">
         <is>
           <t>https://serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKey=e/asC6ieKYwbGjyv8QNoJzSyHNxcE3w8Q8LIU8peBbEKtoOL1HXJumYvC1laTm5V5OAJW3X0HkVvrGmm3NqWEg==</t>
         </is>
-      </c>
-      <c r="AF358" t="n">
-        <v>1</v>
       </c>
       <c r="AG358" t="inlineStr"/>
       <c r="AH358" t="inlineStr"/>
@@ -51347,15 +51347,15 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE359" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF359" t="inlineStr">
         <is>
           <t>https://tlvmed.co.il/</t>
         </is>
-      </c>
-      <c r="AF359" t="n">
-        <v>2</v>
       </c>
       <c r="AG359" t="inlineStr"/>
       <c r="AH359" t="inlineStr"/>
@@ -51496,15 +51496,15 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>242784</v>
-      </c>
-      <c r="AE360" t="inlineStr">
+        <v>728352</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF360" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%96%D7%94%D7%99-%D7%A1%D7%A2%D7%99%D7%93-%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A6%D7%A4%D7%95%D7%9F-%D7%92%D7%9C%D7%99%D7%9C</t>
         </is>
-      </c>
-      <c r="AF360" t="n">
-        <v>1</v>
       </c>
       <c r="AG360" t="inlineStr"/>
       <c r="AH360" t="inlineStr"/>
@@ -51645,15 +51645,15 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE361" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF361" t="inlineStr">
         <is>
           <t>https://dravitalshe.wixsite.com/dravital</t>
         </is>
-      </c>
-      <c r="AF361" t="n">
-        <v>1</v>
       </c>
       <c r="AG361" t="inlineStr"/>
       <c r="AH361" t="inlineStr"/>
@@ -51790,15 +51790,15 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE362" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF362" t="inlineStr">
         <is>
           <t>https://drehuddrucker.com/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF362" t="n">
-        <v>1</v>
       </c>
       <c r="AG362" t="inlineStr"/>
       <c r="AH362" t="inlineStr"/>
@@ -51939,15 +51939,15 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE363" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF363" t="inlineStr">
         <is>
           <t>https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%90%D7%97%D7%9E%D7%93_%D7%92%D7%9E%D7%94%D7%95%D7%A8</t>
         </is>
-      </c>
-      <c r="AF363" t="n">
-        <v>1</v>
       </c>
       <c r="AG363" t="inlineStr"/>
       <c r="AH363" t="inlineStr"/>
@@ -52078,15 +52078,15 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE364" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF364" t="inlineStr">
         <is>
           <t>https://www.irisraz.co.il/</t>
         </is>
-      </c>
-      <c r="AF364" t="n">
-        <v>1</v>
       </c>
       <c r="AG364" t="inlineStr"/>
       <c r="AH364" t="inlineStr"/>
@@ -52227,15 +52227,15 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE365" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF365" t="inlineStr">
         <is>
           <t>https://www.healing-arts.co.il/team/%D7%93%D7%A8-%D7%90%D7%9C%D7%94-%D7%91%D7%A0%D7%92%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF365" t="n">
-        <v>1</v>
       </c>
       <c r="AG365" t="inlineStr"/>
       <c r="AH365" t="inlineStr"/>
@@ -52376,15 +52376,15 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE366" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF366" t="inlineStr">
         <is>
           <t>https://g-news.co.il/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A7%D7%A8%D7%99%D7%99%D7%AA-%D7%A9%D7%9E%D7%95%D7%A0%D7%94-%D7%9E%D7%A8%D7%9B%D7%96-%D7%9E%D7%AA%D7%97%D7%93%D7%A9%D7%AA-%D7%A2%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF366" t="n">
-        <v>1</v>
       </c>
       <c r="AG366" t="inlineStr"/>
       <c r="AH366" t="inlineStr"/>
@@ -52525,15 +52525,15 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE367" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF367" t="inlineStr">
         <is>
           <t>https://geekonomy.net/2020/09/25/geekonony363/</t>
         </is>
-      </c>
-      <c r="AF367" t="n">
-        <v>1</v>
       </c>
       <c r="AG367" t="inlineStr"/>
       <c r="AH367" t="inlineStr"/>
@@ -52672,15 +52672,15 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE368" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF368" t="inlineStr">
         <is>
           <t>https://www.mutarli.co.il/nutritionists</t>
         </is>
-      </c>
-      <c r="AF368" t="n">
-        <v>1</v>
       </c>
       <c r="AG368" t="inlineStr"/>
       <c r="AH368" t="inlineStr"/>
@@ -52817,15 +52817,15 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>236280</v>
-      </c>
-      <c r="AE369" t="inlineStr">
+        <v>708840</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF369" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/doctors-search</t>
         </is>
-      </c>
-      <c r="AF369" t="n">
-        <v>1</v>
       </c>
       <c r="AG369" t="inlineStr"/>
       <c r="AH369" t="inlineStr"/>
@@ -52962,15 +52962,15 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>236280</v>
-      </c>
-      <c r="AE370" t="inlineStr">
+        <v>708840</v>
+      </c>
+      <c r="AE370" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF370" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/doctors-search</t>
         </is>
-      </c>
-      <c r="AF370" t="n">
-        <v>1</v>
       </c>
       <c r="AG370" t="inlineStr"/>
       <c r="AH370" t="inlineStr"/>
@@ -53107,15 +53107,15 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>236280</v>
-      </c>
-      <c r="AE371" t="inlineStr">
+        <v>708840</v>
+      </c>
+      <c r="AE371" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF371" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/doctors-search</t>
         </is>
-      </c>
-      <c r="AF371" t="n">
-        <v>1</v>
       </c>
       <c r="AG371" t="inlineStr"/>
       <c r="AH371" t="inlineStr"/>
@@ -53246,15 +53246,15 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE372" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF372" t="inlineStr">
         <is>
           <t>https://chenaseo.co.il/service/%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%A9%D7%99%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF372" t="n">
-        <v>1</v>
       </c>
       <c r="AG372" t="inlineStr"/>
       <c r="AH372" t="inlineStr"/>
@@ -53391,15 +53391,15 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>295248</v>
-      </c>
-      <c r="AE373" t="inlineStr">
+        <v>885744</v>
+      </c>
+      <c r="AE373" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF373" t="inlineStr">
         <is>
           <t>https://www.caress.co.il/holistic_attachment_approach/</t>
         </is>
-      </c>
-      <c r="AF373" t="n">
-        <v>1</v>
       </c>
       <c r="AG373" t="inlineStr"/>
       <c r="AH373" t="inlineStr"/>
@@ -53538,15 +53538,15 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE374" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE374" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF374" t="inlineStr">
         <is>
           <t>https://www.horimlive.co.il/%D7%9C%D7%99-%D7%A1%D7%9C%D7%A2-%D7%A4%D7%99%D7%96%D7%99%D7%95%D7%AA%D7%A8%D7%A4%D7%99%D7%A1%D7%98%D7%99%D7%AA-%D7%A1%D7%98%D7%95%D7%93%D7%99%D7%95-%D7%90%D7%9E%D7%94%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF374" t="n">
-        <v>1</v>
       </c>
       <c r="AG374" t="inlineStr"/>
       <c r="AH374" t="inlineStr"/>
@@ -53687,15 +53687,15 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE375" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE375" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF375" t="inlineStr">
         <is>
           <t>https://www.drleeorshachar.com/</t>
         </is>
-      </c>
-      <c r="AF375" t="n">
-        <v>1</v>
       </c>
       <c r="AG375" t="inlineStr"/>
       <c r="AH375" t="inlineStr"/>
@@ -53826,15 +53826,15 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE376" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE376" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF376" t="inlineStr">
         <is>
           <t>https://www.lilachofi.co.il/</t>
         </is>
-      </c>
-      <c r="AF376" t="n">
-        <v>1</v>
       </c>
       <c r="AG376" t="inlineStr"/>
       <c r="AH376" t="inlineStr"/>
@@ -53961,15 +53961,15 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE377" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE377" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF377" t="inlineStr">
         <is>
           <t>https://www.refuashlema.co.il/therapists/meital-ron-el</t>
         </is>
-      </c>
-      <c r="AF377" t="n">
-        <v>1</v>
       </c>
       <c r="AG377" t="inlineStr"/>
       <c r="AH377" t="inlineStr"/>
@@ -54100,15 +54100,15 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE378" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE378" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF378" t="inlineStr">
         <is>
           <t>https://meravsleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF378" t="n">
-        <v>1</v>
       </c>
       <c r="AG378" t="inlineStr"/>
       <c r="AH378" t="inlineStr"/>
@@ -54239,15 +54239,15 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE379" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE379" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF379" t="inlineStr">
         <is>
           <t>https://www.ditamidwife.co.il/about</t>
         </is>
-      </c>
-      <c r="AF379" t="n">
-        <v>1</v>
       </c>
       <c r="AG379" t="inlineStr"/>
       <c r="AH379" t="inlineStr"/>
@@ -54388,15 +54388,15 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE380" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE380" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF380" t="inlineStr">
         <is>
           <t>https://menmedical.co.il/doctor/%D7%93%D7%A8-%D7%A1%D7%A2%D7%99%D7%93-%D7%93%D7%9B%D7%95%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF380" t="n">
-        <v>1</v>
       </c>
       <c r="AG380" t="inlineStr"/>
       <c r="AH380" t="inlineStr"/>
@@ -54527,15 +54527,15 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE381" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE381" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF381" t="inlineStr">
         <is>
           <t>https://anatmaron.com/</t>
         </is>
-      </c>
-      <c r="AF381" t="n">
-        <v>1</v>
       </c>
       <c r="AG381" t="inlineStr"/>
       <c r="AH381" t="inlineStr"/>
@@ -54666,15 +54666,15 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE382" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE382" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF382" t="inlineStr">
         <is>
           <t>https://www.omeryael.com/</t>
         </is>
-      </c>
-      <c r="AF382" t="n">
-        <v>1</v>
       </c>
       <c r="AG382" t="inlineStr"/>
       <c r="AH382" t="inlineStr"/>
@@ -54801,15 +54801,15 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE383" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE383" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF383" t="inlineStr">
         <is>
           <t>https://www.refuashlema.co.il/therapists/ronit-ben-eliyahu</t>
         </is>
-      </c>
-      <c r="AF383" t="n">
-        <v>1</v>
       </c>
       <c r="AG383" t="inlineStr"/>
       <c r="AH383" t="inlineStr"/>
@@ -54946,15 +54946,15 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE384" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE384" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF384" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/section/Family-Medicine/%D7%A9%D7%99%D7%97%D7%94-%D7%A2%D7%9D-%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94</t>
         </is>
-      </c>
-      <c r="AF384" t="n">
-        <v>1</v>
       </c>
       <c r="AG384" t="inlineStr"/>
       <c r="AH384" t="inlineStr"/>
@@ -55091,15 +55091,15 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE385" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE385" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF385" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/section/Family-Medicine/%D7%A9%D7%99%D7%97%D7%94-%D7%A2%D7%9D-%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94</t>
         </is>
-      </c>
-      <c r="AF385" t="n">
-        <v>1</v>
       </c>
       <c r="AG385" t="inlineStr"/>
       <c r="AH385" t="inlineStr"/>
@@ -55236,15 +55236,15 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE386" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE386" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF386" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/section/Family-Medicine/%D7%A9%D7%99%D7%97%D7%94-%D7%A2%D7%9D-%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94</t>
         </is>
-      </c>
-      <c r="AF386" t="n">
-        <v>1</v>
       </c>
       <c r="AG386" t="inlineStr"/>
       <c r="AH386" t="inlineStr"/>
@@ -55385,15 +55385,15 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE387" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE387" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF387" t="inlineStr">
         <is>
           <t>https://ashdodnet.com/%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%A7%D7%94%D7%99%D7%9C%D7%94/%D7%9E%D7%99%D7%A0%D7%95%D7%99-%D7%97%D7%93%D7%A9-%D7%93-%D7%A8-%D7%A9%D7%9C%D7%95%D7%9F-%D7%99%D7%A2%D7%A7%D7%91-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%9E%D7%99%D7%A0%D7%94%D7%9C%D7%AA-%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%9E%D7%97%D7%95%D7%96-%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-634820</t>
         </is>
-      </c>
-      <c r="AF387" t="n">
-        <v>1</v>
       </c>
       <c r="AG387" t="inlineStr"/>
       <c r="AH387" t="inlineStr"/>
@@ -55534,15 +55534,15 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE388" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE388" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF388" t="inlineStr">
         <is>
           <t>https://ashdodnet.com/%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%A7%D7%94%D7%99%D7%9C%D7%94/%D7%9E%D7%99%D7%A0%D7%95%D7%99-%D7%97%D7%93%D7%A9-%D7%93-%D7%A8-%D7%A9%D7%9C%D7%95%D7%9F-%D7%99%D7%A2%D7%A7%D7%91-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%9E%D7%99%D7%A0%D7%94%D7%9C%D7%AA-%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%9E%D7%97%D7%95%D7%96-%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-634820</t>
         </is>
-      </c>
-      <c r="AF388" t="n">
-        <v>1</v>
       </c>
       <c r="AG388" t="inlineStr"/>
       <c r="AH388" t="inlineStr"/>
@@ -55683,15 +55683,15 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE389" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE389" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF389" t="inlineStr">
         <is>
           <t>https://www.shiluv-bodymind.co.il/mrtsym/%D7%A9%D7%9E%D7%99%D7%AA-%D7%A7%D7%93%D7%95%D7%A9</t>
         </is>
-      </c>
-      <c r="AF389" t="n">
-        <v>1</v>
       </c>
       <c r="AG389" t="inlineStr"/>
       <c r="AH389" t="inlineStr"/>
@@ -55832,15 +55832,15 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>242784</v>
-      </c>
-      <c r="AE390" t="inlineStr">
+        <v>728352</v>
+      </c>
+      <c r="AE390" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF390" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%96%D7%94%D7%99-%D7%A1%D7%A2%D7%99%D7%93-%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A6%D7%A4%D7%95%D7%9F-%D7%92%D7%9C%D7%99%D7%9C</t>
         </is>
-      </c>
-      <c r="AF390" t="n">
-        <v>1</v>
       </c>
       <c r="AG390" t="inlineStr"/>
       <c r="AH390" t="inlineStr"/>
@@ -55981,15 +55981,15 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE391" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE391" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF391" t="inlineStr">
         <is>
           <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF391" t="n">
-        <v>5</v>
       </c>
       <c r="AG391" t="inlineStr"/>
       <c r="AH391" t="inlineStr"/>
@@ -56130,15 +56130,15 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE392" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE392" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF392" t="inlineStr">
         <is>
           <t>https://www.rashuiot.co.il/html5/arclookup.taf?_id=70247&amp;did=1118&amp;title=%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF392" t="n">
-        <v>1</v>
       </c>
       <c r="AG392" t="inlineStr"/>
       <c r="AH392" t="inlineStr"/>
@@ -56277,15 +56277,15 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE393" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF393" t="inlineStr">
         <is>
           <t>https://www.horuta.co.il/</t>
         </is>
-      </c>
-      <c r="AF393" t="n">
-        <v>1</v>
       </c>
       <c r="AG393" t="inlineStr"/>
       <c r="AH393" t="inlineStr"/>
@@ -56426,15 +56426,15 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE394" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF394" t="inlineStr">
         <is>
           <t>https://www.news1.co.il/ShowPrivateWriterPage.aspx?user_ID=1780&amp;first_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD&amp;last_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF394" t="n">
-        <v>1</v>
       </c>
       <c r="AG394" t="inlineStr"/>
       <c r="AH394" t="inlineStr"/>
@@ -56575,15 +56575,15 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE395" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF395" t="inlineStr">
         <is>
           <t>https://www.news1.co.il/ShowPrivateWriterPage.aspx?user_ID=1780&amp;first_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD&amp;last_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF395" t="n">
-        <v>1</v>
       </c>
       <c r="AG395" t="inlineStr"/>
       <c r="AH395" t="inlineStr"/>
@@ -56724,15 +56724,15 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE396" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF396" t="inlineStr">
         <is>
           <t>https://www.news1.co.il/ShowPrivateWriterPage.aspx?user_ID=1780&amp;first_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD&amp;last_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF396" t="n">
-        <v>1</v>
       </c>
       <c r="AG396" t="inlineStr"/>
       <c r="AH396" t="inlineStr"/>
@@ -56863,15 +56863,15 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE397" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF397" t="inlineStr">
         <is>
           <t>https://etikatz.co.il/services/breastfeeding-and-sleep-consultation/</t>
         </is>
-      </c>
-      <c r="AF397" t="n">
-        <v>1</v>
       </c>
       <c r="AG397" t="inlineStr"/>
       <c r="AH397" t="inlineStr"/>
@@ -57012,15 +57012,15 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE398" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF398" t="inlineStr">
         <is>
           <t>https://shluvim.com/tech/%D7%93%D7%A8-%D7%9E%D7%95%D7%98%D7%99-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
-      </c>
-      <c r="AF398" t="n">
-        <v>1</v>
       </c>
       <c r="AG398" t="inlineStr"/>
       <c r="AH398" t="inlineStr"/>
@@ -57151,15 +57151,15 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE399" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE399" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF399" t="inlineStr">
         <is>
           <t>https://suzisleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF399" t="n">
-        <v>1</v>
       </c>
       <c r="AG399" t="inlineStr"/>
       <c r="AH399" t="inlineStr"/>
@@ -57303,15 +57303,15 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE400" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE400" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF400" t="inlineStr">
         <is>
           <t>https://www.niroleen.com/cosmatisohin-doktor-adi.html</t>
         </is>
-      </c>
-      <c r="AF400" t="n">
-        <v>1</v>
       </c>
       <c r="AG400" t="inlineStr"/>
       <c r="AH400" t="inlineStr"/>
@@ -57452,15 +57452,15 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE401" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF401" t="inlineStr">
         <is>
           <t>https://www.niroleen.com/cosmatisohin-doktor-adi.html</t>
         </is>
-      </c>
-      <c r="AF401" t="n">
-        <v>1</v>
       </c>
       <c r="AG401" t="inlineStr"/>
       <c r="AH401" t="inlineStr"/>
@@ -57601,15 +57601,15 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE402" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE402" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF402" t="inlineStr">
         <is>
           <t>https://medixlife.co.il/our_team/%D7%93%D7%A8-%D7%A2%D7%93%D7%99-%D7%A0%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF402" t="n">
-        <v>1</v>
       </c>
       <c r="AG402" t="inlineStr"/>
       <c r="AH402" t="inlineStr"/>
@@ -57750,15 +57750,15 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE403" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE403" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF403" t="inlineStr">
         <is>
           <t>https://medixlife.co.il/our_team/%D7%93%D7%A8-%D7%A2%D7%93%D7%99-%D7%A0%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF403" t="n">
-        <v>1</v>
       </c>
       <c r="AG403" t="inlineStr"/>
       <c r="AH403" t="inlineStr"/>
@@ -57899,15 +57899,15 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE404" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE404" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF404" t="inlineStr">
         <is>
           <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF404" t="n">
-        <v>1</v>
       </c>
       <c r="AG404" t="inlineStr"/>
       <c r="AH404" t="inlineStr"/>
@@ -58039,15 +58039,15 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE405" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF405" t="inlineStr">
         <is>
           <t>https://michaldalyot.co.il/%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA-%D7%94%D7%95%D7%A8%D7%99%D7%9D/%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%A9%D7%99%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF405" t="n">
-        <v>1</v>
       </c>
       <c r="AG405" t="inlineStr"/>
       <c r="AH405" t="inlineStr"/>
@@ -58178,15 +58178,15 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE406" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE406" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF406" t="inlineStr">
         <is>
           <t>https://www.mcra.co.il/</t>
         </is>
-      </c>
-      <c r="AF406" t="n">
-        <v>2</v>
       </c>
       <c r="AG406" t="inlineStr"/>
       <c r="AH406" t="inlineStr"/>
@@ -58327,15 +58327,15 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE407" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF407" t="inlineStr">
         <is>
           <t>https://www.bekeshevclinic.co.il/</t>
         </is>
-      </c>
-      <c r="AF407" t="n">
-        <v>1</v>
       </c>
       <c r="AG407" t="inlineStr"/>
       <c r="AH407" t="inlineStr"/>
@@ -58472,15 +58472,15 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE408" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF408" t="inlineStr">
         <is>
           <t>https://www.homedical.co.il/services/%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94-%D7%A2%D7%93-%D7%94%D7%91%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF408" t="n">
-        <v>1</v>
       </c>
       <c r="AG408" t="inlineStr"/>
       <c r="AH408" t="inlineStr"/>
@@ -58621,15 +58621,15 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE409" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE409" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF409" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
-      </c>
-      <c r="AF409" t="n">
-        <v>1</v>
       </c>
       <c r="AG409" t="inlineStr"/>
       <c r="AH409" t="inlineStr"/>
@@ -58770,15 +58770,15 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>297432</v>
-      </c>
-      <c r="AE410" t="inlineStr">
+        <v>892296</v>
+      </c>
+      <c r="AE410" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF410" t="inlineStr">
         <is>
           <t>https://www.yaeltzur.co.il/talie-gliksman/</t>
         </is>
-      </c>
-      <c r="AF410" t="n">
-        <v>1</v>
       </c>
       <c r="AG410" t="inlineStr"/>
       <c r="AH410" t="inlineStr"/>
@@ -58917,15 +58917,15 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE411" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE411" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF411" t="inlineStr">
         <is>
           <t>https://www.mutarli.co.il/nutritionists</t>
         </is>
-      </c>
-      <c r="AF411" t="n">
-        <v>1</v>
       </c>
       <c r="AG411" t="inlineStr"/>
       <c r="AH411" t="inlineStr"/>
@@ -59066,15 +59066,15 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE412" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE412" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF412" t="inlineStr">
         <is>
           <t>https://www.rashuiot.co.il/html5/arclookup.taf?_id=70247&amp;did=1118&amp;title=%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF412" t="n">
-        <v>1</v>
       </c>
       <c r="AG412" t="inlineStr"/>
       <c r="AH412" t="inlineStr"/>
@@ -59213,15 +59213,15 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE413" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE413" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF413" t="inlineStr">
         <is>
           <t>https://www.horuta.co.il/</t>
         </is>
-      </c>
-      <c r="AF413" t="n">
-        <v>1</v>
       </c>
       <c r="AG413" t="inlineStr"/>
       <c r="AH413" t="inlineStr"/>
@@ -59360,15 +59360,15 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE414" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE414" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF414" t="inlineStr">
         <is>
           <t>https://www.efratkeidar.co.il/sleep-consultant/</t>
         </is>
-      </c>
-      <c r="AF414" t="n">
-        <v>1</v>
       </c>
       <c r="AG414" t="inlineStr"/>
       <c r="AH414" t="inlineStr"/>
@@ -59509,15 +59509,15 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE415" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE415" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF415" t="inlineStr">
         <is>
           <t>https://medixlife.co.il/our_team/%D7%93%D7%A8-%D7%A2%D7%93%D7%99-%D7%A0%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF415" t="n">
-        <v>1</v>
       </c>
       <c r="AG415" t="inlineStr"/>
       <c r="AH415" t="inlineStr"/>
@@ -59648,15 +59648,15 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE416" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE416" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF416" t="inlineStr">
         <is>
           <t>https://promo.dietangel.co.il/</t>
         </is>
-      </c>
-      <c r="AF416" t="n">
-        <v>1</v>
       </c>
       <c r="AG416" t="inlineStr"/>
       <c r="AH416" t="inlineStr"/>
@@ -59797,15 +59797,15 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE417" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE417" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF417" t="inlineStr">
         <is>
           <t>https://www.linealba.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%9E%D7%98%D7%A4%D7%9C/%D7%93-%D7%A8-%D7%92%D7%99%D7%90-%D7%A2%D7%99%D7%9C%D7%9D</t>
         </is>
-      </c>
-      <c r="AF417" t="n">
-        <v>1</v>
       </c>
       <c r="AG417" t="inlineStr"/>
       <c r="AH417" t="inlineStr"/>
@@ -59946,15 +59946,15 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>242784</v>
-      </c>
-      <c r="AE418" t="inlineStr">
+        <v>728352</v>
+      </c>
+      <c r="AE418" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF418" t="inlineStr">
         <is>
           <t>https://www.myavne.co.il/%D7%94%D7%A8%D7%95%D7%A4%D7%90-%D7%94%D7%9E%D7%A1%D7%95%D7%A8-%D7%A9%D7%9C-%D7%94%D7%9E%D7%93%D7%99%D7%A0%D7%94--%D7%93--%D7%A8-%D7%94%D7%99%D7%9C%D7%94-%D7%A9%D7%9E%D7%95%D7%9C-%D7%9B%D7%A5-%D7%9E%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%99%D7%91%D7%A0%D7%94-%D7%94%D7%99%D7%A8%D7%95%D7%A7%D7%94</t>
         </is>
-      </c>
-      <c r="AF418" t="n">
-        <v>1</v>
       </c>
       <c r="AG418" t="inlineStr"/>
       <c r="AH418" t="inlineStr"/>
@@ -60093,15 +60093,15 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE419" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE419" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF419" t="inlineStr">
         <is>
           <t>https://www.therapwiz.co.il/tdetails/?id=290</t>
         </is>
-      </c>
-      <c r="AF419" t="n">
-        <v>1</v>
       </c>
       <c r="AG419" t="inlineStr"/>
       <c r="AH419" t="inlineStr"/>
@@ -60242,15 +60242,15 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE420" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE420" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF420" t="inlineStr">
         <is>
           <t>https://www.sofia-medical.com/%D7%94%D7%A6%D7%95%D7%95%D7%AA/%D7%93-%D7%A8-%D7%9E%D7%95%D7%90%D7%9E%D7%9F-%D7%97%D7%98%D7%99%D7%91</t>
         </is>
-      </c>
-      <c r="AF420" t="n">
-        <v>1</v>
       </c>
       <c r="AG420" t="inlineStr"/>
       <c r="AH420" t="inlineStr"/>
@@ -60391,15 +60391,15 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE421" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE421" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF421" t="inlineStr">
         <is>
           <t>https://hea-lth.co.il/family-medicine/</t>
         </is>
-      </c>
-      <c r="AF421" t="n">
-        <v>1</v>
       </c>
       <c r="AG421" t="inlineStr"/>
       <c r="AH421" t="inlineStr"/>
@@ -60538,15 +60538,15 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE422" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE422" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF422" t="inlineStr">
         <is>
           <t>https://www.mploy.co.il/job/search/%D7%9E%D7%A0%D7%94%D7%9C-%D7%9E%D7%A8%D7%A4%D7%90%D7%94</t>
         </is>
-      </c>
-      <c r="AF422" t="n">
-        <v>1</v>
       </c>
       <c r="AG422" t="inlineStr"/>
       <c r="AH422" t="inlineStr"/>
@@ -60677,15 +60677,15 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE423" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE423" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF423" t="inlineStr">
         <is>
           <t>https://be-doula.co.il/</t>
         </is>
-      </c>
-      <c r="AF423" t="n">
-        <v>1</v>
       </c>
       <c r="AG423" t="inlineStr"/>
       <c r="AH423" t="inlineStr"/>
@@ -60816,15 +60816,15 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE424" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE424" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF424" t="inlineStr">
         <is>
           <t>https://www.leidaschool.co.il/</t>
         </is>
-      </c>
-      <c r="AF424" t="n">
-        <v>2</v>
       </c>
       <c r="AG424" t="inlineStr"/>
       <c r="AH424" t="inlineStr"/>
@@ -60963,15 +60963,15 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE425" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE425" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF425" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
         </is>
-      </c>
-      <c r="AF425" t="n">
-        <v>5</v>
       </c>
       <c r="AG425" t="inlineStr"/>
       <c r="AH425" t="inlineStr"/>
@@ -61110,15 +61110,15 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE426" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE426" t="n">
+        <v>229</v>
+      </c>
+      <c r="AF426" t="inlineStr">
         <is>
           <t>https://ialp.org.il/lllisrael/</t>
         </is>
-      </c>
-      <c r="AF426" t="n">
-        <v>229</v>
       </c>
       <c r="AG426" t="inlineStr"/>
       <c r="AH426" t="inlineStr"/>
@@ -61249,15 +61249,15 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE427" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE427" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF427" t="inlineStr">
         <is>
           <t>https://sobada.co.il/practitioner/michal_rosen</t>
         </is>
-      </c>
-      <c r="AF427" t="n">
-        <v>1</v>
       </c>
       <c r="AG427" t="inlineStr"/>
       <c r="AH427" t="inlineStr"/>
@@ -61398,15 +61398,15 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE428" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE428" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF428" t="inlineStr">
         <is>
           <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
         </is>
-      </c>
-      <c r="AF428" t="n">
-        <v>4</v>
       </c>
       <c r="AG428" t="inlineStr"/>
       <c r="AH428" t="inlineStr"/>
@@ -61537,15 +61537,15 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE429" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE429" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF429" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/u/research-centers/womancenter/about/</t>
         </is>
-      </c>
-      <c r="AF429" t="n">
-        <v>1</v>
       </c>
       <c r="AG429" t="inlineStr"/>
       <c r="AH429" t="inlineStr"/>
@@ -61680,15 +61680,15 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE430" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE430" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF430" t="inlineStr">
         <is>
           <t>https://inhealthycompany.co.il/category/%D7%91%D7%9C%D7%95%D7%92-%D7%9E%D7%90%D7%9E%D7%A8%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF430" t="n">
-        <v>1</v>
       </c>
       <c r="AG430" t="inlineStr"/>
       <c r="AH430" t="inlineStr"/>
@@ -61819,15 +61819,15 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE431" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE431" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF431" t="inlineStr">
         <is>
           <t>https://balaolam.co.il/</t>
         </is>
-      </c>
-      <c r="AF431" t="n">
-        <v>2</v>
       </c>
       <c r="AG431" t="inlineStr"/>
       <c r="AH431" t="inlineStr"/>
@@ -61966,15 +61966,15 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE432" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE432" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF432" t="inlineStr">
         <is>
           <t>https://global-ivf.com/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF432" t="n">
-        <v>1</v>
       </c>
       <c r="AG432" t="inlineStr"/>
       <c r="AH432" t="inlineStr"/>
@@ -62113,15 +62113,15 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE433" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE433" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF433" t="inlineStr">
         <is>
           <t>https://www.kbria.co.il/product/%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%95%D7%9C%D7%99%D7%93%D7%94/</t>
         </is>
-      </c>
-      <c r="AF433" t="n">
-        <v>1</v>
       </c>
       <c r="AG433" t="inlineStr"/>
       <c r="AH433" t="inlineStr"/>
@@ -62252,15 +62252,15 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE434" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE434" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF434" t="inlineStr">
         <is>
           <t>https://myotonic.co.il/pregnancy</t>
         </is>
-      </c>
-      <c r="AF434" t="n">
-        <v>1</v>
       </c>
       <c r="AG434" t="inlineStr"/>
       <c r="AH434" t="inlineStr"/>
@@ -62391,15 +62391,15 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE435" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF435" t="inlineStr">
         <is>
           <t>https://www.greenfertility.co.il/</t>
         </is>
-      </c>
-      <c r="AF435" t="n">
-        <v>1</v>
       </c>
       <c r="AG435" t="inlineStr"/>
       <c r="AH435" t="inlineStr"/>
@@ -62540,15 +62540,15 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE436" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF436" t="inlineStr">
         <is>
           <t>https://www.reshet-yeruka.net/youth/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%95%D7%A8%D7%99%D7%9D-%D7%9C%D7%92%D7%93%D7%9C-%D7%91%D7%A0%D7%97%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF436" t="n">
-        <v>1</v>
       </c>
       <c r="AG436" t="inlineStr"/>
       <c r="AH436" t="inlineStr"/>
@@ -62689,15 +62689,15 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE437" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF437" t="inlineStr">
         <is>
           <t>https://www.reshet-yeruka.net/youth/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%95%D7%A8%D7%99%D7%9D-%D7%9C%D7%92%D7%93%D7%9C-%D7%91%D7%A0%D7%97%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF437" t="n">
-        <v>1</v>
       </c>
       <c r="AG437" t="inlineStr"/>
       <c r="AH437" t="inlineStr"/>
@@ -62838,15 +62838,15 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE438" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF438" t="inlineStr">
         <is>
           <t>https://www.reshet-yeruka.net/youth/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%95%D7%A8%D7%99%D7%9D-%D7%9C%D7%92%D7%93%D7%9C-%D7%91%D7%A0%D7%97%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF438" t="n">
-        <v>1</v>
       </c>
       <c r="AG438" t="inlineStr"/>
       <c r="AH438" t="inlineStr"/>
@@ -62985,15 +62985,15 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE439" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF439" t="inlineStr">
         <is>
           <t>https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/</t>
         </is>
-      </c>
-      <c r="AF439" t="n">
-        <v>1</v>
       </c>
       <c r="AG439" t="inlineStr"/>
       <c r="AH439" t="inlineStr"/>
@@ -63128,15 +63128,15 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE440" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF440" t="inlineStr">
         <is>
           <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
         </is>
-      </c>
-      <c r="AF440" t="n">
-        <v>3</v>
       </c>
       <c r="AG440" t="inlineStr"/>
       <c r="AH440" t="inlineStr"/>
@@ -63278,15 +63278,15 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE441" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF441" t="inlineStr">
         <is>
           <t>https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/</t>
         </is>
-      </c>
-      <c r="AF441" t="n">
-        <v>1</v>
       </c>
       <c r="AG441" t="inlineStr"/>
       <c r="AH441" t="inlineStr"/>
@@ -63417,15 +63417,15 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE442" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF442" t="inlineStr">
         <is>
           <t>https://mssociety.org.il/category/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%98%D7%A8%D7%A9%D7%AA-%D7%A0%D7%A4%D7%95%D7%A6%D7%94/%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%9C%D7%99%D7%93%D7%94-%D7%95%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
-      </c>
-      <c r="AF442" t="n">
-        <v>1</v>
       </c>
       <c r="AG442" t="inlineStr"/>
       <c r="AH442" t="inlineStr"/>
@@ -63552,15 +63552,15 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE443" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF443" t="inlineStr">
         <is>
           <t>https://find.midwives.org.il/</t>
         </is>
-      </c>
-      <c r="AF443" t="n">
-        <v>1</v>
       </c>
       <c r="AG443" t="inlineStr"/>
       <c r="AH443" t="inlineStr"/>
@@ -63691,15 +63691,15 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE444" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF444" t="inlineStr">
         <is>
           <t>https://www.briah.org/team</t>
         </is>
-      </c>
-      <c r="AF444" t="n">
-        <v>1</v>
       </c>
       <c r="AG444" t="inlineStr"/>
       <c r="AH444" t="inlineStr"/>
@@ -63830,15 +63830,15 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE445" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF445" t="inlineStr">
         <is>
           <t>https://www.briah.org/team</t>
         </is>
-      </c>
-      <c r="AF445" t="n">
-        <v>1</v>
       </c>
       <c r="AG445" t="inlineStr"/>
       <c r="AH445" t="inlineStr"/>
@@ -63969,15 +63969,15 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE446" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF446" t="inlineStr">
         <is>
           <t>https://www.briah.org/team</t>
         </is>
-      </c>
-      <c r="AF446" t="n">
-        <v>1</v>
       </c>
       <c r="AG446" t="inlineStr"/>
       <c r="AH446" t="inlineStr"/>
@@ -64108,15 +64108,15 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE447" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF447" t="inlineStr">
         <is>
           <t>https://puah.org.il/%D7%A7%D7%91%D7%95%D7%A6%D7%95%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%9C%D7%A0%D7%A9%D7%99%D7%9D-%D7%9E%D7%90%D7%95%D7%AA%D7%92%D7%A8%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF447" t="n">
-        <v>1</v>
       </c>
       <c r="AG447" t="inlineStr"/>
       <c r="AH447" t="inlineStr"/>
@@ -64255,15 +64255,15 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE448" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF448" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/mamy-lis/courses/courses-parents/antenatal-classes/</t>
         </is>
-      </c>
-      <c r="AF448" t="n">
-        <v>1</v>
       </c>
       <c r="AG448" t="inlineStr"/>
       <c r="AH448" t="inlineStr"/>
@@ -64404,15 +64404,15 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE449" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF449" t="inlineStr">
         <is>
           <t>https://www.ipts.org.il/?CategoryID=471&amp;ArticleID=2165</t>
         </is>
-      </c>
-      <c r="AF449" t="n">
-        <v>1</v>
       </c>
       <c r="AG449" t="inlineStr"/>
       <c r="AH449" t="inlineStr"/>
@@ -64553,15 +64553,15 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE450" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE450" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF450" t="inlineStr">
         <is>
           <t>https://www.ipts.org.il/?CategoryID=471&amp;ArticleID=2165</t>
         </is>
-      </c>
-      <c r="AF450" t="n">
-        <v>1</v>
       </c>
       <c r="AG450" t="inlineStr"/>
       <c r="AH450" t="inlineStr"/>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>768366</v>
+        <v>2305098</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1065069</v>
+        <v>3195207</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE10" t="n">
         <v>3</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>946971</v>
+        <v>2840913</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>768366</v>
+        <v>2305098</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>768366</v>
+        <v>2305098</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>728271</v>
+        <v>2184813</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>710856</v>
+        <v>2132568</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>710856</v>
+        <v>2132568</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>710856</v>
+        <v>2132568</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>710802</v>
+        <v>2132406</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>886473</v>
+        <v>2659419</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>710802</v>
+        <v>2132406</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE80" t="n">
         <v>5</v>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE85" t="n">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE90" t="n">
         <v>8</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE92" t="n">
         <v>11</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14373,7 +14373,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE96" t="n">
         <v>3</v>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>946971</v>
+        <v>2840913</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE102" t="n">
         <v>3</v>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE103" t="n">
         <v>17</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE106" t="n">
         <v>4</v>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16523,7 +16523,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE116" t="n">
         <v>8</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -17655,7 +17655,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18092,7 +18092,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -18688,7 +18688,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -18837,7 +18837,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -18986,7 +18986,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -19568,7 +19568,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>768366</v>
+        <v>2305098</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -19866,7 +19866,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20015,7 +20015,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20438,7 +20438,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20994,7 +20994,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21133,7 +21133,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21272,7 +21272,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21550,7 +21550,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22245,7 +22245,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22523,7 +22523,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22662,7 +22662,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22801,7 +22801,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22940,7 +22940,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23218,7 +23218,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24052,7 +24052,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24191,7 +24191,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24330,7 +24330,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24747,7 +24747,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25164,7 +25164,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25442,7 +25442,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25581,7 +25581,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25859,7 +25859,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26554,7 +26554,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26971,7 +26971,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27249,7 +27249,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27527,7 +27527,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27666,7 +27666,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27805,7 +27805,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27944,7 +27944,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28083,7 +28083,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28222,7 +28222,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28639,7 +28639,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28778,7 +28778,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28917,7 +28917,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29195,7 +29195,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29334,7 +29334,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29473,7 +29473,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29612,7 +29612,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -29751,7 +29751,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29890,7 +29890,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30029,7 +30029,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30168,7 +30168,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30307,7 +30307,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30446,7 +30446,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -30724,7 +30724,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -30863,7 +30863,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31002,7 +31002,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31141,7 +31141,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31280,7 +31280,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31419,7 +31419,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -31697,7 +31697,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31975,7 +31975,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32253,7 +32253,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32392,7 +32392,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32531,7 +32531,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32809,7 +32809,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32948,7 +32948,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33087,7 +33087,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33226,7 +33226,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33365,7 +33365,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33782,7 +33782,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33921,7 +33921,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34199,7 +34199,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34338,7 +34338,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -34616,7 +34616,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -34755,7 +34755,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34894,7 +34894,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35033,7 +35033,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35172,7 +35172,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35311,7 +35311,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35450,7 +35450,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -35589,7 +35589,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -35728,7 +35728,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -35867,7 +35867,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36145,7 +36145,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -36284,7 +36284,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36423,7 +36423,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -36562,7 +36562,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -36701,7 +36701,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -36840,7 +36840,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -36979,7 +36979,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -37118,7 +37118,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -37257,7 +37257,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -37396,7 +37396,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -37674,7 +37674,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -37813,7 +37813,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -37952,7 +37952,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -38091,7 +38091,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -38230,7 +38230,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -38369,7 +38369,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -38508,7 +38508,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -38647,7 +38647,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -38786,7 +38786,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -38925,7 +38925,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -39203,7 +39203,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -39342,7 +39342,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -39481,7 +39481,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -39620,7 +39620,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -39759,7 +39759,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -40037,7 +40037,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -40176,7 +40176,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -40315,7 +40315,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -41010,7 +41010,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -41149,7 +41149,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -41427,7 +41427,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -41566,7 +41566,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -41705,7 +41705,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -41983,7 +41983,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -42400,7 +42400,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -42539,7 +42539,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -42678,7 +42678,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -42817,7 +42817,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -42956,7 +42956,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -43095,7 +43095,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -43373,7 +43373,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -43512,7 +43512,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -43790,7 +43790,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -43929,7 +43929,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -44068,7 +44068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -44346,7 +44346,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -44485,7 +44485,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -44763,7 +44763,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -44902,7 +44902,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE313" t="n">
         <v>3</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -45180,7 +45180,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -45319,7 +45319,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -45458,7 +45458,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE317" t="n">
         <v>3</v>
@@ -45597,7 +45597,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -45736,7 +45736,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -45875,7 +45875,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -46153,7 +46153,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -46292,7 +46292,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -46431,7 +46431,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -46570,7 +46570,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -46709,7 +46709,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -46848,7 +46848,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -46987,7 +46987,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -47126,7 +47126,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -47265,7 +47265,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -47682,7 +47682,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -47821,7 +47821,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -47960,7 +47960,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -48099,7 +48099,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -48238,7 +48238,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -48377,7 +48377,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -48516,7 +48516,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -48655,7 +48655,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -48794,7 +48794,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -48943,7 +48943,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>728352</v>
+        <v>2185056</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -49088,7 +49088,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>885744</v>
+        <v>2657232</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -49366,7 +49366,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -49505,7 +49505,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -49644,7 +49644,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -49783,7 +49783,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -49922,7 +49922,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -50061,7 +50061,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -50210,7 +50210,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -50349,7 +50349,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -50488,7 +50488,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -50635,7 +50635,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -50783,7 +50783,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -50922,7 +50922,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -51061,7 +51061,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -51208,7 +51208,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -51347,7 +51347,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE359" t="n">
         <v>2</v>
@@ -51496,7 +51496,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>728352</v>
+        <v>2185056</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -51645,7 +51645,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -51790,7 +51790,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -51939,7 +51939,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -52078,7 +52078,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -52227,7 +52227,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -52525,7 +52525,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -52672,7 +52672,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -52817,7 +52817,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>708840</v>
+        <v>2126520</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -52962,7 +52962,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>708840</v>
+        <v>2126520</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -53107,7 +53107,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>708840</v>
+        <v>2126520</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -53246,7 +53246,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -53391,7 +53391,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>885744</v>
+        <v>2657232</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -53538,7 +53538,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -53687,7 +53687,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -53826,7 +53826,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -53961,7 +53961,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -54100,7 +54100,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -54239,7 +54239,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -54388,7 +54388,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -54527,7 +54527,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -54666,7 +54666,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -54801,7 +54801,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -54946,7 +54946,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -55091,7 +55091,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -55236,7 +55236,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -55385,7 +55385,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -55534,7 +55534,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -55683,7 +55683,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -55832,7 +55832,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>728352</v>
+        <v>2185056</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -55981,7 +55981,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE391" t="n">
         <v>5</v>
@@ -56130,7 +56130,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -56277,7 +56277,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -56426,7 +56426,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -56575,7 +56575,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -56724,7 +56724,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -56863,7 +56863,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -57012,7 +57012,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -57151,7 +57151,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -57303,7 +57303,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -57452,7 +57452,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -57601,7 +57601,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -57750,7 +57750,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -57899,7 +57899,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -58039,7 +58039,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -58178,7 +58178,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE406" t="n">
         <v>2</v>
@@ -58327,7 +58327,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -58472,7 +58472,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -58621,7 +58621,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -58770,7 +58770,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>892296</v>
+        <v>2676888</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -58917,7 +58917,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -59066,7 +59066,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -59213,7 +59213,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -59360,7 +59360,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -59509,7 +59509,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -59648,7 +59648,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -59797,7 +59797,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -59946,7 +59946,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>728352</v>
+        <v>2185056</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -60093,7 +60093,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -60242,7 +60242,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -60391,7 +60391,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -60538,7 +60538,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -60677,7 +60677,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -60816,7 +60816,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE424" t="n">
         <v>2</v>
@@ -60963,7 +60963,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE425" t="n">
         <v>5</v>
@@ -61110,7 +61110,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE426" t="n">
         <v>229</v>
@@ -61249,7 +61249,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -61398,7 +61398,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE428" t="n">
         <v>4</v>
@@ -61537,7 +61537,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -61680,7 +61680,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>
@@ -61819,7 +61819,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE431" t="n">
         <v>2</v>
@@ -61966,7 +61966,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -62113,7 +62113,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -62252,7 +62252,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -62391,7 +62391,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -62540,7 +62540,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -62689,7 +62689,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -62838,7 +62838,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -62985,7 +62985,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -63128,7 +63128,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE440" t="n">
         <v>3</v>
@@ -63278,7 +63278,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -63417,7 +63417,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -63552,7 +63552,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE443" t="n">
         <v>1</v>
@@ -63691,7 +63691,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -63830,7 +63830,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -63969,7 +63969,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -64108,7 +64108,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -64255,7 +64255,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -64404,7 +64404,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -64553,7 +64553,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>2305098</v>
+        <v>6915294</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3195207</v>
+        <v>9585621</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE10" t="n">
         <v>3</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2840913</v>
+        <v>8522739</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2305098</v>
+        <v>6915294</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2305098</v>
+        <v>6915294</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>2184813</v>
+        <v>6554439</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2132568</v>
+        <v>6397704</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2132568</v>
+        <v>6397704</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>2132568</v>
+        <v>6397704</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2132406</v>
+        <v>6397218</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2659419</v>
+        <v>7978257</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2132406</v>
+        <v>6397218</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE80" t="n">
         <v>5</v>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE85" t="n">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE90" t="n">
         <v>8</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE92" t="n">
         <v>11</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14373,7 +14373,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE96" t="n">
         <v>3</v>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2840913</v>
+        <v>8522739</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE102" t="n">
         <v>3</v>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE103" t="n">
         <v>17</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE106" t="n">
         <v>4</v>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16523,7 +16523,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE116" t="n">
         <v>8</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -17655,7 +17655,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18092,7 +18092,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -18688,7 +18688,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -18837,7 +18837,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -18986,7 +18986,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -19568,7 +19568,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2305098</v>
+        <v>6915294</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -19866,7 +19866,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20015,7 +20015,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20438,7 +20438,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20994,7 +20994,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21133,7 +21133,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21272,7 +21272,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21550,7 +21550,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22245,7 +22245,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22523,7 +22523,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22662,7 +22662,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22801,7 +22801,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22940,7 +22940,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23218,7 +23218,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24052,7 +24052,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24191,7 +24191,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24330,7 +24330,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24747,7 +24747,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25164,7 +25164,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25442,7 +25442,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25581,7 +25581,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25859,7 +25859,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26554,7 +26554,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26971,7 +26971,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27249,7 +27249,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27527,7 +27527,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27666,7 +27666,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27805,7 +27805,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27944,7 +27944,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28083,7 +28083,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28222,7 +28222,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28639,7 +28639,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28778,7 +28778,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28917,7 +28917,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29195,7 +29195,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29334,7 +29334,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29473,7 +29473,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29612,7 +29612,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -29751,7 +29751,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29890,7 +29890,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30029,7 +30029,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30168,7 +30168,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30307,7 +30307,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30446,7 +30446,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -30724,7 +30724,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -30863,7 +30863,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31002,7 +31002,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31141,7 +31141,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31280,7 +31280,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31419,7 +31419,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -31697,7 +31697,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31975,7 +31975,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32253,7 +32253,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32392,7 +32392,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32531,7 +32531,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32809,7 +32809,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32948,7 +32948,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33087,7 +33087,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33226,7 +33226,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33365,7 +33365,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33782,7 +33782,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33921,7 +33921,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34199,7 +34199,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34338,7 +34338,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -34616,7 +34616,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -34755,7 +34755,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34894,7 +34894,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35033,7 +35033,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35172,7 +35172,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35311,7 +35311,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35450,7 +35450,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -35589,7 +35589,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -35728,7 +35728,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -35867,7 +35867,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36145,7 +36145,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -36284,7 +36284,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36423,7 +36423,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -36562,7 +36562,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -36701,7 +36701,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -36840,7 +36840,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -36979,7 +36979,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -37118,7 +37118,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -37257,7 +37257,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -37396,7 +37396,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -37674,7 +37674,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -37813,7 +37813,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -37952,7 +37952,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -38091,7 +38091,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -38230,7 +38230,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -38369,7 +38369,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -38508,7 +38508,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -38647,7 +38647,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -38786,7 +38786,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -38925,7 +38925,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -39203,7 +39203,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -39342,7 +39342,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -39481,7 +39481,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -39620,7 +39620,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -39759,7 +39759,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -40037,7 +40037,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -40176,7 +40176,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -40315,7 +40315,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -41010,7 +41010,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -41149,7 +41149,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -41427,7 +41427,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -41566,7 +41566,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -41705,7 +41705,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -41983,7 +41983,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -42400,7 +42400,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -42539,7 +42539,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -42678,7 +42678,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -42817,7 +42817,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -42956,7 +42956,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -43095,7 +43095,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -43373,7 +43373,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -43512,7 +43512,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -43790,7 +43790,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -43929,7 +43929,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -44068,7 +44068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -44346,7 +44346,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -44485,7 +44485,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -44763,7 +44763,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -44902,7 +44902,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE313" t="n">
         <v>3</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -45180,7 +45180,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -45319,7 +45319,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -45458,7 +45458,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE317" t="n">
         <v>3</v>
@@ -45597,7 +45597,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -45736,7 +45736,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -45875,7 +45875,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -46153,7 +46153,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -46292,7 +46292,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -46431,7 +46431,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -46570,7 +46570,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -46709,7 +46709,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -46848,7 +46848,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -46987,7 +46987,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -47126,7 +47126,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -47265,7 +47265,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -47682,7 +47682,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -47821,7 +47821,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -47960,7 +47960,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -48099,7 +48099,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -48238,7 +48238,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -48377,7 +48377,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -48516,7 +48516,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -48655,7 +48655,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -48794,7 +48794,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -48943,7 +48943,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>2185056</v>
+        <v>6555168</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -49088,7 +49088,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>2657232</v>
+        <v>7971696</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -49366,7 +49366,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -49505,7 +49505,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -49644,7 +49644,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -49783,7 +49783,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -49922,7 +49922,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -50061,7 +50061,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -50210,7 +50210,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -50349,7 +50349,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -50488,7 +50488,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -50635,7 +50635,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -50783,7 +50783,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -50922,7 +50922,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -51061,7 +51061,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -51208,7 +51208,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -51347,7 +51347,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE359" t="n">
         <v>2</v>
@@ -51496,7 +51496,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>2185056</v>
+        <v>6555168</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -51645,7 +51645,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -51790,7 +51790,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -51939,7 +51939,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -52078,7 +52078,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -52227,7 +52227,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -52525,7 +52525,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -52672,7 +52672,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -52817,7 +52817,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>2126520</v>
+        <v>6379560</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -52962,7 +52962,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>2126520</v>
+        <v>6379560</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -53107,7 +53107,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>2126520</v>
+        <v>6379560</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -53246,7 +53246,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -53391,7 +53391,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>2657232</v>
+        <v>7971696</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -53538,7 +53538,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -53687,7 +53687,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -53826,7 +53826,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -53961,7 +53961,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -54100,7 +54100,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -54239,7 +54239,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -54388,7 +54388,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -54527,7 +54527,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -54666,7 +54666,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -54801,7 +54801,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -54946,7 +54946,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -55091,7 +55091,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -55236,7 +55236,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -55385,7 +55385,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -55534,7 +55534,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -55683,7 +55683,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -55832,7 +55832,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>2185056</v>
+        <v>6555168</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -55981,7 +55981,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE391" t="n">
         <v>5</v>
@@ -56130,7 +56130,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -56277,7 +56277,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -56426,7 +56426,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -56575,7 +56575,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -56724,7 +56724,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -56863,7 +56863,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -57012,7 +57012,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -57151,7 +57151,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -57303,7 +57303,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -57452,7 +57452,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -57601,7 +57601,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -57750,7 +57750,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -57899,7 +57899,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -58039,7 +58039,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -58178,7 +58178,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE406" t="n">
         <v>2</v>
@@ -58327,7 +58327,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -58472,7 +58472,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -58621,7 +58621,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -58770,7 +58770,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>2676888</v>
+        <v>8030664</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -58917,7 +58917,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -59066,7 +59066,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -59213,7 +59213,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -59360,7 +59360,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -59509,7 +59509,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -59648,7 +59648,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -59797,7 +59797,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -59946,7 +59946,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>2185056</v>
+        <v>6555168</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -60093,7 +60093,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -60242,7 +60242,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -60391,7 +60391,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -60538,7 +60538,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -60677,7 +60677,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -60816,7 +60816,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE424" t="n">
         <v>2</v>
@@ -60963,7 +60963,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE425" t="n">
         <v>5</v>
@@ -61110,7 +61110,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE426" t="n">
         <v>229</v>
@@ -61249,7 +61249,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -61398,7 +61398,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE428" t="n">
         <v>4</v>
@@ -61537,7 +61537,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -61680,7 +61680,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE430" t="n">
         <v>1</v>
@@ -61819,7 +61819,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE431" t="n">
         <v>2</v>
@@ -61966,7 +61966,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -62113,7 +62113,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -62252,7 +62252,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -62391,7 +62391,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -62540,7 +62540,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -62689,7 +62689,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -62838,7 +62838,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -62985,7 +62985,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -63128,7 +63128,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE440" t="n">
         <v>3</v>
@@ -63278,7 +63278,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -63417,7 +63417,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -63552,7 +63552,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE443" t="n">
         <v>1</v>
@@ -63691,7 +63691,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -63830,7 +63830,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -63969,7 +63969,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -64108,7 +64108,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -64255,7 +64255,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -64404,7 +64404,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -64553,7 +64553,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -742,15 +742,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.rofenashim.co.il/faq/faq-fertility/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>6</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -891,15 +891,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>20745882</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>62237646</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://www.dr-ravhon.co.il/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>28756863</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>86270589</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.e-piryon.com/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1189,15 +1189,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://www.dr-yinon.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1338,15 +1338,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://www.profyinoncohen.com/</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1487,15 +1487,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://drbraunstein.co.il/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1636,15 +1636,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://www.dr-domniz.co.il/</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1786,15 +1786,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-elkabetz-netanel</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1933,15 +1933,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>3</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2080,15 +2080,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://kerenzohar.com/%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2229,15 +2229,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://hmc.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%93%D7%95%D7%93-%D7%9C%D7%91-%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>19</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2376,15 +2376,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://www.israelidoula.co.il/courses-1/embryo-%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>7</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2525,15 +2525,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>https://www.dr-paz.co.il/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2664,15 +2664,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>https://www.nashim.net/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2811,15 +2811,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>17</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2959,15 +2959,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://boneiolam.co.il/%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA-%D7%94%D7%90%D7%A8%D7%92%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3098,15 +3098,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://www.dranatlavie.com/</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3237,15 +3237,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://www.shvil-haleida.co.il/%D7%A8%D7%99%D7%A9%D7%95%D7%9D-%D7%9C%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%9C%D7%99%D7%93%D7%94/</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3384,15 +3384,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2358</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3532,15 +3532,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3681,15 +3681,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94-9/</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3820,15 +3820,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://harechem.com/</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>3</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -3963,15 +3963,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>http://www.amotatchen.org/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>3</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4110,15 +4110,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://www.hourvitz.co.il/fertility/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4249,15 +4249,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%91%D7%A0%D7%A7%D7%99-%D7%96%D7%A8%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4388,15 +4388,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%91%D7%A0%D7%A7%D7%99-%D7%96%D7%A8%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4527,15 +4527,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://www.shamirbaby.co.il/</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4676,15 +4676,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4825,15 +4825,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>2</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -4974,15 +4974,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://drehudg.co.il/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5123,15 +5123,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://atufa.co.il/team/%D7%93%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%9C%D7%95%D7%99%D7%A0%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5268,15 +5268,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://levitasaesthetic.com/</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5417,15 +5417,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://darkred-ram-504111.hostingersite.com/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>1</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5566,15 +5566,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://www.infomed.co.il/experts/93782/</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>1</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5715,15 +5715,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://doctor-ariel.co.il/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5864,15 +5864,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://www.dr-ariella.com/blank-3</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>1</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -6013,15 +6013,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://www.dr-pomp.com/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6162,15 +6162,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://blinker.co.il/%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA/%D7%9E%D7%93%D7%95%D7%A8%D7%AA-%D7%94%D7%A9%D7%91%D7%98-%D7%91%D7%94%D7%93-%D7%94%D7%A7%D7%A8%D7%99%D7%95%D7%AA/%D7%93%D7%A8-%D7%90%D7%91%D7%95-%D7%96%D7%94%D7%99%D7%94-%D7%A2%D7%90%D7%99%D7%93-%D7%94%D7%A6%D7%98%D7%A8%D7%A3-%D7%9C%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%91%D7%98/443381/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6311,15 +6311,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://roni-avrahami.co.il/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>1</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6460,15 +6460,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://drostrovsky.com/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>1</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6609,15 +6609,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://web.minicard.co.il/card/idelsondoc/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>1</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6758,15 +6758,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://drblecher.co.il/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>1</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6903,15 +6903,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://drblecher.co.il/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>1</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -7052,15 +7052,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>25568217</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>76704651</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://www.drukker.co.il/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7201,15 +7201,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://stop-pregnancy.co.il/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>1</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7350,15 +7350,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>20745882</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>62237646</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://arireissmd.com/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>1</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7499,15 +7499,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>20745882</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>62237646</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://drmeiravschmidt.co.il/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>1</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7648,15 +7648,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://dinadoula.com/%D7%93%D7%95%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7795,15 +7795,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://www.lidoula.co.il/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>1</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -7940,15 +7940,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://dr-carp.co.il/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>1</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -8089,15 +8089,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://dr-carp.co.il/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -8238,15 +8238,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://krissiclinic.com/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>1</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8387,15 +8387,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://krissiclinic.com/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8536,15 +8536,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>19663317</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>58989951</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://fetalmedicine.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8685,15 +8685,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://admcmedical.com/%D7%93%D7%A8-%D7%9C%D7%90%D7%94-%D7%A7%D7%A4%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>1</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8820,15 +8820,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%9C%D7%99%D7%93%D7%94-%D7%A8%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>1</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -8955,15 +8955,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%9C%D7%99%D7%93%D7%94-%D7%A8%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>1</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -9090,15 +9090,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%9C%D7%99%D7%93%D7%94-%D7%A8%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>1</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -9239,15 +9239,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>19193112</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>57579336</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%9E%D7%95%D7%A0%D7%96%D7%A8-%D7%A2%D7%96%D7%90%D7%9D-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%91%D7%97%D7%99%D7%A4%D7%94</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>1</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9388,15 +9388,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>19193112</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>57579336</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://drlewit.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>1</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9537,15 +9537,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>19193112</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>57579336</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://medstream.co.il/doctor/ido-elder/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>1</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9686,15 +9686,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>19191654</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>57574962</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://dr-schwed.co.il/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>1</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9836,15 +9836,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://mdjacob.co.il/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>1</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -9981,15 +9981,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://dr-ivf.co.il/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>1</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -10126,15 +10126,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>23934771</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>71804313</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://www.hypnobirthing.co.il/pashut/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>1</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -10275,15 +10275,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://www.ultra-sound.co.il/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>1</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10424,15 +10424,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://rb-skirot.co.il/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>1</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10573,15 +10573,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://drroteminbar.co.il/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>1</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>19191654</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>57574962</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://bmc-medical.co.il/doctors/%D7%93%D7%A8-%D7%A8%D7%99%D7%A7%D7%99-%D7%91%D7%A8%D7%92%D7%9C-%D7%91%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>1</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10871,15 +10871,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>http://www.prof-haimovich.ipn.co.il/about-2-3/</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>1</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -11020,15 +11020,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%9C%D7%9E%D7%94_%D7%9E%D7%A8%D7%A7%D7%95%D7%91</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>1</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -11169,15 +11169,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://dr-yagel.co.il/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>1</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -11308,15 +11308,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://www.hadoula.co.il/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>1</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11447,15 +11447,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://www.nashim.net/?CategoryID=1146</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>1</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11596,15 +11596,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://www.surmom.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/%D7%A4%D7%A8%D7%95%D7%A4-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F-%D7%90%D7%93%D7%A8%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11745,15 +11745,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://iwn.org.il/%D7%93%D7%95%D7%A8%D7%A9%D7%95%D7%AA-%D7%9C%D7%A9%D7%9C%D7%95%D7%9C-%D7%90%D7%AA-%D7%A8%D7%A9%D7%99%D7%95%D7%A0%D7%95-%D7%A9%D7%9C-%D7%91%D7%A0%D7%99-%D7%A9%D7%9B%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>1</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -11894,15 +11894,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://iwn.org.il/%D7%93%D7%95%D7%A8%D7%A9%D7%95%D7%AA-%D7%9C%D7%A9%D7%9C%D7%95%D7%9C-%D7%90%D7%AA-%D7%A8%D7%A9%D7%99%D7%95%D7%A0%D7%95-%D7%A9%D7%9C-%D7%91%D7%A0%D7%99-%D7%A9%D7%9B%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>1</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -12043,15 +12043,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://iwn.org.il/%D7%93%D7%95%D7%A8%D7%A9%D7%95%D7%AA-%D7%9C%D7%A9%D7%9C%D7%95%D7%9C-%D7%90%D7%AA-%D7%A8%D7%A9%D7%99%D7%95%D7%A0%D7%95-%D7%A9%D7%9C-%D7%91%D7%A0%D7%99-%D7%A9%D7%9B%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>1</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -12192,15 +12192,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://hfhosp.org/he/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/%D7%93%D7%A8-%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%90-%D7%A4%D7%A8%D7%97</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>5</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -12341,15 +12341,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://www.ha-makom.co.il/post-galit-geni-new/</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>1</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12490,15 +12490,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://www.ha-makom.co.il/post-galit-geni-new/</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>1</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12639,15 +12639,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://www.ha-makom.co.il/post-galit-geni-new/</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>1</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12788,15 +12788,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://www.yarongilmd.com/</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>1</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -12927,15 +12927,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://midwives.org.il/%D7%9C%D7%99%D7%95%D7%95%D7%99-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%96%D7%94-%D7%9E%D7%99%D7%99%D7%9C%D7%93%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>9</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -13076,15 +13076,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://sharapplus.co.il/doctors/shlomi-sagi/</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>1</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -13225,15 +13225,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://www.eryaveladan.com/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>1</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -13374,15 +13374,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>1</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13523,15 +13523,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://www.michlalot.co.il/limudim/madrichat-leida.php</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>1</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13670,15 +13670,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>8</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13817,15 +13817,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>11</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -13956,15 +13956,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://www.israelibaby.co.il/where-to-get-birth</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>11</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -14095,15 +14095,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>2</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -14234,15 +14234,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>1</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -14373,15 +14373,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>1</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -14516,15 +14516,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/fertility-research/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>3</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14655,15 +14655,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://www.cryobank.co.il/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>1</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14797,15 +14797,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://www.cryobank.co.il/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>1</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -14946,15 +14946,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>25568217</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>76704651</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://www.mdliora.com/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>1</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -15095,15 +15095,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://www.shellclinic.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A9%D7%9C-%D7%91%D7%99%D7%AA-%D7%A9%D7%9C-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA/%D7%93%D7%A8-%D7%9E%D7%90%D7%A9%D7%94-%D7%93%D7%9B%D7%99%D7%A1</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>1</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -15234,15 +15234,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://barakivf.com/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>3</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -15377,15 +15377,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://demayo.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>3</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -15524,15 +15524,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://bri.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>17</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15663,15 +15663,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>4</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15802,15 +15802,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>4</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -15941,15 +15941,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>4</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -16080,15 +16080,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://www.patients-rights.org/%D7%97%D7%9F-%D7%9C%D7%A4%D7%A8%D7%99%D7%95%D7%9F-%D7%95%D7%9C%D7%97%D7%99%D7%99%D7%9D</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>1</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -16229,15 +16229,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>http://dorclinic.co.il/about-us/%D7%A4%D7%A8%D7%95%D7%A4-%D7%99%D7%94%D7%95%D7%A9%D7%A2-%D7%93%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>1</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -16376,15 +16376,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://www.chesedmatch.org/%D7%9E%D7%95%D7%93%D7%99%D7%A2%D7%99%D7%9F-%D7%A2%D7%99%D7%9C%D7%99%D7%AA/chesed-categories/%D7%9C%D7%92%D7%93%D7%9C-%D7%99%D7%A2%D7%95%D7%A5-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>1</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -16523,15 +16523,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://www.laniado.org.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%9C%D7%99%D7%93%D7%94-%D7%98%D7%91%D7%A2%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>2</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16672,15 +16672,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://www.drmayasharonweiner.com/</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>1</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16811,15 +16811,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=572A93E43CD3B3402A26D525588617E3&amp;RequestId=00000000-0000-0000-0001-000000000086</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>1</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -16950,15 +16950,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=624E1E4C81052B986D35A02439C2DE20&amp;RequestId=00000000-0000-0000-0001-000000000213</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>1</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -17089,15 +17089,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=F6BA64E342379D7CF6706D6EF9A4D7C4&amp;RequestId=00000000-0000-0000-0001-000000000399</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>1</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -17228,15 +17228,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=A6B809CAFEA13537A84D783709CF5EBB&amp;RequestId=00000000-0000-0000-0001-000000000325</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>2</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
@@ -17367,15 +17367,15 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE116" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF116" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF116" t="n">
-        <v>8</v>
       </c>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
@@ -17516,15 +17516,15 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE117" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF117" t="inlineStr">
         <is>
           <t>https://professorneuman.com/he/</t>
         </is>
-      </c>
-      <c r="AF117" t="n">
-        <v>1</v>
       </c>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
@@ -17655,15 +17655,15 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE118" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF118" t="inlineStr">
         <is>
           <t>https://aviv-center.co.il/</t>
         </is>
-      </c>
-      <c r="AF118" t="n">
-        <v>1</v>
       </c>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
@@ -17804,15 +17804,15 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE119" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF119" t="inlineStr">
         <is>
           <t>https://www.laliv.clinic/dr-adi-orenstein</t>
         </is>
-      </c>
-      <c r="AF119" t="n">
-        <v>1</v>
       </c>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
@@ -17943,15 +17943,15 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE120" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="inlineStr">
         <is>
           <t>https://machon-dorot.org.il/</t>
         </is>
-      </c>
-      <c r="AF120" t="n">
-        <v>1</v>
       </c>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
@@ -18092,15 +18092,15 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE121" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="inlineStr">
         <is>
           <t>https://dr-ravid.co.il/dr-eran-kasif/</t>
         </is>
-      </c>
-      <c r="AF121" t="n">
-        <v>1</v>
       </c>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
@@ -18241,15 +18241,15 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE122" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF122" t="inlineStr">
         <is>
           <t>https://drrazbahar.co.il/</t>
         </is>
-      </c>
-      <c r="AF122" t="n">
-        <v>1</v>
       </c>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
@@ -18390,15 +18390,15 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE123" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF123" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/gynecology/</t>
         </is>
-      </c>
-      <c r="AF123" t="n">
-        <v>1</v>
       </c>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
@@ -18539,15 +18539,15 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE124" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF124" t="inlineStr">
         <is>
           <t>https://keshet-refua.co.il/doctors/dr-tamar-green/</t>
         </is>
-      </c>
-      <c r="AF124" t="n">
-        <v>1</v>
       </c>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
@@ -18688,15 +18688,15 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE125" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF125" t="inlineStr">
         <is>
           <t>https://www.yarongilmd.com/</t>
         </is>
-      </c>
-      <c r="AF125" t="n">
-        <v>1</v>
       </c>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
@@ -18837,15 +18837,15 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE126" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF126" t="inlineStr">
         <is>
           <t>https://sharapplus.co.il/doctors/shlomi-sagi/</t>
         </is>
-      </c>
-      <c r="AF126" t="n">
-        <v>1</v>
       </c>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
@@ -18986,15 +18986,15 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE127" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF127" t="inlineStr">
         <is>
           <t>https://sharapplus.co.il/doctors/shlomi-sagi/</t>
         </is>
-      </c>
-      <c r="AF127" t="n">
-        <v>1</v>
       </c>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
@@ -19125,15 +19125,15 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE128" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF128" t="inlineStr">
         <is>
           <t>https://healthwise.co.il/embryologist-ivf-lab/</t>
         </is>
-      </c>
-      <c r="AF128" t="n">
-        <v>1</v>
       </c>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
@@ -19270,15 +19270,15 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE129" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="inlineStr">
         <is>
           <t>https://rtmcmed.co.il/he/mumhim-shelanu/professor-amnon-amit</t>
         </is>
-      </c>
-      <c r="AF129" t="n">
-        <v>1</v>
       </c>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
@@ -19419,15 +19419,15 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE130" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF130" t="inlineStr">
         <is>
           <t>https://www.drw.co.il/%D7%A7%D7%A6%D7%AA-%D7%A2%D7%9C%D7%99/%D7%A7%D7%A6%D7%AA-%D7%A2%D7%9C%D7%99</t>
         </is>
-      </c>
-      <c r="AF130" t="n">
-        <v>1</v>
       </c>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
@@ -19568,15 +19568,15 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>20745882</v>
-      </c>
-      <c r="AE131" t="inlineStr">
+        <v>62237646</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF131" t="inlineStr">
         <is>
           <t>https://www.liatmd.com/%D7%93-%D7%A8-%D7%9C%D7%99%D7%90%D7%AA-%D7%A9%D7%99%D7%9C%D7%94-%D7%96%D7%9C%D7%A6%D7%A8</t>
         </is>
-      </c>
-      <c r="AF131" t="n">
-        <v>1</v>
       </c>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
@@ -19717,15 +19717,15 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE132" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF132" t="inlineStr">
         <is>
           <t>https://www.ksn.co.il/%D7%93%D7%A8-%D7%94%D7%99%D7%9C%D7%94-%D7%94%D7%95%D7%9B%D7%9C%D7%A8-%D7%AA%D7%A9%D7%9E%D7%A9-%D7%A8%D7%90%D7%A9-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%91/</t>
         </is>
-      </c>
-      <c r="AF132" t="n">
-        <v>1</v>
       </c>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
@@ -19866,15 +19866,15 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE133" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF133" t="inlineStr">
         <is>
           <t>https://drzilberberg.co.il/</t>
         </is>
-      </c>
-      <c r="AF133" t="n">
-        <v>1</v>
       </c>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
@@ -20015,15 +20015,15 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE134" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF134" t="inlineStr">
         <is>
           <t>https://medicabri.com/prof-odeh-marwan/</t>
         </is>
-      </c>
-      <c r="AF134" t="n">
-        <v>1</v>
       </c>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
@@ -20160,15 +20160,15 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE135" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF135" t="inlineStr">
         <is>
           <t>https://www.edna-center.co.il/%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%A0%D7%A9%D7%99%D7%9D</t>
         </is>
-      </c>
-      <c r="AF135" t="n">
-        <v>1</v>
       </c>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
@@ -20299,15 +20299,15 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE136" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF136" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%91%D7%9C%D7%94-%D7%A2%D7%91%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF136" t="n">
-        <v>2</v>
       </c>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
@@ -20438,15 +20438,15 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE137" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF137" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%92%D7%9E%D7%95/</t>
         </is>
-      </c>
-      <c r="AF137" t="n">
-        <v>2</v>
       </c>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
@@ -20577,15 +20577,15 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE138" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF138" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%99%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF138" t="n">
-        <v>2</v>
       </c>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
@@ -20716,15 +20716,15 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE139" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF139" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%9F-%D7%90%D7%A8%D7%99-%D7%A6%D7%90%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF139" t="n">
-        <v>2</v>
       </c>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
@@ -20855,15 +20855,15 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE140" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF140" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF140" t="n">
-        <v>2</v>
       </c>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
@@ -20994,15 +20994,15 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE141" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF141" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%95%D7%A8%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%97%D7%99%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF141" t="n">
-        <v>2</v>
       </c>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
@@ -21133,15 +21133,15 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE142" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF142" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%9C%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF142" t="n">
-        <v>2</v>
       </c>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
@@ -21272,15 +21272,15 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE143" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF143" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%9C%D7%A0%D7%93%D7%94-%D7%A1%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF143" t="n">
-        <v>2</v>
       </c>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
@@ -21411,15 +21411,15 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE144" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF144" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%95%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%9C%D7%90/</t>
         </is>
-      </c>
-      <c r="AF144" t="n">
-        <v>2</v>
       </c>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
@@ -21550,15 +21550,15 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE145" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF145" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%9C%D7%99%D7%94-%D7%94%D7%95%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF145" t="n">
-        <v>2</v>
       </c>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
@@ -21689,15 +21689,15 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE146" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF146" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%9E%D7%99%D7%AA-%D7%93%D7%A0%D7%A1%D7%99%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF146" t="n">
-        <v>2</v>
       </c>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
@@ -21828,15 +21828,15 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE147" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF147" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%9E%D7%95%D7%96%D7%A1-%D7%90%D7%9C%D7%91%D7%96/</t>
         </is>
-      </c>
-      <c r="AF147" t="n">
-        <v>2</v>
       </c>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
@@ -21967,15 +21967,15 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE148" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF148" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%A8%D7%95%D7%9F-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF148" t="n">
-        <v>2</v>
       </c>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
@@ -22106,15 +22106,15 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE149" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF149" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%99%D7%A2%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF149" t="n">
-        <v>2</v>
       </c>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
@@ -22245,15 +22245,15 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE150" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF150" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%98%D7%94-%D7%A0%D7%95%D7%91%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF150" t="n">
-        <v>2</v>
       </c>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
@@ -22384,15 +22384,15 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE151" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF151" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%94-%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%A7%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF151" t="n">
-        <v>2</v>
       </c>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
@@ -22523,15 +22523,15 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE152" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF152" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%94-%D7%93%D7%9E%D7%A0%D7%98%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF152" t="n">
-        <v>2</v>
       </c>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
@@ -22662,15 +22662,15 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE153" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF153" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF153" t="n">
-        <v>2</v>
       </c>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
@@ -22801,15 +22801,15 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE154" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF154" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%96%D7%92%D7%95%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF154" t="n">
-        <v>2</v>
       </c>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
@@ -22940,15 +22940,15 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE155" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF155" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF155" t="n">
-        <v>2</v>
       </c>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
@@ -23079,15 +23079,15 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE156" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF156" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF156" t="n">
-        <v>2</v>
       </c>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
@@ -23218,15 +23218,15 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE157" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF157" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%9C%D7%91%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF157" t="n">
-        <v>2</v>
       </c>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
@@ -23357,15 +23357,15 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE158" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF158" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%90%D7%9D-%D7%9E%D7%95%D7%A8%D7%94-%D7%97%D7%9E%D7%90%D7%A8%D7%A9%D7%99/</t>
         </is>
-      </c>
-      <c r="AF158" t="n">
-        <v>2</v>
       </c>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
@@ -23496,15 +23496,15 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE159" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF159" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%91%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF159" t="n">
-        <v>2</v>
       </c>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
@@ -23635,15 +23635,15 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE160" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF160" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%A6%D7%99%D7%91%D7%99%D7%90%D7%A7-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF160" t="n">
-        <v>2</v>
       </c>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
@@ -23774,15 +23774,15 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE161" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF161" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%9E%D7%95%D7%91%D7%A9%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF161" t="n">
-        <v>2</v>
       </c>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
@@ -23913,15 +23913,15 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE162" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF162" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%94-%D7%90%D7%96%D7%91%D7%A0%D7%93/</t>
         </is>
-      </c>
-      <c r="AF162" t="n">
-        <v>2</v>
       </c>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
@@ -24052,15 +24052,15 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE163" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF163" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%AA%D7%A9%D7%91%D7%A2-%D7%92%D7%A8%D7%A0%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF163" t="n">
-        <v>2</v>
       </c>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
@@ -24191,15 +24191,15 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE164" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF164" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%99%D7%9C%D7%99-%D7%90%D7%95%D7%91%D7%A8%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF164" t="n">
-        <v>2</v>
       </c>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
@@ -24330,15 +24330,15 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE165" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF165" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%9C%D7%99%D7%99%D7%A8-%D7%90%D7%9C%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF165" t="n">
-        <v>2</v>
       </c>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
@@ -24469,15 +24469,15 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE166" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF166" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%94%D7%A9%D7%9B%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF166" t="n">
-        <v>2</v>
       </c>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
@@ -24608,15 +24608,15 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE167" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF167" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%98%D7%9C-%D7%91%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF167" t="n">
-        <v>2</v>
       </c>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
@@ -24747,15 +24747,15 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE168" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF168" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%97%D7%95%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF168" t="n">
-        <v>2</v>
       </c>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
@@ -24886,15 +24886,15 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE169" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF169" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%9C%D7%90%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF169" t="n">
-        <v>2</v>
       </c>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
@@ -25025,15 +25025,15 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE170" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF170" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%92%D7%93%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF170" t="n">
-        <v>2</v>
       </c>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
@@ -25164,15 +25164,15 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE171" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF171" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%9E%D7%A8%D7%90%D7%93/</t>
         </is>
-      </c>
-      <c r="AF171" t="n">
-        <v>2</v>
       </c>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
@@ -25303,15 +25303,15 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE172" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF172" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%A9%D7%95%D7%95%D7%A8%D7%A6%D7%91%D7%A8%D7%92/</t>
         </is>
-      </c>
-      <c r="AF172" t="n">
-        <v>2</v>
       </c>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
@@ -25442,15 +25442,15 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE173" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF173" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%99%D7%90%D7%9F-%D7%A9%D7%A4%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF173" t="n">
-        <v>2</v>
       </c>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
@@ -25581,15 +25581,15 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE174" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF174" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8-%D7%91%D7%99%D7%98%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF174" t="n">
-        <v>2</v>
       </c>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
@@ -25720,15 +25720,15 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE175" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF175" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8%D7%99%D7%9F-%D7%90%D7%9C%D7%A2%D7%93/</t>
         </is>
-      </c>
-      <c r="AF175" t="n">
-        <v>2</v>
       </c>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
@@ -25859,15 +25859,15 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE176" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF176" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/332/</t>
         </is>
-      </c>
-      <c r="AF176" t="n">
-        <v>2</v>
       </c>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
@@ -25998,15 +25998,15 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE177" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF177" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%91%D7%9F-%D7%A9%D7%A5-%D7%A4%D7%95%D7%A8%D7%A9%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF177" t="n">
-        <v>2</v>
       </c>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
@@ -26137,15 +26137,15 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE178" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF178" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%95%D7%95%D7%A8%D7%99%D7%99%D7%98/</t>
         </is>
-      </c>
-      <c r="AF178" t="n">
-        <v>2</v>
       </c>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
@@ -26276,15 +26276,15 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE179" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF179" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%99%D7%90%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF179" t="n">
-        <v>2</v>
       </c>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
@@ -26415,15 +26415,15 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE180" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF180" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%91%D7%92%D7%9C%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF180" t="n">
-        <v>2</v>
       </c>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
@@ -26554,15 +26554,15 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE181" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF181" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF181" t="n">
-        <v>2</v>
       </c>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
@@ -26693,15 +26693,15 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE182" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF182" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%9C%D7%A0%D7%94-%D7%A9%D7%99%D7%9C%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF182" t="n">
-        <v>2</v>
       </c>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
@@ -26832,15 +26832,15 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE183" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF183" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A2%D7%A0%D7%94-%D7%92%D7%95%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF183" t="n">
-        <v>2</v>
       </c>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
@@ -26971,15 +26971,15 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE184" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF184" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%91%D7%A8%D7%A7%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF184" t="n">
-        <v>2</v>
       </c>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
@@ -27110,15 +27110,15 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE185" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF185" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A8%D7%96-%D7%92%D7%99%D7%9C%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF185" t="n">
-        <v>2</v>
       </c>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
@@ -27249,15 +27249,15 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE186" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF186" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A9%D7%91%D7%A2-%D7%92%D7%95%D7%A8%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF186" t="n">
-        <v>2</v>
       </c>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
@@ -27388,15 +27388,15 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE187" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF187" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%9C%D7%95%D7%A0%D7%92%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF187" t="n">
-        <v>2</v>
       </c>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
@@ -27527,15 +27527,15 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE188" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF188" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%9F-%D7%A9%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF188" t="n">
-        <v>2</v>
       </c>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
@@ -27666,15 +27666,15 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE189" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF189" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%94-%D7%90%D7%99%D7%AA%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF189" t="n">
-        <v>2</v>
       </c>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
@@ -27805,15 +27805,15 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE190" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF190" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%95%D7%A0%D7%94-%D7%95%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF190" t="n">
-        <v>2</v>
       </c>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
@@ -27944,15 +27944,15 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE191" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF191" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%90%D7%9C%D7%94-%D7%99%D7%A8%D7%A7%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF191" t="n">
-        <v>2</v>
       </c>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
@@ -28083,15 +28083,15 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE192" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF192" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A1%D7%AA%D7%A8-%D7%A4%D7%9C%D7%99%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF192" t="n">
-        <v>2</v>
       </c>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
@@ -28222,15 +28222,15 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE193" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF193" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%AA%D7%99-%D7%A1%D7%93%D7%9F-%D7%A7%D7%A0%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF193" t="n">
-        <v>2</v>
       </c>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
@@ -28361,15 +28361,15 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE194" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF194" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%A8%D7%A0%D7%A1%D7%99%D7%A1-%D7%A4%D7%A8%D7%9F-%D7%91%D7%A8%D7%95%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF194" t="n">
-        <v>2</v>
       </c>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
@@ -28500,15 +28500,15 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE195" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF195" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%91%D7%99-%D7%A4%D7%99%D7%A9%D7%9E%D7%9F-%D7%A4%D7%95%D7%A1%D7%91%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF195" t="n">
-        <v>2</v>
       </c>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
@@ -28639,15 +28639,15 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE196" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF196" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99-%D7%A7%D7%9E%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF196" t="n">
-        <v>2</v>
       </c>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
@@ -28778,15 +28778,15 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE197" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF197" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%90%D7%A4%D7%9C%D7%91%D7%95%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF197" t="n">
-        <v>2</v>
       </c>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
@@ -28917,15 +28917,15 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE198" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF198" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%AA-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF198" t="n">
-        <v>2</v>
       </c>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
@@ -29056,15 +29056,15 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE199" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF199" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF199" t="n">
-        <v>2</v>
       </c>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
@@ -29195,15 +29195,15 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE200" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF200" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%90%D7%99%D7%94-%D7%92%D7%95%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF200" t="n">
-        <v>2</v>
       </c>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
@@ -29334,15 +29334,15 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE201" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF201" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%94-%D7%90%D7%95%D7%A0%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF201" t="n">
-        <v>2</v>
       </c>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
@@ -29473,15 +29473,15 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE202" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF202" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%99%D7%94-%D7%93%D7%95%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF202" t="n">
-        <v>2</v>
       </c>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
@@ -29612,15 +29612,15 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE203" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF203" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%AA%D7%99%D7%AA-%D7%A9%D7%A4%D7%A8%D7%9C%D7%99%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF203" t="n">
-        <v>2</v>
       </c>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
@@ -29751,15 +29751,15 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE204" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF204" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%9E%D7%95%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF204" t="n">
-        <v>2</v>
       </c>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
@@ -29890,15 +29890,15 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE205" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF205" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%98%D7%A1%D7%94/</t>
         </is>
-      </c>
-      <c r="AF205" t="n">
-        <v>2</v>
       </c>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
@@ -30029,15 +30029,15 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE206" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF206" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1%D7%94-%D7%A4%D7%97%D7%9C%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF206" t="n">
-        <v>2</v>
       </c>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
@@ -30168,15 +30168,15 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE207" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF207" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%A0%D7%94-%D7%94%D7%A8%D7%95%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF207" t="n">
-        <v>2</v>
       </c>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
@@ -30307,15 +30307,15 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE208" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF208" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%99-%D7%94%D7%A8%D7%A4%D7%96/</t>
         </is>
-      </c>
-      <c r="AF208" t="n">
-        <v>2</v>
       </c>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
@@ -30446,15 +30446,15 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE209" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF209" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9E%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF209" t="n">
-        <v>2</v>
       </c>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
@@ -30585,15 +30585,15 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE210" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF210" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%99%D7%9C%D7%94-%D7%9C%D7%91-%D7%A8%D7%9F-%D7%97%D7%95%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF210" t="n">
-        <v>2</v>
       </c>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
@@ -30724,15 +30724,15 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE211" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF211" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%95%D7%93%D7%99%D7%94-%D7%90%D7%99%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF211" t="n">
-        <v>2</v>
       </c>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
@@ -30863,15 +30863,15 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE212" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF212" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%9C-%D7%91%D7%95%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF212" t="n">
-        <v>2</v>
       </c>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
@@ -31002,15 +31002,15 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE213" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF213" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%A8-%D7%A7%D7%A8%D7%9F-%D7%A8%D7%98%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF213" t="n">
-        <v>2</v>
       </c>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
@@ -31141,15 +31141,15 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE214" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF214" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%B3%D7%95%D7%9C%D7%99-%D7%90%D7%A1%D7%AA%D7%99-%D7%A9%D7%9E%D7%A2%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF214" t="n">
-        <v>2</v>
       </c>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
@@ -31280,15 +31280,15 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE215" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF215" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%95%D7%9C%D7%99-%D7%A7%D7%A8%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF215" t="n">
-        <v>2</v>
       </c>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
@@ -31419,15 +31419,15 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE216" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF216" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%92%D7%9C%D7%99%D7%9F-%D7%A1%D7%9C%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF216" t="n">
-        <v>2</v>
       </c>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
@@ -31558,15 +31558,15 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE217" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF217" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%92%D7%99%D7%91%D7%A8-%D7%A9%D7%92%D7%91/</t>
         </is>
-      </c>
-      <c r="AF217" t="n">
-        <v>2</v>
       </c>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
@@ -31697,15 +31697,15 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE218" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF218" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%A1%D7%9C%D7%91%D7%95%D7%93%D7%A0%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF218" t="n">
-        <v>2</v>
       </c>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
@@ -31836,15 +31836,15 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE219" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF219" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF219" t="n">
-        <v>2</v>
       </c>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
@@ -31975,15 +31975,15 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE220" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF220" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%90%D7%A0%D7%94-%D7%91%D7%A8%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF220" t="n">
-        <v>2</v>
       </c>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
@@ -32114,15 +32114,15 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE221" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF221" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99-%D7%90%D7%95%D7%A8-%D7%9C%D7%91%D7%A0%D7%96%D7%95%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF221" t="n">
-        <v>2</v>
       </c>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
@@ -32253,15 +32253,15 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE222" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF222" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%A8%D7%95%D7%9F-%D7%A4%D7%99%D7%90%D7%97%D7%95%D7%98%D7%94-%D7%A1%D7%90%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF222" t="n">
-        <v>2</v>
       </c>
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
@@ -32392,15 +32392,15 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE223" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF223" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF223" t="n">
-        <v>2</v>
       </c>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
@@ -32531,15 +32531,15 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE224" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF224" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%94-%D7%A7%D7%95%D7%92%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF224" t="n">
-        <v>2</v>
       </c>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
@@ -32670,15 +32670,15 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE225" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF225" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%90%D7%9F-%D7%A9%D7%95%D7%97%D7%98/</t>
         </is>
-      </c>
-      <c r="AF225" t="n">
-        <v>2</v>
       </c>
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
@@ -32809,15 +32809,15 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE226" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF226" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99-%D7%A2%D7%95%D7%96%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF226" t="n">
-        <v>2</v>
       </c>
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" t="inlineStr"/>
@@ -32948,15 +32948,15 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE227" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF227" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF227" t="n">
-        <v>2</v>
       </c>
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr"/>
@@ -33087,15 +33087,15 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE228" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF228" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8-%D7%9C%D7%95%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF228" t="n">
-        <v>2</v>
       </c>
       <c r="AG228" t="inlineStr"/>
       <c r="AH228" t="inlineStr"/>
@@ -33226,15 +33226,15 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE229" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF229" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF229" t="n">
-        <v>2</v>
       </c>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
@@ -33365,15 +33365,15 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE230" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF230" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%98%D7%95%D7%91-%D7%97%D7%99%D7%94-%D7%90%D7%99%D7%98%D7%94/</t>
         </is>
-      </c>
-      <c r="AF230" t="n">
-        <v>2</v>
       </c>
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
@@ -33504,15 +33504,15 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE231" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF231" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A2%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%9E%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF231" t="n">
-        <v>2</v>
       </c>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr"/>
@@ -33643,15 +33643,15 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE232" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF232" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99-%D7%93%D7%A8%D7%95%D7%A7%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF232" t="n">
-        <v>2</v>
       </c>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
@@ -33782,15 +33782,15 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE233" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%94-%D7%92%D7%95%D7%A8%D7%92%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF233" t="n">
-        <v>2</v>
       </c>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
@@ -33921,15 +33921,15 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE234" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF234" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%99-%D7%90%D7%95%D7%A4%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF234" t="n">
-        <v>2</v>
       </c>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
@@ -34060,15 +34060,15 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE235" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF235" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%A9%D7%97%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF235" t="n">
-        <v>2</v>
       </c>
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" t="inlineStr"/>
@@ -34199,15 +34199,15 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE236" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF236" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%95%D7%A4%D7%A8%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF236" t="n">
-        <v>2</v>
       </c>
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
@@ -34338,15 +34338,15 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE237" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF237" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99-%D7%9C%D7%91-%D7%A7%D7%9C%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF237" t="n">
-        <v>2</v>
       </c>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
@@ -34477,15 +34477,15 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE238" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF238" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99%D7%94-%D7%90%D7%A0%D7%95%D7%9A/</t>
         </is>
-      </c>
-      <c r="AF238" t="n">
-        <v>2</v>
       </c>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
@@ -34616,15 +34616,15 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE239" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF239" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%94-%D7%90%D7%99%D7%96%D7%A7%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF239" t="n">
-        <v>2</v>
       </c>
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
@@ -34755,15 +34755,15 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE240" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF240" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%91-%D7%A0%D7%97%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF240" t="n">
-        <v>2</v>
       </c>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
@@ -34894,15 +34894,15 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE241" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF241" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99%D7%A1%D7%94-%D7%91%D7%A8-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF241" t="n">
-        <v>2</v>
       </c>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
@@ -35033,15 +35033,15 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE242" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF242" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%9B%D7%9C-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%99%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF242" t="n">
-        <v>2</v>
       </c>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
@@ -35172,15 +35172,15 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE243" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF243" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A7%D7%94-%D7%9B%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF243" t="n">
-        <v>2</v>
       </c>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
@@ -35311,15 +35311,15 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE244" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF244" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99-%D7%A4%D7%91%D7%96%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF244" t="n">
-        <v>2</v>
       </c>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
@@ -35450,15 +35450,15 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE245" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF245" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99%D7%AA-%D7%A8%D7%95%D7%96%D7%A0%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF245" t="n">
-        <v>2</v>
       </c>
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
@@ -35589,15 +35589,15 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE246" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF246" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8-%D7%92%D7%95%D7%9C%D7%93%D7%A0%D7%92%D7%95%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF246" t="n">
-        <v>2</v>
       </c>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
@@ -35728,15 +35728,15 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE247" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF247" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%9E%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF247" t="n">
-        <v>2</v>
       </c>
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr"/>
@@ -35867,15 +35867,15 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE248" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF248" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%9C%D7%92%D7%99/</t>
         </is>
-      </c>
-      <c r="AF248" t="n">
-        <v>2</v>
       </c>
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr"/>
@@ -36006,15 +36006,15 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE249" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF249" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%95%D7%95%D7%9C%D7%A4%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF249" t="n">
-        <v>2</v>
       </c>
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr"/>
@@ -36145,15 +36145,15 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE250" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF250" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A2%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF250" t="n">
-        <v>2</v>
       </c>
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr"/>
@@ -36284,15 +36284,15 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE251" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF251" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A8%D7%99%D7%91%D7%9C%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF251" t="n">
-        <v>2</v>
       </c>
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" t="inlineStr"/>
@@ -36423,15 +36423,15 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE252" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF252" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A8%D7%A7%D7%99%D7%A1-%D7%A0%D7%A4%D7%AA%D7%9C%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF252" t="n">
-        <v>2</v>
       </c>
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr"/>
@@ -36562,15 +36562,15 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE253" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF253" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%A7%D7%A9%D7%99%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF253" t="n">
-        <v>2</v>
       </c>
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr"/>
@@ -36701,15 +36701,15 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE254" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF254" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%91%D7%9F-%D7%A9%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF254" t="n">
-        <v>2</v>
       </c>
       <c r="AG254" t="inlineStr"/>
       <c r="AH254" t="inlineStr"/>
@@ -36840,15 +36840,15 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE255" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF255" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%A2-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF255" t="n">
-        <v>2</v>
       </c>
       <c r="AG255" t="inlineStr"/>
       <c r="AH255" t="inlineStr"/>
@@ -36979,15 +36979,15 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE256" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF256" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A0%D7%94-%D7%91%D7%AA%D7%90%D7%A9%D7%95%D7%99%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF256" t="n">
-        <v>2</v>
       </c>
       <c r="AG256" t="inlineStr"/>
       <c r="AH256" t="inlineStr"/>
@@ -37118,15 +37118,15 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE257" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF257" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A8%D7%99%D7%AA-%D7%90%D7%95%D7%9C%D7%99%D7%91%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF257" t="n">
-        <v>2</v>
       </c>
       <c r="AG257" t="inlineStr"/>
       <c r="AH257" t="inlineStr"/>
@@ -37257,15 +37257,15 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE258" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF258" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A6%D7%9F-%D7%99%D7%9E%D7%99%D7%A0%D7%99-%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF258" t="n">
-        <v>2</v>
       </c>
       <c r="AG258" t="inlineStr"/>
       <c r="AH258" t="inlineStr"/>
@@ -37396,15 +37396,15 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE259" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF259" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%91%D7%99-%D7%99%D7%A2%D7%A7%D7%91/</t>
         </is>
-      </c>
-      <c r="AF259" t="n">
-        <v>2</v>
       </c>
       <c r="AG259" t="inlineStr"/>
       <c r="AH259" t="inlineStr"/>
@@ -37535,15 +37535,15 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE260" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF260" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A2%D7%94-%D7%95%D7%99%D7%A6%D7%9E%D7%9F-%D7%A8%D7%91%D7%99%D7%91%D7%95/</t>
         </is>
-      </c>
-      <c r="AF260" t="n">
-        <v>2</v>
       </c>
       <c r="AG260" t="inlineStr"/>
       <c r="AH260" t="inlineStr"/>
@@ -37674,15 +37674,15 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE261" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF261" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%91%D7%95%D7%A8%D7%92-%D7%A1%D7%92%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF261" t="n">
-        <v>2</v>
       </c>
       <c r="AG261" t="inlineStr"/>
       <c r="AH261" t="inlineStr"/>
@@ -37813,15 +37813,15 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE262" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF262" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF262" t="n">
-        <v>2</v>
       </c>
       <c r="AG262" t="inlineStr"/>
       <c r="AH262" t="inlineStr"/>
@@ -37952,15 +37952,15 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE263" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF263" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%A4%D7%99%D7%9C%D7%95%D7%A1%D7%95%D7%A3/</t>
         </is>
-      </c>
-      <c r="AF263" t="n">
-        <v>2</v>
       </c>
       <c r="AG263" t="inlineStr"/>
       <c r="AH263" t="inlineStr"/>
@@ -38091,15 +38091,15 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE264" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF264" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%98%D7%95%D7%A9%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF264" t="n">
-        <v>2</v>
       </c>
       <c r="AG264" t="inlineStr"/>
       <c r="AH264" t="inlineStr"/>
@@ -38230,15 +38230,15 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE265" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF265" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A8%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF265" t="n">
-        <v>2</v>
       </c>
       <c r="AG265" t="inlineStr"/>
       <c r="AH265" t="inlineStr"/>
@@ -38369,15 +38369,15 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE266" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF266" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%9C%D7%9B%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF266" t="n">
-        <v>2</v>
       </c>
       <c r="AG266" t="inlineStr"/>
       <c r="AH266" t="inlineStr"/>
@@ -38508,15 +38508,15 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE267" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF267" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%9C%D7%92%D7%94-%D7%95%D7%A7%D7%A1%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF267" t="n">
-        <v>2</v>
       </c>
       <c r="AG267" t="inlineStr"/>
       <c r="AH267" t="inlineStr"/>
@@ -38647,15 +38647,15 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE268" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF268" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF268" t="n">
-        <v>2</v>
       </c>
       <c r="AG268" t="inlineStr"/>
       <c r="AH268" t="inlineStr"/>
@@ -38786,15 +38786,15 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE269" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF269" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%9E%D7%9C%D7%99-%D7%94%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF269" t="n">
-        <v>2</v>
       </c>
       <c r="AG269" t="inlineStr"/>
       <c r="AH269" t="inlineStr"/>
@@ -38925,15 +38925,15 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE270" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF270" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF270" t="n">
-        <v>2</v>
       </c>
       <c r="AG270" t="inlineStr"/>
       <c r="AH270" t="inlineStr"/>
@@ -39064,15 +39064,15 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE271" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF271" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%99%D7%A2%D7%A7%D7%91%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF271" t="n">
-        <v>2</v>
       </c>
       <c r="AG271" t="inlineStr"/>
       <c r="AH271" t="inlineStr"/>
@@ -39203,15 +39203,15 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE272" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF272" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7-%D7%A0%D7%A7%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF272" t="n">
-        <v>2</v>
       </c>
       <c r="AG272" t="inlineStr"/>
       <c r="AH272" t="inlineStr"/>
@@ -39342,15 +39342,15 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE273" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF273" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF273" t="n">
-        <v>2</v>
       </c>
       <c r="AG273" t="inlineStr"/>
       <c r="AH273" t="inlineStr"/>
@@ -39481,15 +39481,15 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE274" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF274" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%96-%D7%A8%D7%99%D7%99%D7%9B%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF274" t="n">
-        <v>2</v>
       </c>
       <c r="AG274" t="inlineStr"/>
       <c r="AH274" t="inlineStr"/>
@@ -39620,15 +39620,15 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE275" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF275" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%97%D7%9C-%D7%A4%D7%99%D7%A8%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF275" t="n">
-        <v>2</v>
       </c>
       <c r="AG275" t="inlineStr"/>
       <c r="AH275" t="inlineStr"/>
@@ -39759,15 +39759,15 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE276" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF276" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%AA-%D7%9C%D7%91%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF276" t="n">
-        <v>2</v>
       </c>
       <c r="AG276" t="inlineStr"/>
       <c r="AH276" t="inlineStr"/>
@@ -39898,15 +39898,15 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE277" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF277" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%96-%D7%A2%D7%96%D7%A8%D7%90/</t>
         </is>
-      </c>
-      <c r="AF277" t="n">
-        <v>2</v>
       </c>
       <c r="AG277" t="inlineStr"/>
       <c r="AH277" t="inlineStr"/>
@@ -40037,15 +40037,15 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE278" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF278" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A0%D7%A0%D7%94-%D7%95%D7%99%D7%A8%D7%A6%D7%91%D7%95%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF278" t="n">
-        <v>2</v>
       </c>
       <c r="AG278" t="inlineStr"/>
       <c r="AH278" t="inlineStr"/>
@@ -40176,15 +40176,15 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE279" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF279" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A2%D7%95%D7%AA-%D7%94%D7%A8%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF279" t="n">
-        <v>2</v>
       </c>
       <c r="AG279" t="inlineStr"/>
       <c r="AH279" t="inlineStr"/>
@@ -40315,15 +40315,15 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE280" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF280" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%98%D7%9C-%D7%90%D7%99%D7%A9-%D7%A9%D7%9C%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF280" t="n">
-        <v>2</v>
       </c>
       <c r="AG280" t="inlineStr"/>
       <c r="AH280" t="inlineStr"/>
@@ -40454,15 +40454,15 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE281" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF281" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A7%D7%99-%D7%96%D7%9C%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF281" t="n">
-        <v>2</v>
       </c>
       <c r="AG281" t="inlineStr"/>
       <c r="AH281" t="inlineStr"/>
@@ -40593,15 +40593,15 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE282" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF282" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A0%D7%AA-%D7%90%D7%9C%D7%93%D7%A8-%D7%92%D7%A8%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF282" t="n">
-        <v>2</v>
       </c>
       <c r="AG282" t="inlineStr"/>
       <c r="AH282" t="inlineStr"/>
@@ -40732,15 +40732,15 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE283" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF283" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%97%D7%99-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF283" t="n">
-        <v>2</v>
       </c>
       <c r="AG283" t="inlineStr"/>
       <c r="AH283" t="inlineStr"/>
@@ -40871,15 +40871,15 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE284" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF284" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99-%D7%A4%D7%A8%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF284" t="n">
-        <v>2</v>
       </c>
       <c r="AG284" t="inlineStr"/>
       <c r="AH284" t="inlineStr"/>
@@ -41010,15 +41010,15 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE285" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF285" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF285" t="n">
-        <v>2</v>
       </c>
       <c r="AG285" t="inlineStr"/>
       <c r="AH285" t="inlineStr"/>
@@ -41149,15 +41149,15 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE286" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF286" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%9D-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
-      </c>
-      <c r="AF286" t="n">
-        <v>2</v>
       </c>
       <c r="AG286" t="inlineStr"/>
       <c r="AH286" t="inlineStr"/>
@@ -41288,15 +41288,15 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE287" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF287" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%99-%D7%98%D7%9C-%D7%9E%D7%99%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF287" t="n">
-        <v>2</v>
       </c>
       <c r="AG287" t="inlineStr"/>
       <c r="AH287" t="inlineStr"/>
@@ -41427,15 +41427,15 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE288" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF288" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%92%D7%99%D7%AA-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF288" t="n">
-        <v>2</v>
       </c>
       <c r="AG288" t="inlineStr"/>
       <c r="AH288" t="inlineStr"/>
@@ -41566,15 +41566,15 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE289" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF289" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF289" t="n">
-        <v>2</v>
       </c>
       <c r="AG289" t="inlineStr"/>
       <c r="AH289" t="inlineStr"/>
@@ -41705,15 +41705,15 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE290" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF290" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%A9%D7%97%D7%A8-%D7%91%D7%9F-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF290" t="n">
-        <v>2</v>
       </c>
       <c r="AG290" t="inlineStr"/>
       <c r="AH290" t="inlineStr"/>
@@ -41844,15 +41844,15 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE291" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF291" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A7%D7%93-%D7%9C%D7%99%D7%91%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF291" t="n">
-        <v>2</v>
       </c>
       <c r="AG291" t="inlineStr"/>
       <c r="AH291" t="inlineStr"/>
@@ -41983,15 +41983,15 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE292" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF292" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%A0%D7%94-%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF292" t="n">
-        <v>2</v>
       </c>
       <c r="AG292" t="inlineStr"/>
       <c r="AH292" t="inlineStr"/>
@@ -42122,15 +42122,15 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE293" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF293" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%9F-%D7%96%D7%9C%D7%9E%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF293" t="n">
-        <v>2</v>
       </c>
       <c r="AG293" t="inlineStr"/>
       <c r="AH293" t="inlineStr"/>
@@ -42261,15 +42261,15 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE294" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF294" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%99-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF294" t="n">
-        <v>2</v>
       </c>
       <c r="AG294" t="inlineStr"/>
       <c r="AH294" t="inlineStr"/>
@@ -42400,15 +42400,15 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE295" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF295" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%94-%D7%A1%D7%95%D7%A1%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF295" t="n">
-        <v>2</v>
       </c>
       <c r="AG295" t="inlineStr"/>
       <c r="AH295" t="inlineStr"/>
@@ -42539,15 +42539,15 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE296" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF296" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%90%D7%9C-%D7%A8%D7%91%D7%A7%D7%94-%D7%99%D7%A4%D7%94/</t>
         </is>
-      </c>
-      <c r="AF296" t="n">
-        <v>2</v>
       </c>
       <c r="AG296" t="inlineStr"/>
       <c r="AH296" t="inlineStr"/>
@@ -42678,15 +42678,15 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE297" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF297" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A4%D7%99%D7%99%D7%98%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF297" t="n">
-        <v>2</v>
       </c>
       <c r="AG297" t="inlineStr"/>
       <c r="AH297" t="inlineStr"/>
@@ -42817,15 +42817,15 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE298" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF298" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%95%D7%98%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF298" t="n">
-        <v>2</v>
       </c>
       <c r="AG298" t="inlineStr"/>
       <c r="AH298" t="inlineStr"/>
@@ -42956,15 +42956,15 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE299" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF299" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%A8%D7%95%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF299" t="n">
-        <v>2</v>
       </c>
       <c r="AG299" t="inlineStr"/>
       <c r="AH299" t="inlineStr"/>
@@ -43095,15 +43095,15 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE300" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF300" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%98-%D7%93%D7%A8%D7%A1%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF300" t="n">
-        <v>2</v>
       </c>
       <c r="AG300" t="inlineStr"/>
       <c r="AH300" t="inlineStr"/>
@@ -43234,15 +43234,15 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE301" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF301" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%92%D7%95%D7%96%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF301" t="n">
-        <v>2</v>
       </c>
       <c r="AG301" t="inlineStr"/>
       <c r="AH301" t="inlineStr"/>
@@ -43373,15 +43373,15 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE302" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF302" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%94%D7%95%D7%9C%D7%A6%D7%91%D7%A8%D7%92-%D7%97%D7%99%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF302" t="n">
-        <v>2</v>
       </c>
       <c r="AG302" t="inlineStr"/>
       <c r="AH302" t="inlineStr"/>
@@ -43512,15 +43512,15 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE303" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF303" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A0%D7%93%D7%9C%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF303" t="n">
-        <v>2</v>
       </c>
       <c r="AG303" t="inlineStr"/>
       <c r="AH303" t="inlineStr"/>
@@ -43651,15 +43651,15 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE304" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF304" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF304" t="n">
-        <v>2</v>
       </c>
       <c r="AG304" t="inlineStr"/>
       <c r="AH304" t="inlineStr"/>
@@ -43790,15 +43790,15 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE305" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF305" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%9E%D7%9C%D7%9B%D7%94-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF305" t="n">
-        <v>2</v>
       </c>
       <c r="AG305" t="inlineStr"/>
       <c r="AH305" t="inlineStr"/>
@@ -43929,15 +43929,15 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE306" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF306" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%94%D7%9C%D7%A4%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF306" t="n">
-        <v>2</v>
       </c>
       <c r="AG306" t="inlineStr"/>
       <c r="AH306" t="inlineStr"/>
@@ -44068,15 +44068,15 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE307" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF307" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%95%D7%A4%D7%99%D7%94-%D7%9E%D7%9C%D7%97%D7%96%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF307" t="n">
-        <v>2</v>
       </c>
       <c r="AG307" t="inlineStr"/>
       <c r="AH307" t="inlineStr"/>
@@ -44207,15 +44207,15 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE308" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF308" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%9E%D7%99%D7%98%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF308" t="n">
-        <v>2</v>
       </c>
       <c r="AG308" t="inlineStr"/>
       <c r="AH308" t="inlineStr"/>
@@ -44346,15 +44346,15 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE309" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF309" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%A6%D7%A0%D7%A6%D7%99%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF309" t="n">
-        <v>2</v>
       </c>
       <c r="AG309" t="inlineStr"/>
       <c r="AH309" t="inlineStr"/>
@@ -44485,15 +44485,15 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE310" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF310" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%91%D7%99%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF310" t="n">
-        <v>2</v>
       </c>
       <c r="AG310" t="inlineStr"/>
       <c r="AH310" t="inlineStr"/>
@@ -44624,15 +44624,15 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE311" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF311" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF311" t="n">
-        <v>2</v>
       </c>
       <c r="AG311" t="inlineStr"/>
       <c r="AH311" t="inlineStr"/>
@@ -44763,15 +44763,15 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE312" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF312" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99%D7%94-%D7%91%D7%9F-%D7%9E%D7%96%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF312" t="n">
-        <v>2</v>
       </c>
       <c r="AG312" t="inlineStr"/>
       <c r="AH312" t="inlineStr"/>
@@ -44902,15 +44902,15 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE313" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF313" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%A8-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF313" t="n">
-        <v>3</v>
       </c>
       <c r="AG313" t="inlineStr"/>
       <c r="AH313" t="inlineStr"/>
@@ -45041,15 +45041,15 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE314" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF314" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A9%D7%92%D7%91-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF314" t="n">
-        <v>2</v>
       </c>
       <c r="AG314" t="inlineStr"/>
       <c r="AH314" t="inlineStr"/>
@@ -45180,15 +45180,15 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE315" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF315" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A2%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF315" t="n">
-        <v>2</v>
       </c>
       <c r="AG315" t="inlineStr"/>
       <c r="AH315" t="inlineStr"/>
@@ -45319,15 +45319,15 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE316" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF316" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99%D7%9E%D7%94-%D7%A9%D7%A2%D7%A9%D7%95%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF316" t="n">
-        <v>2</v>
       </c>
       <c r="AG316" t="inlineStr"/>
       <c r="AH316" t="inlineStr"/>
@@ -45458,15 +45458,15 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE317" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF317" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%A7%D7%95%D7%94-%D7%A6%D7%93%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF317" t="n">
-        <v>3</v>
       </c>
       <c r="AG317" t="inlineStr"/>
       <c r="AH317" t="inlineStr"/>
@@ -45597,15 +45597,15 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE318" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF318" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%95%D7%91%D7%94-%D7%99%D7%95%D7%A1%D7%A4%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF318" t="n">
-        <v>2</v>
       </c>
       <c r="AG318" t="inlineStr"/>
       <c r="AH318" t="inlineStr"/>
@@ -45736,15 +45736,15 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE319" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF319" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%91%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF319" t="n">
-        <v>2</v>
       </c>
       <c r="AG319" t="inlineStr"/>
       <c r="AH319" t="inlineStr"/>
@@ -45875,15 +45875,15 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE320" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF320" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%95%D7%A4%D7%99%D7%AA-%D7%93%D7%99%D7%A1%D7%98%D7%9C%D7%9E%D7%9F-%D7%9E%D7%99%D7%A8%D7%A7%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF320" t="n">
-        <v>2</v>
       </c>
       <c r="AG320" t="inlineStr"/>
       <c r="AH320" t="inlineStr"/>
@@ -46014,15 +46014,15 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE321" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF321" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%9C%D7%A8%D7%99-%D7%9E%D7%99%D7%9C%D7%94%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF321" t="n">
-        <v>2</v>
       </c>
       <c r="AG321" t="inlineStr"/>
       <c r="AH321" t="inlineStr"/>
@@ -46153,15 +46153,15 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE322" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF322" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%91%D7%90%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF322" t="n">
-        <v>2</v>
       </c>
       <c r="AG322" t="inlineStr"/>
       <c r="AH322" t="inlineStr"/>
@@ -46292,15 +46292,15 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE323" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF323" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%99%D7%A7%D7%98%D7%95%D7%A8%D7%99%D7%94-%D7%A7%D7%9E%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF323" t="n">
-        <v>2</v>
       </c>
       <c r="AG323" t="inlineStr"/>
       <c r="AH323" t="inlineStr"/>
@@ -46431,15 +46431,15 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE324" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF324" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A4%D7%90%D7%90-%D7%90%D7%91%D7%95-%D7%90%D7%A1%D7%9E%D7%90%D7%A2%D7%99%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF324" t="n">
-        <v>2</v>
       </c>
       <c r="AG324" t="inlineStr"/>
       <c r="AH324" t="inlineStr"/>
@@ -46570,15 +46570,15 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE325" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF325" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%91%D7%90%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF325" t="n">
-        <v>2</v>
       </c>
       <c r="AG325" t="inlineStr"/>
       <c r="AH325" t="inlineStr"/>
@@ -46709,15 +46709,15 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE326" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF326" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%93%D7%95%D7%91%D7%93%D7%91%D7%9F-%D7%92%D7%9C%D7%95%D7%96%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF326" t="n">
-        <v>2</v>
       </c>
       <c r="AG326" t="inlineStr"/>
       <c r="AH326" t="inlineStr"/>
@@ -46848,15 +46848,15 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE327" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF327" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%90%D7%98%D7%99%D7%90%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF327" t="n">
-        <v>2</v>
       </c>
       <c r="AG327" t="inlineStr"/>
       <c r="AH327" t="inlineStr"/>
@@ -46987,15 +46987,15 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE328" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF328" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%93%D7%95%D7%91%D7%A1%D7%98%D7%A8-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF328" t="n">
-        <v>2</v>
       </c>
       <c r="AG328" t="inlineStr"/>
       <c r="AH328" t="inlineStr"/>
@@ -47126,15 +47126,15 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE329" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF329" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/291/</t>
         </is>
-      </c>
-      <c r="AF329" t="n">
-        <v>2</v>
       </c>
       <c r="AG329" t="inlineStr"/>
       <c r="AH329" t="inlineStr"/>
@@ -47265,15 +47265,15 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE330" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF330" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%96%D7%99%D7%AA-%D7%97%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF330" t="n">
-        <v>2</v>
       </c>
       <c r="AG330" t="inlineStr"/>
       <c r="AH330" t="inlineStr"/>
@@ -47404,15 +47404,15 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE331" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF331" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%A6%D7%A0%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF331" t="n">
-        <v>2</v>
       </c>
       <c r="AG331" t="inlineStr"/>
       <c r="AH331" t="inlineStr"/>
@@ -47543,15 +47543,15 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE332" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF332" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A4%D7%9C%D7%92/</t>
         </is>
-      </c>
-      <c r="AF332" t="n">
-        <v>2</v>
       </c>
       <c r="AG332" t="inlineStr"/>
       <c r="AH332" t="inlineStr"/>
@@ -47682,15 +47682,15 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE333" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF333" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF333" t="n">
-        <v>2</v>
       </c>
       <c r="AG333" t="inlineStr"/>
       <c r="AH333" t="inlineStr"/>
@@ -47821,15 +47821,15 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE334" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF334" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%90%D7%A0%D7%94-%D7%A4%D7%99%D7%A9%D7%91%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF334" t="n">
-        <v>2</v>
       </c>
       <c r="AG334" t="inlineStr"/>
       <c r="AH334" t="inlineStr"/>
@@ -47960,15 +47960,15 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE335" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF335" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%9E%D7%95%D7%A8%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF335" t="n">
-        <v>2</v>
       </c>
       <c r="AG335" t="inlineStr"/>
       <c r="AH335" t="inlineStr"/>
@@ -48099,15 +48099,15 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE336" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF336" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%A8%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF336" t="n">
-        <v>2</v>
       </c>
       <c r="AG336" t="inlineStr"/>
       <c r="AH336" t="inlineStr"/>
@@ -48238,15 +48238,15 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE337" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE337" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF337" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%99%D7%AA-%D7%9B%D7%A5-%D7%91%D7%A1%D7%98%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF337" t="n">
-        <v>2</v>
       </c>
       <c r="AG337" t="inlineStr"/>
       <c r="AH337" t="inlineStr"/>
@@ -48377,15 +48377,15 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE338" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF338" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A2%D7%9E%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF338" t="n">
-        <v>2</v>
       </c>
       <c r="AG338" t="inlineStr"/>
       <c r="AH338" t="inlineStr"/>
@@ -48516,15 +48516,15 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE339" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF339" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A8%D7%91%D7%99%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF339" t="n">
-        <v>2</v>
       </c>
       <c r="AG339" t="inlineStr"/>
       <c r="AH339" t="inlineStr"/>
@@ -48655,15 +48655,15 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE340" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF340" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%91%D7%9C-%D7%A7%D7%A1%D7%98%D7%99%D7%9F-%D7%9B%D7%94%D7%A0%D7%90/</t>
         </is>
-      </c>
-      <c r="AF340" t="n">
-        <v>2</v>
       </c>
       <c r="AG340" t="inlineStr"/>
       <c r="AH340" t="inlineStr"/>
@@ -48794,15 +48794,15 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE341" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF341" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF341" t="n">
-        <v>2</v>
       </c>
       <c r="AG341" t="inlineStr"/>
       <c r="AH341" t="inlineStr"/>
@@ -48943,15 +48943,15 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>19665504</v>
-      </c>
-      <c r="AE342" t="inlineStr">
+        <v>58996512</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF342" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%96%D7%94%D7%99-%D7%A1%D7%A2%D7%99%D7%93-%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A6%D7%A4%D7%95%D7%9F-%D7%92%D7%9C%D7%99%D7%9C</t>
         </is>
-      </c>
-      <c r="AF342" t="n">
-        <v>1</v>
       </c>
       <c r="AG342" t="inlineStr"/>
       <c r="AH342" t="inlineStr"/>
@@ -49088,15 +49088,15 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>23915088</v>
-      </c>
-      <c r="AE343" t="inlineStr">
+        <v>71745264</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF343" t="inlineStr">
         <is>
           <t>https://nefeshachat.co.il/</t>
         </is>
-      </c>
-      <c r="AF343" t="n">
-        <v>2</v>
       </c>
       <c r="AG343" t="inlineStr"/>
       <c r="AH343" t="inlineStr"/>
@@ -49227,15 +49227,15 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE344" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF344" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9B%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF344" t="n">
-        <v>2</v>
       </c>
       <c r="AG344" t="inlineStr"/>
       <c r="AH344" t="inlineStr"/>
@@ -49366,15 +49366,15 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE345" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF345" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A9%D7%9C-%D7%98%D7%95%D7%94%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF345" t="n">
-        <v>2</v>
       </c>
       <c r="AG345" t="inlineStr"/>
       <c r="AH345" t="inlineStr"/>
@@ -49505,15 +49505,15 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE346" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF346" t="inlineStr">
         <is>
           <t>https://tzuna-tova.co.il/</t>
         </is>
-      </c>
-      <c r="AF346" t="n">
-        <v>2</v>
       </c>
       <c r="AG346" t="inlineStr"/>
       <c r="AH346" t="inlineStr"/>
@@ -49644,15 +49644,15 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE347" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF347" t="inlineStr">
         <is>
           <t>https://www.shiri-sleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF347" t="n">
-        <v>2</v>
       </c>
       <c r="AG347" t="inlineStr"/>
       <c r="AH347" t="inlineStr"/>
@@ -49791,15 +49791,15 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE348" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF348" t="inlineStr">
         <is>
           <t>https://www.goodnights.co.il/</t>
         </is>
-      </c>
-      <c r="AF348" t="n">
-        <v>2</v>
       </c>
       <c r="AG348" t="inlineStr"/>
       <c r="AH348" t="inlineStr"/>
@@ -49930,15 +49930,15 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE349" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF349" t="inlineStr">
         <is>
           <t>https://www.lev-hasharon.co.il/?page_id=35</t>
         </is>
-      </c>
-      <c r="AF349" t="n">
-        <v>1</v>
       </c>
       <c r="AG349" t="inlineStr"/>
       <c r="AH349" t="inlineStr"/>
@@ -50069,15 +50069,15 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE350" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF350" t="inlineStr">
         <is>
           <t>https://www.ofirbaby.com/</t>
         </is>
-      </c>
-      <c r="AF350" t="n">
-        <v>1</v>
       </c>
       <c r="AG350" t="inlineStr"/>
       <c r="AH350" t="inlineStr"/>
@@ -50208,15 +50208,15 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE351" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF351" t="inlineStr">
         <is>
           <t>https://www.friendsoftzafon.org.il/</t>
         </is>
-      </c>
-      <c r="AF351" t="n">
-        <v>1</v>
       </c>
       <c r="AG351" t="inlineStr"/>
       <c r="AH351" t="inlineStr"/>
@@ -50357,15 +50357,15 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE352" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF352" t="inlineStr">
         <is>
           <t>https://www.medicalhasharon.co.il/home</t>
         </is>
-      </c>
-      <c r="AF352" t="n">
-        <v>1</v>
       </c>
       <c r="AG352" t="inlineStr"/>
       <c r="AH352" t="inlineStr"/>
@@ -50496,15 +50496,15 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE353" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF353" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=7E14A2CD72AD61B21153C2A004D48174&amp;RequestId=00000000-0005-0000-0000-000000000352&amp;Source=undefinedResults</t>
         </is>
-      </c>
-      <c r="AF353" t="n">
-        <v>1</v>
       </c>
       <c r="AG353" t="inlineStr"/>
       <c r="AH353" t="inlineStr"/>
@@ -50635,15 +50635,15 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE354" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF354" t="inlineStr">
         <is>
           <t>https://hpmc-prime.com/</t>
         </is>
-      </c>
-      <c r="AF354" t="n">
-        <v>1</v>
       </c>
       <c r="AG354" t="inlineStr"/>
       <c r="AH354" t="inlineStr"/>
@@ -50782,15 +50782,15 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE355" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF355" t="inlineStr">
         <is>
           <t>https://serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKey=eSo86qER4ZaETCy38wvA4mjeISWyXbtFtJE0SP1qB0MfcsZFamqNWVBcon12iX8vQI0ry3v3SHcFjBSvLlmzhA==</t>
         </is>
-      </c>
-      <c r="AF355" t="n">
-        <v>1</v>
       </c>
       <c r="AG355" t="inlineStr"/>
       <c r="AH355" t="inlineStr"/>
@@ -50930,15 +50930,15 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE356" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF356" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=2CA020F3C4C5B067993FAF75328AF758&amp;RequestId=00000000-0000-0000-0005-000000000105</t>
         </is>
-      </c>
-      <c r="AF356" t="n">
-        <v>1</v>
       </c>
       <c r="AG356" t="inlineStr"/>
       <c r="AH356" t="inlineStr"/>
@@ -51069,15 +51069,15 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE357" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF357" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKeyIndex=BA945B3FBAF6DC188D0C119454B56441&amp;RequestId=00000000-0000-0000-0005-000000000233</t>
         </is>
-      </c>
-      <c r="AF357" t="n">
-        <v>1</v>
       </c>
       <c r="AG357" t="inlineStr"/>
       <c r="AH357" t="inlineStr"/>
@@ -51208,15 +51208,15 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE358" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF358" t="inlineStr">
         <is>
           <t>https://serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKey=rdeOMLyOOZ3wrrZqiL2qbhlKZltQO6skkT2FVfXJExM50B1rgVU80GQZKUJnBoyTj1TxaXxEeeb6fiB1NDU5pw==</t>
         </is>
-      </c>
-      <c r="AF358" t="n">
-        <v>1</v>
       </c>
       <c r="AG358" t="inlineStr"/>
       <c r="AH358" t="inlineStr"/>
@@ -51355,15 +51355,15 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE359" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF359" t="inlineStr">
         <is>
           <t>https://serguide.maccabi4u.co.il/heb/medicalcentres/medicalcentressearchresults/medicalcentresinfopage/?ItemKey=e/asC6ieKYwbGjyv8QNoJzSyHNxcE3w8Q8LIU8peBbEKtoOL1HXJumYvC1laTm5V5OAJW3X0HkVvrGmm3NqWEg==</t>
         </is>
-      </c>
-      <c r="AF359" t="n">
-        <v>1</v>
       </c>
       <c r="AG359" t="inlineStr"/>
       <c r="AH359" t="inlineStr"/>
@@ -51494,15 +51494,15 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE360" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF360" t="inlineStr">
         <is>
           <t>https://tlvmed.co.il/</t>
         </is>
-      </c>
-      <c r="AF360" t="n">
-        <v>2</v>
       </c>
       <c r="AG360" t="inlineStr"/>
       <c r="AH360" t="inlineStr"/>
@@ -51643,15 +51643,15 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>19665504</v>
-      </c>
-      <c r="AE361" t="inlineStr">
+        <v>58996512</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF361" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%96%D7%94%D7%99-%D7%A1%D7%A2%D7%99%D7%93-%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A6%D7%A4%D7%95%D7%9F-%D7%92%D7%9C%D7%99%D7%9C</t>
         </is>
-      </c>
-      <c r="AF361" t="n">
-        <v>1</v>
       </c>
       <c r="AG361" t="inlineStr"/>
       <c r="AH361" t="inlineStr"/>
@@ -51792,15 +51792,15 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE362" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF362" t="inlineStr">
         <is>
           <t>https://dravitalshe.wixsite.com/dravital</t>
         </is>
-      </c>
-      <c r="AF362" t="n">
-        <v>1</v>
       </c>
       <c r="AG362" t="inlineStr"/>
       <c r="AH362" t="inlineStr"/>
@@ -51937,15 +51937,15 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE363" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF363" t="inlineStr">
         <is>
           <t>https://drehuddrucker.com/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF363" t="n">
-        <v>1</v>
       </c>
       <c r="AG363" t="inlineStr"/>
       <c r="AH363" t="inlineStr"/>
@@ -52086,15 +52086,15 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE364" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF364" t="inlineStr">
         <is>
           <t>https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%90%D7%97%D7%9E%D7%93_%D7%92%D7%9E%D7%94%D7%95%D7%A8</t>
         </is>
-      </c>
-      <c r="AF364" t="n">
-        <v>1</v>
       </c>
       <c r="AG364" t="inlineStr"/>
       <c r="AH364" t="inlineStr"/>
@@ -52225,15 +52225,15 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE365" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF365" t="inlineStr">
         <is>
           <t>https://www.irisraz.co.il/</t>
         </is>
-      </c>
-      <c r="AF365" t="n">
-        <v>1</v>
       </c>
       <c r="AG365" t="inlineStr"/>
       <c r="AH365" t="inlineStr"/>
@@ -52374,15 +52374,15 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE366" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF366" t="inlineStr">
         <is>
           <t>https://www.healing-arts.co.il/team/%D7%93%D7%A8-%D7%90%D7%9C%D7%94-%D7%91%D7%A0%D7%92%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF366" t="n">
-        <v>1</v>
       </c>
       <c r="AG366" t="inlineStr"/>
       <c r="AH366" t="inlineStr"/>
@@ -52523,15 +52523,15 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE367" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF367" t="inlineStr">
         <is>
           <t>https://g-news.co.il/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A7%D7%A8%D7%99%D7%99%D7%AA-%D7%A9%D7%9E%D7%95%D7%A0%D7%94-%D7%9E%D7%A8%D7%9B%D7%96-%D7%9E%D7%AA%D7%97%D7%93%D7%A9%D7%AA-%D7%A2%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF367" t="n">
-        <v>1</v>
       </c>
       <c r="AG367" t="inlineStr"/>
       <c r="AH367" t="inlineStr"/>
@@ -52672,15 +52672,15 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE368" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF368" t="inlineStr">
         <is>
           <t>https://geekonomy.net/2020/09/25/geekonony363/</t>
         </is>
-      </c>
-      <c r="AF368" t="n">
-        <v>1</v>
       </c>
       <c r="AG368" t="inlineStr"/>
       <c r="AH368" t="inlineStr"/>
@@ -52819,15 +52819,15 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE369" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF369" t="inlineStr">
         <is>
           <t>https://www.mutarli.co.il/nutritionists</t>
         </is>
-      </c>
-      <c r="AF369" t="n">
-        <v>1</v>
       </c>
       <c r="AG369" t="inlineStr"/>
       <c r="AH369" t="inlineStr"/>
@@ -52964,15 +52964,15 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>19138680</v>
-      </c>
-      <c r="AE370" t="inlineStr">
+        <v>57416040</v>
+      </c>
+      <c r="AE370" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF370" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/doctors-search</t>
         </is>
-      </c>
-      <c r="AF370" t="n">
-        <v>1</v>
       </c>
       <c r="AG370" t="inlineStr"/>
       <c r="AH370" t="inlineStr"/>
@@ -53109,15 +53109,15 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>19138680</v>
-      </c>
-      <c r="AE371" t="inlineStr">
+        <v>57416040</v>
+      </c>
+      <c r="AE371" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF371" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/doctors-search</t>
         </is>
-      </c>
-      <c r="AF371" t="n">
-        <v>1</v>
       </c>
       <c r="AG371" t="inlineStr"/>
       <c r="AH371" t="inlineStr"/>
@@ -53254,15 +53254,15 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>19138680</v>
-      </c>
-      <c r="AE372" t="inlineStr">
+        <v>57416040</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF372" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/doctors-search</t>
         </is>
-      </c>
-      <c r="AF372" t="n">
-        <v>1</v>
       </c>
       <c r="AG372" t="inlineStr"/>
       <c r="AH372" t="inlineStr"/>
@@ -53393,15 +53393,15 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE373" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE373" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF373" t="inlineStr">
         <is>
           <t>https://chenaseo.co.il/service/%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%A9%D7%99%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF373" t="n">
-        <v>1</v>
       </c>
       <c r="AG373" t="inlineStr"/>
       <c r="AH373" t="inlineStr"/>
@@ -53538,15 +53538,15 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>23915088</v>
-      </c>
-      <c r="AE374" t="inlineStr">
+        <v>71745264</v>
+      </c>
+      <c r="AE374" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF374" t="inlineStr">
         <is>
           <t>https://www.caress.co.il/holistic_attachment_approach/</t>
         </is>
-      </c>
-      <c r="AF374" t="n">
-        <v>1</v>
       </c>
       <c r="AG374" t="inlineStr"/>
       <c r="AH374" t="inlineStr"/>
@@ -53685,15 +53685,15 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE375" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE375" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF375" t="inlineStr">
         <is>
           <t>https://www.horimlive.co.il/%D7%9C%D7%99-%D7%A1%D7%9C%D7%A2-%D7%A4%D7%99%D7%96%D7%99%D7%95%D7%AA%D7%A8%D7%A4%D7%99%D7%A1%D7%98%D7%99%D7%AA-%D7%A1%D7%98%D7%95%D7%93%D7%99%D7%95-%D7%90%D7%9E%D7%94%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF375" t="n">
-        <v>1</v>
       </c>
       <c r="AG375" t="inlineStr"/>
       <c r="AH375" t="inlineStr"/>
@@ -53834,15 +53834,15 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE376" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE376" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF376" t="inlineStr">
         <is>
           <t>https://www.drleeorshachar.com/</t>
         </is>
-      </c>
-      <c r="AF376" t="n">
-        <v>1</v>
       </c>
       <c r="AG376" t="inlineStr"/>
       <c r="AH376" t="inlineStr"/>
@@ -53973,15 +53973,15 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE377" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE377" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF377" t="inlineStr">
         <is>
           <t>https://www.lilachofi.co.il/</t>
         </is>
-      </c>
-      <c r="AF377" t="n">
-        <v>1</v>
       </c>
       <c r="AG377" t="inlineStr"/>
       <c r="AH377" t="inlineStr"/>
@@ -54108,15 +54108,15 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE378" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE378" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF378" t="inlineStr">
         <is>
           <t>https://www.refuashlema.co.il/therapists/meital-ron-el</t>
         </is>
-      </c>
-      <c r="AF378" t="n">
-        <v>1</v>
       </c>
       <c r="AG378" t="inlineStr"/>
       <c r="AH378" t="inlineStr"/>
@@ -54247,15 +54247,15 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE379" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE379" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF379" t="inlineStr">
         <is>
           <t>https://meravsleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF379" t="n">
-        <v>1</v>
       </c>
       <c r="AG379" t="inlineStr"/>
       <c r="AH379" t="inlineStr"/>
@@ -54386,15 +54386,15 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE380" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE380" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF380" t="inlineStr">
         <is>
           <t>https://www.ditamidwife.co.il/about</t>
         </is>
-      </c>
-      <c r="AF380" t="n">
-        <v>1</v>
       </c>
       <c r="AG380" t="inlineStr"/>
       <c r="AH380" t="inlineStr"/>
@@ -54535,15 +54535,15 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE381" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE381" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF381" t="inlineStr">
         <is>
           <t>https://menmedical.co.il/doctor/%D7%93%D7%A8-%D7%A1%D7%A2%D7%99%D7%93-%D7%93%D7%9B%D7%95%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF381" t="n">
-        <v>1</v>
       </c>
       <c r="AG381" t="inlineStr"/>
       <c r="AH381" t="inlineStr"/>
@@ -54674,15 +54674,15 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE382" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE382" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF382" t="inlineStr">
         <is>
           <t>https://anatmaron.com/</t>
         </is>
-      </c>
-      <c r="AF382" t="n">
-        <v>1</v>
       </c>
       <c r="AG382" t="inlineStr"/>
       <c r="AH382" t="inlineStr"/>
@@ -54813,15 +54813,15 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE383" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE383" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF383" t="inlineStr">
         <is>
           <t>https://www.omeryael.com/</t>
         </is>
-      </c>
-      <c r="AF383" t="n">
-        <v>1</v>
       </c>
       <c r="AG383" t="inlineStr"/>
       <c r="AH383" t="inlineStr"/>
@@ -54948,15 +54948,15 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE384" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE384" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF384" t="inlineStr">
         <is>
           <t>https://www.refuashlema.co.il/therapists/ronit-ben-eliyahu</t>
         </is>
-      </c>
-      <c r="AF384" t="n">
-        <v>1</v>
       </c>
       <c r="AG384" t="inlineStr"/>
       <c r="AH384" t="inlineStr"/>
@@ -55093,15 +55093,15 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE385" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE385" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF385" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/section/Family-Medicine/%D7%A9%D7%99%D7%97%D7%94-%D7%A2%D7%9D-%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94</t>
         </is>
-      </c>
-      <c r="AF385" t="n">
-        <v>1</v>
       </c>
       <c r="AG385" t="inlineStr"/>
       <c r="AH385" t="inlineStr"/>
@@ -55238,15 +55238,15 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE386" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE386" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF386" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/section/Family-Medicine/%D7%A9%D7%99%D7%97%D7%94-%D7%A2%D7%9D-%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94</t>
         </is>
-      </c>
-      <c r="AF386" t="n">
-        <v>1</v>
       </c>
       <c r="AG386" t="inlineStr"/>
       <c r="AH386" t="inlineStr"/>
@@ -55383,15 +55383,15 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE387" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE387" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF387" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/section/Family-Medicine/%D7%A9%D7%99%D7%97%D7%94-%D7%A2%D7%9D-%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94</t>
         </is>
-      </c>
-      <c r="AF387" t="n">
-        <v>1</v>
       </c>
       <c r="AG387" t="inlineStr"/>
       <c r="AH387" t="inlineStr"/>
@@ -55532,15 +55532,15 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE388" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE388" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF388" t="inlineStr">
         <is>
           <t>https://ashdodnet.com/%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%A7%D7%94%D7%99%D7%9C%D7%94/%D7%9E%D7%99%D7%A0%D7%95%D7%99-%D7%97%D7%93%D7%A9-%D7%93-%D7%A8-%D7%A9%D7%9C%D7%95%D7%9F-%D7%99%D7%A2%D7%A7%D7%91-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%9E%D7%99%D7%A0%D7%94%D7%9C%D7%AA-%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%9E%D7%97%D7%95%D7%96-%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-634820</t>
         </is>
-      </c>
-      <c r="AF388" t="n">
-        <v>1</v>
       </c>
       <c r="AG388" t="inlineStr"/>
       <c r="AH388" t="inlineStr"/>
@@ -55681,15 +55681,15 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE389" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE389" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF389" t="inlineStr">
         <is>
           <t>https://ashdodnet.com/%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%A7%D7%94%D7%99%D7%9C%D7%94/%D7%9E%D7%99%D7%A0%D7%95%D7%99-%D7%97%D7%93%D7%A9-%D7%93-%D7%A8-%D7%A9%D7%9C%D7%95%D7%9F-%D7%99%D7%A2%D7%A7%D7%91-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%9E%D7%99%D7%A0%D7%94%D7%9C%D7%AA-%D7%90%D7%A9%D7%93%D7%95%D7%93-%D7%91%D7%9E%D7%97%D7%95%D7%96-%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-634820</t>
         </is>
-      </c>
-      <c r="AF389" t="n">
-        <v>1</v>
       </c>
       <c r="AG389" t="inlineStr"/>
       <c r="AH389" t="inlineStr"/>
@@ -55830,15 +55830,15 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE390" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE390" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF390" t="inlineStr">
         <is>
           <t>https://www.shiluv-bodymind.co.il/mrtsym/%D7%A9%D7%9E%D7%99%D7%AA-%D7%A7%D7%93%D7%95%D7%A9</t>
         </is>
-      </c>
-      <c r="AF390" t="n">
-        <v>1</v>
       </c>
       <c r="AG390" t="inlineStr"/>
       <c r="AH390" t="inlineStr"/>
@@ -55979,15 +55979,15 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>19665504</v>
-      </c>
-      <c r="AE391" t="inlineStr">
+        <v>58996512</v>
+      </c>
+      <c r="AE391" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF391" t="inlineStr">
         <is>
           <t>https://www.medonline.co.il/expert/%D7%96%D7%94%D7%99-%D7%A1%D7%A2%D7%99%D7%93-%D7%9E%D7%A0%D7%94%D7%9C-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%A6%D7%A4%D7%95%D7%9F-%D7%92%D7%9C%D7%99%D7%9C</t>
         </is>
-      </c>
-      <c r="AF391" t="n">
-        <v>1</v>
       </c>
       <c r="AG391" t="inlineStr"/>
       <c r="AH391" t="inlineStr"/>
@@ -56128,15 +56128,15 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE392" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE392" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF392" t="inlineStr">
         <is>
           <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF392" t="n">
-        <v>5</v>
       </c>
       <c r="AG392" t="inlineStr"/>
       <c r="AH392" t="inlineStr"/>
@@ -56277,15 +56277,15 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE393" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF393" t="inlineStr">
         <is>
           <t>https://www.rashuiot.co.il/html5/arclookup.taf?_id=70247&amp;did=1118&amp;title=%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF393" t="n">
-        <v>1</v>
       </c>
       <c r="AG393" t="inlineStr"/>
       <c r="AH393" t="inlineStr"/>
@@ -56424,15 +56424,15 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE394" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF394" t="inlineStr">
         <is>
           <t>https://www.horuta.co.il/</t>
         </is>
-      </c>
-      <c r="AF394" t="n">
-        <v>1</v>
       </c>
       <c r="AG394" t="inlineStr"/>
       <c r="AH394" t="inlineStr"/>
@@ -56573,15 +56573,15 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE395" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF395" t="inlineStr">
         <is>
           <t>https://www.news1.co.il/ShowPrivateWriterPage.aspx?user_ID=1780&amp;first_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD&amp;last_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF395" t="n">
-        <v>1</v>
       </c>
       <c r="AG395" t="inlineStr"/>
       <c r="AH395" t="inlineStr"/>
@@ -56722,15 +56722,15 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE396" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF396" t="inlineStr">
         <is>
           <t>https://www.news1.co.il/ShowPrivateWriterPage.aspx?user_ID=1780&amp;first_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD&amp;last_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF396" t="n">
-        <v>1</v>
       </c>
       <c r="AG396" t="inlineStr"/>
       <c r="AH396" t="inlineStr"/>
@@ -56871,15 +56871,15 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE397" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF397" t="inlineStr">
         <is>
           <t>https://www.news1.co.il/ShowPrivateWriterPage.aspx?user_ID=1780&amp;first_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD&amp;last_name=%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF397" t="n">
-        <v>1</v>
       </c>
       <c r="AG397" t="inlineStr"/>
       <c r="AH397" t="inlineStr"/>
@@ -57010,15 +57010,15 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE398" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF398" t="inlineStr">
         <is>
           <t>https://etikatz.co.il/services/breastfeeding-and-sleep-consultation/</t>
         </is>
-      </c>
-      <c r="AF398" t="n">
-        <v>1</v>
       </c>
       <c r="AG398" t="inlineStr"/>
       <c r="AH398" t="inlineStr"/>
@@ -57159,15 +57159,15 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE399" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE399" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF399" t="inlineStr">
         <is>
           <t>https://shluvim.com/tech/%D7%93%D7%A8-%D7%9E%D7%95%D7%98%D7%99-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
-      </c>
-      <c r="AF399" t="n">
-        <v>1</v>
       </c>
       <c r="AG399" t="inlineStr"/>
       <c r="AH399" t="inlineStr"/>
@@ -57298,15 +57298,15 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE400" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE400" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF400" t="inlineStr">
         <is>
           <t>https://suzisleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF400" t="n">
-        <v>1</v>
       </c>
       <c r="AG400" t="inlineStr"/>
       <c r="AH400" t="inlineStr"/>
@@ -57450,15 +57450,15 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE401" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF401" t="inlineStr">
         <is>
           <t>https://www.niroleen.com/cosmatisohin-doktor-adi.html</t>
         </is>
-      </c>
-      <c r="AF401" t="n">
-        <v>1</v>
       </c>
       <c r="AG401" t="inlineStr"/>
       <c r="AH401" t="inlineStr"/>
@@ -57599,15 +57599,15 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE402" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE402" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF402" t="inlineStr">
         <is>
           <t>https://www.niroleen.com/cosmatisohin-doktor-adi.html</t>
         </is>
-      </c>
-      <c r="AF402" t="n">
-        <v>1</v>
       </c>
       <c r="AG402" t="inlineStr"/>
       <c r="AH402" t="inlineStr"/>
@@ -57748,15 +57748,15 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE403" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE403" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF403" t="inlineStr">
         <is>
           <t>https://medixlife.co.il/our_team/%D7%93%D7%A8-%D7%A2%D7%93%D7%99-%D7%A0%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF403" t="n">
-        <v>1</v>
       </c>
       <c r="AG403" t="inlineStr"/>
       <c r="AH403" t="inlineStr"/>
@@ -57897,15 +57897,15 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE404" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE404" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF404" t="inlineStr">
         <is>
           <t>https://medixlife.co.il/our_team/%D7%93%D7%A8-%D7%A2%D7%93%D7%99-%D7%A0%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF404" t="n">
-        <v>1</v>
       </c>
       <c r="AG404" t="inlineStr"/>
       <c r="AH404" t="inlineStr"/>
@@ -58046,15 +58046,15 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE405" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF405" t="inlineStr">
         <is>
           <t>https://shrir-sheled.co.il/therapists/%D7%90%D7%99%D7%94-%D7%A9%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF405" t="n">
-        <v>1</v>
       </c>
       <c r="AG405" t="inlineStr"/>
       <c r="AH405" t="inlineStr"/>
@@ -58186,15 +58186,15 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE406" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE406" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF406" t="inlineStr">
         <is>
           <t>https://michaldalyot.co.il/%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA-%D7%94%D7%95%D7%A8%D7%99%D7%9D/%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%A9%D7%99%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF406" t="n">
-        <v>1</v>
       </c>
       <c r="AG406" t="inlineStr"/>
       <c r="AH406" t="inlineStr"/>
@@ -58325,15 +58325,15 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE407" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE407" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF407" t="inlineStr">
         <is>
           <t>https://www.mcra.co.il/</t>
         </is>
-      </c>
-      <c r="AF407" t="n">
-        <v>2</v>
       </c>
       <c r="AG407" t="inlineStr"/>
       <c r="AH407" t="inlineStr"/>
@@ -58474,15 +58474,15 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE408" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF408" t="inlineStr">
         <is>
           <t>https://www.bekeshevclinic.co.il/</t>
         </is>
-      </c>
-      <c r="AF408" t="n">
-        <v>1</v>
       </c>
       <c r="AG408" t="inlineStr"/>
       <c r="AH408" t="inlineStr"/>
@@ -58619,15 +58619,15 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE409" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE409" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF409" t="inlineStr">
         <is>
           <t>https://www.homedical.co.il/services/%D7%A8%D7%95%D7%A4%D7%90-%D7%9E%D7%A9%D7%A4%D7%97%D7%94-%D7%A2%D7%93-%D7%94%D7%91%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF409" t="n">
-        <v>1</v>
       </c>
       <c r="AG409" t="inlineStr"/>
       <c r="AH409" t="inlineStr"/>
@@ -58768,15 +58768,15 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE410" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE410" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF410" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
-      </c>
-      <c r="AF410" t="n">
-        <v>1</v>
       </c>
       <c r="AG410" t="inlineStr"/>
       <c r="AH410" t="inlineStr"/>
@@ -58917,15 +58917,15 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>24091992</v>
-      </c>
-      <c r="AE411" t="inlineStr">
+        <v>72275976</v>
+      </c>
+      <c r="AE411" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF411" t="inlineStr">
         <is>
           <t>https://www.yaeltzur.co.il/talie-gliksman/</t>
         </is>
-      </c>
-      <c r="AF411" t="n">
-        <v>1</v>
       </c>
       <c r="AG411" t="inlineStr"/>
       <c r="AH411" t="inlineStr"/>
@@ -59064,15 +59064,15 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE412" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE412" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF412" t="inlineStr">
         <is>
           <t>https://www.mutarli.co.il/nutritionists</t>
         </is>
-      </c>
-      <c r="AF412" t="n">
-        <v>1</v>
       </c>
       <c r="AG412" t="inlineStr"/>
       <c r="AH412" t="inlineStr"/>
@@ -59213,15 +59213,15 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE413" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE413" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF413" t="inlineStr">
         <is>
           <t>https://www.rashuiot.co.il/html5/arclookup.taf?_id=70247&amp;did=1118&amp;title=%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD+%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD%EF%BF%BD</t>
         </is>
-      </c>
-      <c r="AF413" t="n">
-        <v>1</v>
       </c>
       <c r="AG413" t="inlineStr"/>
       <c r="AH413" t="inlineStr"/>
@@ -59360,15 +59360,15 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE414" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE414" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF414" t="inlineStr">
         <is>
           <t>https://www.horuta.co.il/</t>
         </is>
-      </c>
-      <c r="AF414" t="n">
-        <v>1</v>
       </c>
       <c r="AG414" t="inlineStr"/>
       <c r="AH414" t="inlineStr"/>
@@ -59507,15 +59507,15 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE415" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE415" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF415" t="inlineStr">
         <is>
           <t>https://www.efratkeidar.co.il/sleep-consultant/</t>
         </is>
-      </c>
-      <c r="AF415" t="n">
-        <v>1</v>
       </c>
       <c r="AG415" t="inlineStr"/>
       <c r="AH415" t="inlineStr"/>
@@ -59656,15 +59656,15 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE416" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE416" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF416" t="inlineStr">
         <is>
           <t>https://medixlife.co.il/our_team/%D7%93%D7%A8-%D7%A2%D7%93%D7%99-%D7%A0%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF416" t="n">
-        <v>1</v>
       </c>
       <c r="AG416" t="inlineStr"/>
       <c r="AH416" t="inlineStr"/>
@@ -59795,15 +59795,15 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE417" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE417" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF417" t="inlineStr">
         <is>
           <t>https://promo.dietangel.co.il/</t>
         </is>
-      </c>
-      <c r="AF417" t="n">
-        <v>1</v>
       </c>
       <c r="AG417" t="inlineStr"/>
       <c r="AH417" t="inlineStr"/>
@@ -59944,15 +59944,15 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE418" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE418" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF418" t="inlineStr">
         <is>
           <t>https://www.linealba.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%9E%D7%98%D7%A4%D7%9C/%D7%93-%D7%A8-%D7%92%D7%99%D7%90-%D7%A2%D7%99%D7%9C%D7%9D</t>
         </is>
-      </c>
-      <c r="AF418" t="n">
-        <v>1</v>
       </c>
       <c r="AG418" t="inlineStr"/>
       <c r="AH418" t="inlineStr"/>
@@ -60093,15 +60093,15 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>19665504</v>
-      </c>
-      <c r="AE419" t="inlineStr">
+        <v>58996512</v>
+      </c>
+      <c r="AE419" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF419" t="inlineStr">
         <is>
           <t>https://www.myavne.co.il/%D7%94%D7%A8%D7%95%D7%A4%D7%90-%D7%94%D7%9E%D7%A1%D7%95%D7%A8-%D7%A9%D7%9C-%D7%94%D7%9E%D7%93%D7%99%D7%A0%D7%94--%D7%93--%D7%A8-%D7%94%D7%99%D7%9C%D7%94-%D7%A9%D7%9E%D7%95%D7%9C-%D7%9B%D7%A5-%D7%9E%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%9B%D7%9C%D7%9C%D7%99%D7%AA-%D7%99%D7%91%D7%A0%D7%94-%D7%94%D7%99%D7%A8%D7%95%D7%A7%D7%94</t>
         </is>
-      </c>
-      <c r="AF419" t="n">
-        <v>1</v>
       </c>
       <c r="AG419" t="inlineStr"/>
       <c r="AH419" t="inlineStr"/>
@@ -60242,15 +60242,15 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>19193358</v>
-      </c>
-      <c r="AE420" t="inlineStr">
+        <v>57580074</v>
+      </c>
+      <c r="AE420" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF420" t="inlineStr">
         <is>
           <t>https://biz.tovm.org/business/5540/</t>
         </is>
-      </c>
-      <c r="AF420" t="n">
-        <v>1</v>
       </c>
       <c r="AG420" t="inlineStr"/>
       <c r="AH420" t="inlineStr"/>
@@ -60389,15 +60389,15 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE421" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE421" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF421" t="inlineStr">
         <is>
           <t>https://www.therapwiz.co.il/tdetails/?id=290</t>
         </is>
-      </c>
-      <c r="AF421" t="n">
-        <v>1</v>
       </c>
       <c r="AG421" t="inlineStr"/>
       <c r="AH421" t="inlineStr"/>
@@ -60538,15 +60538,15 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE422" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE422" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF422" t="inlineStr">
         <is>
           <t>https://www.sofia-medical.com/%D7%94%D7%A6%D7%95%D7%95%D7%AA/%D7%93-%D7%A8-%D7%9E%D7%95%D7%90%D7%9E%D7%9F-%D7%97%D7%98%D7%99%D7%91</t>
         </is>
-      </c>
-      <c r="AF422" t="n">
-        <v>1</v>
       </c>
       <c r="AG422" t="inlineStr"/>
       <c r="AH422" t="inlineStr"/>
@@ -60687,15 +60687,15 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE423" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE423" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF423" t="inlineStr">
         <is>
           <t>https://hea-lth.co.il/family-medicine/</t>
         </is>
-      </c>
-      <c r="AF423" t="n">
-        <v>1</v>
       </c>
       <c r="AG423" t="inlineStr"/>
       <c r="AH423" t="inlineStr"/>
@@ -60834,15 +60834,15 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE424" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE424" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF424" t="inlineStr">
         <is>
           <t>https://www.mploy.co.il/job/search/%D7%9E%D7%A0%D7%94%D7%9C-%D7%9E%D7%A8%D7%A4%D7%90%D7%94</t>
         </is>
-      </c>
-      <c r="AF424" t="n">
-        <v>1</v>
       </c>
       <c r="AG424" t="inlineStr"/>
       <c r="AH424" t="inlineStr"/>
@@ -60973,15 +60973,15 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE425" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE425" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF425" t="inlineStr">
         <is>
           <t>https://be-doula.co.il/</t>
         </is>
-      </c>
-      <c r="AF425" t="n">
-        <v>1</v>
       </c>
       <c r="AG425" t="inlineStr"/>
       <c r="AH425" t="inlineStr"/>
@@ -61112,15 +61112,15 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE426" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE426" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF426" t="inlineStr">
         <is>
           <t>https://www.leidaschool.co.il/</t>
         </is>
-      </c>
-      <c r="AF426" t="n">
-        <v>2</v>
       </c>
       <c r="AG426" t="inlineStr"/>
       <c r="AH426" t="inlineStr"/>
@@ -61259,15 +61259,15 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE427" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE427" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF427" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
         </is>
-      </c>
-      <c r="AF427" t="n">
-        <v>5</v>
       </c>
       <c r="AG427" t="inlineStr"/>
       <c r="AH427" t="inlineStr"/>
@@ -61406,15 +61406,15 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE428" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE428" t="n">
+        <v>229</v>
+      </c>
+      <c r="AF428" t="inlineStr">
         <is>
           <t>https://ialp.org.il/lllisrael/</t>
         </is>
-      </c>
-      <c r="AF428" t="n">
-        <v>229</v>
       </c>
       <c r="AG428" t="inlineStr"/>
       <c r="AH428" t="inlineStr"/>
@@ -61545,15 +61545,15 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE429" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE429" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF429" t="inlineStr">
         <is>
           <t>https://sobada.co.il/practitioner/michal_rosen</t>
         </is>
-      </c>
-      <c r="AF429" t="n">
-        <v>1</v>
       </c>
       <c r="AG429" t="inlineStr"/>
       <c r="AH429" t="inlineStr"/>
@@ -61694,15 +61694,15 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE430" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE430" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF430" t="inlineStr">
         <is>
           <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
         </is>
-      </c>
-      <c r="AF430" t="n">
-        <v>4</v>
       </c>
       <c r="AG430" t="inlineStr"/>
       <c r="AH430" t="inlineStr"/>
@@ -61833,15 +61833,15 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE431" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE431" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF431" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/u/research-centers/womancenter/about/</t>
         </is>
-      </c>
-      <c r="AF431" t="n">
-        <v>1</v>
       </c>
       <c r="AG431" t="inlineStr"/>
       <c r="AH431" t="inlineStr"/>
@@ -61976,15 +61976,15 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE432" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE432" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF432" t="inlineStr">
         <is>
           <t>https://inhealthycompany.co.il/category/%D7%91%D7%9C%D7%95%D7%92-%D7%9E%D7%90%D7%9E%D7%A8%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF432" t="n">
-        <v>1</v>
       </c>
       <c r="AG432" t="inlineStr"/>
       <c r="AH432" t="inlineStr"/>
@@ -62115,15 +62115,15 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE433" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE433" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF433" t="inlineStr">
         <is>
           <t>https://balaolam.co.il/</t>
         </is>
-      </c>
-      <c r="AF433" t="n">
-        <v>2</v>
       </c>
       <c r="AG433" t="inlineStr"/>
       <c r="AH433" t="inlineStr"/>
@@ -62262,15 +62262,15 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE434" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE434" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF434" t="inlineStr">
         <is>
           <t>https://global-ivf.com/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF434" t="n">
-        <v>1</v>
       </c>
       <c r="AG434" t="inlineStr"/>
       <c r="AH434" t="inlineStr"/>
@@ -62409,15 +62409,15 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE435" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF435" t="inlineStr">
         <is>
           <t>https://www.kbria.co.il/product/%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%95%D7%9C%D7%99%D7%93%D7%94/</t>
         </is>
-      </c>
-      <c r="AF435" t="n">
-        <v>1</v>
       </c>
       <c r="AG435" t="inlineStr"/>
       <c r="AH435" t="inlineStr"/>
@@ -62548,15 +62548,15 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE436" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF436" t="inlineStr">
         <is>
           <t>https://myotonic.co.il/pregnancy</t>
         </is>
-      </c>
-      <c r="AF436" t="n">
-        <v>1</v>
       </c>
       <c r="AG436" t="inlineStr"/>
       <c r="AH436" t="inlineStr"/>
@@ -62687,15 +62687,15 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE437" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF437" t="inlineStr">
         <is>
           <t>https://www.greenfertility.co.il/</t>
         </is>
-      </c>
-      <c r="AF437" t="n">
-        <v>1</v>
       </c>
       <c r="AG437" t="inlineStr"/>
       <c r="AH437" t="inlineStr"/>
@@ -62836,15 +62836,15 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE438" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF438" t="inlineStr">
         <is>
           <t>https://www.reshet-yeruka.net/youth/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%95%D7%A8%D7%99%D7%9D-%D7%9C%D7%92%D7%93%D7%9C-%D7%91%D7%A0%D7%97%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF438" t="n">
-        <v>1</v>
       </c>
       <c r="AG438" t="inlineStr"/>
       <c r="AH438" t="inlineStr"/>
@@ -62985,15 +62985,15 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE439" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF439" t="inlineStr">
         <is>
           <t>https://www.reshet-yeruka.net/youth/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%95%D7%A8%D7%99%D7%9D-%D7%9C%D7%92%D7%93%D7%9C-%D7%91%D7%A0%D7%97%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF439" t="n">
-        <v>1</v>
       </c>
       <c r="AG439" t="inlineStr"/>
       <c r="AH439" t="inlineStr"/>
@@ -63134,15 +63134,15 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE440" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF440" t="inlineStr">
         <is>
           <t>https://www.reshet-yeruka.net/youth/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%95%D7%A8%D7%99%D7%9D-%D7%9C%D7%92%D7%93%D7%9C-%D7%91%D7%A0%D7%97%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF440" t="n">
-        <v>1</v>
       </c>
       <c r="AG440" t="inlineStr"/>
       <c r="AH440" t="inlineStr"/>
@@ -63281,15 +63281,15 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE441" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF441" t="inlineStr">
         <is>
           <t>https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/</t>
         </is>
-      </c>
-      <c r="AF441" t="n">
-        <v>1</v>
       </c>
       <c r="AG441" t="inlineStr"/>
       <c r="AH441" t="inlineStr"/>
@@ -63424,15 +63424,15 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE442" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF442" t="inlineStr">
         <is>
           <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
         </is>
-      </c>
-      <c r="AF442" t="n">
-        <v>3</v>
       </c>
       <c r="AG442" t="inlineStr"/>
       <c r="AH442" t="inlineStr"/>
@@ -63574,15 +63574,15 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE443" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF443" t="inlineStr">
         <is>
           <t>https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/</t>
         </is>
-      </c>
-      <c r="AF443" t="n">
-        <v>1</v>
       </c>
       <c r="AG443" t="inlineStr"/>
       <c r="AH443" t="inlineStr"/>
@@ -63713,15 +63713,15 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE444" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF444" t="inlineStr">
         <is>
           <t>https://mssociety.org.il/category/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%98%D7%A8%D7%A9%D7%AA-%D7%A0%D7%A4%D7%95%D7%A6%D7%94/%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%9C%D7%99%D7%93%D7%94-%D7%95%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
-      </c>
-      <c r="AF444" t="n">
-        <v>1</v>
       </c>
       <c r="AG444" t="inlineStr"/>
       <c r="AH444" t="inlineStr"/>
@@ -63848,15 +63848,15 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE445" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF445" t="inlineStr">
         <is>
           <t>https://find.midwives.org.il/</t>
         </is>
-      </c>
-      <c r="AF445" t="n">
-        <v>1</v>
       </c>
       <c r="AG445" t="inlineStr"/>
       <c r="AH445" t="inlineStr"/>
@@ -63987,15 +63987,15 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE446" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF446" t="inlineStr">
         <is>
           <t>https://www.briah.org/team</t>
         </is>
-      </c>
-      <c r="AF446" t="n">
-        <v>1</v>
       </c>
       <c r="AG446" t="inlineStr"/>
       <c r="AH446" t="inlineStr"/>
@@ -64126,15 +64126,15 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE447" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF447" t="inlineStr">
         <is>
           <t>https://www.briah.org/team</t>
         </is>
-      </c>
-      <c r="AF447" t="n">
-        <v>1</v>
       </c>
       <c r="AG447" t="inlineStr"/>
       <c r="AH447" t="inlineStr"/>
@@ -64265,15 +64265,15 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE448" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF448" t="inlineStr">
         <is>
           <t>https://www.briah.org/team</t>
         </is>
-      </c>
-      <c r="AF448" t="n">
-        <v>1</v>
       </c>
       <c r="AG448" t="inlineStr"/>
       <c r="AH448" t="inlineStr"/>
@@ -64404,15 +64404,15 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE449" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF449" t="inlineStr">
         <is>
           <t>https://puah.org.il/%D7%A7%D7%91%D7%95%D7%A6%D7%95%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%9C%D7%A0%D7%A9%D7%99%D7%9D-%D7%9E%D7%90%D7%95%D7%AA%D7%92%D7%A8%D7%95%D7%AA-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF449" t="n">
-        <v>1</v>
       </c>
       <c r="AG449" t="inlineStr"/>
       <c r="AH449" t="inlineStr"/>
@@ -64551,15 +64551,15 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE450" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE450" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF450" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/mamy-lis/courses/courses-parents/antenatal-classes/</t>
         </is>
-      </c>
-      <c r="AF450" t="n">
-        <v>1</v>
       </c>
       <c r="AG450" t="inlineStr"/>
       <c r="AH450" t="inlineStr"/>
@@ -64700,15 +64700,15 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE451" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE451" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF451" t="inlineStr">
         <is>
           <t>https://www.ipts.org.il/?CategoryID=471&amp;ArticleID=2165</t>
         </is>
-      </c>
-      <c r="AF451" t="n">
-        <v>1</v>
       </c>
       <c r="AG451" t="inlineStr"/>
       <c r="AH451" t="inlineStr"/>
@@ -64849,15 +64849,15 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE452" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE452" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF452" t="inlineStr">
         <is>
           <t>https://www.ipts.org.il/?CategoryID=471&amp;ArticleID=2165</t>
         </is>
-      </c>
-      <c r="AF452" t="n">
-        <v>1</v>
       </c>
       <c r="AG452" t="inlineStr"/>
       <c r="AH452" t="inlineStr"/>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>62237646</v>
+        <v>186712938</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>86270589</v>
+        <v>258811767</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE10" t="n">
         <v>3</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>76704651</v>
+        <v>230113953</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>62237646</v>
+        <v>186712938</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>62237646</v>
+        <v>186712938</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>58989951</v>
+        <v>176969853</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>57579336</v>
+        <v>172738008</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>57579336</v>
+        <v>172738008</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>57579336</v>
+        <v>172738008</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>57574962</v>
+        <v>172724886</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>71804313</v>
+        <v>215412939</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>57574962</v>
+        <v>172724886</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE80" t="n">
         <v>5</v>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE85" t="n">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE90" t="n">
         <v>8</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE92" t="n">
         <v>11</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14373,7 +14373,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE96" t="n">
         <v>3</v>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>76704651</v>
+        <v>230113953</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE102" t="n">
         <v>3</v>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE103" t="n">
         <v>17</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE106" t="n">
         <v>4</v>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16523,7 +16523,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE116" t="n">
         <v>8</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -17655,7 +17655,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18092,7 +18092,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -18688,7 +18688,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -18837,7 +18837,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -18986,7 +18986,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -19568,7 +19568,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>62237646</v>
+        <v>186712938</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -19866,7 +19866,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20015,7 +20015,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20438,7 +20438,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20994,7 +20994,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21133,7 +21133,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21272,7 +21272,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21550,7 +21550,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22245,7 +22245,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22523,7 +22523,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22662,7 +22662,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22801,7 +22801,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22940,7 +22940,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23218,7 +23218,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24052,7 +24052,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24191,7 +24191,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24330,7 +24330,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24747,7 +24747,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25164,7 +25164,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25442,7 +25442,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25581,7 +25581,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25859,7 +25859,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26554,7 +26554,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26971,7 +26971,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27249,7 +27249,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27527,7 +27527,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27666,7 +27666,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27805,7 +27805,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27944,7 +27944,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28083,7 +28083,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28222,7 +28222,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28639,7 +28639,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28778,7 +28778,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28917,7 +28917,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29195,7 +29195,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29334,7 +29334,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29473,7 +29473,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29612,7 +29612,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -29751,7 +29751,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29890,7 +29890,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30029,7 +30029,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30168,7 +30168,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30307,7 +30307,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30446,7 +30446,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -30724,7 +30724,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -30863,7 +30863,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31002,7 +31002,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31141,7 +31141,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31280,7 +31280,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31419,7 +31419,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -31697,7 +31697,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31975,7 +31975,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32253,7 +32253,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32392,7 +32392,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32531,7 +32531,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32809,7 +32809,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32948,7 +32948,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33087,7 +33087,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33226,7 +33226,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33365,7 +33365,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33782,7 +33782,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33921,7 +33921,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34199,7 +34199,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34338,7 +34338,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -34616,7 +34616,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -34755,7 +34755,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34894,7 +34894,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35033,7 +35033,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35172,7 +35172,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35311,7 +35311,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35450,7 +35450,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -35589,7 +35589,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -35728,7 +35728,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -35867,7 +35867,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36145,7 +36145,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -36284,7 +36284,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36423,7 +36423,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -36562,7 +36562,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -36701,7 +36701,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -36840,7 +36840,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -36979,7 +36979,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -37118,7 +37118,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -37257,7 +37257,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -37396,7 +37396,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -37674,7 +37674,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -37813,7 +37813,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -37952,7 +37952,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -38091,7 +38091,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -38230,7 +38230,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -38369,7 +38369,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -38508,7 +38508,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -38647,7 +38647,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -38786,7 +38786,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -38925,7 +38925,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -39203,7 +39203,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -39342,7 +39342,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -39481,7 +39481,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -39620,7 +39620,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -39759,7 +39759,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -40037,7 +40037,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -40176,7 +40176,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -40315,7 +40315,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -41010,7 +41010,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -41149,7 +41149,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -41427,7 +41427,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -41566,7 +41566,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -41705,7 +41705,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -41983,7 +41983,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -42400,7 +42400,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -42539,7 +42539,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -42678,7 +42678,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -42817,7 +42817,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -42956,7 +42956,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -43095,7 +43095,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -43373,7 +43373,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -43512,7 +43512,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -43790,7 +43790,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -43929,7 +43929,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -44068,7 +44068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -44346,7 +44346,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -44485,7 +44485,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -44763,7 +44763,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -44902,7 +44902,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE313" t="n">
         <v>3</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -45180,7 +45180,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -45319,7 +45319,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -45458,7 +45458,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE317" t="n">
         <v>3</v>
@@ -45597,7 +45597,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -45736,7 +45736,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -45875,7 +45875,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -46153,7 +46153,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -46292,7 +46292,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -46431,7 +46431,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -46570,7 +46570,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -46709,7 +46709,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -46848,7 +46848,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -46987,7 +46987,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -47126,7 +47126,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -47265,7 +47265,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -47682,7 +47682,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -47821,7 +47821,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -47960,7 +47960,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -48099,7 +48099,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -48238,7 +48238,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -48377,7 +48377,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -48516,7 +48516,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -48655,7 +48655,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -48794,7 +48794,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -48943,7 +48943,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>58996512</v>
+        <v>176989536</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -49088,7 +49088,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>71745264</v>
+        <v>215235792</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -49366,7 +49366,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -49505,7 +49505,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -49644,7 +49644,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -49791,7 +49791,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE348" t="n">
         <v>2</v>
@@ -49930,7 +49930,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -50069,7 +50069,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -50208,7 +50208,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -50357,7 +50357,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -50496,7 +50496,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -50635,7 +50635,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -50782,7 +50782,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -50930,7 +50930,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -51069,7 +51069,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -51208,7 +51208,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -51355,7 +51355,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -51494,7 +51494,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE360" t="n">
         <v>2</v>
@@ -51643,7 +51643,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>58996512</v>
+        <v>176989536</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -51792,7 +51792,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -51937,7 +51937,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -52086,7 +52086,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -52225,7 +52225,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -52374,7 +52374,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -52523,7 +52523,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -52672,7 +52672,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -52819,7 +52819,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -52964,7 +52964,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>57416040</v>
+        <v>172248120</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -53109,7 +53109,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>57416040</v>
+        <v>172248120</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -53254,7 +53254,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>57416040</v>
+        <v>172248120</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -53393,7 +53393,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -53538,7 +53538,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>71745264</v>
+        <v>215235792</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -53685,7 +53685,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -53834,7 +53834,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -53973,7 +53973,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -54108,7 +54108,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -54247,7 +54247,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -54386,7 +54386,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -54535,7 +54535,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -54674,7 +54674,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -54813,7 +54813,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -54948,7 +54948,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -55093,7 +55093,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -55238,7 +55238,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -55383,7 +55383,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -55532,7 +55532,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -55681,7 +55681,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -55830,7 +55830,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -55979,7 +55979,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>58996512</v>
+        <v>176989536</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -56128,7 +56128,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE392" t="n">
         <v>5</v>
@@ -56277,7 +56277,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -56424,7 +56424,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -56573,7 +56573,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -56871,7 +56871,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -57010,7 +57010,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -57159,7 +57159,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -57298,7 +57298,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -57450,7 +57450,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -57599,7 +57599,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -57748,7 +57748,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -57897,7 +57897,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -58046,7 +58046,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -58186,7 +58186,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -58325,7 +58325,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE407" t="n">
         <v>2</v>
@@ -58474,7 +58474,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -58619,7 +58619,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -58768,7 +58768,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -58917,7 +58917,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>72275976</v>
+        <v>216827928</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -59064,7 +59064,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -59213,7 +59213,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -59360,7 +59360,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -59507,7 +59507,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -59795,7 +59795,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -59944,7 +59944,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -60093,7 +60093,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>58996512</v>
+        <v>176989536</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -60242,7 +60242,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>57580074</v>
+        <v>172740222</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -60389,7 +60389,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -60538,7 +60538,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -60687,7 +60687,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -60973,7 +60973,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -61112,7 +61112,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE426" t="n">
         <v>2</v>
@@ -61259,7 +61259,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE427" t="n">
         <v>5</v>
@@ -61406,7 +61406,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE428" t="n">
         <v>229</v>
@@ -61545,7 +61545,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -61694,7 +61694,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE430" t="n">
         <v>4</v>
@@ -61833,7 +61833,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -61976,7 +61976,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -62115,7 +62115,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE433" t="n">
         <v>2</v>
@@ -62262,7 +62262,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -62409,7 +62409,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -62548,7 +62548,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -62687,7 +62687,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -62836,7 +62836,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -62985,7 +62985,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -63134,7 +63134,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -63281,7 +63281,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -63424,7 +63424,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE442" t="n">
         <v>3</v>
@@ -63574,7 +63574,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE443" t="n">
         <v>1</v>
@@ -63713,7 +63713,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -63848,7 +63848,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -63987,7 +63987,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -64126,7 +64126,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -64265,7 +64265,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -64404,7 +64404,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -64551,7 +64551,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -64700,7 +64700,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -64849,7 +64849,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>186712938</v>
+        <v>560138814</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>258811767</v>
+        <v>776435301</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE10" t="n">
         <v>3</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>230113953</v>
+        <v>690341859</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>186712938</v>
+        <v>560138814</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>186712938</v>
+        <v>560138814</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>176969853</v>
+        <v>530909559</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>172738008</v>
+        <v>518214024</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>172738008</v>
+        <v>518214024</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>172738008</v>
+        <v>518214024</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>172724886</v>
+        <v>518174658</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>215412939</v>
+        <v>646238817</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>172724886</v>
+        <v>518174658</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE80" t="n">
         <v>5</v>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE85" t="n">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE90" t="n">
         <v>8</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE92" t="n">
         <v>11</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14373,7 +14373,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE96" t="n">
         <v>3</v>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>230113953</v>
+        <v>690341859</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE102" t="n">
         <v>3</v>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE103" t="n">
         <v>17</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE106" t="n">
         <v>4</v>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16523,7 +16523,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE116" t="n">
         <v>8</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -17655,7 +17655,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18092,7 +18092,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -18688,7 +18688,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -18837,7 +18837,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -18986,7 +18986,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -19568,7 +19568,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>186712938</v>
+        <v>560138814</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -19866,7 +19866,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20015,7 +20015,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20438,7 +20438,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20994,7 +20994,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21133,7 +21133,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21272,7 +21272,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21550,7 +21550,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22245,7 +22245,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22523,7 +22523,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22662,7 +22662,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22801,7 +22801,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22940,7 +22940,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23218,7 +23218,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24052,7 +24052,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24191,7 +24191,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24330,7 +24330,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24747,7 +24747,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25164,7 +25164,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25442,7 +25442,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25581,7 +25581,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25859,7 +25859,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26554,7 +26554,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26971,7 +26971,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27249,7 +27249,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27527,7 +27527,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27666,7 +27666,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27805,7 +27805,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27944,7 +27944,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28083,7 +28083,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28222,7 +28222,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28639,7 +28639,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28778,7 +28778,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28917,7 +28917,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29195,7 +29195,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29334,7 +29334,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29473,7 +29473,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29612,7 +29612,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -29751,7 +29751,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29890,7 +29890,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30029,7 +30029,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30168,7 +30168,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30307,7 +30307,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30446,7 +30446,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -30724,7 +30724,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -30863,7 +30863,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31002,7 +31002,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31141,7 +31141,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31280,7 +31280,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31419,7 +31419,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -31697,7 +31697,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31975,7 +31975,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32253,7 +32253,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32392,7 +32392,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32531,7 +32531,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32809,7 +32809,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32948,7 +32948,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33087,7 +33087,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33226,7 +33226,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33365,7 +33365,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33782,7 +33782,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33921,7 +33921,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34199,7 +34199,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34338,7 +34338,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -34616,7 +34616,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -34755,7 +34755,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34894,7 +34894,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35033,7 +35033,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35172,7 +35172,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35311,7 +35311,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35450,7 +35450,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -35589,7 +35589,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -35728,7 +35728,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -35867,7 +35867,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36145,7 +36145,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -36284,7 +36284,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36423,7 +36423,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -36562,7 +36562,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -36701,7 +36701,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -36840,7 +36840,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -36979,7 +36979,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -37118,7 +37118,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -37257,7 +37257,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -37396,7 +37396,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -37674,7 +37674,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -37813,7 +37813,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -37952,7 +37952,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -38091,7 +38091,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -38230,7 +38230,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -38369,7 +38369,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -38508,7 +38508,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -38647,7 +38647,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -38786,7 +38786,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -38925,7 +38925,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -39203,7 +39203,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -39342,7 +39342,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -39481,7 +39481,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -39620,7 +39620,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -39759,7 +39759,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -40037,7 +40037,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -40176,7 +40176,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -40315,7 +40315,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -41010,7 +41010,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -41149,7 +41149,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -41427,7 +41427,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -41566,7 +41566,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -41705,7 +41705,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -41983,7 +41983,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -42400,7 +42400,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -42539,7 +42539,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -42678,7 +42678,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -42817,7 +42817,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -42956,7 +42956,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -43095,7 +43095,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -43373,7 +43373,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -43512,7 +43512,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -43790,7 +43790,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -43929,7 +43929,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -44068,7 +44068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -44346,7 +44346,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -44485,7 +44485,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -44763,7 +44763,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -44902,7 +44902,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE313" t="n">
         <v>3</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -45180,7 +45180,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -45319,7 +45319,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -45458,7 +45458,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE317" t="n">
         <v>3</v>
@@ -45597,7 +45597,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -45736,7 +45736,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -45875,7 +45875,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -46153,7 +46153,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -46292,7 +46292,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -46431,7 +46431,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -46570,7 +46570,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -46709,7 +46709,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -46848,7 +46848,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -46987,7 +46987,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -47126,7 +47126,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -47265,7 +47265,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -47682,7 +47682,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -47821,7 +47821,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -47960,7 +47960,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -48099,7 +48099,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -48238,7 +48238,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -48377,7 +48377,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -48516,7 +48516,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -48655,7 +48655,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -48794,7 +48794,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -48943,7 +48943,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>176989536</v>
+        <v>530968608</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -49088,7 +49088,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>215235792</v>
+        <v>645707376</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -49366,7 +49366,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -49505,7 +49505,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -49644,7 +49644,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -49791,7 +49791,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE348" t="n">
         <v>2</v>
@@ -49930,7 +49930,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -50069,7 +50069,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -50208,7 +50208,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -50357,7 +50357,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -50496,7 +50496,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -50635,7 +50635,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -50782,7 +50782,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -50930,7 +50930,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -51069,7 +51069,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -51208,7 +51208,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -51355,7 +51355,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -51494,7 +51494,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE360" t="n">
         <v>2</v>
@@ -51643,7 +51643,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>176989536</v>
+        <v>530968608</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -51792,7 +51792,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -51937,7 +51937,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -52086,7 +52086,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -52225,7 +52225,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -52374,7 +52374,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -52523,7 +52523,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -52672,7 +52672,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -52819,7 +52819,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -52964,7 +52964,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>172248120</v>
+        <v>516744360</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -53109,7 +53109,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>172248120</v>
+        <v>516744360</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -53254,7 +53254,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>172248120</v>
+        <v>516744360</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -53393,7 +53393,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -53538,7 +53538,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>215235792</v>
+        <v>645707376</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -53685,7 +53685,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -53834,7 +53834,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -53973,7 +53973,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -54108,7 +54108,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -54247,7 +54247,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -54386,7 +54386,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -54535,7 +54535,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -54674,7 +54674,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -54813,7 +54813,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -54948,7 +54948,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -55093,7 +55093,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -55238,7 +55238,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -55383,7 +55383,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -55532,7 +55532,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -55681,7 +55681,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -55830,7 +55830,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -55979,7 +55979,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>176989536</v>
+        <v>530968608</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -56128,7 +56128,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE392" t="n">
         <v>5</v>
@@ -56277,7 +56277,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -56424,7 +56424,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -56573,7 +56573,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -56871,7 +56871,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -57010,7 +57010,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -57159,7 +57159,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -57298,7 +57298,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -57450,7 +57450,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -57599,7 +57599,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -57748,7 +57748,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -57897,7 +57897,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -58046,7 +58046,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -58186,7 +58186,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -58325,7 +58325,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE407" t="n">
         <v>2</v>
@@ -58474,7 +58474,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -58619,7 +58619,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -58768,7 +58768,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -58917,7 +58917,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>216827928</v>
+        <v>650483784</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -59064,7 +59064,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -59213,7 +59213,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -59360,7 +59360,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -59507,7 +59507,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -59795,7 +59795,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -59944,7 +59944,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -60093,7 +60093,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>176989536</v>
+        <v>530968608</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -60242,7 +60242,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>172740222</v>
+        <v>518220666</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -60389,7 +60389,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -60538,7 +60538,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -60687,7 +60687,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -60973,7 +60973,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -61112,7 +61112,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE426" t="n">
         <v>2</v>
@@ -61259,7 +61259,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE427" t="n">
         <v>5</v>
@@ -61406,7 +61406,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE428" t="n">
         <v>229</v>
@@ -61545,7 +61545,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -61694,7 +61694,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE430" t="n">
         <v>4</v>
@@ -61833,7 +61833,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -61976,7 +61976,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -62115,7 +62115,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE433" t="n">
         <v>2</v>
@@ -62262,7 +62262,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -62409,7 +62409,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -62548,7 +62548,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -62687,7 +62687,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -62836,7 +62836,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -62985,7 +62985,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -63134,7 +63134,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -63281,7 +63281,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -63424,7 +63424,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE442" t="n">
         <v>3</v>
@@ -63574,7 +63574,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE443" t="n">
         <v>1</v>
@@ -63713,7 +63713,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -63848,7 +63848,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -63987,7 +63987,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -64126,7 +64126,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -64265,7 +64265,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -64404,7 +64404,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -64551,7 +64551,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -64700,7 +64700,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -64849,7 +64849,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>560138814</v>
+        <v>1680416442</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>776435301</v>
+        <v>2329305903</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE10" t="n">
         <v>3</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>690341859</v>
+        <v>2071025577</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>560138814</v>
+        <v>1680416442</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>560138814</v>
+        <v>1680416442</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>530909559</v>
+        <v>1592728677</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>518214024</v>
+        <v>1554642072</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>518214024</v>
+        <v>1554642072</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>518214024</v>
+        <v>1554642072</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>518174658</v>
+        <v>1554523974</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>646238817</v>
+        <v>1938716451</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>518174658</v>
+        <v>1554523974</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE80" t="n">
         <v>5</v>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE85" t="n">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE90" t="n">
         <v>8</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE92" t="n">
         <v>11</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14373,7 +14373,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE96" t="n">
         <v>3</v>
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>690341859</v>
+        <v>2071025577</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE102" t="n">
         <v>3</v>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE103" t="n">
         <v>17</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE106" t="n">
         <v>4</v>
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16523,7 +16523,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE116" t="n">
         <v>8</v>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -17655,7 +17655,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18092,7 +18092,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -18688,7 +18688,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -18837,7 +18837,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -18986,7 +18986,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -19419,7 +19419,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -19568,7 +19568,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>560138814</v>
+        <v>1680416442</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -19866,7 +19866,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20015,7 +20015,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20438,7 +20438,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20994,7 +20994,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21133,7 +21133,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21272,7 +21272,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21550,7 +21550,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22245,7 +22245,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22523,7 +22523,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22662,7 +22662,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22801,7 +22801,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22940,7 +22940,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23218,7 +23218,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24052,7 +24052,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24191,7 +24191,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24330,7 +24330,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24747,7 +24747,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25164,7 +25164,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25442,7 +25442,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25581,7 +25581,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25859,7 +25859,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26554,7 +26554,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26971,7 +26971,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27249,7 +27249,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27527,7 +27527,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27666,7 +27666,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27805,7 +27805,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27944,7 +27944,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28083,7 +28083,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28222,7 +28222,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28639,7 +28639,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28778,7 +28778,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28917,7 +28917,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29195,7 +29195,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29334,7 +29334,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29473,7 +29473,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29612,7 +29612,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -29751,7 +29751,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29890,7 +29890,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30029,7 +30029,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30168,7 +30168,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30307,7 +30307,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30446,7 +30446,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -30724,7 +30724,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -30863,7 +30863,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31002,7 +31002,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31141,7 +31141,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31280,7 +31280,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31419,7 +31419,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31558,7 +31558,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -31697,7 +31697,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31975,7 +31975,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32253,7 +32253,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32392,7 +32392,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32531,7 +32531,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32809,7 +32809,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32948,7 +32948,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33087,7 +33087,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33226,7 +33226,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33365,7 +33365,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33782,7 +33782,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33921,7 +33921,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34060,7 +34060,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34199,7 +34199,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34338,7 +34338,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -34616,7 +34616,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -34755,7 +34755,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34894,7 +34894,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35033,7 +35033,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35172,7 +35172,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35311,7 +35311,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35450,7 +35450,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -35589,7 +35589,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -35728,7 +35728,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -35867,7 +35867,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36145,7 +36145,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -36284,7 +36284,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36423,7 +36423,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -36562,7 +36562,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -36701,7 +36701,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -36840,7 +36840,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -36979,7 +36979,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -37118,7 +37118,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -37257,7 +37257,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -37396,7 +37396,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -37674,7 +37674,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -37813,7 +37813,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -37952,7 +37952,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -38091,7 +38091,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -38230,7 +38230,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -38369,7 +38369,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -38508,7 +38508,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -38647,7 +38647,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -38786,7 +38786,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -38925,7 +38925,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -39203,7 +39203,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -39342,7 +39342,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -39481,7 +39481,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -39620,7 +39620,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -39759,7 +39759,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -40037,7 +40037,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -40176,7 +40176,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -40315,7 +40315,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -40454,7 +40454,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -41010,7 +41010,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -41149,7 +41149,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -41427,7 +41427,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -41566,7 +41566,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -41705,7 +41705,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -41983,7 +41983,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -42400,7 +42400,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -42539,7 +42539,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -42678,7 +42678,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -42817,7 +42817,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -42956,7 +42956,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -43095,7 +43095,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -43234,7 +43234,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -43373,7 +43373,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -43512,7 +43512,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -43790,7 +43790,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -43929,7 +43929,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -44068,7 +44068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -44346,7 +44346,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -44485,7 +44485,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -44763,7 +44763,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -44902,7 +44902,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE313" t="n">
         <v>3</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -45180,7 +45180,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -45319,7 +45319,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -45458,7 +45458,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE317" t="n">
         <v>3</v>
@@ -45597,7 +45597,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -45736,7 +45736,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -45875,7 +45875,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -46153,7 +46153,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -46292,7 +46292,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -46431,7 +46431,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -46570,7 +46570,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -46709,7 +46709,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -46848,7 +46848,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -46987,7 +46987,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -47126,7 +47126,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -47265,7 +47265,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -47682,7 +47682,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -47821,7 +47821,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -47960,7 +47960,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -48099,7 +48099,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -48238,7 +48238,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -48377,7 +48377,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -48516,7 +48516,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -48655,7 +48655,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -48794,7 +48794,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -48943,7 +48943,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>530968608</v>
+        <v>1592905824</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -49088,7 +49088,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>645707376</v>
+        <v>1937122128</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -49366,7 +49366,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -49505,7 +49505,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -49644,7 +49644,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -49791,7 +49791,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE348" t="n">
         <v>2</v>
@@ -49930,7 +49930,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -50069,7 +50069,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -50208,7 +50208,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -50357,7 +50357,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -50496,7 +50496,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -50635,7 +50635,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -50782,7 +50782,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -50930,7 +50930,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -51069,7 +51069,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -51208,7 +51208,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -51355,7 +51355,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -51494,7 +51494,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE360" t="n">
         <v>2</v>
@@ -51643,7 +51643,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>530968608</v>
+        <v>1592905824</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -51792,7 +51792,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -51937,7 +51937,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -52086,7 +52086,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -52225,7 +52225,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -52374,7 +52374,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -52523,7 +52523,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -52672,7 +52672,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -52819,7 +52819,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -52964,7 +52964,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>516744360</v>
+        <v>1550233080</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -53109,7 +53109,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>516744360</v>
+        <v>1550233080</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -53254,7 +53254,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>516744360</v>
+        <v>1550233080</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -53393,7 +53393,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -53538,7 +53538,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>645707376</v>
+        <v>1937122128</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -53685,7 +53685,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -53834,7 +53834,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -53973,7 +53973,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -54108,7 +54108,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -54247,7 +54247,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -54386,7 +54386,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -54535,7 +54535,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -54674,7 +54674,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -54813,7 +54813,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -54948,7 +54948,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -55093,7 +55093,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -55238,7 +55238,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -55383,7 +55383,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -55532,7 +55532,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -55681,7 +55681,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -55830,7 +55830,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -55979,7 +55979,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>530968608</v>
+        <v>1592905824</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -56128,7 +56128,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE392" t="n">
         <v>5</v>
@@ -56277,7 +56277,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -56424,7 +56424,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -56573,7 +56573,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -56871,7 +56871,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -57010,7 +57010,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -57159,7 +57159,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -57298,7 +57298,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -57450,7 +57450,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -57599,7 +57599,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -57748,7 +57748,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -57897,7 +57897,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -58046,7 +58046,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -58186,7 +58186,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -58325,7 +58325,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE407" t="n">
         <v>2</v>
@@ -58474,7 +58474,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -58619,7 +58619,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -58768,7 +58768,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -58917,7 +58917,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>650483784</v>
+        <v>1951451352</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -59064,7 +59064,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -59213,7 +59213,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -59360,7 +59360,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -59507,7 +59507,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -59795,7 +59795,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -59944,7 +59944,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -60093,7 +60093,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>530968608</v>
+        <v>1592905824</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -60242,7 +60242,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>518220666</v>
+        <v>1554661998</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -60389,7 +60389,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -60538,7 +60538,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -60687,7 +60687,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -60973,7 +60973,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -61112,7 +61112,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE426" t="n">
         <v>2</v>
@@ -61259,7 +61259,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE427" t="n">
         <v>5</v>
@@ -61406,7 +61406,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE428" t="n">
         <v>229</v>
@@ -61545,7 +61545,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -61694,7 +61694,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE430" t="n">
         <v>4</v>
@@ -61833,7 +61833,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -61976,7 +61976,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -62115,7 +62115,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE433" t="n">
         <v>2</v>
@@ -62262,7 +62262,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -62409,7 +62409,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -62548,7 +62548,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -62687,7 +62687,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -62836,7 +62836,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -62985,7 +62985,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -63134,7 +63134,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -63281,7 +63281,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -63424,7 +63424,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE442" t="n">
         <v>3</v>
@@ -63574,7 +63574,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE443" t="n">
         <v>1</v>
@@ -63713,7 +63713,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -63848,7 +63848,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -63987,7 +63987,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -64126,7 +64126,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -64265,7 +64265,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -64404,7 +64404,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -64551,7 +64551,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -64700,7 +64700,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -64849,7 +64849,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,217 +429,217 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>algo_version</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>physician_search_version</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>shared_target_count</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>unchanged_search_count</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_reason</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>search_fingerprint</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>resolution_reason</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>search_fingerprint</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>candidate_rank</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>shared_contact</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>send_eligible</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>personalization_safe</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -750,7 +762,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -905,7 +917,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>30247495956</v>
+        <v>90742487868</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -919,11 +931,11 @@
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
         <v>1</v>
@@ -1062,7 +1074,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>41927506254</v>
+        <v>125782518762</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1076,11 +1088,11 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AK4" t="b">
+        <v>0</v>
+      </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
         <v>1</v>
@@ -1219,7 +1231,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1233,11 +1245,11 @@
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AK5" t="b">
+        <v>0</v>
+      </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
         <v>1</v>
@@ -1376,7 +1388,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1390,11 +1402,11 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
         <v>1</v>
@@ -1533,7 +1545,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1547,11 +1559,11 @@
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
         <v>1</v>
@@ -1690,7 +1702,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1704,11 +1716,11 @@
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
         <v>1</v>
@@ -1848,7 +1860,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1862,11 +1874,11 @@
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+      <c r="AK9" t="b">
+        <v>0</v>
+      </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
         <v>1</v>
@@ -2003,7 +2015,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2158,7 +2170,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE11" t="n">
         <v>19</v>
@@ -2172,11 +2184,11 @@
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+      <c r="AK11" t="b">
+        <v>0</v>
+      </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
         <v>1</v>
@@ -2313,7 +2325,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2468,7 +2480,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2482,11 +2494,11 @@
         </is>
       </c>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+      <c r="AK13" t="b">
+        <v>0</v>
+      </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="n">
         <v>1</v>
@@ -2615,7 +2627,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2768,7 +2780,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE15" t="n">
         <v>17</v>
@@ -2922,7 +2934,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3067,7 +3079,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3212,7 +3224,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3365,7 +3377,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3519,7 +3531,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3674,7 +3686,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
@@ -3819,7 +3831,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -3968,7 +3980,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4121,7 +4133,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4266,7 +4278,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4411,7 +4423,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4556,7 +4568,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4711,7 +4723,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4725,11 +4737,11 @@
         </is>
       </c>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
+      <c r="AK28" t="b">
+        <v>0</v>
+      </c>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="n">
         <v>2</v>
@@ -4868,7 +4880,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -4882,11 +4894,11 @@
         </is>
       </c>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
+      <c r="AK29" t="b">
+        <v>0</v>
+      </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="n">
         <v>2</v>
@@ -5025,7 +5037,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5039,11 +5051,11 @@
         </is>
       </c>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
+      <c r="AK30" t="b">
+        <v>0</v>
+      </c>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="n">
         <v>1</v>
@@ -5182,7 +5194,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5196,11 +5208,11 @@
         </is>
       </c>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
+      <c r="AK31" t="b">
+        <v>0</v>
+      </c>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="n">
         <v>1</v>
@@ -5335,7 +5347,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5349,11 +5361,11 @@
         </is>
       </c>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
+      <c r="AK32" t="b">
+        <v>0</v>
+      </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
         <v>1</v>
@@ -5492,7 +5504,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5506,11 +5518,11 @@
         </is>
       </c>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
+      <c r="AK33" t="b">
+        <v>0</v>
+      </c>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="n">
         <v>1</v>
@@ -5649,7 +5661,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5663,11 +5675,11 @@
         </is>
       </c>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
+      <c r="AK34" t="b">
+        <v>0</v>
+      </c>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="n">
         <v>2</v>
@@ -5806,7 +5818,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5820,11 +5832,11 @@
         </is>
       </c>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
+      <c r="AK35" t="b">
+        <v>0</v>
+      </c>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="n">
         <v>1</v>
@@ -5963,7 +5975,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5977,11 +5989,11 @@
         </is>
       </c>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
+      <c r="AK36" t="b">
+        <v>0</v>
+      </c>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="n">
         <v>1</v>
@@ -6120,7 +6132,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6134,11 +6146,11 @@
         </is>
       </c>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
+      <c r="AK37" t="b">
+        <v>0</v>
+      </c>
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="n">
         <v>1</v>
@@ -6277,7 +6289,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6291,11 +6303,11 @@
         </is>
       </c>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
+      <c r="AK38" t="b">
+        <v>0</v>
+      </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="n">
         <v>1</v>
@@ -6434,7 +6446,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6448,11 +6460,11 @@
         </is>
       </c>
       <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
+      <c r="AK39" t="b">
+        <v>0</v>
+      </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="n">
         <v>1</v>
@@ -6591,7 +6603,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6605,11 +6617,11 @@
         </is>
       </c>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
+      <c r="AK40" t="b">
+        <v>0</v>
+      </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="n">
         <v>1</v>
@@ -6748,7 +6760,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6762,11 +6774,11 @@
         </is>
       </c>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
+      <c r="AK41" t="b">
+        <v>0</v>
+      </c>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="n">
         <v>1</v>
@@ -6905,7 +6917,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6919,11 +6931,11 @@
         </is>
       </c>
       <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
+      <c r="AK42" t="b">
+        <v>0</v>
+      </c>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="n">
         <v>1</v>
@@ -7058,7 +7070,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7072,11 +7084,11 @@
         </is>
       </c>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
+      <c r="AK43" t="b">
+        <v>0</v>
+      </c>
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="n">
         <v>2</v>
@@ -7215,7 +7227,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>37278460386</v>
+        <v>111835381158</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7229,11 +7241,11 @@
         </is>
       </c>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
+      <c r="AK44" t="b">
+        <v>0</v>
+      </c>
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="n">
         <v>1</v>
@@ -7372,7 +7384,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7386,11 +7398,11 @@
         </is>
       </c>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
+      <c r="AK45" t="b">
+        <v>0</v>
+      </c>
       <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="n">
         <v>1</v>
@@ -7529,7 +7541,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>30247495956</v>
+        <v>90742487868</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7543,11 +7555,11 @@
         </is>
       </c>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
+      <c r="AK46" t="b">
+        <v>0</v>
+      </c>
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="n">
         <v>1</v>
@@ -7686,7 +7698,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>30247495956</v>
+        <v>90742487868</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7700,11 +7712,11 @@
         </is>
       </c>
       <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
+      <c r="AK47" t="b">
+        <v>0</v>
+      </c>
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="n">
         <v>1</v>
@@ -7843,7 +7855,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7996,7 +8008,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8147,7 +8159,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8161,11 +8173,11 @@
         </is>
       </c>
       <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
+      <c r="AK50" t="b">
+        <v>0</v>
+      </c>
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="n">
         <v>1</v>
@@ -8304,7 +8316,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8318,11 +8330,11 @@
         </is>
       </c>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
+      <c r="AK51" t="b">
+        <v>0</v>
+      </c>
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="n">
         <v>2</v>
@@ -8461,7 +8473,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8475,11 +8487,11 @@
         </is>
       </c>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
+      <c r="AK52" t="b">
+        <v>0</v>
+      </c>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="n">
         <v>1</v>
@@ -8618,7 +8630,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8632,11 +8644,11 @@
         </is>
       </c>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
+      <c r="AK53" t="b">
+        <v>0</v>
+      </c>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="n">
         <v>2</v>
@@ -8775,7 +8787,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>28669116186</v>
+        <v>86007348558</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8789,11 +8801,11 @@
         </is>
       </c>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
+      <c r="AK54" t="b">
+        <v>0</v>
+      </c>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="n">
         <v>1</v>
@@ -8932,7 +8944,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8946,11 +8958,11 @@
         </is>
       </c>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
+      <c r="AK55" t="b">
+        <v>0</v>
+      </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="n">
         <v>1</v>
@@ -9075,7 +9087,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9216,7 +9228,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9357,7 +9369,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9512,7 +9524,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>27983557296</v>
+        <v>83950671888</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9526,11 +9538,11 @@
         </is>
       </c>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
+      <c r="AK59" t="b">
+        <v>0</v>
+      </c>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="n">
         <v>1</v>
@@ -9669,7 +9681,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>27983557296</v>
+        <v>83950671888</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9683,11 +9695,11 @@
         </is>
       </c>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
+      <c r="AK60" t="b">
+        <v>0</v>
+      </c>
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="n">
         <v>1</v>
@@ -9826,7 +9838,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>27983557296</v>
+        <v>83950671888</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9840,11 +9852,11 @@
         </is>
       </c>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AK61" t="b">
+        <v>0</v>
+      </c>
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="n">
         <v>1</v>
@@ -9983,7 +9995,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>27981431532</v>
+        <v>83944294596</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9997,11 +10009,11 @@
         </is>
       </c>
       <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
+      <c r="AK62" t="b">
+        <v>0</v>
+      </c>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="n">
         <v>1</v>
@@ -10141,7 +10153,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10155,11 +10167,11 @@
         </is>
       </c>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
+      <c r="AK63" t="b">
+        <v>0</v>
+      </c>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="n">
         <v>1</v>
@@ -10294,7 +10306,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10308,11 +10320,11 @@
         </is>
       </c>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
+      <c r="AK64" t="b">
+        <v>0</v>
+      </c>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="n">
         <v>1</v>
@@ -10447,7 +10459,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>34896896118</v>
+        <v>104690688354</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10602,7 +10614,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10616,11 +10628,11 @@
         </is>
       </c>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
+      <c r="AK66" t="b">
+        <v>0</v>
+      </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="n">
         <v>1</v>
@@ -10759,7 +10771,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10773,11 +10785,11 @@
         </is>
       </c>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
+      <c r="AK67" t="b">
+        <v>0</v>
+      </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="n">
         <v>1</v>
@@ -10916,7 +10928,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10930,11 +10942,11 @@
         </is>
       </c>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI68" t="inlineStr"/>
       <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
+      <c r="AK68" t="b">
+        <v>0</v>
+      </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="n">
         <v>1</v>
@@ -11073,7 +11085,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>27981431532</v>
+        <v>83944294596</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11087,11 +11099,11 @@
         </is>
       </c>
       <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr"/>
-      <c r="AK69" t="inlineStr"/>
+      <c r="AK69" t="b">
+        <v>0</v>
+      </c>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="n">
         <v>1</v>
@@ -11230,7 +11242,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11244,11 +11256,11 @@
         </is>
       </c>
       <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI70" t="inlineStr"/>
       <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr"/>
+      <c r="AK70" t="b">
+        <v>0</v>
+      </c>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="n">
         <v>1</v>
@@ -11387,7 +11399,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11401,11 +11413,11 @@
         </is>
       </c>
       <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI71" t="inlineStr"/>
       <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
+      <c r="AK71" t="b">
+        <v>0</v>
+      </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="n">
         <v>1</v>
@@ -11544,7 +11556,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11558,11 +11570,11 @@
         </is>
       </c>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI72" t="inlineStr"/>
       <c r="AJ72" t="inlineStr"/>
-      <c r="AK72" t="inlineStr"/>
+      <c r="AK72" t="b">
+        <v>0</v>
+      </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="n">
         <v>1</v>
@@ -11691,7 +11703,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11836,7 +11848,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11991,7 +12003,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12005,11 +12017,11 @@
         </is>
       </c>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI75" t="inlineStr"/>
       <c r="AJ75" t="inlineStr"/>
-      <c r="AK75" t="inlineStr"/>
+      <c r="AK75" t="b">
+        <v>0</v>
+      </c>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="n">
         <v>1</v>
@@ -12148,7 +12160,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12162,11 +12174,11 @@
         </is>
       </c>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI76" t="inlineStr"/>
       <c r="AJ76" t="inlineStr"/>
-      <c r="AK76" t="inlineStr"/>
+      <c r="AK76" t="b">
+        <v>0</v>
+      </c>
       <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="n">
         <v>1</v>
@@ -12305,7 +12317,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12319,11 +12331,11 @@
         </is>
       </c>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
+      <c r="AK77" t="b">
+        <v>0</v>
+      </c>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="n">
         <v>2</v>
@@ -12462,7 +12474,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12476,11 +12488,11 @@
         </is>
       </c>
       <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI78" t="inlineStr"/>
       <c r="AJ78" t="inlineStr"/>
-      <c r="AK78" t="inlineStr"/>
+      <c r="AK78" t="b">
+        <v>0</v>
+      </c>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="n">
         <v>3</v>
@@ -12619,7 +12631,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE79" t="n">
         <v>5</v>
@@ -12633,11 +12645,11 @@
         </is>
       </c>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr"/>
-      <c r="AK79" t="inlineStr"/>
+      <c r="AK79" t="b">
+        <v>0</v>
+      </c>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="n">
         <v>1</v>
@@ -12776,7 +12788,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12790,11 +12802,11 @@
         </is>
       </c>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
+      <c r="AK80" t="b">
+        <v>0</v>
+      </c>
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="n">
         <v>1</v>
@@ -12933,7 +12945,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12947,11 +12959,11 @@
         </is>
       </c>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
-      <c r="AK81" t="inlineStr"/>
+      <c r="AK81" t="b">
+        <v>0</v>
+      </c>
       <c r="AL81" t="inlineStr"/>
       <c r="AM81" t="n">
         <v>2</v>
@@ -13090,7 +13102,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13104,11 +13116,11 @@
         </is>
       </c>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
+      <c r="AK82" t="b">
+        <v>0</v>
+      </c>
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="n">
         <v>3</v>
@@ -13247,7 +13259,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13261,11 +13273,11 @@
         </is>
       </c>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
+      <c r="AK83" t="b">
+        <v>0</v>
+      </c>
       <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="n">
         <v>1</v>
@@ -13394,7 +13406,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE84" t="n">
         <v>9</v>
@@ -13549,7 +13561,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13563,11 +13575,11 @@
         </is>
       </c>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr"/>
-      <c r="AK85" t="inlineStr"/>
+      <c r="AK85" t="b">
+        <v>0</v>
+      </c>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="n">
         <v>1</v>
@@ -13706,7 +13718,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13720,11 +13732,11 @@
         </is>
       </c>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI86" t="inlineStr"/>
       <c r="AJ86" t="inlineStr"/>
-      <c r="AK86" t="inlineStr"/>
+      <c r="AK86" t="b">
+        <v>0</v>
+      </c>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="n">
         <v>2</v>
@@ -13863,7 +13875,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13877,11 +13889,11 @@
         </is>
       </c>
       <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI87" t="inlineStr"/>
       <c r="AJ87" t="inlineStr"/>
-      <c r="AK87" t="inlineStr"/>
+      <c r="AK87" t="b">
+        <v>0</v>
+      </c>
       <c r="AL87" t="inlineStr"/>
       <c r="AM87" t="n">
         <v>2</v>
@@ -14020,7 +14032,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14173,7 +14185,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE89" t="n">
         <v>8</v>
@@ -14326,7 +14338,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE90" t="n">
         <v>11</v>
@@ -14471,7 +14483,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -14616,7 +14628,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14761,7 +14773,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14906,7 +14918,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15055,7 +15067,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE95" t="n">
         <v>3</v>
@@ -15200,7 +15212,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15348,7 +15360,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15503,7 +15515,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>37278460386</v>
+        <v>111835381158</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15517,11 +15529,11 @@
         </is>
       </c>
       <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI98" t="inlineStr"/>
       <c r="AJ98" t="inlineStr"/>
-      <c r="AK98" t="inlineStr"/>
+      <c r="AK98" t="b">
+        <v>0</v>
+      </c>
       <c r="AL98" t="inlineStr"/>
       <c r="AM98" t="n">
         <v>1</v>
@@ -15660,7 +15672,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15674,11 +15686,11 @@
         </is>
       </c>
       <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI99" t="inlineStr"/>
       <c r="AJ99" t="inlineStr"/>
-      <c r="AK99" t="inlineStr"/>
+      <c r="AK99" t="b">
+        <v>0</v>
+      </c>
       <c r="AL99" t="inlineStr"/>
       <c r="AM99" t="n">
         <v>1</v>
@@ -15807,7 +15819,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE100" t="n">
         <v>3</v>
@@ -15956,7 +15968,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -16109,7 +16121,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE102" t="n">
         <v>17</v>
@@ -16254,7 +16266,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE103" t="n">
         <v>4</v>
@@ -16399,7 +16411,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -16544,7 +16556,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -16689,7 +16701,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16844,7 +16856,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16858,11 +16870,11 @@
         </is>
       </c>
       <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI107" t="inlineStr"/>
       <c r="AJ107" t="inlineStr"/>
-      <c r="AK107" t="inlineStr"/>
+      <c r="AK107" t="b">
+        <v>0</v>
+      </c>
       <c r="AL107" t="inlineStr"/>
       <c r="AM107" t="n">
         <v>1</v>
@@ -16999,7 +17011,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17152,7 +17164,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17307,7 +17319,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17321,11 +17333,11 @@
         </is>
       </c>
       <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI110" t="inlineStr"/>
       <c r="AJ110" t="inlineStr"/>
-      <c r="AK110" t="inlineStr"/>
+      <c r="AK110" t="b">
+        <v>0</v>
+      </c>
       <c r="AL110" t="inlineStr"/>
       <c r="AM110" t="n">
         <v>1</v>
@@ -17454,7 +17466,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17599,7 +17611,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17744,7 +17756,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17889,7 +17901,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18034,7 +18046,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE115" t="n">
         <v>8</v>
@@ -18189,7 +18201,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18203,11 +18215,11 @@
         </is>
       </c>
       <c r="AH116" t="inlineStr"/>
-      <c r="AI116" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI116" t="inlineStr"/>
       <c r="AJ116" t="inlineStr"/>
-      <c r="AK116" t="inlineStr"/>
+      <c r="AK116" t="b">
+        <v>0</v>
+      </c>
       <c r="AL116" t="inlineStr"/>
       <c r="AM116" t="n">
         <v>1</v>
@@ -18336,7 +18348,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -18491,7 +18503,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -18505,11 +18517,11 @@
         </is>
       </c>
       <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr"/>
-      <c r="AK118" t="inlineStr"/>
+      <c r="AK118" t="b">
+        <v>0</v>
+      </c>
       <c r="AL118" t="inlineStr"/>
       <c r="AM118" t="n">
         <v>1</v>
@@ -18638,7 +18650,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -18793,7 +18805,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18807,11 +18819,11 @@
         </is>
       </c>
       <c r="AH120" t="inlineStr"/>
-      <c r="AI120" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr"/>
-      <c r="AK120" t="inlineStr"/>
+      <c r="AK120" t="b">
+        <v>0</v>
+      </c>
       <c r="AL120" t="inlineStr"/>
       <c r="AM120" t="n">
         <v>1</v>
@@ -18950,7 +18962,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18964,11 +18976,11 @@
         </is>
       </c>
       <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI121" t="inlineStr"/>
       <c r="AJ121" t="inlineStr"/>
-      <c r="AK121" t="inlineStr"/>
+      <c r="AK121" t="b">
+        <v>0</v>
+      </c>
       <c r="AL121" t="inlineStr"/>
       <c r="AM121" t="n">
         <v>1</v>
@@ -19107,7 +19119,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19262,7 +19274,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -19276,11 +19288,11 @@
         </is>
       </c>
       <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI123" t="inlineStr"/>
       <c r="AJ123" t="inlineStr"/>
-      <c r="AK123" t="inlineStr"/>
+      <c r="AK123" t="b">
+        <v>0</v>
+      </c>
       <c r="AL123" t="inlineStr"/>
       <c r="AM123" t="n">
         <v>1</v>
@@ -19419,7 +19431,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -19433,11 +19445,11 @@
         </is>
       </c>
       <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI124" t="inlineStr"/>
       <c r="AJ124" t="inlineStr"/>
-      <c r="AK124" t="inlineStr"/>
+      <c r="AK124" t="b">
+        <v>0</v>
+      </c>
       <c r="AL124" t="inlineStr"/>
       <c r="AM124" t="n">
         <v>2</v>
@@ -19576,7 +19588,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -19590,11 +19602,11 @@
         </is>
       </c>
       <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI125" t="inlineStr"/>
       <c r="AJ125" t="inlineStr"/>
-      <c r="AK125" t="inlineStr"/>
+      <c r="AK125" t="b">
+        <v>0</v>
+      </c>
       <c r="AL125" t="inlineStr"/>
       <c r="AM125" t="n">
         <v>2</v>
@@ -19733,7 +19745,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -19747,11 +19759,11 @@
         </is>
       </c>
       <c r="AH126" t="inlineStr"/>
-      <c r="AI126" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI126" t="inlineStr"/>
       <c r="AJ126" t="inlineStr"/>
-      <c r="AK126" t="inlineStr"/>
+      <c r="AK126" t="b">
+        <v>0</v>
+      </c>
       <c r="AL126" t="inlineStr"/>
       <c r="AM126" t="n">
         <v>3</v>
@@ -19880,7 +19892,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -20031,7 +20043,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -20045,11 +20057,11 @@
         </is>
       </c>
       <c r="AH128" t="inlineStr"/>
-      <c r="AI128" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI128" t="inlineStr"/>
       <c r="AJ128" t="inlineStr"/>
-      <c r="AK128" t="inlineStr"/>
+      <c r="AK128" t="b">
+        <v>0</v>
+      </c>
       <c r="AL128" t="inlineStr"/>
       <c r="AM128" t="n">
         <v>1</v>
@@ -20188,7 +20200,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -20202,11 +20214,11 @@
         </is>
       </c>
       <c r="AH129" t="inlineStr"/>
-      <c r="AI129" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI129" t="inlineStr"/>
       <c r="AJ129" t="inlineStr"/>
-      <c r="AK129" t="inlineStr"/>
+      <c r="AK129" t="b">
+        <v>0</v>
+      </c>
       <c r="AL129" t="inlineStr"/>
       <c r="AM129" t="n">
         <v>1</v>
@@ -20345,7 +20357,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>30247495956</v>
+        <v>90742487868</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -20359,11 +20371,11 @@
         </is>
       </c>
       <c r="AH130" t="inlineStr"/>
-      <c r="AI130" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI130" t="inlineStr"/>
       <c r="AJ130" t="inlineStr"/>
-      <c r="AK130" t="inlineStr"/>
+      <c r="AK130" t="b">
+        <v>0</v>
+      </c>
       <c r="AL130" t="inlineStr"/>
       <c r="AM130" t="n">
         <v>1</v>
@@ -20502,7 +20514,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -20516,11 +20528,11 @@
         </is>
       </c>
       <c r="AH131" t="inlineStr"/>
-      <c r="AI131" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI131" t="inlineStr"/>
       <c r="AJ131" t="inlineStr"/>
-      <c r="AK131" t="inlineStr"/>
+      <c r="AK131" t="b">
+        <v>0</v>
+      </c>
       <c r="AL131" t="inlineStr"/>
       <c r="AM131" t="n">
         <v>1</v>
@@ -20659,7 +20671,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -20673,11 +20685,11 @@
         </is>
       </c>
       <c r="AH132" t="inlineStr"/>
-      <c r="AI132" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI132" t="inlineStr"/>
       <c r="AJ132" t="inlineStr"/>
-      <c r="AK132" t="inlineStr"/>
+      <c r="AK132" t="b">
+        <v>0</v>
+      </c>
       <c r="AL132" t="inlineStr"/>
       <c r="AM132" t="n">
         <v>1</v>
@@ -20816,7 +20828,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20830,11 +20842,11 @@
         </is>
       </c>
       <c r="AH133" t="inlineStr"/>
-      <c r="AI133" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI133" t="inlineStr"/>
       <c r="AJ133" t="inlineStr"/>
-      <c r="AK133" t="inlineStr"/>
+      <c r="AK133" t="b">
+        <v>0</v>
+      </c>
       <c r="AL133" t="inlineStr"/>
       <c r="AM133" t="n">
         <v>1</v>
@@ -20969,7 +20981,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20983,11 +20995,11 @@
         </is>
       </c>
       <c r="AH134" t="inlineStr"/>
-      <c r="AI134" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI134" t="inlineStr"/>
       <c r="AJ134" t="inlineStr"/>
-      <c r="AK134" t="inlineStr"/>
+      <c r="AK134" t="b">
+        <v>0</v>
+      </c>
       <c r="AL134" t="inlineStr"/>
       <c r="AM134" t="n">
         <v>1</v>
@@ -21116,7 +21128,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21261,7 +21273,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21406,7 +21418,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21551,7 +21563,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21696,7 +21708,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21841,7 +21853,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21986,7 +21998,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22131,7 +22143,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22276,7 +22288,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22421,7 +22433,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22566,7 +22578,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22711,7 +22723,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22856,7 +22868,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23001,7 +23013,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23146,7 +23158,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23291,7 +23303,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23436,7 +23448,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23581,7 +23593,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23726,7 +23738,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23871,7 +23883,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24016,7 +24028,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24161,7 +24173,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24306,7 +24318,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24451,7 +24463,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24596,7 +24608,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24741,7 +24753,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24886,7 +24898,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25031,7 +25043,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25176,7 +25188,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25321,7 +25333,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25466,7 +25478,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25611,7 +25623,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25756,7 +25768,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25901,7 +25913,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26046,7 +26058,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26191,7 +26203,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26336,7 +26348,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26481,7 +26493,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26626,7 +26638,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26771,7 +26783,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26916,7 +26928,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27061,7 +27073,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27206,7 +27218,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27351,7 +27363,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27496,7 +27508,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27641,7 +27653,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27786,7 +27798,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27931,7 +27943,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28076,7 +28088,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28221,7 +28233,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28366,7 +28378,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28511,7 +28523,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28656,7 +28668,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28801,7 +28813,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28946,7 +28958,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29091,7 +29103,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29236,7 +29248,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29381,7 +29393,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29526,7 +29538,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29671,7 +29683,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29816,7 +29828,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29961,7 +29973,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30106,7 +30118,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30251,7 +30263,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30396,7 +30408,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30541,7 +30553,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30686,7 +30698,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30831,7 +30843,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30976,7 +30988,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31121,7 +31133,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31266,7 +31278,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31411,7 +31423,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31556,7 +31568,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31701,7 +31713,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31846,7 +31858,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -31991,7 +32003,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32136,7 +32148,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32281,7 +32293,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32426,7 +32438,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32571,7 +32583,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32716,7 +32728,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32861,7 +32873,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33006,7 +33018,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33151,7 +33163,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33296,7 +33308,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33441,7 +33453,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33586,7 +33598,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33731,7 +33743,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -33876,7 +33888,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34021,7 +34033,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34166,7 +34178,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34311,7 +34323,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34456,7 +34468,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34601,7 +34613,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34746,7 +34758,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34891,7 +34903,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35036,7 +35048,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35181,7 +35193,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35326,7 +35338,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35471,7 +35483,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35616,7 +35628,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -35761,7 +35773,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35906,7 +35918,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36051,7 +36063,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36196,7 +36208,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36341,7 +36353,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36486,7 +36498,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36631,7 +36643,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -36776,7 +36788,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36921,7 +36933,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37066,7 +37078,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37211,7 +37223,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37356,7 +37368,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -37501,7 +37513,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -37646,7 +37658,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -37791,7 +37803,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -37936,7 +37948,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38081,7 +38093,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38226,7 +38238,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38371,7 +38383,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -38516,7 +38528,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -38661,7 +38673,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -38806,7 +38818,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -38951,7 +38963,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39096,7 +39108,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39241,7 +39253,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39386,7 +39398,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -39531,7 +39543,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -39676,7 +39688,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -39821,7 +39833,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -39966,7 +39978,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40111,7 +40123,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40256,7 +40268,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40401,7 +40413,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -40546,7 +40558,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -40691,7 +40703,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -40836,7 +40848,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -40981,7 +40993,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41126,7 +41138,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41271,7 +41283,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -41416,7 +41428,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -41561,7 +41573,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -41706,7 +41718,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -41851,7 +41863,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -41996,7 +42008,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42141,7 +42153,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42286,7 +42298,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -42431,7 +42443,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -42576,7 +42588,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -42721,7 +42733,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -42866,7 +42878,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -43011,7 +43023,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -43156,7 +43168,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -43301,7 +43313,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -43446,7 +43458,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -43591,7 +43603,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -43736,7 +43748,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -43881,7 +43893,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -44026,7 +44038,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -44171,7 +44183,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -44316,7 +44328,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -44461,7 +44473,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -44606,7 +44618,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -44751,7 +44763,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -44896,7 +44908,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -45041,7 +45053,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -45186,7 +45198,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -45331,7 +45343,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -45476,7 +45488,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -45621,7 +45633,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -45766,7 +45778,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -45911,7 +45923,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -46056,7 +46068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -46201,7 +46213,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -46346,7 +46358,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -46491,7 +46503,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -46636,7 +46648,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -46781,7 +46793,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE312" t="n">
         <v>3</v>
@@ -46926,7 +46938,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -47071,7 +47083,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -47216,7 +47228,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -47361,7 +47373,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE316" t="n">
         <v>3</v>
@@ -47506,7 +47518,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -47651,7 +47663,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -47796,7 +47808,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -47941,7 +47953,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -48086,7 +48098,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -48231,7 +48243,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -48376,7 +48388,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -48521,7 +48533,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -48666,7 +48678,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -48811,7 +48823,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -48956,7 +48968,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -49101,7 +49113,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -49246,7 +49258,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -49391,7 +49403,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -49536,7 +49548,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -49681,7 +49693,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -49826,7 +49838,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -49971,7 +49983,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -50116,7 +50128,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -50261,7 +50273,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -50406,7 +50418,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -50551,7 +50563,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -50696,7 +50708,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -50841,7 +50853,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -50996,7 +51008,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>28672304832</v>
+        <v>86016914496</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -51010,11 +51022,11 @@
         </is>
       </c>
       <c r="AH341" t="inlineStr"/>
-      <c r="AI341" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI341" t="inlineStr"/>
       <c r="AJ341" t="inlineStr"/>
-      <c r="AK341" t="inlineStr"/>
+      <c r="AK341" t="b">
+        <v>0</v>
+      </c>
       <c r="AL341" t="inlineStr"/>
       <c r="AM341" t="n">
         <v>1</v>
@@ -51149,7 +51161,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>34868198304</v>
+        <v>104604594912</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -51294,7 +51306,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -51439,7 +51451,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -51584,7 +51596,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -51729,7 +51741,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -51874,7 +51886,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -52019,7 +52031,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -52164,7 +52176,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -52319,7 +52331,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -52464,7 +52476,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -52609,7 +52621,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -52762,7 +52774,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -52916,7 +52928,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -53061,7 +53073,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -53206,7 +53218,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -53359,7 +53371,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -53504,7 +53516,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE358" t="n">
         <v>2</v>
@@ -53659,7 +53671,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>28672304832</v>
+        <v>86016914496</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -53673,11 +53685,11 @@
         </is>
       </c>
       <c r="AH359" t="inlineStr"/>
-      <c r="AI359" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI359" t="inlineStr"/>
       <c r="AJ359" t="inlineStr"/>
-      <c r="AK359" t="inlineStr"/>
+      <c r="AK359" t="b">
+        <v>0</v>
+      </c>
       <c r="AL359" t="inlineStr"/>
       <c r="AM359" t="n">
         <v>2</v>
@@ -53816,7 +53828,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -53830,11 +53842,11 @@
         </is>
       </c>
       <c r="AH360" t="inlineStr"/>
-      <c r="AI360" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI360" t="inlineStr"/>
       <c r="AJ360" t="inlineStr"/>
-      <c r="AK360" t="inlineStr"/>
+      <c r="AK360" t="b">
+        <v>0</v>
+      </c>
       <c r="AL360" t="inlineStr"/>
       <c r="AM360" t="n">
         <v>1</v>
@@ -53969,7 +53981,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -53983,11 +53995,11 @@
         </is>
       </c>
       <c r="AH361" t="inlineStr"/>
-      <c r="AI361" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI361" t="inlineStr"/>
       <c r="AJ361" t="inlineStr"/>
-      <c r="AK361" t="inlineStr"/>
+      <c r="AK361" t="b">
+        <v>0</v>
+      </c>
       <c r="AL361" t="inlineStr"/>
       <c r="AM361" t="n">
         <v>1</v>
@@ -54126,7 +54138,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -54140,11 +54152,11 @@
         </is>
       </c>
       <c r="AH362" t="inlineStr"/>
-      <c r="AI362" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI362" t="inlineStr"/>
       <c r="AJ362" t="inlineStr"/>
-      <c r="AK362" t="inlineStr"/>
+      <c r="AK362" t="b">
+        <v>0</v>
+      </c>
       <c r="AL362" t="inlineStr"/>
       <c r="AM362" t="n">
         <v>1</v>
@@ -54273,7 +54285,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -54428,7 +54440,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -54442,11 +54454,11 @@
         </is>
       </c>
       <c r="AH364" t="inlineStr"/>
-      <c r="AI364" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI364" t="inlineStr"/>
       <c r="AJ364" t="inlineStr"/>
-      <c r="AK364" t="inlineStr"/>
+      <c r="AK364" t="b">
+        <v>0</v>
+      </c>
       <c r="AL364" t="inlineStr"/>
       <c r="AM364" t="n">
         <v>1</v>
@@ -54585,7 +54597,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -54599,11 +54611,11 @@
         </is>
       </c>
       <c r="AH365" t="inlineStr"/>
-      <c r="AI365" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI365" t="inlineStr"/>
       <c r="AJ365" t="inlineStr"/>
-      <c r="AK365" t="inlineStr"/>
+      <c r="AK365" t="b">
+        <v>0</v>
+      </c>
       <c r="AL365" t="inlineStr"/>
       <c r="AM365" t="n">
         <v>1</v>
@@ -54742,7 +54754,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -54756,11 +54768,11 @@
         </is>
       </c>
       <c r="AH366" t="inlineStr"/>
-      <c r="AI366" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI366" t="inlineStr"/>
       <c r="AJ366" t="inlineStr"/>
-      <c r="AK366" t="inlineStr"/>
+      <c r="AK366" t="b">
+        <v>0</v>
+      </c>
       <c r="AL366" t="inlineStr"/>
       <c r="AM366" t="n">
         <v>1</v>
@@ -54897,7 +54909,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -55048,7 +55060,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>27904195440</v>
+        <v>83712586320</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -55062,11 +55074,11 @@
         </is>
       </c>
       <c r="AH368" t="inlineStr"/>
-      <c r="AI368" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI368" t="inlineStr"/>
       <c r="AJ368" t="inlineStr"/>
-      <c r="AK368" t="inlineStr"/>
+      <c r="AK368" t="b">
+        <v>0</v>
+      </c>
       <c r="AL368" t="inlineStr"/>
       <c r="AM368" t="n">
         <v>1</v>
@@ -55201,7 +55213,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>27904195440</v>
+        <v>83712586320</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -55215,11 +55227,11 @@
         </is>
       </c>
       <c r="AH369" t="inlineStr"/>
-      <c r="AI369" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI369" t="inlineStr"/>
       <c r="AJ369" t="inlineStr"/>
-      <c r="AK369" t="inlineStr"/>
+      <c r="AK369" t="b">
+        <v>0</v>
+      </c>
       <c r="AL369" t="inlineStr"/>
       <c r="AM369" t="n">
         <v>2</v>
@@ -55354,7 +55366,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>27904195440</v>
+        <v>83712586320</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -55368,11 +55380,11 @@
         </is>
       </c>
       <c r="AH370" t="inlineStr"/>
-      <c r="AI370" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI370" t="inlineStr"/>
       <c r="AJ370" t="inlineStr"/>
-      <c r="AK370" t="inlineStr"/>
+      <c r="AK370" t="b">
+        <v>0</v>
+      </c>
       <c r="AL370" t="inlineStr"/>
       <c r="AM370" t="n">
         <v>3</v>
@@ -55501,7 +55513,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -55652,7 +55664,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>34868198304</v>
+        <v>104604594912</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -55805,7 +55817,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -55960,7 +55972,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -55974,11 +55986,11 @@
         </is>
       </c>
       <c r="AH374" t="inlineStr"/>
-      <c r="AI374" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI374" t="inlineStr"/>
       <c r="AJ374" t="inlineStr"/>
-      <c r="AK374" t="inlineStr"/>
+      <c r="AK374" t="b">
+        <v>0</v>
+      </c>
       <c r="AL374" t="inlineStr"/>
       <c r="AM374" t="n">
         <v>1</v>
@@ -56107,7 +56119,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -56248,7 +56260,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -56393,7 +56405,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -56538,7 +56550,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -56693,7 +56705,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -56707,11 +56719,11 @@
         </is>
       </c>
       <c r="AH379" t="inlineStr"/>
-      <c r="AI379" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI379" t="inlineStr"/>
       <c r="AJ379" t="inlineStr"/>
-      <c r="AK379" t="inlineStr"/>
+      <c r="AK379" t="b">
+        <v>0</v>
+      </c>
       <c r="AL379" t="inlineStr"/>
       <c r="AM379" t="n">
         <v>1</v>
@@ -56840,7 +56852,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -56985,7 +56997,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -57126,7 +57138,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -57277,7 +57289,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -57291,11 +57303,11 @@
         </is>
       </c>
       <c r="AH383" t="inlineStr"/>
-      <c r="AI383" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI383" t="inlineStr"/>
       <c r="AJ383" t="inlineStr"/>
-      <c r="AK383" t="inlineStr"/>
+      <c r="AK383" t="b">
+        <v>0</v>
+      </c>
       <c r="AL383" t="inlineStr"/>
       <c r="AM383" t="n">
         <v>1</v>
@@ -57430,7 +57442,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -57444,11 +57456,11 @@
         </is>
       </c>
       <c r="AH384" t="inlineStr"/>
-      <c r="AI384" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI384" t="inlineStr"/>
       <c r="AJ384" t="inlineStr"/>
-      <c r="AK384" t="inlineStr"/>
+      <c r="AK384" t="b">
+        <v>0</v>
+      </c>
       <c r="AL384" t="inlineStr"/>
       <c r="AM384" t="n">
         <v>2</v>
@@ -57583,7 +57595,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -57597,11 +57609,11 @@
         </is>
       </c>
       <c r="AH385" t="inlineStr"/>
-      <c r="AI385" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI385" t="inlineStr"/>
       <c r="AJ385" t="inlineStr"/>
-      <c r="AK385" t="inlineStr"/>
+      <c r="AK385" t="b">
+        <v>0</v>
+      </c>
       <c r="AL385" t="inlineStr"/>
       <c r="AM385" t="n">
         <v>3</v>
@@ -57740,7 +57752,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -57754,11 +57766,11 @@
         </is>
       </c>
       <c r="AH386" t="inlineStr"/>
-      <c r="AI386" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI386" t="inlineStr"/>
       <c r="AJ386" t="inlineStr"/>
-      <c r="AK386" t="inlineStr"/>
+      <c r="AK386" t="b">
+        <v>0</v>
+      </c>
       <c r="AL386" t="inlineStr"/>
       <c r="AM386" t="n">
         <v>1</v>
@@ -57897,7 +57909,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -57911,11 +57923,11 @@
         </is>
       </c>
       <c r="AH387" t="inlineStr"/>
-      <c r="AI387" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI387" t="inlineStr"/>
       <c r="AJ387" t="inlineStr"/>
-      <c r="AK387" t="inlineStr"/>
+      <c r="AK387" t="b">
+        <v>0</v>
+      </c>
       <c r="AL387" t="inlineStr"/>
       <c r="AM387" t="n">
         <v>2</v>
@@ -58054,7 +58066,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -58068,11 +58080,11 @@
         </is>
       </c>
       <c r="AH388" t="inlineStr"/>
-      <c r="AI388" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI388" t="inlineStr"/>
       <c r="AJ388" t="inlineStr"/>
-      <c r="AK388" t="inlineStr"/>
+      <c r="AK388" t="b">
+        <v>0</v>
+      </c>
       <c r="AL388" t="inlineStr"/>
       <c r="AM388" t="n">
         <v>1</v>
@@ -58211,7 +58223,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>28672304832</v>
+        <v>86016914496</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -58225,11 +58237,11 @@
         </is>
       </c>
       <c r="AH389" t="inlineStr"/>
-      <c r="AI389" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI389" t="inlineStr"/>
       <c r="AJ389" t="inlineStr"/>
-      <c r="AK389" t="inlineStr"/>
+      <c r="AK389" t="b">
+        <v>0</v>
+      </c>
       <c r="AL389" t="inlineStr"/>
       <c r="AM389" t="n">
         <v>3</v>
@@ -58368,7 +58380,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE390" t="n">
         <v>5</v>
@@ -58382,11 +58394,11 @@
         </is>
       </c>
       <c r="AH390" t="inlineStr"/>
-      <c r="AI390" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI390" t="inlineStr"/>
       <c r="AJ390" t="inlineStr"/>
-      <c r="AK390" t="inlineStr"/>
+      <c r="AK390" t="b">
+        <v>0</v>
+      </c>
       <c r="AL390" t="inlineStr"/>
       <c r="AM390" t="n">
         <v>1</v>
@@ -58525,7 +58537,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -58539,11 +58551,11 @@
         </is>
       </c>
       <c r="AH391" t="inlineStr"/>
-      <c r="AI391" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI391" t="inlineStr"/>
       <c r="AJ391" t="inlineStr"/>
-      <c r="AK391" t="inlineStr"/>
+      <c r="AK391" t="b">
+        <v>0</v>
+      </c>
       <c r="AL391" t="inlineStr"/>
       <c r="AM391" t="n">
         <v>1</v>
@@ -58680,7 +58692,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -58835,7 +58847,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -58849,11 +58861,11 @@
         </is>
       </c>
       <c r="AH393" t="inlineStr"/>
-      <c r="AI393" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI393" t="inlineStr"/>
       <c r="AJ393" t="inlineStr"/>
-      <c r="AK393" t="inlineStr"/>
+      <c r="AK393" t="b">
+        <v>0</v>
+      </c>
       <c r="AL393" t="inlineStr"/>
       <c r="AM393" t="n">
         <v>1</v>
@@ -58992,7 +59004,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -59006,11 +59018,11 @@
         </is>
       </c>
       <c r="AH394" t="inlineStr"/>
-      <c r="AI394" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI394" t="inlineStr"/>
       <c r="AJ394" t="inlineStr"/>
-      <c r="AK394" t="inlineStr"/>
+      <c r="AK394" t="b">
+        <v>0</v>
+      </c>
       <c r="AL394" t="inlineStr"/>
       <c r="AM394" t="n">
         <v>2</v>
@@ -59149,7 +59161,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -59163,11 +59175,11 @@
         </is>
       </c>
       <c r="AH395" t="inlineStr"/>
-      <c r="AI395" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI395" t="inlineStr"/>
       <c r="AJ395" t="inlineStr"/>
-      <c r="AK395" t="inlineStr"/>
+      <c r="AK395" t="b">
+        <v>0</v>
+      </c>
       <c r="AL395" t="inlineStr"/>
       <c r="AM395" t="n">
         <v>3</v>
@@ -59306,7 +59318,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -59320,11 +59332,11 @@
         </is>
       </c>
       <c r="AH396" t="inlineStr"/>
-      <c r="AI396" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI396" t="inlineStr"/>
       <c r="AJ396" t="inlineStr"/>
-      <c r="AK396" t="inlineStr"/>
+      <c r="AK396" t="b">
+        <v>0</v>
+      </c>
       <c r="AL396" t="inlineStr"/>
       <c r="AM396" t="n">
         <v>1</v>
@@ -59453,7 +59465,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -59611,7 +59623,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -59625,11 +59637,11 @@
         </is>
       </c>
       <c r="AH398" t="inlineStr"/>
-      <c r="AI398" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI398" t="inlineStr"/>
       <c r="AJ398" t="inlineStr"/>
-      <c r="AK398" t="inlineStr"/>
+      <c r="AK398" t="b">
+        <v>0</v>
+      </c>
       <c r="AL398" t="inlineStr"/>
       <c r="AM398" t="n">
         <v>1</v>
@@ -59768,7 +59780,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -59782,11 +59794,11 @@
         </is>
       </c>
       <c r="AH399" t="inlineStr"/>
-      <c r="AI399" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI399" t="inlineStr"/>
       <c r="AJ399" t="inlineStr"/>
-      <c r="AK399" t="inlineStr"/>
+      <c r="AK399" t="b">
+        <v>0</v>
+      </c>
       <c r="AL399" t="inlineStr"/>
       <c r="AM399" t="n">
         <v>2</v>
@@ -59925,7 +59937,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -59939,11 +59951,11 @@
         </is>
       </c>
       <c r="AH400" t="inlineStr"/>
-      <c r="AI400" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI400" t="inlineStr"/>
       <c r="AJ400" t="inlineStr"/>
-      <c r="AK400" t="inlineStr"/>
+      <c r="AK400" t="b">
+        <v>0</v>
+      </c>
       <c r="AL400" t="inlineStr"/>
       <c r="AM400" t="n">
         <v>1</v>
@@ -60082,7 +60094,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -60096,11 +60108,11 @@
         </is>
       </c>
       <c r="AH401" t="inlineStr"/>
-      <c r="AI401" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI401" t="inlineStr"/>
       <c r="AJ401" t="inlineStr"/>
-      <c r="AK401" t="inlineStr"/>
+      <c r="AK401" t="b">
+        <v>0</v>
+      </c>
       <c r="AL401" t="inlineStr"/>
       <c r="AM401" t="n">
         <v>2</v>
@@ -60239,7 +60251,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>34868202678</v>
+        <v>104604608034</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -60394,7 +60406,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -60408,11 +60420,11 @@
         </is>
       </c>
       <c r="AH403" t="inlineStr"/>
-      <c r="AI403" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI403" t="inlineStr"/>
       <c r="AJ403" t="inlineStr"/>
-      <c r="AK403" t="inlineStr"/>
+      <c r="AK403" t="b">
+        <v>0</v>
+      </c>
       <c r="AL403" t="inlineStr"/>
       <c r="AM403" t="n">
         <v>1</v>
@@ -60542,7 +60554,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -60697,7 +60709,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>34896900510</v>
+        <v>104690701530</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -60852,7 +60864,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>34896900510</v>
+        <v>104690701530</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -61007,7 +61019,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>34896900510</v>
+        <v>104690701530</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -61152,7 +61164,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE408" t="n">
         <v>2</v>
@@ -61307,7 +61319,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -61321,11 +61333,11 @@
         </is>
       </c>
       <c r="AH409" t="inlineStr"/>
-      <c r="AI409" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI409" t="inlineStr"/>
       <c r="AJ409" t="inlineStr"/>
-      <c r="AK409" t="inlineStr"/>
+      <c r="AK409" t="b">
+        <v>0</v>
+      </c>
       <c r="AL409" t="inlineStr"/>
       <c r="AM409" t="n">
         <v>1</v>
@@ -61460,7 +61472,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -61474,11 +61486,11 @@
         </is>
       </c>
       <c r="AH410" t="inlineStr"/>
-      <c r="AI410" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI410" t="inlineStr"/>
       <c r="AJ410" t="inlineStr"/>
-      <c r="AK410" t="inlineStr"/>
+      <c r="AK410" t="b">
+        <v>0</v>
+      </c>
       <c r="AL410" t="inlineStr"/>
       <c r="AM410" t="n">
         <v>1</v>
@@ -61617,7 +61629,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -61631,11 +61643,11 @@
         </is>
       </c>
       <c r="AH411" t="inlineStr"/>
-      <c r="AI411" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI411" t="inlineStr"/>
       <c r="AJ411" t="inlineStr"/>
-      <c r="AK411" t="inlineStr"/>
+      <c r="AK411" t="b">
+        <v>0</v>
+      </c>
       <c r="AL411" t="inlineStr"/>
       <c r="AM411" t="n">
         <v>2</v>
@@ -61774,7 +61786,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>35126124336</v>
+        <v>105378373008</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -61927,7 +61939,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -62082,7 +62094,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -62096,11 +62108,11 @@
         </is>
       </c>
       <c r="AH414" t="inlineStr"/>
-      <c r="AI414" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI414" t="inlineStr"/>
       <c r="AJ414" t="inlineStr"/>
-      <c r="AK414" t="inlineStr"/>
+      <c r="AK414" t="b">
+        <v>0</v>
+      </c>
       <c r="AL414" t="inlineStr"/>
       <c r="AM414" t="n">
         <v>2</v>
@@ -62237,7 +62249,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -62390,7 +62402,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -62545,7 +62557,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -62559,11 +62571,11 @@
         </is>
       </c>
       <c r="AH417" t="inlineStr"/>
-      <c r="AI417" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI417" t="inlineStr"/>
       <c r="AJ417" t="inlineStr"/>
-      <c r="AK417" t="inlineStr"/>
+      <c r="AK417" t="b">
+        <v>0</v>
+      </c>
       <c r="AL417" t="inlineStr"/>
       <c r="AM417" t="n">
         <v>3</v>
@@ -62692,7 +62704,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -62847,7 +62859,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -62861,11 +62873,11 @@
         </is>
       </c>
       <c r="AH419" t="inlineStr"/>
-      <c r="AI419" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI419" t="inlineStr"/>
       <c r="AJ419" t="inlineStr"/>
-      <c r="AK419" t="inlineStr"/>
+      <c r="AK419" t="b">
+        <v>0</v>
+      </c>
       <c r="AL419" t="inlineStr"/>
       <c r="AM419" t="n">
         <v>1</v>
@@ -63004,7 +63016,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>28672304832</v>
+        <v>86016914496</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -63018,11 +63030,11 @@
         </is>
       </c>
       <c r="AH420" t="inlineStr"/>
-      <c r="AI420" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI420" t="inlineStr"/>
       <c r="AJ420" t="inlineStr"/>
-      <c r="AK420" t="inlineStr"/>
+      <c r="AK420" t="b">
+        <v>0</v>
+      </c>
       <c r="AL420" t="inlineStr"/>
       <c r="AM420" t="n">
         <v>1</v>
@@ -63161,7 +63173,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>27983915964</v>
+        <v>83951747892</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -63175,11 +63187,11 @@
         </is>
       </c>
       <c r="AH421" t="inlineStr"/>
-      <c r="AI421" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI421" t="inlineStr"/>
       <c r="AJ421" t="inlineStr"/>
-      <c r="AK421" t="inlineStr"/>
+      <c r="AK421" t="b">
+        <v>0</v>
+      </c>
       <c r="AL421" t="inlineStr"/>
       <c r="AM421" t="n">
         <v>1</v>
@@ -63316,7 +63328,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -63471,7 +63483,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -63485,11 +63497,11 @@
         </is>
       </c>
       <c r="AH423" t="inlineStr"/>
-      <c r="AI423" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI423" t="inlineStr"/>
       <c r="AJ423" t="inlineStr"/>
-      <c r="AK423" t="inlineStr"/>
+      <c r="AK423" t="b">
+        <v>0</v>
+      </c>
       <c r="AL423" t="inlineStr"/>
       <c r="AM423" t="n">
         <v>1</v>
@@ -63628,7 +63640,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -63642,11 +63654,11 @@
         </is>
       </c>
       <c r="AH424" t="inlineStr"/>
-      <c r="AI424" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI424" t="inlineStr"/>
       <c r="AJ424" t="inlineStr"/>
-      <c r="AK424" t="inlineStr"/>
+      <c r="AK424" t="b">
+        <v>0</v>
+      </c>
       <c r="AL424" t="inlineStr"/>
       <c r="AM424" t="n">
         <v>1</v>
@@ -63775,7 +63787,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -63920,7 +63932,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE426" t="n">
         <v>2</v>
@@ -64073,7 +64085,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE427" t="n">
         <v>5</v>
@@ -64226,7 +64238,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE428" t="n">
         <v>229</v>
@@ -64371,7 +64383,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -64516,7 +64528,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE430" t="n">
         <v>2</v>
@@ -64671,7 +64683,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE431" t="n">
         <v>4</v>
@@ -64816,7 +64828,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -64965,7 +64977,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -65110,7 +65122,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE434" t="n">
         <v>2</v>
@@ -65263,7 +65275,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -65416,7 +65428,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -65561,7 +65573,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -65706,7 +65718,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -65861,7 +65873,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -66016,7 +66028,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -66171,7 +66183,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -66324,7 +66336,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -66473,7 +66485,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE443" t="n">
         <v>3</v>
@@ -66629,7 +66641,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -66774,7 +66786,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -66915,7 +66927,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -67060,7 +67072,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -67205,7 +67217,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -67350,7 +67362,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -67495,7 +67507,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -67648,7 +67660,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -67803,7 +67815,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>
@@ -67958,7 +67970,7 @@
         </is>
       </c>
       <c r="AD453" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE453" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>90742487868</v>
+        <v>272227463604</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>125782518762</v>
+        <v>377347556286</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE11" t="n">
         <v>19</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE15" t="n">
         <v>17</v>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>111835381158</v>
+        <v>335506143474</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>90742487868</v>
+        <v>272227463604</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>90742487868</v>
+        <v>272227463604</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>86007348558</v>
+        <v>258022045674</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9087,7 +9087,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>83950671888</v>
+        <v>251852015664</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>83950671888</v>
+        <v>251852015664</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>83950671888</v>
+        <v>251852015664</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>83944294596</v>
+        <v>251832883788</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10306,7 +10306,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>104690688354</v>
+        <v>314072065062</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>83944294596</v>
+        <v>251832883788</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12474,7 +12474,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE79" t="n">
         <v>5</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE84" t="n">
         <v>9</v>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14032,7 +14032,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE89" t="n">
         <v>8</v>
@@ -14338,7 +14338,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE90" t="n">
         <v>11</v>
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14918,7 +14918,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE95" t="n">
         <v>3</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>111835381158</v>
+        <v>335506143474</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE100" t="n">
         <v>3</v>
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE102" t="n">
         <v>17</v>
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE103" t="n">
         <v>4</v>
@@ -16411,7 +16411,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -16556,7 +16556,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -16701,7 +16701,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17164,7 +17164,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18046,7 +18046,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE115" t="n">
         <v>8</v>
@@ -18201,7 +18201,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18962,7 +18962,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19119,7 +19119,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19274,7 +19274,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -19431,7 +19431,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -19588,7 +19588,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -19745,7 +19745,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -19892,7 +19892,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -20043,7 +20043,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -20200,7 +20200,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -20357,7 +20357,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>90742487868</v>
+        <v>272227463604</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -20514,7 +20514,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -20671,7 +20671,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20981,7 +20981,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21273,7 +21273,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21418,7 +21418,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21563,7 +21563,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21708,7 +21708,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21853,7 +21853,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22143,7 +22143,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22288,7 +22288,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22433,7 +22433,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22578,7 +22578,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22723,7 +22723,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22868,7 +22868,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23013,7 +23013,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23158,7 +23158,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23303,7 +23303,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23593,7 +23593,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23738,7 +23738,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23883,7 +23883,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24028,7 +24028,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24173,7 +24173,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24463,7 +24463,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24753,7 +24753,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24898,7 +24898,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25043,7 +25043,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25333,7 +25333,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25478,7 +25478,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25623,7 +25623,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25768,7 +25768,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25913,7 +25913,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26058,7 +26058,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26203,7 +26203,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26348,7 +26348,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26493,7 +26493,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26638,7 +26638,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26783,7 +26783,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27073,7 +27073,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27218,7 +27218,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27363,7 +27363,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27508,7 +27508,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27798,7 +27798,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27943,7 +27943,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28233,7 +28233,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28378,7 +28378,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28813,7 +28813,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28958,7 +28958,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29103,7 +29103,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29248,7 +29248,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29393,7 +29393,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29538,7 +29538,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29683,7 +29683,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29828,7 +29828,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30118,7 +30118,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30263,7 +30263,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30553,7 +30553,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30698,7 +30698,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30843,7 +30843,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30988,7 +30988,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31133,7 +31133,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31278,7 +31278,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31423,7 +31423,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31713,7 +31713,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31858,7 +31858,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32003,7 +32003,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32148,7 +32148,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32438,7 +32438,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32728,7 +32728,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32873,7 +32873,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33018,7 +33018,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33163,7 +33163,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33308,7 +33308,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33453,7 +33453,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33598,7 +33598,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33743,7 +33743,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -33888,7 +33888,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34033,7 +34033,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34178,7 +34178,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34323,7 +34323,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34468,7 +34468,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34613,7 +34613,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34758,7 +34758,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34903,7 +34903,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35048,7 +35048,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35193,7 +35193,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35338,7 +35338,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35483,7 +35483,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -35773,7 +35773,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35918,7 +35918,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36063,7 +36063,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36208,7 +36208,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36353,7 +36353,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36643,7 +36643,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -36788,7 +36788,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37078,7 +37078,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37223,7 +37223,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37368,7 +37368,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -37513,7 +37513,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -37658,7 +37658,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -37803,7 +37803,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -37948,7 +37948,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38093,7 +38093,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38238,7 +38238,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38383,7 +38383,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -38528,7 +38528,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -38673,7 +38673,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -38818,7 +38818,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -38963,7 +38963,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39108,7 +39108,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39253,7 +39253,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39398,7 +39398,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -39543,7 +39543,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -39688,7 +39688,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -39833,7 +39833,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -39978,7 +39978,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40123,7 +40123,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40268,7 +40268,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40413,7 +40413,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -40558,7 +40558,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -40848,7 +40848,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -40993,7 +40993,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41283,7 +41283,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -41428,7 +41428,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -41573,7 +41573,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -41718,7 +41718,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -41863,7 +41863,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42153,7 +42153,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42298,7 +42298,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -42443,7 +42443,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -42588,7 +42588,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -42733,7 +42733,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -42878,7 +42878,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -43023,7 +43023,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -43168,7 +43168,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -43313,7 +43313,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -43458,7 +43458,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -43603,7 +43603,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -43748,7 +43748,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -43893,7 +43893,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -44038,7 +44038,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -44183,7 +44183,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -44328,7 +44328,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -44473,7 +44473,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -44618,7 +44618,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -44763,7 +44763,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -44908,7 +44908,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -45053,7 +45053,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -45198,7 +45198,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -45343,7 +45343,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -45488,7 +45488,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -45633,7 +45633,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -45923,7 +45923,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -46068,7 +46068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -46213,7 +46213,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -46358,7 +46358,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -46503,7 +46503,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -46648,7 +46648,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -46793,7 +46793,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE312" t="n">
         <v>3</v>
@@ -46938,7 +46938,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -47083,7 +47083,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -47228,7 +47228,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -47373,7 +47373,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE316" t="n">
         <v>3</v>
@@ -47518,7 +47518,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -47663,7 +47663,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -47808,7 +47808,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -47953,7 +47953,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -48098,7 +48098,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -48243,7 +48243,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -48388,7 +48388,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -48533,7 +48533,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -48678,7 +48678,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -48823,7 +48823,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -48968,7 +48968,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -49113,7 +49113,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -49258,7 +49258,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -49403,7 +49403,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -49548,7 +49548,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -49693,7 +49693,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -49838,7 +49838,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -50128,7 +50128,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -50273,7 +50273,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -50418,7 +50418,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -50563,7 +50563,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -50708,7 +50708,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -50853,7 +50853,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -51008,7 +51008,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>86016914496</v>
+        <v>258050743488</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -51161,7 +51161,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>104604594912</v>
+        <v>313813784736</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -51306,7 +51306,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -51451,7 +51451,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -51596,7 +51596,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -51741,7 +51741,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -51886,7 +51886,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -52031,7 +52031,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -52176,7 +52176,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -52331,7 +52331,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -52476,7 +52476,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -52621,7 +52621,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -52774,7 +52774,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -52928,7 +52928,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -53073,7 +53073,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -53371,7 +53371,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -53516,7 +53516,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE358" t="n">
         <v>2</v>
@@ -53671,7 +53671,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>86016914496</v>
+        <v>258050743488</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -53828,7 +53828,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -53981,7 +53981,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -54138,7 +54138,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -54285,7 +54285,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -54440,7 +54440,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -54597,7 +54597,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -54754,7 +54754,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -54909,7 +54909,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -55060,7 +55060,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>83712586320</v>
+        <v>251137758960</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -55213,7 +55213,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>83712586320</v>
+        <v>251137758960</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -55366,7 +55366,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>83712586320</v>
+        <v>251137758960</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -55513,7 +55513,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -55664,7 +55664,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>104604594912</v>
+        <v>313813784736</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -55817,7 +55817,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -55972,7 +55972,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -56119,7 +56119,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -56260,7 +56260,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -56405,7 +56405,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -56550,7 +56550,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -56705,7 +56705,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -56852,7 +56852,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -56997,7 +56997,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -57138,7 +57138,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -57289,7 +57289,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -57442,7 +57442,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -57595,7 +57595,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -57752,7 +57752,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -57909,7 +57909,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -58066,7 +58066,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -58223,7 +58223,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>86016914496</v>
+        <v>258050743488</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -58380,7 +58380,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE390" t="n">
         <v>5</v>
@@ -58537,7 +58537,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -58692,7 +58692,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -58847,7 +58847,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -59004,7 +59004,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -59161,7 +59161,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -59318,7 +59318,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -59465,7 +59465,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -59623,7 +59623,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -59780,7 +59780,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -59937,7 +59937,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -60094,7 +60094,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -60251,7 +60251,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>104604608034</v>
+        <v>313813824102</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -60406,7 +60406,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -60554,7 +60554,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -60709,7 +60709,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>104690701530</v>
+        <v>314072104590</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>104690701530</v>
+        <v>314072104590</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -61019,7 +61019,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>104690701530</v>
+        <v>314072104590</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -61164,7 +61164,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE408" t="n">
         <v>2</v>
@@ -61319,7 +61319,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -61472,7 +61472,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -61629,7 +61629,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -61786,7 +61786,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>105378373008</v>
+        <v>316135119024</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -61939,7 +61939,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -62094,7 +62094,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -62249,7 +62249,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -62402,7 +62402,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -62557,7 +62557,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -62704,7 +62704,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -62859,7 +62859,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -63016,7 +63016,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>86016914496</v>
+        <v>258050743488</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -63173,7 +63173,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>83951747892</v>
+        <v>251855243676</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -63328,7 +63328,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -63483,7 +63483,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -63640,7 +63640,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -63787,7 +63787,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -63932,7 +63932,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE426" t="n">
         <v>2</v>
@@ -64085,7 +64085,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE427" t="n">
         <v>5</v>
@@ -64238,7 +64238,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE428" t="n">
         <v>229</v>
@@ -64383,7 +64383,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -64528,7 +64528,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE430" t="n">
         <v>2</v>
@@ -64683,7 +64683,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE431" t="n">
         <v>4</v>
@@ -64828,7 +64828,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -64977,7 +64977,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -65122,7 +65122,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE434" t="n">
         <v>2</v>
@@ -65275,7 +65275,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -65428,7 +65428,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -65573,7 +65573,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -65718,7 +65718,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -65873,7 +65873,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -66028,7 +66028,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -66183,7 +66183,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -66336,7 +66336,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -66485,7 +66485,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE443" t="n">
         <v>3</v>
@@ -66641,7 +66641,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -66786,7 +66786,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -66927,7 +66927,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -67072,7 +67072,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -67217,7 +67217,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -67362,7 +67362,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -67507,7 +67507,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -67660,7 +67660,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -67815,7 +67815,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>
@@ -67970,7 +67970,7 @@
         </is>
       </c>
       <c r="AD453" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE453" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>272227463604</v>
+        <v>816682390812</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>377347556286</v>
+        <v>1132042668858</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE11" t="n">
         <v>19</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE15" t="n">
         <v>17</v>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>335506143474</v>
+        <v>1006518430422</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>272227463604</v>
+        <v>816682390812</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>272227463604</v>
+        <v>816682390812</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>258022045674</v>
+        <v>774066137022</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9087,7 +9087,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>251852015664</v>
+        <v>755556046992</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>251852015664</v>
+        <v>755556046992</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>251852015664</v>
+        <v>755556046992</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>251832883788</v>
+        <v>755498651364</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10306,7 +10306,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>314072065062</v>
+        <v>942216195186</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>251832883788</v>
+        <v>755498651364</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12474,7 +12474,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE79" t="n">
         <v>5</v>
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE84" t="n">
         <v>9</v>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14032,7 +14032,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE89" t="n">
         <v>8</v>
@@ -14338,7 +14338,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE90" t="n">
         <v>11</v>
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14918,7 +14918,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE95" t="n">
         <v>3</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>335506143474</v>
+        <v>1006518430422</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE100" t="n">
         <v>3</v>
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE102" t="n">
         <v>17</v>
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE103" t="n">
         <v>4</v>
@@ -16411,7 +16411,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -16556,7 +16556,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -16701,7 +16701,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17164,7 +17164,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17611,7 +17611,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18046,7 +18046,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE115" t="n">
         <v>8</v>
@@ -18201,7 +18201,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18962,7 +18962,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19119,7 +19119,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19274,7 +19274,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -19431,7 +19431,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -19588,7 +19588,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -19745,7 +19745,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -19892,7 +19892,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -20043,7 +20043,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -20200,7 +20200,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -20357,7 +20357,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>272227463604</v>
+        <v>816682390812</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -20514,7 +20514,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -20671,7 +20671,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20981,7 +20981,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21273,7 +21273,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21418,7 +21418,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21563,7 +21563,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21708,7 +21708,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21853,7 +21853,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22143,7 +22143,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22288,7 +22288,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22433,7 +22433,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22578,7 +22578,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22723,7 +22723,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22868,7 +22868,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23013,7 +23013,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23158,7 +23158,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23303,7 +23303,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23593,7 +23593,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23738,7 +23738,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23883,7 +23883,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24028,7 +24028,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24173,7 +24173,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24463,7 +24463,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24608,7 +24608,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24753,7 +24753,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24898,7 +24898,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25043,7 +25043,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25333,7 +25333,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25478,7 +25478,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25623,7 +25623,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25768,7 +25768,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25913,7 +25913,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26058,7 +26058,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26203,7 +26203,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26348,7 +26348,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26493,7 +26493,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26638,7 +26638,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26783,7 +26783,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27073,7 +27073,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27218,7 +27218,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27363,7 +27363,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27508,7 +27508,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27798,7 +27798,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27943,7 +27943,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28233,7 +28233,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28378,7 +28378,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28813,7 +28813,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28958,7 +28958,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29103,7 +29103,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29248,7 +29248,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29393,7 +29393,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29538,7 +29538,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29683,7 +29683,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29828,7 +29828,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30118,7 +30118,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30263,7 +30263,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30553,7 +30553,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30698,7 +30698,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30843,7 +30843,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30988,7 +30988,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31133,7 +31133,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31278,7 +31278,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31423,7 +31423,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31568,7 +31568,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31713,7 +31713,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31858,7 +31858,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32003,7 +32003,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32148,7 +32148,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32438,7 +32438,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32728,7 +32728,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32873,7 +32873,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33018,7 +33018,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33163,7 +33163,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33308,7 +33308,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33453,7 +33453,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33598,7 +33598,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33743,7 +33743,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -33888,7 +33888,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34033,7 +34033,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34178,7 +34178,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34323,7 +34323,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34468,7 +34468,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34613,7 +34613,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34758,7 +34758,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34903,7 +34903,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35048,7 +35048,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35193,7 +35193,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35338,7 +35338,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35483,7 +35483,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -35773,7 +35773,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35918,7 +35918,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36063,7 +36063,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36208,7 +36208,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36353,7 +36353,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36643,7 +36643,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -36788,7 +36788,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37078,7 +37078,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37223,7 +37223,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37368,7 +37368,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -37513,7 +37513,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -37658,7 +37658,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -37803,7 +37803,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -37948,7 +37948,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38093,7 +38093,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38238,7 +38238,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38383,7 +38383,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -38528,7 +38528,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -38673,7 +38673,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -38818,7 +38818,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -38963,7 +38963,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39108,7 +39108,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39253,7 +39253,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39398,7 +39398,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -39543,7 +39543,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -39688,7 +39688,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -39833,7 +39833,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -39978,7 +39978,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40123,7 +40123,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40268,7 +40268,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40413,7 +40413,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -40558,7 +40558,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -40848,7 +40848,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -40993,7 +40993,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41283,7 +41283,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -41428,7 +41428,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -41573,7 +41573,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -41718,7 +41718,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -41863,7 +41863,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42153,7 +42153,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42298,7 +42298,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -42443,7 +42443,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -42588,7 +42588,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -42733,7 +42733,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -42878,7 +42878,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -43023,7 +43023,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -43168,7 +43168,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -43313,7 +43313,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -43458,7 +43458,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -43603,7 +43603,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -43748,7 +43748,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -43893,7 +43893,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -44038,7 +44038,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -44183,7 +44183,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -44328,7 +44328,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -44473,7 +44473,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -44618,7 +44618,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -44763,7 +44763,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -44908,7 +44908,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -45053,7 +45053,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -45198,7 +45198,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -45343,7 +45343,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -45488,7 +45488,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -45633,7 +45633,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -45923,7 +45923,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -46068,7 +46068,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -46213,7 +46213,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -46358,7 +46358,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -46503,7 +46503,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -46648,7 +46648,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -46793,7 +46793,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE312" t="n">
         <v>3</v>
@@ -46938,7 +46938,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -47083,7 +47083,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -47228,7 +47228,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -47373,7 +47373,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE316" t="n">
         <v>3</v>
@@ -47518,7 +47518,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -47663,7 +47663,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -47808,7 +47808,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -47953,7 +47953,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -48098,7 +48098,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -48243,7 +48243,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -48388,7 +48388,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -48533,7 +48533,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -48678,7 +48678,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -48823,7 +48823,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -48968,7 +48968,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -49113,7 +49113,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -49258,7 +49258,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -49403,7 +49403,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -49548,7 +49548,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -49693,7 +49693,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -49838,7 +49838,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -50128,7 +50128,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -50273,7 +50273,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -50418,7 +50418,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -50563,7 +50563,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -50708,7 +50708,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -50853,7 +50853,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -51008,7 +51008,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>258050743488</v>
+        <v>774152230464</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -51161,7 +51161,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>313813784736</v>
+        <v>941441354208</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -51306,7 +51306,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -51451,7 +51451,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -51596,7 +51596,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -51741,7 +51741,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -51886,7 +51886,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -52031,7 +52031,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -52176,7 +52176,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -52331,7 +52331,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -52476,7 +52476,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -52621,7 +52621,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -52774,7 +52774,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -52928,7 +52928,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -53073,7 +53073,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -53371,7 +53371,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -53516,7 +53516,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE358" t="n">
         <v>2</v>
@@ -53671,7 +53671,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>258050743488</v>
+        <v>774152230464</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -53828,7 +53828,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -53981,7 +53981,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -54138,7 +54138,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -54285,7 +54285,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -54440,7 +54440,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -54597,7 +54597,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -54754,7 +54754,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -54909,7 +54909,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -55060,7 +55060,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>251137758960</v>
+        <v>753413276880</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -55213,7 +55213,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>251137758960</v>
+        <v>753413276880</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -55366,7 +55366,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>251137758960</v>
+        <v>753413276880</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -55513,7 +55513,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -55664,7 +55664,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>313813784736</v>
+        <v>941441354208</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -55817,7 +55817,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -55972,7 +55972,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -56119,7 +56119,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -56260,7 +56260,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -56405,7 +56405,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -56550,7 +56550,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -56705,7 +56705,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -56852,7 +56852,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -56997,7 +56997,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -57138,7 +57138,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -57289,7 +57289,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -57442,7 +57442,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -57595,7 +57595,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -57752,7 +57752,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -57909,7 +57909,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -58066,7 +58066,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -58223,7 +58223,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>258050743488</v>
+        <v>774152230464</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -58380,7 +58380,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE390" t="n">
         <v>5</v>
@@ -58537,7 +58537,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -58692,7 +58692,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -58847,7 +58847,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -59004,7 +59004,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -59161,7 +59161,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -59318,7 +59318,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -59465,7 +59465,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -59623,7 +59623,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -59780,7 +59780,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -59937,7 +59937,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -60094,7 +60094,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -60251,7 +60251,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>313813824102</v>
+        <v>941441472306</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -60406,7 +60406,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -60554,7 +60554,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -60709,7 +60709,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>314072104590</v>
+        <v>942216313770</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>314072104590</v>
+        <v>942216313770</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -61019,7 +61019,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>314072104590</v>
+        <v>942216313770</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -61164,7 +61164,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE408" t="n">
         <v>2</v>
@@ -61319,7 +61319,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -61472,7 +61472,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -61629,7 +61629,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -61786,7 +61786,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>316135119024</v>
+        <v>948405357072</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -61939,7 +61939,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -62094,7 +62094,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -62249,7 +62249,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -62402,7 +62402,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -62557,7 +62557,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -62704,7 +62704,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -62859,7 +62859,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -63016,7 +63016,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>258050743488</v>
+        <v>774152230464</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -63173,7 +63173,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>251855243676</v>
+        <v>755565731028</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -63328,7 +63328,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -63483,7 +63483,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -63640,7 +63640,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -63787,7 +63787,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -63932,7 +63932,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE426" t="n">
         <v>2</v>
@@ -64085,7 +64085,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE427" t="n">
         <v>5</v>
@@ -64238,7 +64238,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE428" t="n">
         <v>229</v>
@@ -64383,7 +64383,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -64528,7 +64528,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE430" t="n">
         <v>2</v>
@@ -64683,7 +64683,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE431" t="n">
         <v>4</v>
@@ -64828,7 +64828,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -64977,7 +64977,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -65122,7 +65122,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE434" t="n">
         <v>2</v>
@@ -65275,7 +65275,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -65428,7 +65428,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -65573,7 +65573,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -65718,7 +65718,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -65873,7 +65873,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -66028,7 +66028,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -66183,7 +66183,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -66336,7 +66336,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -66485,7 +66485,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE443" t="n">
         <v>3</v>
@@ -66641,7 +66641,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -66786,7 +66786,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -66927,7 +66927,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -67072,7 +67072,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -67217,7 +67217,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -67362,7 +67362,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -67507,7 +67507,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -67660,7 +67660,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -67815,7 +67815,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>
@@ -67970,7 +67970,7 @@
         </is>
       </c>
       <c r="AD453" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE453" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>22050424551924</v>
+        <v>66151273655772</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>30565152059166</v>
+        <v>91695456177498</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE11" t="n">
         <v>19</v>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE15" t="n">
         <v>17</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>25439840472528</v>
+        <v>76319521417584</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>27175997621394</v>
+        <v>81527992864182</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>22050424551924</v>
+        <v>66151273655772</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>22050424551924</v>
+        <v>66151273655772</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>20899785699594</v>
+        <v>62699357098782</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9042,7 +9042,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>20400013268784</v>
+        <v>61200039806352</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>20400013268784</v>
+        <v>61200039806352</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>20400013268784</v>
+        <v>61200039806352</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>20398463586828</v>
+        <v>61195390760484</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>25439837270022</v>
+        <v>76319511810066</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11013,7 +11013,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>20398463586828</v>
+        <v>61195390760484</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>20356622174016</v>
+        <v>61069866522048</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11481,7 +11481,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11783,7 +11783,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12393,7 +12393,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12705,7 +12705,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE80" t="n">
         <v>5</v>
@@ -12861,7 +12861,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE85" t="n">
         <v>9</v>
@@ -13629,7 +13629,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13941,7 +13941,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE89" t="n">
         <v>8</v>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE90" t="n">
         <v>11</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE91" t="n">
         <v>11</v>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14677,7 +14677,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14821,7 +14821,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE95" t="n">
         <v>3</v>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15414,7 +15414,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>27175997621394</v>
+        <v>81527992864182</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15570,7 +15570,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15716,7 +15716,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE100" t="n">
         <v>3</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE101" t="n">
         <v>3</v>
@@ -16016,7 +16016,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE102" t="n">
         <v>18</v>
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE103" t="n">
         <v>4</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE104" t="n">
         <v>4</v>
@@ -16448,7 +16448,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE105" t="n">
         <v>4</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16746,7 +16746,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17496,7 +17496,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17640,7 +17640,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17784,7 +17784,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE115" t="n">
         <v>8</v>
@@ -18082,7 +18082,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -18382,7 +18382,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18838,7 +18838,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18994,7 +18994,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19148,7 +19148,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>20356622174016</v>
+        <v>61069866522048</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -19460,7 +19460,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>20356622174016</v>
+        <v>61069866522048</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -19616,7 +19616,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>20356622174016</v>
+        <v>61069866522048</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -19762,7 +19762,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19912,7 +19912,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -20068,7 +20068,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -20224,7 +20224,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>22050424551924</v>
+        <v>66151273655772</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -20380,7 +20380,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -20536,7 +20536,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -20692,7 +20692,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20844,7 +20844,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20990,7 +20990,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21278,7 +21278,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21422,7 +21422,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21566,7 +21566,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21710,7 +21710,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21854,7 +21854,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22142,7 +22142,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22286,7 +22286,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22430,7 +22430,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22574,7 +22574,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22718,7 +22718,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23006,7 +23006,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23150,7 +23150,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23294,7 +23294,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23582,7 +23582,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23726,7 +23726,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23870,7 +23870,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24014,7 +24014,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24590,7 +24590,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24878,7 +24878,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25022,7 +25022,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25166,7 +25166,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25310,7 +25310,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25454,7 +25454,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25598,7 +25598,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25742,7 +25742,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25886,7 +25886,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26030,7 +26030,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26318,7 +26318,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26462,7 +26462,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26606,7 +26606,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26750,7 +26750,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26894,7 +26894,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27038,7 +27038,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27182,7 +27182,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27326,7 +27326,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27614,7 +27614,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27758,7 +27758,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27902,7 +27902,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28046,7 +28046,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28190,7 +28190,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28334,7 +28334,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28478,7 +28478,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28622,7 +28622,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28910,7 +28910,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29054,7 +29054,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29198,7 +29198,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29342,7 +29342,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29486,7 +29486,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29630,7 +29630,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29774,7 +29774,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29918,7 +29918,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30062,7 +30062,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30206,7 +30206,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30350,7 +30350,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30494,7 +30494,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30638,7 +30638,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30782,7 +30782,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30926,7 +30926,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31070,7 +31070,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31214,7 +31214,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31358,7 +31358,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31502,7 +31502,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31646,7 +31646,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -31790,7 +31790,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31934,7 +31934,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32078,7 +32078,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32222,7 +32222,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32366,7 +32366,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32510,7 +32510,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32654,7 +32654,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32942,7 +32942,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33230,7 +33230,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33374,7 +33374,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33518,7 +33518,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -33662,7 +33662,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -33806,7 +33806,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33950,7 +33950,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34094,7 +34094,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34238,7 +34238,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34382,7 +34382,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34526,7 +34526,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34670,7 +34670,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -34814,7 +34814,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34958,7 +34958,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35102,7 +35102,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35246,7 +35246,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35390,7 +35390,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -35534,7 +35534,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35678,7 +35678,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -35822,7 +35822,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35966,7 +35966,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36110,7 +36110,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36398,7 +36398,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -36542,7 +36542,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36686,7 +36686,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -36830,7 +36830,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36974,7 +36974,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37118,7 +37118,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -37262,7 +37262,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -37406,7 +37406,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -37550,7 +37550,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -37694,7 +37694,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -37838,7 +37838,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -37982,7 +37982,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38126,7 +38126,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -38270,7 +38270,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -38414,7 +38414,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -38558,7 +38558,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -38846,7 +38846,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -38990,7 +38990,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39134,7 +39134,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -39278,7 +39278,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -39422,7 +39422,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -39566,7 +39566,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -39710,7 +39710,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -39854,7 +39854,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -39998,7 +39998,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40142,7 +40142,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -40286,7 +40286,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -40430,7 +40430,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -40718,7 +40718,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -40862,7 +40862,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41006,7 +41006,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -41150,7 +41150,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -41294,7 +41294,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -41438,7 +41438,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -41582,7 +41582,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -41726,7 +41726,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42014,7 +42014,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -42158,7 +42158,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -42302,7 +42302,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -42446,7 +42446,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -42590,7 +42590,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -42734,7 +42734,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -42878,7 +42878,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -43022,7 +43022,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -43166,7 +43166,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -43310,7 +43310,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -43454,7 +43454,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -43598,7 +43598,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -43742,7 +43742,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -43886,7 +43886,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -44030,7 +44030,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -44318,7 +44318,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -44462,7 +44462,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -44606,7 +44606,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -44750,7 +44750,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -44894,7 +44894,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -45038,7 +45038,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -45182,7 +45182,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -45326,7 +45326,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -45470,7 +45470,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -45614,7 +45614,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -45758,7 +45758,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -45902,7 +45902,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -46046,7 +46046,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -46190,7 +46190,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -46334,7 +46334,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -46478,7 +46478,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE312" t="n">
         <v>3</v>
@@ -46622,7 +46622,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -46766,7 +46766,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -46910,7 +46910,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -47054,7 +47054,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE316" t="n">
         <v>3</v>
@@ -47198,7 +47198,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -47342,7 +47342,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -47630,7 +47630,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -47774,7 +47774,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -47918,7 +47918,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -48062,7 +48062,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -48206,7 +48206,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -48350,7 +48350,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -48494,7 +48494,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -48638,7 +48638,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -48782,7 +48782,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -48926,7 +48926,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -49070,7 +49070,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -49214,7 +49214,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -49358,7 +49358,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -49502,7 +49502,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -49646,7 +49646,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -49790,7 +49790,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -49934,7 +49934,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -50078,7 +50078,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -50222,7 +50222,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -50366,7 +50366,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -50510,7 +50510,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -50664,7 +50664,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>20902110222528</v>
+        <v>62706330667584</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -50816,7 +50816,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>25418916563616</v>
+        <v>76256749690848</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -50960,7 +50960,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -51104,7 +51104,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -51248,7 +51248,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -51392,7 +51392,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -51536,7 +51536,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -51680,7 +51680,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -51824,7 +51824,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -51978,7 +51978,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -52122,7 +52122,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -52418,7 +52418,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -52571,7 +52571,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -52715,7 +52715,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -52859,7 +52859,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -53011,7 +53011,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -53155,7 +53155,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE358" t="n">
         <v>2</v>
@@ -53309,7 +53309,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>20902110222528</v>
+        <v>62706330667584</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -53465,7 +53465,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -53617,7 +53617,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -53773,7 +53773,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -53919,7 +53919,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -54073,7 +54073,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -54229,7 +54229,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -54385,7 +54385,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -54539,7 +54539,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -54689,7 +54689,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>20342158475760</v>
+        <v>61026475427280</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -54841,7 +54841,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>20342158475760</v>
+        <v>61026475427280</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -54993,7 +54993,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>20342158475760</v>
+        <v>61026475427280</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -55139,7 +55139,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -55289,7 +55289,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>25418916563616</v>
+        <v>76256749690848</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -55441,7 +55441,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -55595,7 +55595,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -55741,7 +55741,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -55881,7 +55881,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -56025,7 +56025,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -56169,7 +56169,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -56323,7 +56323,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -56469,7 +56469,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -56613,7 +56613,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -56753,7 +56753,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -56903,7 +56903,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -57055,7 +57055,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -57207,7 +57207,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -57363,7 +57363,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -57519,7 +57519,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -57675,7 +57675,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -57831,7 +57831,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>20902110222528</v>
+        <v>62706330667584</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -57987,7 +57987,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE390" t="n">
         <v>5</v>
@@ -58143,7 +58143,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -58297,7 +58297,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -58451,7 +58451,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -58607,7 +58607,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -58763,7 +58763,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -58919,7 +58919,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -59065,7 +59065,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -59222,7 +59222,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -59378,7 +59378,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -59534,7 +59534,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -59690,7 +59690,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>25418919752262</v>
+        <v>76256759256786</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -60000,7 +60000,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -60147,7 +60147,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -60301,7 +60301,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>25439840471790</v>
+        <v>76319521415370</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>25439840471790</v>
+        <v>76319521415370</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -60609,7 +60609,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>25439840471790</v>
+        <v>76319521415370</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -60753,7 +60753,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE408" t="n">
         <v>3</v>
@@ -60907,7 +60907,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -61059,7 +61059,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -61215,7 +61215,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -61371,7 +61371,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>25606944640944</v>
+        <v>76820833922832</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -61523,7 +61523,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -61677,7 +61677,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -61831,7 +61831,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -61983,7 +61983,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -62137,7 +62137,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -62283,7 +62283,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -62437,7 +62437,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -62593,7 +62593,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>20902110222528</v>
+        <v>62706330667584</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -62749,7 +62749,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>20400274737756</v>
+        <v>61200824213268</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -62903,7 +62903,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -63057,7 +63057,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -63213,7 +63213,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -63359,7 +63359,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -63503,7 +63503,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE426" t="n">
         <v>2</v>
@@ -63655,7 +63655,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE427" t="n">
         <v>5</v>
@@ -63807,7 +63807,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE428" t="n">
         <v>229</v>
@@ -63951,7 +63951,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE429" t="n">
         <v>1</v>
@@ -64095,7 +64095,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE430" t="n">
         <v>2</v>
@@ -64249,7 +64249,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE431" t="n">
         <v>4</v>
@@ -64393,7 +64393,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE432" t="n">
         <v>1</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE433" t="n">
         <v>1</v>
@@ -64685,7 +64685,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE434" t="n">
         <v>2</v>
@@ -64837,7 +64837,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -64989,7 +64989,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE436" t="n">
         <v>1</v>
@@ -65133,7 +65133,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -65277,7 +65277,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -65431,7 +65431,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -65585,7 +65585,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -65739,7 +65739,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -65891,7 +65891,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -66039,7 +66039,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE443" t="n">
         <v>3</v>
@@ -66194,7 +66194,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -66338,7 +66338,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE445" t="n">
         <v>1</v>
@@ -66478,7 +66478,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -66622,7 +66622,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -66766,7 +66766,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -66910,7 +66910,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -67054,7 +67054,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -67206,7 +67206,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -67360,7 +67360,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>
@@ -67514,7 +67514,7 @@
         </is>
       </c>
       <c r="AD453" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE453" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>198453820967316</v>
+        <v>595361462901948</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>275086368532494</v>
+        <v>825259105597482</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE11" t="n">
         <v>19</v>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE15" t="n">
         <v>17</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>228958564252752</v>
+        <v>686875692758256</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>244583978592546</v>
+        <v>733751935777638</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>198453820967316</v>
+        <v>595361462901948</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>198453820967316</v>
+        <v>595361462901948</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>188098071296346</v>
+        <v>564294213889038</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>183600119419056</v>
+        <v>550800358257168</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>183600119419056</v>
+        <v>550800358257168</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10392,7 +10392,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>183600119419056</v>
+        <v>550800358257168</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>183586172281452</v>
+        <v>550758516844356</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>228958535430198</v>
+        <v>686875606290594</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11631,7 +11631,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>183586172281452</v>
+        <v>550758516844356</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>183209599566144</v>
+        <v>549628798698432</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE83" t="n">
         <v>5</v>
@@ -13323,7 +13323,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13937,7 +13937,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE88" t="n">
         <v>9</v>
@@ -14091,7 +14091,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14555,7 +14555,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE92" t="n">
         <v>8</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE93" t="n">
         <v>11</v>
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE94" t="n">
         <v>11</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15283,7 +15283,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15431,7 +15431,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE98" t="n">
         <v>3</v>
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15722,7 +15722,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>244583978592546</v>
+        <v>733751935777638</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16032,7 +16032,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE103" t="n">
         <v>3</v>
@@ -16326,7 +16326,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE104" t="n">
         <v>3</v>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE105" t="n">
         <v>18</v>
@@ -16622,7 +16622,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE106" t="n">
         <v>4</v>
@@ -16766,7 +16766,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE107" t="n">
         <v>4</v>
@@ -16910,7 +16910,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE108" t="n">
         <v>4</v>
@@ -17054,7 +17054,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17208,7 +17208,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17362,7 +17362,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17514,7 +17514,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17814,7 +17814,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18102,7 +18102,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18246,7 +18246,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE118" t="n">
         <v>8</v>
@@ -18544,7 +18544,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18844,7 +18844,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18990,7 +18990,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19144,7 +19144,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -19456,7 +19456,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -19610,7 +19610,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>183209599566144</v>
+        <v>549628798698432</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -19766,7 +19766,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>183209599566144</v>
+        <v>549628798698432</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>183209599566144</v>
+        <v>549628798698432</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -20224,7 +20224,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -20374,7 +20374,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -20530,7 +20530,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -20686,7 +20686,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>198453820967316</v>
+        <v>595361462901948</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20842,7 +20842,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20998,7 +20998,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -21154,7 +21154,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE136" t="n">
         <v>1</v>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -21452,7 +21452,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22172,7 +22172,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22316,7 +22316,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22460,7 +22460,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22604,7 +22604,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22748,7 +22748,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22892,7 +22892,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23180,7 +23180,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23324,7 +23324,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23468,7 +23468,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23756,7 +23756,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23900,7 +23900,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24044,7 +24044,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24188,7 +24188,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24332,7 +24332,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24476,7 +24476,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24764,7 +24764,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25052,7 +25052,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25196,7 +25196,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25340,7 +25340,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25484,7 +25484,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25628,7 +25628,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25772,7 +25772,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25916,7 +25916,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26060,7 +26060,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26204,7 +26204,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26348,7 +26348,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26492,7 +26492,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26636,7 +26636,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26780,7 +26780,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26924,7 +26924,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27068,7 +27068,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27212,7 +27212,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27500,7 +27500,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27644,7 +27644,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27788,7 +27788,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27932,7 +27932,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28076,7 +28076,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28220,7 +28220,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28364,7 +28364,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28652,7 +28652,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28796,7 +28796,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28940,7 +28940,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29084,7 +29084,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29228,7 +29228,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29372,7 +29372,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29516,7 +29516,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29660,7 +29660,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29804,7 +29804,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29948,7 +29948,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30092,7 +30092,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30236,7 +30236,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30380,7 +30380,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30668,7 +30668,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30812,7 +30812,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30956,7 +30956,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31100,7 +31100,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31244,7 +31244,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31388,7 +31388,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31532,7 +31532,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31676,7 +31676,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -31820,7 +31820,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31964,7 +31964,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32108,7 +32108,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32252,7 +32252,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32396,7 +32396,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32540,7 +32540,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32684,7 +32684,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -32828,7 +32828,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32972,7 +32972,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33116,7 +33116,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33260,7 +33260,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33404,7 +33404,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33548,7 +33548,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -33836,7 +33836,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33980,7 +33980,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34124,7 +34124,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34268,7 +34268,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34412,7 +34412,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34556,7 +34556,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34700,7 +34700,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -34844,7 +34844,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34988,7 +34988,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35132,7 +35132,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35276,7 +35276,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35420,7 +35420,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -35564,7 +35564,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35708,7 +35708,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -35852,7 +35852,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35996,7 +35996,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36284,7 +36284,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36428,7 +36428,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -36572,7 +36572,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -36860,7 +36860,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37004,7 +37004,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37148,7 +37148,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -37292,7 +37292,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -37436,7 +37436,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -37580,7 +37580,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -37724,7 +37724,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -37868,7 +37868,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38012,7 +38012,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38156,7 +38156,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -38300,7 +38300,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -38444,7 +38444,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -38588,7 +38588,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -38732,7 +38732,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -38876,7 +38876,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39020,7 +39020,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39164,7 +39164,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -39452,7 +39452,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -39596,7 +39596,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -39740,7 +39740,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -39884,7 +39884,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40028,7 +40028,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40172,7 +40172,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -40316,7 +40316,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -40460,7 +40460,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -40604,7 +40604,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -40748,7 +40748,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -40892,7 +40892,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41036,7 +41036,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -41180,7 +41180,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -41468,7 +41468,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -41612,7 +41612,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -41756,7 +41756,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -41900,7 +41900,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42044,7 +42044,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -42188,7 +42188,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -42332,7 +42332,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -42476,7 +42476,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -42620,7 +42620,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -42764,7 +42764,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -42908,7 +42908,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -43196,7 +43196,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -43340,7 +43340,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -43484,7 +43484,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -43628,7 +43628,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -43772,7 +43772,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -43916,7 +43916,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -44060,7 +44060,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -44204,7 +44204,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -44348,7 +44348,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -44492,7 +44492,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -44636,7 +44636,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -44780,7 +44780,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -45068,7 +45068,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -45212,7 +45212,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -45356,7 +45356,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -45500,7 +45500,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -45644,7 +45644,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -45788,7 +45788,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -45932,7 +45932,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -46076,7 +46076,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -46220,7 +46220,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -46364,7 +46364,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -46508,7 +46508,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -46652,7 +46652,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -46796,7 +46796,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -46940,7 +46940,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE315" t="n">
         <v>3</v>
@@ -47084,7 +47084,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE316" t="n">
         <v>2</v>
@@ -47228,7 +47228,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -47372,7 +47372,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -47516,7 +47516,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE319" t="n">
         <v>3</v>
@@ -47660,7 +47660,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE320" t="n">
         <v>2</v>
@@ -47804,7 +47804,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -47948,7 +47948,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -48092,7 +48092,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -48236,7 +48236,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -48380,7 +48380,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -48524,7 +48524,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -48668,7 +48668,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -48812,7 +48812,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -48956,7 +48956,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -49100,7 +49100,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -49244,7 +49244,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -49388,7 +49388,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -49532,7 +49532,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -49676,7 +49676,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -49820,7 +49820,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -49964,7 +49964,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -50108,7 +50108,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -50252,7 +50252,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -50396,7 +50396,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -50540,7 +50540,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -50684,7 +50684,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -50828,7 +50828,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -50972,7 +50972,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -51126,7 +51126,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>188118992002752</v>
+        <v>564356976008256</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -51278,7 +51278,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>228770249072544</v>
+        <v>686310747217632</v>
       </c>
       <c r="AE345" t="n">
         <v>2</v>
@@ -51422,7 +51422,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -51566,7 +51566,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -51710,7 +51710,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE348" t="n">
         <v>2</v>
@@ -51854,7 +51854,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE349" t="n">
         <v>2</v>
@@ -51998,7 +51998,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -52142,7 +52142,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -52286,7 +52286,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -52440,7 +52440,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -52584,7 +52584,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -52728,7 +52728,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -52880,7 +52880,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -53033,7 +53033,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -53177,7 +53177,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -53321,7 +53321,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -53617,7 +53617,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE361" t="n">
         <v>2</v>
@@ -53771,7 +53771,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>188118992002752</v>
+        <v>564356976008256</v>
       </c>
       <c r="AE362" t="n">
         <v>1</v>
@@ -53927,7 +53927,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -54079,7 +54079,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -54235,7 +54235,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -54381,7 +54381,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -54535,7 +54535,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -54691,7 +54691,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -54845,7 +54845,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -54995,7 +54995,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>183079426281840</v>
+        <v>549238278845520</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -55147,7 +55147,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>183079426281840</v>
+        <v>549238278845520</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -55299,7 +55299,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>183079426281840</v>
+        <v>549238278845520</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -55445,7 +55445,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -55595,7 +55595,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>228770249072544</v>
+        <v>686310747217632</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -55747,7 +55747,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -55901,7 +55901,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -56047,7 +56047,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -56187,7 +56187,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -56331,7 +56331,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -56475,7 +56475,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -56629,7 +56629,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -56775,7 +56775,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -56919,7 +56919,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -57059,7 +57059,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -57209,7 +57209,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -57361,7 +57361,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -57513,7 +57513,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -57669,7 +57669,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -57825,7 +57825,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -57981,7 +57981,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -58137,7 +58137,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>188118992002752</v>
+        <v>564356976008256</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -58293,7 +58293,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE392" t="n">
         <v>5</v>
@@ -58449,7 +58449,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE393" t="n">
         <v>1</v>
@@ -58603,7 +58603,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -58757,7 +58757,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -58913,7 +58913,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -59069,7 +59069,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -59225,7 +59225,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -59371,7 +59371,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -59528,7 +59528,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -59684,7 +59684,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -59840,7 +59840,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -60152,7 +60152,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>228770277770358</v>
+        <v>686310833311074</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -60306,7 +60306,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -60453,7 +60453,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -60607,7 +60607,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>228958564246110</v>
+        <v>686875692738330</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -60761,7 +60761,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>228958564246110</v>
+        <v>686875692738330</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -60915,7 +60915,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>228958564246110</v>
+        <v>686875692738330</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -61059,7 +61059,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE410" t="n">
         <v>3</v>
@@ -61213,7 +61213,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE411" t="n">
         <v>1</v>
@@ -61365,7 +61365,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -61521,7 +61521,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -61677,7 +61677,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>230462501768496</v>
+        <v>691387505305488</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -61829,7 +61829,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -61983,7 +61983,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -62137,7 +62137,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -62289,7 +62289,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -62443,7 +62443,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -62589,7 +62589,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -62743,7 +62743,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -62899,7 +62899,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>188118992002752</v>
+        <v>564356976008256</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -63055,7 +63055,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>183602472639804</v>
+        <v>550807417919412</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -63209,7 +63209,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -63363,7 +63363,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -63519,7 +63519,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -63665,7 +63665,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -63809,7 +63809,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE428" t="n">
         <v>2</v>
@@ -63961,7 +63961,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE429" t="n">
         <v>5</v>
@@ -64113,7 +64113,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE430" t="n">
         <v>229</v>
@@ -64257,7 +64257,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -64401,7 +64401,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE432" t="n">
         <v>2</v>
@@ -64555,7 +64555,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE433" t="n">
         <v>4</v>
@@ -64699,7 +64699,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -64847,7 +64847,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -64991,7 +64991,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE436" t="n">
         <v>2</v>
@@ -65143,7 +65143,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -65295,7 +65295,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -65439,7 +65439,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -65583,7 +65583,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -65737,7 +65737,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -65891,7 +65891,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -66045,7 +66045,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE443" t="n">
         <v>1</v>
@@ -66197,7 +66197,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -66345,7 +66345,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE445" t="n">
         <v>3</v>
@@ -66500,7 +66500,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -66644,7 +66644,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -66784,7 +66784,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -66928,7 +66928,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -67072,7 +67072,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -67216,7 +67216,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -67360,7 +67360,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>
@@ -67512,7 +67512,7 @@
         </is>
       </c>
       <c r="AD453" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE453" t="n">
         <v>1</v>
@@ -67666,7 +67666,7 @@
         </is>
       </c>
       <c r="AD454" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE454" t="n">
         <v>1</v>
@@ -67820,7 +67820,7 @@
         </is>
       </c>
       <c r="AD455" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE455" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1786084388705844</v>
+        <v>5358253166117532</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2475777316792446</v>
+        <v>7427331950377338</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE11" t="n">
         <v>19</v>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE15" t="n">
         <v>17</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1786105568815239</v>
+        <v>5358316706445717</v>
       </c>
       <c r="AE29" t="n">
         <v>3</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6089,7 +6089,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2060627078274768</v>
+        <v>6181881234824304</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2201255807332914</v>
+        <v>6603767421998742</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1786084388705844</v>
+        <v>5358253166117532</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1786084388705844</v>
+        <v>5358253166117532</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1784599277913912</v>
+        <v>5353797833741736</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1692882641667114</v>
+        <v>5078647925001342</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10233,7 +10233,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1652401074771504</v>
+        <v>4957203224314512</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1652401074771504</v>
+        <v>4957203224314512</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1652401074771504</v>
+        <v>4957203224314512</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1652275550533068</v>
+        <v>4956826651599204</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10858,7 +10858,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11162,7 +11162,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2060626818871782</v>
+        <v>6181880456615346</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1652275550533068</v>
+        <v>4956826651599204</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1648886396095296</v>
+        <v>4946659188285888</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12542,7 +12542,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12852,7 +12852,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13320,7 +13320,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE84" t="n">
         <v>5</v>
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13788,7 +13788,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13944,7 +13944,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE89" t="n">
         <v>9</v>
@@ -14244,7 +14244,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14556,7 +14556,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14708,7 +14708,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE93" t="n">
         <v>8</v>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE94" t="n">
         <v>11</v>
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE95" t="n">
         <v>11</v>
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15292,7 +15292,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE99" t="n">
         <v>3</v>
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15875,7 +15875,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16029,7 +16029,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2201255807332914</v>
+        <v>6603767421998742</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16331,7 +16331,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE104" t="n">
         <v>3</v>
@@ -16479,7 +16479,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE105" t="n">
         <v>3</v>
@@ -16631,7 +16631,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE106" t="n">
         <v>18</v>
@@ -16775,7 +16775,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE107" t="n">
         <v>4</v>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE108" t="n">
         <v>4</v>
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE109" t="n">
         <v>4</v>
@@ -17207,7 +17207,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17361,7 +17361,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17515,7 +17515,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17967,7 +17967,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18111,7 +18111,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18255,7 +18255,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -18399,7 +18399,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18543,7 +18543,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE119" t="n">
         <v>8</v>
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -18843,7 +18843,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -19763,7 +19763,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1648886396095296</v>
+        <v>4946659188285888</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -19919,7 +19919,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -20075,7 +20075,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1648886396095296</v>
+        <v>4946659188285888</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -20231,7 +20231,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1648886396095296</v>
+        <v>4946659188285888</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -20377,7 +20377,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -20683,7 +20683,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -20839,7 +20839,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1786084388705844</v>
+        <v>5358253166117532</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -20995,7 +20995,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -21151,7 +21151,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE136" t="n">
         <v>1</v>
@@ -21307,7 +21307,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -21459,7 +21459,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE138" t="n">
         <v>1</v>
@@ -21605,7 +21605,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21749,7 +21749,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21893,7 +21893,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22037,7 +22037,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22181,7 +22181,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22325,7 +22325,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22469,7 +22469,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22613,7 +22613,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22757,7 +22757,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22901,7 +22901,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23045,7 +23045,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23189,7 +23189,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23333,7 +23333,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23477,7 +23477,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23621,7 +23621,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23765,7 +23765,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23909,7 +23909,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24053,7 +24053,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24197,7 +24197,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24341,7 +24341,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24629,7 +24629,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24773,7 +24773,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24917,7 +24917,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25061,7 +25061,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25205,7 +25205,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25349,7 +25349,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25493,7 +25493,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25637,7 +25637,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25781,7 +25781,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25925,7 +25925,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26069,7 +26069,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26213,7 +26213,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26357,7 +26357,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26501,7 +26501,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26645,7 +26645,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26789,7 +26789,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27077,7 +27077,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27221,7 +27221,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27365,7 +27365,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27509,7 +27509,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27797,7 +27797,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27941,7 +27941,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28229,7 +28229,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28373,7 +28373,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28517,7 +28517,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28661,7 +28661,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28805,7 +28805,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28949,7 +28949,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29093,7 +29093,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29237,7 +29237,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29381,7 +29381,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29525,7 +29525,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29669,7 +29669,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29813,7 +29813,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29957,7 +29957,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30101,7 +30101,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30245,7 +30245,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30389,7 +30389,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30533,7 +30533,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30677,7 +30677,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30965,7 +30965,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31109,7 +31109,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31253,7 +31253,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31397,7 +31397,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31541,7 +31541,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31685,7 +31685,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -31829,7 +31829,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31973,7 +31973,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32117,7 +32117,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32261,7 +32261,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32405,7 +32405,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32549,7 +32549,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32693,7 +32693,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -32837,7 +32837,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32981,7 +32981,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33125,7 +33125,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33413,7 +33413,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33557,7 +33557,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -33701,7 +33701,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -33845,7 +33845,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33989,7 +33989,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34133,7 +34133,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34277,7 +34277,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34421,7 +34421,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34565,7 +34565,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34709,7 +34709,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -34853,7 +34853,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34997,7 +34997,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35141,7 +35141,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35285,7 +35285,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35429,7 +35429,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -35573,7 +35573,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35717,7 +35717,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -35861,7 +35861,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36005,7 +36005,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36149,7 +36149,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36293,7 +36293,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -36581,7 +36581,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36725,7 +36725,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -36869,7 +36869,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37013,7 +37013,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37157,7 +37157,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -37301,7 +37301,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -37445,7 +37445,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -37589,7 +37589,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -37733,7 +37733,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -37877,7 +37877,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38021,7 +38021,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38165,7 +38165,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -38309,7 +38309,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -38453,7 +38453,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -38597,7 +38597,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -38741,7 +38741,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39029,7 +39029,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39173,7 +39173,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -39317,7 +39317,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -39461,7 +39461,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -39605,7 +39605,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -39749,7 +39749,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -39893,7 +39893,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40037,7 +40037,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40181,7 +40181,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -40325,7 +40325,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -40469,7 +40469,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -40757,7 +40757,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -40901,7 +40901,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41045,7 +41045,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -41189,7 +41189,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -41333,7 +41333,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -41477,7 +41477,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -41621,7 +41621,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -41765,7 +41765,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -42197,7 +42197,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -42341,7 +42341,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -42485,7 +42485,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -42629,7 +42629,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -42773,7 +42773,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -42917,7 +42917,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -43061,7 +43061,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -43205,7 +43205,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -43349,7 +43349,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -43493,7 +43493,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE291" t="n">
         <v>2</v>
@@ -43637,7 +43637,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE292" t="n">
         <v>2</v>
@@ -43781,7 +43781,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -43925,7 +43925,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE294" t="n">
         <v>2</v>
@@ -44069,7 +44069,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -44213,7 +44213,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE296" t="n">
         <v>2</v>
@@ -44357,7 +44357,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE297" t="n">
         <v>2</v>
@@ -44501,7 +44501,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE298" t="n">
         <v>2</v>
@@ -44645,7 +44645,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE299" t="n">
         <v>2</v>
@@ -44789,7 +44789,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE300" t="n">
         <v>2</v>
@@ -44933,7 +44933,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE301" t="n">
         <v>2</v>
@@ -45077,7 +45077,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -45221,7 +45221,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE303" t="n">
         <v>2</v>
@@ -45365,7 +45365,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE304" t="n">
         <v>2</v>
@@ -45509,7 +45509,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE305" t="n">
         <v>2</v>
@@ -45653,7 +45653,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE306" t="n">
         <v>2</v>
@@ -45797,7 +45797,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE307" t="n">
         <v>2</v>
@@ -45941,7 +45941,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE308" t="n">
         <v>2</v>
@@ -46085,7 +46085,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE309" t="n">
         <v>2</v>
@@ -46229,7 +46229,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE310" t="n">
         <v>2</v>
@@ -46373,7 +46373,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE311" t="n">
         <v>2</v>
@@ -46517,7 +46517,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE312" t="n">
         <v>2</v>
@@ -46661,7 +46661,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE313" t="n">
         <v>2</v>
@@ -46805,7 +46805,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE314" t="n">
         <v>2</v>
@@ -46949,7 +46949,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE315" t="n">
         <v>2</v>
@@ -47093,7 +47093,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE316" t="n">
         <v>3</v>
@@ -47237,7 +47237,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE317" t="n">
         <v>2</v>
@@ -47381,7 +47381,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE318" t="n">
         <v>2</v>
@@ -47525,7 +47525,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE319" t="n">
         <v>2</v>
@@ -47669,7 +47669,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE320" t="n">
         <v>3</v>
@@ -47813,7 +47813,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE321" t="n">
         <v>2</v>
@@ -47957,7 +47957,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -48101,7 +48101,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE323" t="n">
         <v>2</v>
@@ -48245,7 +48245,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -48389,7 +48389,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -48533,7 +48533,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE326" t="n">
         <v>2</v>
@@ -48677,7 +48677,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -48821,7 +48821,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE328" t="n">
         <v>2</v>
@@ -48965,7 +48965,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE329" t="n">
         <v>2</v>
@@ -49109,7 +49109,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -49253,7 +49253,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -49397,7 +49397,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -49541,7 +49541,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE333" t="n">
         <v>2</v>
@@ -49685,7 +49685,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -49829,7 +49829,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE335" t="n">
         <v>2</v>
@@ -49973,7 +49973,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE336" t="n">
         <v>2</v>
@@ -50117,7 +50117,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE337" t="n">
         <v>2</v>
@@ -50261,7 +50261,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE338" t="n">
         <v>2</v>
@@ -50405,7 +50405,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -50549,7 +50549,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE340" t="n">
         <v>2</v>
@@ -50693,7 +50693,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE341" t="n">
         <v>2</v>
@@ -50837,7 +50837,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE342" t="n">
         <v>2</v>
@@ -50981,7 +50981,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE343" t="n">
         <v>2</v>
@@ -51125,7 +51125,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE344" t="n">
         <v>2</v>
@@ -51279,7 +51279,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>1693070928024768</v>
+        <v>5079212784074304</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -51431,7 +51431,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>2058932241652896</v>
+        <v>6176796724958688</v>
       </c>
       <c r="AE346" t="n">
         <v>2</v>
@@ -51575,7 +51575,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE347" t="n">
         <v>2</v>
@@ -51719,7 +51719,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE348" t="n">
         <v>2</v>
@@ -51863,7 +51863,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE349" t="n">
         <v>2</v>
@@ -52007,7 +52007,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE350" t="n">
         <v>2</v>
@@ -52151,7 +52151,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -52295,7 +52295,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -52439,7 +52439,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -52593,7 +52593,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -52737,7 +52737,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -52881,7 +52881,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -53033,7 +53033,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>
@@ -53186,7 +53186,7 @@
         </is>
       </c>
       <c r="AD358" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE358" t="n">
         <v>1</v>
@@ -53330,7 +53330,7 @@
         </is>
       </c>
       <c r="AD359" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE359" t="n">
         <v>1</v>
@@ -53474,7 +53474,7 @@
         </is>
       </c>
       <c r="AD360" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE360" t="n">
         <v>1</v>
@@ -53626,7 +53626,7 @@
         </is>
       </c>
       <c r="AD361" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE361" t="n">
         <v>1</v>
@@ -53770,7 +53770,7 @@
         </is>
       </c>
       <c r="AD362" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE362" t="n">
         <v>2</v>
@@ -53924,7 +53924,7 @@
         </is>
       </c>
       <c r="AD363" t="n">
-        <v>1693070928024768</v>
+        <v>5079212784074304</v>
       </c>
       <c r="AE363" t="n">
         <v>1</v>
@@ -54080,7 +54080,7 @@
         </is>
       </c>
       <c r="AD364" t="n">
-        <v>1784578097844612</v>
+        <v>5353734293533836</v>
       </c>
       <c r="AE364" t="n">
         <v>1</v>
@@ -54232,7 +54232,7 @@
         </is>
       </c>
       <c r="AD365" t="n">
-        <v>1784578097844612</v>
+        <v>5353734293533836</v>
       </c>
       <c r="AE365" t="n">
         <v>1</v>
@@ -54388,7 +54388,7 @@
         </is>
       </c>
       <c r="AD366" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE366" t="n">
         <v>1</v>
@@ -54534,7 +54534,7 @@
         </is>
       </c>
       <c r="AD367" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE367" t="n">
         <v>1</v>
@@ -54688,7 +54688,7 @@
         </is>
       </c>
       <c r="AD368" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE368" t="n">
         <v>1</v>
@@ -54844,7 +54844,7 @@
         </is>
       </c>
       <c r="AD369" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE369" t="n">
         <v>1</v>
@@ -54998,7 +54998,7 @@
         </is>
       </c>
       <c r="AD370" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE370" t="n">
         <v>1</v>
@@ -55148,7 +55148,7 @@
         </is>
       </c>
       <c r="AD371" t="n">
-        <v>1647714836536560</v>
+        <v>4943144509609680</v>
       </c>
       <c r="AE371" t="n">
         <v>1</v>
@@ -55300,7 +55300,7 @@
         </is>
       </c>
       <c r="AD372" t="n">
-        <v>1647714836536560</v>
+        <v>4943144509609680</v>
       </c>
       <c r="AE372" t="n">
         <v>1</v>
@@ -55452,7 +55452,7 @@
         </is>
       </c>
       <c r="AD373" t="n">
-        <v>1647714836536560</v>
+        <v>4943144509609680</v>
       </c>
       <c r="AE373" t="n">
         <v>1</v>
@@ -55598,7 +55598,7 @@
         </is>
       </c>
       <c r="AD374" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE374" t="n">
         <v>1</v>
@@ -55748,7 +55748,7 @@
         </is>
       </c>
       <c r="AD375" t="n">
-        <v>2058932241652896</v>
+        <v>6176796724958688</v>
       </c>
       <c r="AE375" t="n">
         <v>1</v>
@@ -55900,7 +55900,7 @@
         </is>
       </c>
       <c r="AD376" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE376" t="n">
         <v>1</v>
@@ -56054,7 +56054,7 @@
         </is>
       </c>
       <c r="AD377" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE377" t="n">
         <v>1</v>
@@ -56200,7 +56200,7 @@
         </is>
       </c>
       <c r="AD378" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE378" t="n">
         <v>1</v>
@@ -56340,7 +56340,7 @@
         </is>
       </c>
       <c r="AD379" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE379" t="n">
         <v>1</v>
@@ -56484,7 +56484,7 @@
         </is>
       </c>
       <c r="AD380" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE380" t="n">
         <v>1</v>
@@ -56628,7 +56628,7 @@
         </is>
       </c>
       <c r="AD381" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE381" t="n">
         <v>1</v>
@@ -56782,7 +56782,7 @@
         </is>
       </c>
       <c r="AD382" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE382" t="n">
         <v>1</v>
@@ -56928,7 +56928,7 @@
         </is>
       </c>
       <c r="AD383" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE383" t="n">
         <v>1</v>
@@ -57072,7 +57072,7 @@
         </is>
       </c>
       <c r="AD384" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE384" t="n">
         <v>1</v>
@@ -57212,7 +57212,7 @@
         </is>
       </c>
       <c r="AD385" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE385" t="n">
         <v>1</v>
@@ -57362,7 +57362,7 @@
         </is>
       </c>
       <c r="AD386" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE386" t="n">
         <v>1</v>
@@ -57514,7 +57514,7 @@
         </is>
       </c>
       <c r="AD387" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE387" t="n">
         <v>1</v>
@@ -57666,7 +57666,7 @@
         </is>
       </c>
       <c r="AD388" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE388" t="n">
         <v>1</v>
@@ -57822,7 +57822,7 @@
         </is>
       </c>
       <c r="AD389" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE389" t="n">
         <v>1</v>
@@ -57978,7 +57978,7 @@
         </is>
       </c>
       <c r="AD390" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE390" t="n">
         <v>1</v>
@@ -58134,7 +58134,7 @@
         </is>
       </c>
       <c r="AD391" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE391" t="n">
         <v>1</v>
@@ -58290,7 +58290,7 @@
         </is>
       </c>
       <c r="AD392" t="n">
-        <v>1693070928024768</v>
+        <v>5079212784074304</v>
       </c>
       <c r="AE392" t="n">
         <v>1</v>
@@ -58446,7 +58446,7 @@
         </is>
       </c>
       <c r="AD393" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE393" t="n">
         <v>5</v>
@@ -58602,7 +58602,7 @@
         </is>
       </c>
       <c r="AD394" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE394" t="n">
         <v>1</v>
@@ -58756,7 +58756,7 @@
         </is>
       </c>
       <c r="AD395" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE395" t="n">
         <v>1</v>
@@ -58910,7 +58910,7 @@
         </is>
       </c>
       <c r="AD396" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE396" t="n">
         <v>1</v>
@@ -59066,7 +59066,7 @@
         </is>
       </c>
       <c r="AD397" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE397" t="n">
         <v>1</v>
@@ -59222,7 +59222,7 @@
         </is>
       </c>
       <c r="AD398" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE398" t="n">
         <v>1</v>
@@ -59378,7 +59378,7 @@
         </is>
       </c>
       <c r="AD399" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE399" t="n">
         <v>1</v>
@@ -59524,7 +59524,7 @@
         </is>
       </c>
       <c r="AD400" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE400" t="n">
         <v>1</v>
@@ -59681,7 +59681,7 @@
         </is>
       </c>
       <c r="AD401" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE401" t="n">
         <v>1</v>
@@ -59837,7 +59837,7 @@
         </is>
       </c>
       <c r="AD402" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE402" t="n">
         <v>1</v>
@@ -59993,7 +59993,7 @@
         </is>
       </c>
       <c r="AD403" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE403" t="n">
         <v>1</v>
@@ -60149,7 +60149,7 @@
         </is>
       </c>
       <c r="AD404" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE404" t="n">
         <v>1</v>
@@ -60305,7 +60305,7 @@
         </is>
       </c>
       <c r="AD405" t="n">
-        <v>2058932499933222</v>
+        <v>6176797499799666</v>
       </c>
       <c r="AE405" t="n">
         <v>1</v>
@@ -60459,7 +60459,7 @@
         </is>
       </c>
       <c r="AD406" t="n">
-        <v>1784578097844612</v>
+        <v>5353734293533836</v>
       </c>
       <c r="AE406" t="n">
         <v>1</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="AD407" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE407" t="n">
         <v>1</v>
@@ -60760,7 +60760,7 @@
         </is>
       </c>
       <c r="AD408" t="n">
-        <v>2060627078214990</v>
+        <v>6181881234644970</v>
       </c>
       <c r="AE408" t="n">
         <v>1</v>
@@ -60914,7 +60914,7 @@
         </is>
       </c>
       <c r="AD409" t="n">
-        <v>2060627078214990</v>
+        <v>6181881234644970</v>
       </c>
       <c r="AE409" t="n">
         <v>1</v>
@@ -61068,7 +61068,7 @@
         </is>
       </c>
       <c r="AD410" t="n">
-        <v>2060627078214990</v>
+        <v>6181881234644970</v>
       </c>
       <c r="AE410" t="n">
         <v>1</v>
@@ -61212,7 +61212,7 @@
         </is>
       </c>
       <c r="AD411" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE411" t="n">
         <v>3</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="AD412" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE412" t="n">
         <v>1</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="AD413" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE413" t="n">
         <v>1</v>
@@ -61674,7 +61674,7 @@
         </is>
       </c>
       <c r="AD414" t="n">
-        <v>2074162515916464</v>
+        <v>6222487547749392</v>
       </c>
       <c r="AE414" t="n">
         <v>1</v>
@@ -61826,7 +61826,7 @@
         </is>
       </c>
       <c r="AD415" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE415" t="n">
         <v>1</v>
@@ -61980,7 +61980,7 @@
         </is>
       </c>
       <c r="AD416" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE416" t="n">
         <v>1</v>
@@ -62134,7 +62134,7 @@
         </is>
       </c>
       <c r="AD417" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE417" t="n">
         <v>1</v>
@@ -62286,7 +62286,7 @@
         </is>
       </c>
       <c r="AD418" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE418" t="n">
         <v>1</v>
@@ -62440,7 +62440,7 @@
         </is>
       </c>
       <c r="AD419" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE419" t="n">
         <v>1</v>
@@ -62586,7 +62586,7 @@
         </is>
       </c>
       <c r="AD420" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE420" t="n">
         <v>1</v>
@@ -62740,7 +62740,7 @@
         </is>
       </c>
       <c r="AD421" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE421" t="n">
         <v>1</v>
@@ -62896,7 +62896,7 @@
         </is>
       </c>
       <c r="AD422" t="n">
-        <v>1693070928024768</v>
+        <v>5079212784074304</v>
       </c>
       <c r="AE422" t="n">
         <v>1</v>
@@ -63052,7 +63052,7 @@
         </is>
       </c>
       <c r="AD423" t="n">
-        <v>1652422253758236</v>
+        <v>4957266761274708</v>
       </c>
       <c r="AE423" t="n">
         <v>1</v>
@@ -63206,7 +63206,7 @@
         </is>
       </c>
       <c r="AD424" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE424" t="n">
         <v>1</v>
@@ -63360,7 +63360,7 @@
         </is>
       </c>
       <c r="AD425" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE425" t="n">
         <v>1</v>
@@ -63516,7 +63516,7 @@
         </is>
       </c>
       <c r="AD426" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE426" t="n">
         <v>1</v>
@@ -63662,7 +63662,7 @@
         </is>
       </c>
       <c r="AD427" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE427" t="n">
         <v>1</v>
@@ -63806,7 +63806,7 @@
         </is>
       </c>
       <c r="AD428" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE428" t="n">
         <v>2</v>
@@ -63958,7 +63958,7 @@
         </is>
       </c>
       <c r="AD429" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE429" t="n">
         <v>5</v>
@@ -64110,7 +64110,7 @@
         </is>
       </c>
       <c r="AD430" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE430" t="n">
         <v>229</v>
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="AD431" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE431" t="n">
         <v>1</v>
@@ -64398,7 +64398,7 @@
         </is>
       </c>
       <c r="AD432" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE432" t="n">
         <v>2</v>
@@ -64552,7 +64552,7 @@
         </is>
       </c>
       <c r="AD433" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE433" t="n">
         <v>4</v>
@@ -64696,7 +64696,7 @@
         </is>
       </c>
       <c r="AD434" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE434" t="n">
         <v>1</v>
@@ -64844,7 +64844,7 @@
         </is>
       </c>
       <c r="AD435" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE435" t="n">
         <v>1</v>
@@ -64988,7 +64988,7 @@
         </is>
       </c>
       <c r="AD436" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE436" t="n">
         <v>2</v>
@@ -65140,7 +65140,7 @@
         </is>
       </c>
       <c r="AD437" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE437" t="n">
         <v>1</v>
@@ -65292,7 +65292,7 @@
         </is>
       </c>
       <c r="AD438" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE438" t="n">
         <v>1</v>
@@ -65436,7 +65436,7 @@
         </is>
       </c>
       <c r="AD439" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE439" t="n">
         <v>1</v>
@@ -65580,7 +65580,7 @@
         </is>
       </c>
       <c r="AD440" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE440" t="n">
         <v>1</v>
@@ -65734,7 +65734,7 @@
         </is>
       </c>
       <c r="AD441" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE441" t="n">
         <v>1</v>
@@ -65888,7 +65888,7 @@
         </is>
       </c>
       <c r="AD442" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE442" t="n">
         <v>1</v>
@@ -66042,7 +66042,7 @@
         </is>
       </c>
       <c r="AD443" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE443" t="n">
         <v>1</v>
@@ -66194,7 +66194,7 @@
         </is>
       </c>
       <c r="AD444" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE444" t="n">
         <v>1</v>
@@ -66342,7 +66342,7 @@
         </is>
       </c>
       <c r="AD445" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE445" t="n">
         <v>3</v>
@@ -66497,7 +66497,7 @@
         </is>
       </c>
       <c r="AD446" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE446" t="n">
         <v>1</v>
@@ -66641,7 +66641,7 @@
         </is>
       </c>
       <c r="AD447" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE447" t="n">
         <v>1</v>
@@ -66781,7 +66781,7 @@
         </is>
       </c>
       <c r="AD448" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE448" t="n">
         <v>1</v>
@@ -66925,7 +66925,7 @@
         </is>
       </c>
       <c r="AD449" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE449" t="n">
         <v>1</v>
@@ -67069,7 +67069,7 @@
         </is>
       </c>
       <c r="AD450" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE450" t="n">
         <v>1</v>
@@ -67213,7 +67213,7 @@
         </is>
       </c>
       <c r="AD451" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE451" t="n">
         <v>1</v>
@@ -67357,7 +67357,7 @@
         </is>
       </c>
       <c r="AD452" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE452" t="n">
         <v>1</v>
@@ -67509,7 +67509,7 @@
         </is>
       </c>
       <c r="AD453" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE453" t="n">
         <v>1</v>
@@ -67663,7 +67663,7 @@
         </is>
       </c>
       <c r="AD454" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE454" t="n">
         <v>1</v>
@@ -67817,7 +67817,7 @@
         </is>
       </c>
       <c r="AD455" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE455" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.822427849505779e+16</v>
+        <v>1.446728354851734e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>5.563692410953811e+16</v>
+        <v>1.669107723286143e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>9</v>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>7.041476717636996e+16</v>
+        <v>2.112443015291099e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>4</v>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>11</v>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>3</v>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>3</v>
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>4</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>4</v>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>4</v>
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>4</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>4</v>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>4.460974528876827e+16</v>
+        <v>1.338292358663048e+17</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10517,7 +10517,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>4.451993269457299e+16</v>
+        <v>1.33559798083719e+17</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>5.929664604485323e+16</v>
+        <v>1.778899381345597e+17</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11437,7 +11437,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12637,7 +12637,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -13087,7 +13087,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13237,7 +13237,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13837,7 +13837,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13987,7 +13987,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -14137,7 +14137,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14287,7 +14287,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15187,7 +15187,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15337,7 +15337,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15937,7 +15937,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16237,7 +16237,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16837,7 +16837,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -17137,7 +17137,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17437,7 +17437,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18787,7 +18787,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18937,7 +18937,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -19087,7 +19087,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19237,7 +19237,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19387,7 +19387,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19537,7 +19537,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19687,7 +19687,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19837,7 +19837,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19987,7 +19987,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20137,7 +20137,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20287,7 +20287,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20437,7 +20437,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20587,7 +20587,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21037,7 +21037,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21337,7 +21337,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21487,7 +21487,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21637,7 +21637,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21787,7 +21787,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21937,7 +21937,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22087,7 +22087,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22237,7 +22237,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22387,7 +22387,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22687,7 +22687,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22837,7 +22837,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22987,7 +22987,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23137,7 +23137,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23437,7 +23437,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23587,7 +23587,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23737,7 +23737,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24037,7 +24037,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24187,7 +24187,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24337,7 +24337,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24487,7 +24487,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24787,7 +24787,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24937,7 +24937,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25087,7 +25087,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25237,7 +25237,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25387,7 +25387,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25537,7 +25537,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25687,7 +25687,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25837,7 +25837,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25987,7 +25987,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26587,7 +26587,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26737,7 +26737,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26887,7 +26887,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27037,7 +27037,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27187,7 +27187,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27337,7 +27337,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27487,7 +27487,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27637,7 +27637,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27937,7 +27937,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28087,7 +28087,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28237,7 +28237,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28387,7 +28387,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28537,7 +28537,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28687,7 +28687,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28837,7 +28837,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29137,7 +29137,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29287,7 +29287,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29437,7 +29437,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29587,7 +29587,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29737,7 +29737,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29887,7 +29887,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30037,7 +30037,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30187,7 +30187,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30487,7 +30487,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30637,7 +30637,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30787,7 +30787,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30937,7 +30937,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31087,7 +31087,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31237,7 +31237,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31387,7 +31387,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31537,7 +31537,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31837,7 +31837,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31987,7 +31987,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32137,7 +32137,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32287,7 +32287,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32437,7 +32437,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32737,7 +32737,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32887,7 +32887,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33037,7 +33037,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33187,7 +33187,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33337,7 +33337,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33487,7 +33487,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33637,7 +33637,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33787,7 +33787,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33937,7 +33937,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34087,7 +34087,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34237,7 +34237,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34387,7 +34387,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34537,7 +34537,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34687,7 +34687,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34837,7 +34837,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34987,7 +34987,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35137,7 +35137,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35287,7 +35287,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35437,7 +35437,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35737,7 +35737,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35887,7 +35887,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36037,7 +36037,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36187,7 +36187,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36337,7 +36337,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36487,7 +36487,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36637,7 +36637,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36787,7 +36787,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36937,7 +36937,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37087,7 +37087,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37237,7 +37237,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37387,7 +37387,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37537,7 +37537,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37687,7 +37687,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37837,7 +37837,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE247" t="n">
         <v>3</v>
@@ -37987,7 +37987,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38137,7 +38137,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38287,7 +38287,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE251" t="n">
         <v>3</v>
@@ -38587,7 +38587,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38737,7 +38737,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38887,7 +38887,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39037,7 +39037,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39187,7 +39187,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -39337,7 +39337,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE258" t="n">
         <v>229</v>
@@ -39637,7 +39637,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39787,7 +39787,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39937,7 +39937,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40087,7 +40087,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40237,7 +40237,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40387,7 +40387,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -40537,7 +40537,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40687,7 +40687,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40987,7 +40987,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41137,7 +41137,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41287,7 +41287,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -41437,7 +41437,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -41587,7 +41587,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41737,7 +41737,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41887,7 +41887,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42037,7 +42037,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42187,7 +42187,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42343,7 +42343,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>5.559117052462819e+16</v>
+        <v>1.667735115738846e+17</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -42493,7 +42493,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42643,7 +42643,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42793,7 +42793,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42943,7 +42943,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43093,7 +43093,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE282" t="n">
         <v>1</v>
@@ -43243,7 +43243,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE283" t="n">
         <v>1</v>
@@ -43393,7 +43393,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE284" t="n">
         <v>1</v>
@@ -43553,7 +43553,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE285" t="n">
         <v>1</v>
@@ -43703,7 +43703,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE286" t="n">
         <v>1</v>
@@ -43853,7 +43853,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE287" t="n">
         <v>1</v>
@@ -44011,7 +44011,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE288" t="n">
         <v>1</v>
@@ -44170,7 +44170,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE289" t="n">
         <v>1</v>
@@ -44320,7 +44320,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE290" t="n">
         <v>1</v>
@@ -44470,7 +44470,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE291" t="n">
         <v>1</v>
@@ -44628,7 +44628,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE292" t="n">
         <v>1</v>
@@ -44778,7 +44778,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -44928,7 +44928,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE294" t="n">
         <v>1</v>
@@ -45086,7 +45086,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE295" t="n">
         <v>1</v>
@@ -45236,7 +45236,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE296" t="n">
         <v>1</v>
@@ -45392,7 +45392,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>5.559117052462819e+16</v>
+        <v>1.667735115738846e+17</v>
       </c>
       <c r="AE297" t="n">
         <v>1</v>
@@ -45550,7 +45550,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE298" t="n">
         <v>1</v>
@@ -45700,7 +45700,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE299" t="n">
         <v>1</v>
@@ -45846,7 +45846,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE300" t="n">
         <v>1</v>
@@ -45996,7 +45996,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE301" t="n">
         <v>1</v>
@@ -46146,7 +46146,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE302" t="n">
         <v>1</v>
@@ -46296,7 +46296,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE303" t="n">
         <v>1</v>
@@ -46446,7 +46446,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE304" t="n">
         <v>1</v>
@@ -46592,7 +46592,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE305" t="n">
         <v>1</v>
@@ -46750,7 +46750,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE306" t="n">
         <v>1</v>
@@ -46900,7 +46900,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE307" t="n">
         <v>1</v>
@@ -47060,7 +47060,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>5.559117749819699e+16</v>
+        <v>1.66773532494591e+17</v>
       </c>
       <c r="AE308" t="n">
         <v>1</v>
@@ -47220,7 +47220,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE309" t="n">
         <v>1</v>
@@ -47373,7 +47373,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE310" t="n">
         <v>1</v>
@@ -47533,7 +47533,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>5.563693111180473e+16</v>
+        <v>1.669107933354142e+17</v>
       </c>
       <c r="AE311" t="n">
         <v>1</v>
@@ -47693,7 +47693,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>5.563693111180473e+16</v>
+        <v>1.669107933354142e+17</v>
       </c>
       <c r="AE312" t="n">
         <v>1</v>
@@ -47853,7 +47853,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>5.563693111180473e+16</v>
+        <v>1.669107933354142e+17</v>
       </c>
       <c r="AE313" t="n">
         <v>1</v>
@@ -48003,7 +48003,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE314" t="n">
         <v>1</v>
@@ -48163,7 +48163,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>5.600238792974453e+16</v>
+        <v>1.680071637892336e+17</v>
       </c>
       <c r="AE315" t="n">
         <v>1</v>
@@ -48321,7 +48321,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE316" t="n">
         <v>1</v>
@@ -48479,7 +48479,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE317" t="n">
         <v>1</v>
@@ -48637,7 +48637,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE318" t="n">
         <v>1</v>
@@ -48787,7 +48787,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE319" t="n">
         <v>1</v>
@@ -48945,7 +48945,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE320" t="n">
         <v>1</v>
@@ -49095,7 +49095,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE321" t="n">
         <v>1</v>
@@ -49245,7 +49245,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -49403,7 +49403,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE323" t="n">
         <v>1</v>
@@ -49553,7 +49553,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE324" t="n">
         <v>1</v>
@@ -49703,7 +49703,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE326" t="n">
         <v>1</v>
@@ -50021,7 +50021,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE327" t="n">
         <v>4</v>
@@ -50171,7 +50171,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE328" t="n">
         <v>1</v>
@@ -50325,7 +50325,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE329" t="n">
         <v>1</v>
@@ -50475,7 +50475,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -50633,7 +50633,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE331" t="n">
         <v>1</v>
@@ -50791,7 +50791,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE332" t="n">
         <v>1</v>
@@ -50941,7 +50941,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE333" t="n">
         <v>1</v>
@@ -51091,7 +51091,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE334" t="n">
         <v>1</v>
@@ -51251,7 +51251,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51411,7 +51411,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE336" t="n">
         <v>1</v>
@@ -51571,7 +51571,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE337" t="n">
         <v>1</v>
@@ -51729,7 +51729,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -51890,7 +51890,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE339" t="n">
         <v>1</v>
@@ -52048,7 +52048,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52198,7 +52198,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -52344,7 +52344,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -52644,7 +52644,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -52794,7 +52794,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -52944,7 +52944,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE346" t="n">
         <v>1</v>
@@ -53102,7 +53102,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53262,7 +53262,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.446728354851734e+17</v>
+        <v>4.340185064555201e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.669107723286143e+17</v>
+        <v>5.00732316985843e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>9</v>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2.112443015291099e+17</v>
+        <v>6.337329045873297e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>4</v>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>11</v>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>3</v>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>3</v>
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>4</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>4</v>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>4</v>
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>4</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>4</v>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.338292358663048e+17</v>
+        <v>4.014877075989144e+17</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10517,7 +10517,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.33559798083719e+17</v>
+        <v>4.006793942511569e+17</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.778899381345597e+17</v>
+        <v>5.336698144036791e+17</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11437,7 +11437,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12637,7 +12637,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -13087,7 +13087,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13237,7 +13237,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13837,7 +13837,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13987,7 +13987,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -14137,7 +14137,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14287,7 +14287,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15187,7 +15187,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15337,7 +15337,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15937,7 +15937,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16237,7 +16237,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16837,7 +16837,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -17137,7 +17137,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17437,7 +17437,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18787,7 +18787,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18937,7 +18937,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -19087,7 +19087,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19237,7 +19237,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19387,7 +19387,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19537,7 +19537,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19687,7 +19687,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19837,7 +19837,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19987,7 +19987,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20137,7 +20137,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20287,7 +20287,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20437,7 +20437,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20587,7 +20587,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21037,7 +21037,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21337,7 +21337,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21487,7 +21487,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21637,7 +21637,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21787,7 +21787,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21937,7 +21937,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22087,7 +22087,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22237,7 +22237,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22387,7 +22387,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22687,7 +22687,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22837,7 +22837,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22987,7 +22987,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23137,7 +23137,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23437,7 +23437,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23587,7 +23587,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23737,7 +23737,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24037,7 +24037,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24187,7 +24187,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24337,7 +24337,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24487,7 +24487,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24787,7 +24787,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24937,7 +24937,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25087,7 +25087,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25237,7 +25237,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25387,7 +25387,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25537,7 +25537,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25687,7 +25687,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25837,7 +25837,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25987,7 +25987,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26587,7 +26587,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26737,7 +26737,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26887,7 +26887,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27037,7 +27037,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27187,7 +27187,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27337,7 +27337,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27487,7 +27487,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27637,7 +27637,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27937,7 +27937,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28087,7 +28087,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28237,7 +28237,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28387,7 +28387,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28537,7 +28537,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28687,7 +28687,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28837,7 +28837,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29137,7 +29137,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29287,7 +29287,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29437,7 +29437,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29587,7 +29587,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29737,7 +29737,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29887,7 +29887,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30037,7 +30037,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30187,7 +30187,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30487,7 +30487,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30637,7 +30637,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30787,7 +30787,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30937,7 +30937,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31087,7 +31087,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31237,7 +31237,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31387,7 +31387,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31537,7 +31537,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31837,7 +31837,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31987,7 +31987,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32137,7 +32137,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32287,7 +32287,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32437,7 +32437,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32737,7 +32737,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32887,7 +32887,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33037,7 +33037,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33187,7 +33187,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33337,7 +33337,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33487,7 +33487,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33637,7 +33637,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33787,7 +33787,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33937,7 +33937,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34087,7 +34087,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34237,7 +34237,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34387,7 +34387,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34537,7 +34537,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34687,7 +34687,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34837,7 +34837,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34987,7 +34987,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35137,7 +35137,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35287,7 +35287,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35437,7 +35437,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35737,7 +35737,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35887,7 +35887,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36037,7 +36037,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36187,7 +36187,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36337,7 +36337,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36487,7 +36487,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36637,7 +36637,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36787,7 +36787,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36937,7 +36937,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37087,7 +37087,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37237,7 +37237,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37387,7 +37387,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37537,7 +37537,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37687,7 +37687,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37837,7 +37837,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE247" t="n">
         <v>3</v>
@@ -37987,7 +37987,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38137,7 +38137,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38287,7 +38287,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE251" t="n">
         <v>3</v>
@@ -38587,7 +38587,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38737,7 +38737,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -38887,7 +38887,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39037,7 +39037,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39187,7 +39187,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -39337,7 +39337,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE258" t="n">
         <v>229</v>
@@ -39637,7 +39637,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39787,7 +39787,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE260" t="n">
         <v>2</v>
@@ -39937,7 +39937,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40087,7 +40087,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40237,7 +40237,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40387,7 +40387,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -40537,7 +40537,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40687,7 +40687,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -40987,7 +40987,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41137,7 +41137,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41287,7 +41287,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -41437,7 +41437,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -41587,7 +41587,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41737,7 +41737,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41887,7 +41887,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42037,7 +42037,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42187,7 +42187,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42343,7 +42343,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>1.667735115738846e+17</v>
+        <v>5.003205347216538e+17</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -42493,7 +42493,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42643,7 +42643,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42793,7 +42793,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42943,7 +42943,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43093,7 +43093,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE282" t="n">
         <v>1</v>
@@ -43243,7 +43243,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE283" t="n">
         <v>1</v>
@@ -43393,7 +43393,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE284" t="n">
         <v>1</v>
@@ -43553,7 +43553,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE285" t="n">
         <v>1</v>
@@ -43703,7 +43703,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE286" t="n">
         <v>1</v>
@@ -43853,7 +43853,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE287" t="n">
         <v>1</v>
@@ -44011,7 +44011,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE288" t="n">
         <v>1</v>
@@ -44170,7 +44170,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE289" t="n">
         <v>1</v>
@@ -44320,7 +44320,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE290" t="n">
         <v>1</v>
@@ -44470,7 +44470,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE291" t="n">
         <v>1</v>
@@ -44628,7 +44628,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE292" t="n">
         <v>1</v>
@@ -44778,7 +44778,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE293" t="n">
         <v>2</v>
@@ -44928,7 +44928,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE294" t="n">
         <v>1</v>
@@ -45086,7 +45086,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE295" t="n">
         <v>1</v>
@@ -45236,7 +45236,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE296" t="n">
         <v>1</v>
@@ -45392,7 +45392,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>1.667735115738846e+17</v>
+        <v>5.003205347216538e+17</v>
       </c>
       <c r="AE297" t="n">
         <v>1</v>
@@ -45550,7 +45550,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE298" t="n">
         <v>1</v>
@@ -45700,7 +45700,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE299" t="n">
         <v>1</v>
@@ -45846,7 +45846,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE300" t="n">
         <v>1</v>
@@ -45996,7 +45996,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE301" t="n">
         <v>1</v>
@@ -46146,7 +46146,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE302" t="n">
         <v>1</v>
@@ -46296,7 +46296,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE303" t="n">
         <v>1</v>
@@ -46446,7 +46446,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE304" t="n">
         <v>1</v>
@@ -46592,7 +46592,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE305" t="n">
         <v>1</v>
@@ -46750,7 +46750,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE306" t="n">
         <v>1</v>
@@ -46900,7 +46900,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE307" t="n">
         <v>1</v>
@@ -47060,7 +47060,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>1.66773532494591e+17</v>
+        <v>5.003205974837729e+17</v>
       </c>
       <c r="AE308" t="n">
         <v>1</v>
@@ -47220,7 +47220,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>1.445508259254136e+17</v>
+        <v>4.336524777762407e+17</v>
       </c>
       <c r="AE309" t="n">
         <v>1</v>
@@ -47373,7 +47373,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE310" t="n">
         <v>1</v>
@@ -47533,7 +47533,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>1.669107933354142e+17</v>
+        <v>5.007323800062426e+17</v>
       </c>
       <c r="AE311" t="n">
         <v>1</v>
@@ -47693,7 +47693,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>1.669107933354142e+17</v>
+        <v>5.007323800062426e+17</v>
       </c>
       <c r="AE312" t="n">
         <v>1</v>
@@ -47853,7 +47853,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>1.669107933354142e+17</v>
+        <v>5.007323800062426e+17</v>
       </c>
       <c r="AE313" t="n">
         <v>1</v>
@@ -48003,7 +48003,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE314" t="n">
         <v>1</v>
@@ -48163,7 +48163,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>1.680071637892336e+17</v>
+        <v>5.040214913677007e+17</v>
       </c>
       <c r="AE315" t="n">
         <v>1</v>
@@ -48321,7 +48321,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE316" t="n">
         <v>1</v>
@@ -48479,7 +48479,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE317" t="n">
         <v>1</v>
@@ -48637,7 +48637,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE318" t="n">
         <v>1</v>
@@ -48787,7 +48787,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE319" t="n">
         <v>1</v>
@@ -48945,7 +48945,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE320" t="n">
         <v>1</v>
@@ -49095,7 +49095,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE321" t="n">
         <v>1</v>
@@ -49245,7 +49245,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE322" t="n">
         <v>2</v>
@@ -49403,7 +49403,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE323" t="n">
         <v>1</v>
@@ -49553,7 +49553,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE324" t="n">
         <v>1</v>
@@ -49703,7 +49703,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE325" t="n">
         <v>2</v>
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE326" t="n">
         <v>1</v>
@@ -50021,7 +50021,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE327" t="n">
         <v>4</v>
@@ -50171,7 +50171,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE328" t="n">
         <v>1</v>
@@ -50325,7 +50325,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE329" t="n">
         <v>1</v>
@@ -50475,7 +50475,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE330" t="n">
         <v>2</v>
@@ -50633,7 +50633,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE331" t="n">
         <v>1</v>
@@ -50791,7 +50791,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE332" t="n">
         <v>1</v>
@@ -50941,7 +50941,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE333" t="n">
         <v>1</v>
@@ -51091,7 +51091,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE334" t="n">
         <v>1</v>
@@ -51251,7 +51251,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51411,7 +51411,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE336" t="n">
         <v>1</v>
@@ -51571,7 +51571,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE337" t="n">
         <v>1</v>
@@ -51729,7 +51729,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -51890,7 +51890,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE339" t="n">
         <v>1</v>
@@ -52048,7 +52048,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52198,7 +52198,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -52344,7 +52344,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -52644,7 +52644,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -52794,7 +52794,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -52944,7 +52944,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE346" t="n">
         <v>1</v>
@@ -53102,7 +53102,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53262,7 +53262,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.30205551936656e+18</v>
+        <v>3.906166558099681e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.502196950957529e+18</v>
+        <v>4.506590852872587e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.234264146800576e+18</v>
+        <v>3.702792440401727e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>9</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.901198713761989e+18</v>
+        <v>5.703596141285967e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>4</v>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>7</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>11</v>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>3</v>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>3</v>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>4</v>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>4</v>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>4</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>4</v>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.234538668338751e+18</v>
+        <v>3.703616005016253e+18</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9162,7 +9162,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9624,7 +9624,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -10074,7 +10074,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>4</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10546,7 +10546,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.204463122796743e+18</v>
+        <v>3.61338936839023e+18</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10698,7 +10698,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10858,7 +10858,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.202038182753471e+18</v>
+        <v>3.606114548260412e+18</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11180,7 +11180,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.601009443211037e+18</v>
+        <v>4.803028329633112e+18</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21078,7 +21078,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21528,7 +21528,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21678,7 +21678,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22278,7 +22278,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22428,7 +22428,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22578,7 +22578,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22728,7 +22728,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22878,7 +22878,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23478,7 +23478,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23628,7 +23628,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24078,7 +24078,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24228,7 +24228,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24378,7 +24378,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24528,7 +24528,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24978,7 +24978,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25128,7 +25128,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25428,7 +25428,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25578,7 +25578,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25878,7 +25878,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26328,7 +26328,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26478,7 +26478,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26778,7 +26778,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27078,7 +27078,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27228,7 +27228,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27378,7 +27378,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27678,7 +27678,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27978,7 +27978,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28128,7 +28128,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28278,7 +28278,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28728,7 +28728,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28878,7 +28878,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29028,7 +29028,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29478,7 +29478,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29628,7 +29628,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29778,7 +29778,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29928,7 +29928,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30078,7 +30078,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30678,7 +30678,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30828,7 +30828,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30978,7 +30978,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31278,7 +31278,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31428,7 +31428,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31578,7 +31578,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31728,7 +31728,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31878,7 +31878,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32178,7 +32178,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32328,7 +32328,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32478,7 +32478,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32628,7 +32628,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32778,7 +32778,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33078,7 +33078,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33228,7 +33228,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33378,7 +33378,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33528,7 +33528,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33678,7 +33678,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33978,7 +33978,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34128,7 +34128,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34278,7 +34278,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34578,7 +34578,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34878,7 +34878,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35178,7 +35178,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35328,7 +35328,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35478,7 +35478,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35778,7 +35778,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35928,7 +35928,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36078,7 +36078,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36228,7 +36228,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36378,7 +36378,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36678,7 +36678,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36828,7 +36828,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36978,7 +36978,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37128,7 +37128,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37278,7 +37278,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37428,7 +37428,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37578,7 +37578,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37728,7 +37728,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -37878,7 +37878,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38028,7 +38028,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38178,7 +38178,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE249" t="n">
         <v>3</v>
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -38478,7 +38478,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38628,7 +38628,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38778,7 +38778,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE253" t="n">
         <v>3</v>
@@ -38928,7 +38928,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39078,7 +39078,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39228,7 +39228,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE256" t="n">
         <v>2</v>
@@ -39378,7 +39378,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -39528,7 +39528,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39828,7 +39828,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE260" t="n">
         <v>229</v>
@@ -39978,7 +39978,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40128,7 +40128,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40278,7 +40278,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40428,7 +40428,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -40578,7 +40578,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40728,7 +40728,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -40878,7 +40878,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE267" t="n">
         <v>2</v>
@@ -41028,7 +41028,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41178,7 +41178,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41328,7 +41328,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -41478,7 +41478,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -41628,7 +41628,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41778,7 +41778,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -41928,7 +41928,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42078,7 +42078,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42228,7 +42228,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42378,7 +42378,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -42528,7 +42528,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42684,7 +42684,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>1.500961604164961e+18</v>
+        <v>4.502884812494883e+18</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42834,7 +42834,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -42984,7 +42984,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43134,7 +43134,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -43284,7 +43284,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -43434,7 +43434,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE284" t="n">
         <v>1</v>
@@ -43584,7 +43584,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE285" t="n">
         <v>1</v>
@@ -43734,7 +43734,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE286" t="n">
         <v>1</v>
@@ -43894,7 +43894,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE287" t="n">
         <v>1</v>
@@ -44044,7 +44044,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE288" t="n">
         <v>1</v>
@@ -44194,7 +44194,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE289" t="n">
         <v>1</v>
@@ -44352,7 +44352,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE290" t="n">
         <v>1</v>
@@ -44511,7 +44511,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE291" t="n">
         <v>1</v>
@@ -44661,7 +44661,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE292" t="n">
         <v>1</v>
@@ -44811,7 +44811,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE293" t="n">
         <v>1</v>
@@ -44969,7 +44969,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE294" t="n">
         <v>1</v>
@@ -45119,7 +45119,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE295" t="n">
         <v>2</v>
@@ -45269,7 +45269,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE296" t="n">
         <v>1</v>
@@ -45427,7 +45427,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE297" t="n">
         <v>1</v>
@@ -45577,7 +45577,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE298" t="n">
         <v>1</v>
@@ -45733,7 +45733,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>1.500961604164961e+18</v>
+        <v>4.502884812494883e+18</v>
       </c>
       <c r="AE299" t="n">
         <v>1</v>
@@ -45891,7 +45891,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE300" t="n">
         <v>1</v>
@@ -46041,7 +46041,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE301" t="n">
         <v>1</v>
@@ -46187,7 +46187,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE302" t="n">
         <v>1</v>
@@ -46337,7 +46337,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE303" t="n">
         <v>1</v>
@@ -46487,7 +46487,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE304" t="n">
         <v>1</v>
@@ -46637,7 +46637,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE305" t="n">
         <v>1</v>
@@ -46787,7 +46787,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE306" t="n">
         <v>1</v>
@@ -46933,7 +46933,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE307" t="n">
         <v>1</v>
@@ -47091,7 +47091,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE308" t="n">
         <v>1</v>
@@ -47241,7 +47241,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE309" t="n">
         <v>1</v>
@@ -47401,7 +47401,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>1.500961792451319e+18</v>
+        <v>4.502885377353956e+18</v>
       </c>
       <c r="AE310" t="n">
         <v>1</v>
@@ -47561,7 +47561,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE311" t="n">
         <v>1</v>
@@ -47714,7 +47714,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE312" t="n">
         <v>1</v>
@@ -47874,7 +47874,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>1.502197140018728e+18</v>
+        <v>4.506591420056183e+18</v>
       </c>
       <c r="AE313" t="n">
         <v>1</v>
@@ -48034,7 +48034,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>1.502197140018728e+18</v>
+        <v>4.506591420056183e+18</v>
       </c>
       <c r="AE314" t="n">
         <v>1</v>
@@ -48194,7 +48194,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>1.502197140018728e+18</v>
+        <v>4.506591420056183e+18</v>
       </c>
       <c r="AE315" t="n">
         <v>1</v>
@@ -48344,7 +48344,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE316" t="n">
         <v>1</v>
@@ -48504,7 +48504,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>1.512064474103102e+18</v>
+        <v>4.536193422309307e+18</v>
       </c>
       <c r="AE317" t="n">
         <v>1</v>
@@ -48662,7 +48662,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE318" t="n">
         <v>1</v>
@@ -48820,7 +48820,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE319" t="n">
         <v>1</v>
@@ -48978,7 +48978,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE320" t="n">
         <v>1</v>
@@ -49128,7 +49128,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE321" t="n">
         <v>1</v>
@@ -49286,7 +49286,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE322" t="n">
         <v>1</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE323" t="n">
         <v>1</v>
@@ -49586,7 +49586,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE324" t="n">
         <v>2</v>
@@ -49744,7 +49744,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE325" t="n">
         <v>1</v>
@@ -49894,7 +49894,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE326" t="n">
         <v>1</v>
@@ -50044,7 +50044,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE327" t="n">
         <v>2</v>
@@ -50202,7 +50202,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE328" t="n">
         <v>1</v>
@@ -50362,7 +50362,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE329" t="n">
         <v>4</v>
@@ -50512,7 +50512,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE330" t="n">
         <v>1</v>
@@ -50666,7 +50666,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE331" t="n">
         <v>1</v>
@@ -50816,7 +50816,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE332" t="n">
         <v>2</v>
@@ -50974,7 +50974,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE333" t="n">
         <v>1</v>
@@ -51132,7 +51132,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE334" t="n">
         <v>1</v>
@@ -51282,7 +51282,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51432,7 +51432,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE336" t="n">
         <v>1</v>
@@ -51592,7 +51592,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE337" t="n">
         <v>1</v>
@@ -51752,7 +51752,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -51912,7 +51912,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE339" t="n">
         <v>1</v>
@@ -52070,7 +52070,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52231,7 +52231,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -52389,7 +52389,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52539,7 +52539,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -52685,7 +52685,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -52835,7 +52835,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -52985,7 +52985,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE346" t="n">
         <v>1</v>
@@ -53135,7 +53135,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53285,7 +53285,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53443,7 +53443,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -53603,7 +53603,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -53763,7 +53763,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>21879</v>
+        <v>65637</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.054664970686914e+20</v>
+        <v>3.163994912060741e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>9.756151294304942e+19</v>
+        <v>2.926845388291483e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE9" t="n">
         <v>7</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>9.736263742693297e+19</v>
+        <v>2.920879122807989e+20</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.216779530275598e+20</v>
+        <v>3.650338590826795e+20</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE36" t="n">
         <v>4</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>9.997539589084663e+19</v>
+        <v>2.999261876725399e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>9</v>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.539970958147211e+20</v>
+        <v>4.619912874441633e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.296817648966072e+20</v>
+        <v>3.890452946898217e+20</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>4</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>7</v>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>11</v>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>3</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE54" t="n">
         <v>3</v>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE55" t="n">
         <v>4</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>4</v>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE57" t="n">
         <v>4</v>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>4</v>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>9.999763213543884e+19</v>
+        <v>2.999928964063166e+20</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>9.999638147120076e+19</v>
+        <v>2.999891444136023e+20</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>9.756151294653622e+19</v>
+        <v>2.926845388396086e+20</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>9.736509280303114e+19</v>
+        <v>2.920952784090934e+20</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.29681764900094e+20</v>
+        <v>3.890452947002821e+20</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13571,7 +13571,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14471,7 +14471,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15521,7 +15521,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15821,7 +15821,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16271,7 +16271,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16421,7 +16421,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16871,7 +16871,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -17321,7 +17321,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17621,7 +17621,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18521,7 +18521,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18671,7 +18671,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18971,7 +18971,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19421,7 +19421,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19571,7 +19571,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20171,7 +20171,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20321,7 +20321,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20771,7 +20771,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20921,7 +20921,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21671,7 +21671,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22721,7 +22721,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22871,7 +22871,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23171,7 +23171,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23321,7 +23321,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23621,7 +23621,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23771,7 +23771,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23921,7 +23921,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24071,7 +24071,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24221,7 +24221,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24371,7 +24371,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24521,7 +24521,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24671,7 +24671,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24821,7 +24821,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24971,7 +24971,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25121,7 +25121,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25271,7 +25271,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25421,7 +25421,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25571,7 +25571,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25721,7 +25721,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25871,7 +25871,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26021,7 +26021,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26171,7 +26171,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26621,7 +26621,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26771,7 +26771,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27071,7 +27071,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27221,7 +27221,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27521,7 +27521,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27821,7 +27821,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28421,7 +28421,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28571,7 +28571,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28721,7 +28721,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28871,7 +28871,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29021,7 +29021,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29321,7 +29321,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29471,7 +29471,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29621,7 +29621,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29921,7 +29921,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30071,7 +30071,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30221,7 +30221,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30521,7 +30521,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30671,7 +30671,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30971,7 +30971,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31121,7 +31121,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31271,7 +31271,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31421,7 +31421,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31571,7 +31571,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31721,7 +31721,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32021,7 +32021,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32321,7 +32321,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32471,7 +32471,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32621,7 +32621,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32771,7 +32771,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32921,7 +32921,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33071,7 +33071,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33221,7 +33221,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33371,7 +33371,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33521,7 +33521,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33671,7 +33671,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33821,7 +33821,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34121,7 +34121,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34271,7 +34271,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34421,7 +34421,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34571,7 +34571,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34721,7 +34721,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34871,7 +34871,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35021,7 +35021,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -35171,7 +35171,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35321,7 +35321,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35471,7 +35471,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35621,7 +35621,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35771,7 +35771,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36371,7 +36371,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36521,7 +36521,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36671,7 +36671,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36971,7 +36971,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37121,7 +37121,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37271,7 +37271,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37871,7 +37871,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38021,7 +38021,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38171,7 +38171,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38321,7 +38321,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38471,7 +38471,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -38621,7 +38621,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38771,7 +38771,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38921,7 +38921,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39071,7 +39071,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39221,7 +39221,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39371,7 +39371,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE256" t="n">
         <v>3</v>
@@ -39521,7 +39521,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -39671,7 +39671,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39821,7 +39821,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39971,7 +39971,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE260" t="n">
         <v>3</v>
@@ -40121,7 +40121,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40421,7 +40421,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40571,7 +40571,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -40721,7 +40721,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41021,7 +41021,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE267" t="n">
         <v>229</v>
@@ -41171,7 +41171,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41471,7 +41471,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -41621,7 +41621,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -41771,7 +41771,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41921,7 +41921,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42071,7 +42071,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42221,7 +42221,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42371,7 +42371,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42521,7 +42521,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -42671,7 +42671,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42821,7 +42821,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42971,7 +42971,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43121,7 +43121,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43271,7 +43271,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -43421,7 +43421,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -43571,7 +43571,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -43721,7 +43721,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -43877,7 +43877,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>1.215778899373619e+20</v>
+        <v>3.647336698120856e+20</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44027,7 +44027,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44177,7 +44177,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -44327,7 +44327,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -44477,7 +44477,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -44627,7 +44627,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE291" t="n">
         <v>1</v>
@@ -44777,7 +44777,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE292" t="n">
         <v>1</v>
@@ -44927,7 +44927,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE293" t="n">
         <v>1</v>
@@ -45087,7 +45087,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE294" t="n">
         <v>1</v>
@@ -45237,7 +45237,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE295" t="n">
         <v>1</v>
@@ -45387,7 +45387,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE296" t="n">
         <v>1</v>
@@ -45545,7 +45545,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE297" t="n">
         <v>1</v>
@@ -45704,7 +45704,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE298" t="n">
         <v>1</v>
@@ -45854,7 +45854,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE299" t="n">
         <v>1</v>
@@ -46004,7 +46004,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE300" t="n">
         <v>1</v>
@@ -46162,7 +46162,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE301" t="n">
         <v>1</v>
@@ -46312,7 +46312,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -46462,7 +46462,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE303" t="n">
         <v>1</v>
@@ -46620,7 +46620,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE304" t="n">
         <v>1</v>
@@ -46770,7 +46770,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE305" t="n">
         <v>1</v>
@@ -46926,7 +46926,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>1.215778899373619e+20</v>
+        <v>3.647336698120856e+20</v>
       </c>
       <c r="AE306" t="n">
         <v>1</v>
@@ -47084,7 +47084,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE307" t="n">
         <v>1</v>
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE308" t="n">
         <v>1</v>
@@ -47380,7 +47380,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE309" t="n">
         <v>1</v>
@@ -47530,7 +47530,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE310" t="n">
         <v>1</v>
@@ -47680,7 +47680,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE311" t="n">
         <v>1</v>
@@ -47830,7 +47830,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE312" t="n">
         <v>1</v>
@@ -47980,7 +47980,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE313" t="n">
         <v>1</v>
@@ -48126,7 +48126,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE314" t="n">
         <v>1</v>
@@ -48284,7 +48284,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE315" t="n">
         <v>1</v>
@@ -48434,7 +48434,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE316" t="n">
         <v>1</v>
@@ -48594,7 +48594,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>1.215779051885568e+20</v>
+        <v>3.647337155656705e+20</v>
       </c>
       <c r="AE317" t="n">
         <v>1</v>
@@ -48754,7 +48754,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>1.053775520996265e+20</v>
+        <v>3.161326562988795e+20</v>
       </c>
       <c r="AE318" t="n">
         <v>1</v>
@@ -48907,7 +48907,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE319" t="n">
         <v>1</v>
@@ -49067,7 +49067,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>1.216779683415169e+20</v>
+        <v>3.650339050245508e+20</v>
       </c>
       <c r="AE320" t="n">
         <v>1</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>1.216779683415169e+20</v>
+        <v>3.650339050245508e+20</v>
       </c>
       <c r="AE321" t="n">
         <v>1</v>
@@ -49387,7 +49387,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>1.216779683415169e+20</v>
+        <v>3.650339050245508e+20</v>
       </c>
       <c r="AE322" t="n">
         <v>1</v>
@@ -49537,7 +49537,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE323" t="n">
         <v>1</v>
@@ -49697,7 +49697,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>1.224772224023513e+20</v>
+        <v>3.674316672070538e+20</v>
       </c>
       <c r="AE324" t="n">
         <v>1</v>
@@ -49855,7 +49855,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE325" t="n">
         <v>1</v>
@@ -50013,7 +50013,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE326" t="n">
         <v>1</v>
@@ -50171,7 +50171,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE327" t="n">
         <v>1</v>
@@ -50321,7 +50321,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE328" t="n">
         <v>1</v>
@@ -50479,7 +50479,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE329" t="n">
         <v>1</v>
@@ -50629,7 +50629,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE330" t="n">
         <v>1</v>
@@ -50779,7 +50779,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -50937,7 +50937,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE332" t="n">
         <v>1</v>
@@ -51087,7 +51087,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE333" t="n">
         <v>1</v>
@@ -51237,7 +51237,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51395,7 +51395,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51555,7 +51555,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE336" t="n">
         <v>4</v>
@@ -51705,7 +51705,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE337" t="n">
         <v>1</v>
@@ -51859,7 +51859,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -52009,7 +52009,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52167,7 +52167,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52325,7 +52325,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -52475,7 +52475,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52625,7 +52625,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -52785,7 +52785,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -52945,7 +52945,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -53105,7 +53105,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE346" t="n">
         <v>1</v>
@@ -53263,7 +53263,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53424,7 +53424,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53574,7 +53574,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -53720,7 +53720,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -53870,7 +53870,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54020,7 +54020,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54170,7 +54170,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54320,7 +54320,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -54478,7 +54478,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -54638,7 +54638,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -54798,7 +54798,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>65637</v>
+        <v>196911</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.163994912060741e+20</v>
+        <v>9.491984736182225e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2.926845388291483e+20</v>
+        <v>8.780536164874449e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>7</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2.920879122807989e+20</v>
+        <v>8.762637368423968e+20</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>3.650338590826795e+20</v>
+        <v>1.095101577248039e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE36" t="n">
         <v>4</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2.999261876725399e+20</v>
+        <v>8.997785630176197e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>9</v>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.619912874441633e+20</v>
+        <v>1.38597386233249e+21</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.890452946898217e+20</v>
+        <v>1.167135884069465e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>4</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>7</v>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>11</v>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>3</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>3</v>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>4</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>4</v>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE57" t="n">
         <v>4</v>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>4</v>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2.999928964063166e+20</v>
+        <v>8.999786892189497e+20</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2.999891444136023e+20</v>
+        <v>8.999674332408067e+20</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2.926845388396086e+20</v>
+        <v>8.780536165188259e+20</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2.920952784090934e+20</v>
+        <v>8.762858352272802e+20</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>3.890452947002821e+20</v>
+        <v>1.167135884100846e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13571,7 +13571,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14471,7 +14471,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15521,7 +15521,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15821,7 +15821,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16271,7 +16271,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16421,7 +16421,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16871,7 +16871,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -17321,7 +17321,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17621,7 +17621,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18521,7 +18521,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18671,7 +18671,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18971,7 +18971,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19421,7 +19421,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19571,7 +19571,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20171,7 +20171,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20321,7 +20321,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20771,7 +20771,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20921,7 +20921,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21671,7 +21671,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22721,7 +22721,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22871,7 +22871,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23171,7 +23171,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23321,7 +23321,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23621,7 +23621,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23771,7 +23771,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23921,7 +23921,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24071,7 +24071,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24221,7 +24221,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24371,7 +24371,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24521,7 +24521,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24671,7 +24671,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24821,7 +24821,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24971,7 +24971,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25121,7 +25121,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25271,7 +25271,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25421,7 +25421,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25571,7 +25571,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25721,7 +25721,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25871,7 +25871,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26021,7 +26021,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26171,7 +26171,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26621,7 +26621,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26771,7 +26771,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27071,7 +27071,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27221,7 +27221,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27521,7 +27521,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27821,7 +27821,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28421,7 +28421,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28571,7 +28571,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28721,7 +28721,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28871,7 +28871,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29021,7 +29021,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29321,7 +29321,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29471,7 +29471,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29621,7 +29621,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29921,7 +29921,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30071,7 +30071,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30221,7 +30221,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30521,7 +30521,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30671,7 +30671,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30971,7 +30971,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31121,7 +31121,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31271,7 +31271,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31421,7 +31421,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31571,7 +31571,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31721,7 +31721,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32021,7 +32021,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32321,7 +32321,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32471,7 +32471,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32621,7 +32621,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32771,7 +32771,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32921,7 +32921,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33071,7 +33071,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33221,7 +33221,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33371,7 +33371,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33521,7 +33521,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33671,7 +33671,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33821,7 +33821,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34121,7 +34121,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34271,7 +34271,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34421,7 +34421,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34571,7 +34571,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34721,7 +34721,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34871,7 +34871,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35021,7 +35021,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -35171,7 +35171,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35321,7 +35321,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35471,7 +35471,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35621,7 +35621,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35771,7 +35771,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36371,7 +36371,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36521,7 +36521,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36671,7 +36671,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36971,7 +36971,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37121,7 +37121,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37271,7 +37271,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37871,7 +37871,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38021,7 +38021,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38171,7 +38171,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38321,7 +38321,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38471,7 +38471,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -38621,7 +38621,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38771,7 +38771,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38921,7 +38921,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39071,7 +39071,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39221,7 +39221,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39371,7 +39371,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE256" t="n">
         <v>3</v>
@@ -39521,7 +39521,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -39671,7 +39671,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39821,7 +39821,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39971,7 +39971,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE260" t="n">
         <v>3</v>
@@ -40121,7 +40121,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40421,7 +40421,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40571,7 +40571,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -40721,7 +40721,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41021,7 +41021,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE267" t="n">
         <v>229</v>
@@ -41171,7 +41171,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41471,7 +41471,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -41621,7 +41621,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -41771,7 +41771,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41921,7 +41921,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42071,7 +42071,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42221,7 +42221,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42371,7 +42371,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42521,7 +42521,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -42671,7 +42671,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42821,7 +42821,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42971,7 +42971,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43121,7 +43121,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43271,7 +43271,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -43421,7 +43421,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -43571,7 +43571,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -43721,7 +43721,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -43877,7 +43877,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>3.647336698120856e+20</v>
+        <v>1.094201009436257e+21</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44027,7 +44027,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44177,7 +44177,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -44327,7 +44327,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -44477,7 +44477,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -44627,7 +44627,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE291" t="n">
         <v>1</v>
@@ -44777,7 +44777,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE292" t="n">
         <v>1</v>
@@ -44927,7 +44927,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE293" t="n">
         <v>1</v>
@@ -45087,7 +45087,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE294" t="n">
         <v>1</v>
@@ -45237,7 +45237,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE295" t="n">
         <v>1</v>
@@ -45387,7 +45387,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE296" t="n">
         <v>1</v>
@@ -45545,7 +45545,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE297" t="n">
         <v>1</v>
@@ -45704,7 +45704,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE298" t="n">
         <v>1</v>
@@ -45854,7 +45854,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE299" t="n">
         <v>1</v>
@@ -46004,7 +46004,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE300" t="n">
         <v>1</v>
@@ -46162,7 +46162,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE301" t="n">
         <v>1</v>
@@ -46312,7 +46312,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -46462,7 +46462,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE303" t="n">
         <v>1</v>
@@ -46620,7 +46620,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE304" t="n">
         <v>1</v>
@@ -46770,7 +46770,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE305" t="n">
         <v>1</v>
@@ -46926,7 +46926,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>3.647336698120856e+20</v>
+        <v>1.094201009436257e+21</v>
       </c>
       <c r="AE306" t="n">
         <v>1</v>
@@ -47084,7 +47084,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE307" t="n">
         <v>1</v>
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE308" t="n">
         <v>1</v>
@@ -47380,7 +47380,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE309" t="n">
         <v>1</v>
@@ -47530,7 +47530,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE310" t="n">
         <v>1</v>
@@ -47680,7 +47680,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE311" t="n">
         <v>1</v>
@@ -47830,7 +47830,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE312" t="n">
         <v>1</v>
@@ -47980,7 +47980,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE313" t="n">
         <v>1</v>
@@ -48126,7 +48126,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE314" t="n">
         <v>1</v>
@@ -48284,7 +48284,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE315" t="n">
         <v>1</v>
@@ -48434,7 +48434,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE316" t="n">
         <v>1</v>
@@ -48594,7 +48594,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>3.647337155656705e+20</v>
+        <v>1.094201146697011e+21</v>
       </c>
       <c r="AE317" t="n">
         <v>1</v>
@@ -48754,7 +48754,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>3.161326562988795e+20</v>
+        <v>9.483979688966385e+20</v>
       </c>
       <c r="AE318" t="n">
         <v>1</v>
@@ -48907,7 +48907,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE319" t="n">
         <v>1</v>
@@ -49067,7 +49067,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>3.650339050245508e+20</v>
+        <v>1.095101715073652e+21</v>
       </c>
       <c r="AE320" t="n">
         <v>1</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>3.650339050245508e+20</v>
+        <v>1.095101715073652e+21</v>
       </c>
       <c r="AE321" t="n">
         <v>1</v>
@@ -49387,7 +49387,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>3.650339050245508e+20</v>
+        <v>1.095101715073652e+21</v>
       </c>
       <c r="AE322" t="n">
         <v>1</v>
@@ -49537,7 +49537,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE323" t="n">
         <v>1</v>
@@ -49697,7 +49697,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>3.674316672070538e+20</v>
+        <v>1.102295001621162e+21</v>
       </c>
       <c r="AE324" t="n">
         <v>1</v>
@@ -49855,7 +49855,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE325" t="n">
         <v>1</v>
@@ -50013,7 +50013,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE326" t="n">
         <v>1</v>
@@ -50171,7 +50171,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE327" t="n">
         <v>1</v>
@@ -50321,7 +50321,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE328" t="n">
         <v>1</v>
@@ -50479,7 +50479,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE329" t="n">
         <v>1</v>
@@ -50629,7 +50629,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE330" t="n">
         <v>1</v>
@@ -50779,7 +50779,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -50937,7 +50937,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE332" t="n">
         <v>1</v>
@@ -51087,7 +51087,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE333" t="n">
         <v>1</v>
@@ -51237,7 +51237,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51395,7 +51395,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51555,7 +51555,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE336" t="n">
         <v>4</v>
@@ -51705,7 +51705,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE337" t="n">
         <v>1</v>
@@ -51859,7 +51859,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -52009,7 +52009,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52167,7 +52167,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52325,7 +52325,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -52475,7 +52475,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52625,7 +52625,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -52785,7 +52785,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -52945,7 +52945,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -53105,7 +53105,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE346" t="n">
         <v>1</v>
@@ -53263,7 +53263,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53424,7 +53424,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53574,7 +53574,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -53720,7 +53720,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -53870,7 +53870,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54020,7 +54020,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54170,7 +54170,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54320,7 +54320,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -54478,7 +54478,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -54638,7 +54638,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -54798,7 +54798,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>196911</v>
+        <v>590733</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>9.491984736182225e+20</v>
+        <v>2.847595420854667e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>8.780536164874449e+20</v>
+        <v>2.634160849462334e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>7</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>8.762637368423968e+20</v>
+        <v>2.62879121052719e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.095101577248039e+21</v>
+        <v>3.285304731744116e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE36" t="n">
         <v>4</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>8.997785630176197e+20</v>
+        <v>2.699335689052859e+21</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>9</v>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.38597386233249e+21</v>
+        <v>4.15792158699747e+21</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.167135884069465e+21</v>
+        <v>3.501407652208396e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>4</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>7</v>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE46" t="n">
         <v>11</v>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE50" t="n">
         <v>3</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>3</v>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>4</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE56" t="n">
         <v>4</v>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE57" t="n">
         <v>4</v>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE58" t="n">
         <v>4</v>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>8.999786892189497e+20</v>
+        <v>2.699936067656849e+21</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>8.999674332408067e+20</v>
+        <v>2.69990229972242e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>8.780536165188259e+20</v>
+        <v>2.634160849556478e+21</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>8.762858352272802e+20</v>
+        <v>2.628857505681841e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.167135884100846e+21</v>
+        <v>3.501407652302539e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13571,7 +13571,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14471,7 +14471,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15521,7 +15521,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15821,7 +15821,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16271,7 +16271,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16421,7 +16421,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16871,7 +16871,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -17321,7 +17321,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17621,7 +17621,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18521,7 +18521,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18671,7 +18671,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18971,7 +18971,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19421,7 +19421,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19571,7 +19571,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20171,7 +20171,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20321,7 +20321,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20771,7 +20771,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20921,7 +20921,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21671,7 +21671,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22721,7 +22721,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22871,7 +22871,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23171,7 +23171,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23321,7 +23321,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23621,7 +23621,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23771,7 +23771,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23921,7 +23921,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24071,7 +24071,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24221,7 +24221,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24371,7 +24371,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24521,7 +24521,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24671,7 +24671,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24821,7 +24821,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24971,7 +24971,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25121,7 +25121,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25271,7 +25271,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25421,7 +25421,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25571,7 +25571,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25721,7 +25721,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25871,7 +25871,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26021,7 +26021,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26171,7 +26171,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26621,7 +26621,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26771,7 +26771,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27071,7 +27071,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27221,7 +27221,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27521,7 +27521,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27821,7 +27821,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28421,7 +28421,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28571,7 +28571,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28721,7 +28721,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28871,7 +28871,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29021,7 +29021,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29321,7 +29321,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29471,7 +29471,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29621,7 +29621,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29921,7 +29921,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30071,7 +30071,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30221,7 +30221,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30521,7 +30521,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30671,7 +30671,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30971,7 +30971,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31121,7 +31121,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31271,7 +31271,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31421,7 +31421,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31571,7 +31571,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31721,7 +31721,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32021,7 +32021,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32321,7 +32321,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32471,7 +32471,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32621,7 +32621,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32771,7 +32771,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32921,7 +32921,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33071,7 +33071,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33221,7 +33221,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33371,7 +33371,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33521,7 +33521,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33671,7 +33671,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33821,7 +33821,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34121,7 +34121,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34271,7 +34271,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34421,7 +34421,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34571,7 +34571,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34721,7 +34721,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34871,7 +34871,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35021,7 +35021,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -35171,7 +35171,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35321,7 +35321,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35471,7 +35471,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35621,7 +35621,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35771,7 +35771,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36371,7 +36371,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36521,7 +36521,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36671,7 +36671,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36971,7 +36971,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37121,7 +37121,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37271,7 +37271,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37871,7 +37871,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38021,7 +38021,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38171,7 +38171,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38321,7 +38321,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38471,7 +38471,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -38621,7 +38621,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38771,7 +38771,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38921,7 +38921,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39071,7 +39071,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39221,7 +39221,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39371,7 +39371,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE256" t="n">
         <v>3</v>
@@ -39521,7 +39521,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -39671,7 +39671,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39821,7 +39821,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39971,7 +39971,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE260" t="n">
         <v>3</v>
@@ -40121,7 +40121,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40421,7 +40421,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40571,7 +40571,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -40721,7 +40721,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41021,7 +41021,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE267" t="n">
         <v>229</v>
@@ -41171,7 +41171,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41471,7 +41471,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -41621,7 +41621,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -41771,7 +41771,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41921,7 +41921,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42071,7 +42071,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE274" t="n">
         <v>2</v>
@@ -42221,7 +42221,7 @@
         </is>
       </c>
       <c r="AD275" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE275" t="n">
         <v>2</v>
@@ -42371,7 +42371,7 @@
         </is>
       </c>
       <c r="AD276" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE276" t="n">
         <v>2</v>
@@ -42521,7 +42521,7 @@
         </is>
       </c>
       <c r="AD277" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE277" t="n">
         <v>2</v>
@@ -42671,7 +42671,7 @@
         </is>
       </c>
       <c r="AD278" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE278" t="n">
         <v>2</v>
@@ -42821,7 +42821,7 @@
         </is>
       </c>
       <c r="AD279" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE279" t="n">
         <v>2</v>
@@ -42971,7 +42971,7 @@
         </is>
       </c>
       <c r="AD280" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE280" t="n">
         <v>2</v>
@@ -43121,7 +43121,7 @@
         </is>
       </c>
       <c r="AD281" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE281" t="n">
         <v>2</v>
@@ -43271,7 +43271,7 @@
         </is>
       </c>
       <c r="AD282" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE282" t="n">
         <v>2</v>
@@ -43421,7 +43421,7 @@
         </is>
       </c>
       <c r="AD283" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE283" t="n">
         <v>2</v>
@@ -43571,7 +43571,7 @@
         </is>
       </c>
       <c r="AD284" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE284" t="n">
         <v>2</v>
@@ -43721,7 +43721,7 @@
         </is>
       </c>
       <c r="AD285" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE285" t="n">
         <v>2</v>
@@ -43877,7 +43877,7 @@
         </is>
       </c>
       <c r="AD286" t="n">
-        <v>1.094201009436257e+21</v>
+        <v>3.28260302830877e+21</v>
       </c>
       <c r="AE286" t="n">
         <v>2</v>
@@ -44027,7 +44027,7 @@
         </is>
       </c>
       <c r="AD287" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE287" t="n">
         <v>2</v>
@@ -44177,7 +44177,7 @@
         </is>
       </c>
       <c r="AD288" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE288" t="n">
         <v>2</v>
@@ -44327,7 +44327,7 @@
         </is>
       </c>
       <c r="AD289" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE289" t="n">
         <v>2</v>
@@ -44477,7 +44477,7 @@
         </is>
       </c>
       <c r="AD290" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE290" t="n">
         <v>2</v>
@@ -44627,7 +44627,7 @@
         </is>
       </c>
       <c r="AD291" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE291" t="n">
         <v>1</v>
@@ -44777,7 +44777,7 @@
         </is>
       </c>
       <c r="AD292" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE292" t="n">
         <v>1</v>
@@ -44927,7 +44927,7 @@
         </is>
       </c>
       <c r="AD293" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE293" t="n">
         <v>1</v>
@@ -45087,7 +45087,7 @@
         </is>
       </c>
       <c r="AD294" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE294" t="n">
         <v>1</v>
@@ -45237,7 +45237,7 @@
         </is>
       </c>
       <c r="AD295" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE295" t="n">
         <v>1</v>
@@ -45387,7 +45387,7 @@
         </is>
       </c>
       <c r="AD296" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE296" t="n">
         <v>1</v>
@@ -45545,7 +45545,7 @@
         </is>
       </c>
       <c r="AD297" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE297" t="n">
         <v>1</v>
@@ -45704,7 +45704,7 @@
         </is>
       </c>
       <c r="AD298" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE298" t="n">
         <v>1</v>
@@ -45854,7 +45854,7 @@
         </is>
       </c>
       <c r="AD299" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE299" t="n">
         <v>1</v>
@@ -46004,7 +46004,7 @@
         </is>
       </c>
       <c r="AD300" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE300" t="n">
         <v>1</v>
@@ -46162,7 +46162,7 @@
         </is>
       </c>
       <c r="AD301" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE301" t="n">
         <v>1</v>
@@ -46312,7 +46312,7 @@
         </is>
       </c>
       <c r="AD302" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE302" t="n">
         <v>2</v>
@@ -46462,7 +46462,7 @@
         </is>
       </c>
       <c r="AD303" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE303" t="n">
         <v>1</v>
@@ -46620,7 +46620,7 @@
         </is>
       </c>
       <c r="AD304" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE304" t="n">
         <v>1</v>
@@ -46770,7 +46770,7 @@
         </is>
       </c>
       <c r="AD305" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE305" t="n">
         <v>1</v>
@@ -46926,7 +46926,7 @@
         </is>
       </c>
       <c r="AD306" t="n">
-        <v>1.094201009436257e+21</v>
+        <v>3.28260302830877e+21</v>
       </c>
       <c r="AE306" t="n">
         <v>1</v>
@@ -47084,7 +47084,7 @@
         </is>
       </c>
       <c r="AD307" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE307" t="n">
         <v>1</v>
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="AD308" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE308" t="n">
         <v>1</v>
@@ -47380,7 +47380,7 @@
         </is>
       </c>
       <c r="AD309" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE309" t="n">
         <v>1</v>
@@ -47530,7 +47530,7 @@
         </is>
       </c>
       <c r="AD310" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE310" t="n">
         <v>1</v>
@@ -47680,7 +47680,7 @@
         </is>
       </c>
       <c r="AD311" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE311" t="n">
         <v>1</v>
@@ -47830,7 +47830,7 @@
         </is>
       </c>
       <c r="AD312" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE312" t="n">
         <v>1</v>
@@ -47980,7 +47980,7 @@
         </is>
       </c>
       <c r="AD313" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE313" t="n">
         <v>1</v>
@@ -48126,7 +48126,7 @@
         </is>
       </c>
       <c r="AD314" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE314" t="n">
         <v>1</v>
@@ -48284,7 +48284,7 @@
         </is>
       </c>
       <c r="AD315" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE315" t="n">
         <v>1</v>
@@ -48434,7 +48434,7 @@
         </is>
       </c>
       <c r="AD316" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE316" t="n">
         <v>1</v>
@@ -48594,7 +48594,7 @@
         </is>
       </c>
       <c r="AD317" t="n">
-        <v>1.094201146697011e+21</v>
+        <v>3.282603440091035e+21</v>
       </c>
       <c r="AE317" t="n">
         <v>1</v>
@@ -48754,7 +48754,7 @@
         </is>
       </c>
       <c r="AD318" t="n">
-        <v>9.483979688966385e+20</v>
+        <v>2.845193906689915e+21</v>
       </c>
       <c r="AE318" t="n">
         <v>1</v>
@@ -48907,7 +48907,7 @@
         </is>
       </c>
       <c r="AD319" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE319" t="n">
         <v>1</v>
@@ -49067,7 +49067,7 @@
         </is>
       </c>
       <c r="AD320" t="n">
-        <v>1.095101715073652e+21</v>
+        <v>3.285305145220957e+21</v>
       </c>
       <c r="AE320" t="n">
         <v>1</v>
@@ -49227,7 +49227,7 @@
         </is>
       </c>
       <c r="AD321" t="n">
-        <v>1.095101715073652e+21</v>
+        <v>3.285305145220957e+21</v>
       </c>
       <c r="AE321" t="n">
         <v>1</v>
@@ -49387,7 +49387,7 @@
         </is>
       </c>
       <c r="AD322" t="n">
-        <v>1.095101715073652e+21</v>
+        <v>3.285305145220957e+21</v>
       </c>
       <c r="AE322" t="n">
         <v>1</v>
@@ -49537,7 +49537,7 @@
         </is>
       </c>
       <c r="AD323" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE323" t="n">
         <v>1</v>
@@ -49697,7 +49697,7 @@
         </is>
       </c>
       <c r="AD324" t="n">
-        <v>1.102295001621162e+21</v>
+        <v>3.306885004863485e+21</v>
       </c>
       <c r="AE324" t="n">
         <v>1</v>
@@ -49855,7 +49855,7 @@
         </is>
       </c>
       <c r="AD325" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE325" t="n">
         <v>1</v>
@@ -50013,7 +50013,7 @@
         </is>
       </c>
       <c r="AD326" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE326" t="n">
         <v>1</v>
@@ -50171,7 +50171,7 @@
         </is>
       </c>
       <c r="AD327" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE327" t="n">
         <v>1</v>
@@ -50321,7 +50321,7 @@
         </is>
       </c>
       <c r="AD328" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE328" t="n">
         <v>1</v>
@@ -50479,7 +50479,7 @@
         </is>
       </c>
       <c r="AD329" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE329" t="n">
         <v>1</v>
@@ -50629,7 +50629,7 @@
         </is>
       </c>
       <c r="AD330" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE330" t="n">
         <v>1</v>
@@ -50779,7 +50779,7 @@
         </is>
       </c>
       <c r="AD331" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE331" t="n">
         <v>2</v>
@@ -50937,7 +50937,7 @@
         </is>
       </c>
       <c r="AD332" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE332" t="n">
         <v>1</v>
@@ -51087,7 +51087,7 @@
         </is>
       </c>
       <c r="AD333" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE333" t="n">
         <v>1</v>
@@ -51237,7 +51237,7 @@
         </is>
       </c>
       <c r="AD334" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE334" t="n">
         <v>2</v>
@@ -51395,7 +51395,7 @@
         </is>
       </c>
       <c r="AD335" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE335" t="n">
         <v>1</v>
@@ -51555,7 +51555,7 @@
         </is>
       </c>
       <c r="AD336" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE336" t="n">
         <v>4</v>
@@ -51705,7 +51705,7 @@
         </is>
       </c>
       <c r="AD337" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE337" t="n">
         <v>1</v>
@@ -51859,7 +51859,7 @@
         </is>
       </c>
       <c r="AD338" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE338" t="n">
         <v>1</v>
@@ -52009,7 +52009,7 @@
         </is>
       </c>
       <c r="AD339" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE339" t="n">
         <v>2</v>
@@ -52167,7 +52167,7 @@
         </is>
       </c>
       <c r="AD340" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE340" t="n">
         <v>1</v>
@@ -52325,7 +52325,7 @@
         </is>
       </c>
       <c r="AD341" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE341" t="n">
         <v>1</v>
@@ -52475,7 +52475,7 @@
         </is>
       </c>
       <c r="AD342" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE342" t="n">
         <v>1</v>
@@ -52625,7 +52625,7 @@
         </is>
       </c>
       <c r="AD343" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE343" t="n">
         <v>1</v>
@@ -52785,7 +52785,7 @@
         </is>
       </c>
       <c r="AD344" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE344" t="n">
         <v>1</v>
@@ -52945,7 +52945,7 @@
         </is>
       </c>
       <c r="AD345" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE345" t="n">
         <v>1</v>
@@ -53105,7 +53105,7 @@
         </is>
       </c>
       <c r="AD346" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE346" t="n">
         <v>1</v>
@@ -53263,7 +53263,7 @@
         </is>
       </c>
       <c r="AD347" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE347" t="n">
         <v>1</v>
@@ -53424,7 +53424,7 @@
         </is>
       </c>
       <c r="AD348" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE348" t="n">
         <v>1</v>
@@ -53574,7 +53574,7 @@
         </is>
       </c>
       <c r="AD349" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE349" t="n">
         <v>1</v>
@@ -53720,7 +53720,7 @@
         </is>
       </c>
       <c r="AD350" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE350" t="n">
         <v>1</v>
@@ -53870,7 +53870,7 @@
         </is>
       </c>
       <c r="AD351" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE351" t="n">
         <v>1</v>
@@ -54020,7 +54020,7 @@
         </is>
       </c>
       <c r="AD352" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE352" t="n">
         <v>1</v>
@@ -54170,7 +54170,7 @@
         </is>
       </c>
       <c r="AD353" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE353" t="n">
         <v>1</v>
@@ -54320,7 +54320,7 @@
         </is>
       </c>
       <c r="AD354" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE354" t="n">
         <v>1</v>
@@ -54478,7 +54478,7 @@
         </is>
       </c>
       <c r="AD355" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE355" t="n">
         <v>1</v>
@@ -54638,7 +54638,7 @@
         </is>
       </c>
       <c r="AD356" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE356" t="n">
         <v>1</v>
@@ -54798,7 +54798,7 @@
         </is>
       </c>
       <c r="AD357" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE357" t="n">
         <v>1</v>

--- a/output/contacts_organization.xlsx
+++ b/output/contacts_organization.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>590733</v>
+        <v>1772199</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2.847595420854667e+21</v>
+        <v>8.542786262564002e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2.634160849462334e+21</v>
+        <v>7.902482548387003e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>7</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2.62879121052719e+21</v>
+        <v>7.886373631581571e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>3.285304731744116e+21</v>
+        <v>9.855914195232349e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE36" t="n">
         <v>4</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2.699335689052859e+21</v>
+        <v>8.098007067158577e+21</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>9</v>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.15792158699747e+21</v>
+        <v>1.247376476099241e+22</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.501407652208396e+21</v>
+        <v>1.050422295662519e+22</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>4</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>7</v>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE46" t="n">
         <v>11</v>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE50" t="n">
         <v>3</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>3</v>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>4</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE56" t="n">
         <v>4</v>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE57" t="n">
         <v>4</v>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE58" t="n">
         <v>4</v>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2.699936067656849e+21</v>
+        <v>8.099808202970546e+21</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>3.282569673945371e+21</v>
+        <v>9.847709021836113e+21</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE68" t="n">
         <v>4</v>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2.69990229972242e+21</v>
+        <v>8.09970689916726e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2.634160849556478e+21</v>
+        <v>7.902482548669433e+21</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>3.285271377380717e+21</v>
+        <v>9.855814132142151e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2.628857505681841e+21</v>
+        <v>7.886572517045521e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>3.501407652302539e+21</v>
+        <v>1.050422295690762e+22</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12661,7 +12661,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>551205</v>
+        <v>1653615</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13571,7 +13571,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14471,7 +14471,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -15071,7 +15071,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15521,7 +15521,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15821,7 +15821,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -16271,7 +16271,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16421,7 +16421,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16871,7 +16871,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -17321,7 +17321,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17621,7 +17621,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18521,7 +18521,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18671,7 +18671,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18971,7 +18971,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19421,7 +19421,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19571,7 +19571,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -20171,7 +20171,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -20321,7 +20321,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20771,7 +20771,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20921,7 +20921,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21371,7 +21371,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21671,7 +21671,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22421,7 +22421,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22721,7 +22721,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22871,7 +22871,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -23171,7 +23171,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -23321,7 +23321,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23621,7 +23621,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23771,7 +23771,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23921,7 +23921,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -24071,7 +24071,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -24221,7 +24221,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24371,7 +24371,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24521,7 +24521,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24671,7 +24671,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24821,7 +24821,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24971,7 +24971,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -25121,7 +25121,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -25271,7 +25271,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25421,7 +25421,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25571,7 +25571,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25721,7 +25721,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25871,7 +25871,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -26021,7 +26021,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -26171,7 +26171,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26621,7 +26621,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26771,7 +26771,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -27071,7 +27071,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -27221,7 +27221,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27521,7 +27521,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27671,7 +27671,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27821,7 +27821,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28421,7 +28421,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28571,7 +28571,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28721,7 +28721,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28871,7 +28871,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -29021,7 +29021,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -29321,7 +29321,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29471,7 +29471,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29621,7 +29621,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29771,7 +29771,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29921,7 +29921,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -30071,7 +30071,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -30221,7 +30221,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30521,7 +30521,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30671,7 +30671,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30971,7 +30971,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -31121,7 +31121,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -31271,7 +31271,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31421,7 +31421,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31571,7 +31571,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31721,7 +31721,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31871,7 +31871,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -32021,7 +32021,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -32321,7 +32321,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32471,7 +32471,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32621,7 +32621,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32771,7 +32771,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32921,7 +32921,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -33071,7 +33071,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -33221,7 +33221,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33371,7 +33371,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33521,7 +33521,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33671,7 +33671,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33821,7 +33821,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -34121,7 +34121,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -34271,7 +34271,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34421,7 +34421,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34571,7 +34571,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34721,7 +34721,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34871,7 +34871,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -35021,7 +35021,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -35171,7 +35171,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -35321,7 +35321,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35471,7 +35471,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35621,7 +35621,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35771,7 +35771,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -36221,7 +36221,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36371,7 +36371,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36521,7 +36521,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36671,7 +36671,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36971,7 +36971,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -37121,7 +37121,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -37271,7 +37271,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -37871,7 +37871,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -38021,7 +38021,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -38171,7 +38171,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -38321,7 +38321,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -38471,7 +38471,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE250" t="n">
         <v>2</v>
@@ -38621,7 +38621,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -38771,7 +38771,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -38921,7 +38921,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -39071,7 +39071,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -39221,7 +39221,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE255" t="n">
         <v>2</v>
@@ -39371,7 +39371,7 @@
         </is>
       </c>
       <c r="AD256" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE256" t="n">
         <v>3</v>
@@ -39521,7 +39521,7 @@
         </is>
       </c>
       <c r="AD257" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE257" t="n">
         <v>2</v>
@@ -39671,7 +39671,7 @@
         </is>
       </c>
       <c r="AD258" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE258" t="n">
         <v>2</v>
@@ -39821,7 +39821,7 @@
         </is>
       </c>
       <c r="AD259" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE259" t="n">
         <v>2</v>
@@ -39971,7 +39971,7 @@
         </is>
       </c>
       <c r="AD260" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE260" t="n">
         <v>3</v>
@@ -40121,7 +40121,7 @@
         </is>
       </c>
       <c r="AD261" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE261" t="n">
         <v>2</v>
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="AD262" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE262" t="n">
         <v>2</v>
@@ -40421,7 +40421,7 @@
         </is>
       </c>
       <c r="AD263" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE263" t="n">
         <v>2</v>
@@ -40571,7 +40571,7 @@
         </is>
       </c>
       <c r="AD264" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE264" t="n">
         <v>2</v>
@@ -40721,7 +40721,7 @@
         </is>
       </c>
       <c r="AD265" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE265" t="n">
         <v>2</v>
@@ -40871,7 +40871,7 @@
         </is>
       </c>
       <c r="AD266" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE266" t="n">
         <v>2</v>
@@ -41021,7 +41021,7 @@
         </is>
       </c>
       <c r="AD267" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE267" t="n">
         <v>229</v>
@@ -41171,7 +41171,7 @@
         </is>
       </c>
       <c r="AD268" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE268" t="n">
         <v>2</v>
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="AD269" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE269" t="n">
         <v>2</v>
@@ -41471,7 +41471,7 @@
         </is>
       </c>
       <c r="AD270" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE270" t="n">
         <v>2</v>
@@ -41621,7 +41621,7 @@
         </is>
       </c>
       <c r="AD271" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE271" t="n">
         <v>2</v>
@@ -41771,7 +41771,7 @@
         </is>
       </c>
       <c r="AD272" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE272" t="n">
         <v>2</v>
@@ -41921,7 +41921,7 @@
         </is>
       </c>
       <c r="AD273" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
       <c r="AE273" t="n">
         <v>2</v>
@@ -42071,7 +42071,7 @@
         </is>
       </c>
       <c r="AD274" t="n">
-        <v>2.626055739156296e+21</v>
+        <v>7.87816721746889e+21</v>
       </c>
  